--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grants" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parcels" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA findings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -60325,6 +60326,3442 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C201"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>check</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>project_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>duplicate-sheet-rows</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>76/182</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>multiple sheet projects map to one authorization (1451 w mlk blvd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2025 New Jersey Apartments (CMFA, 2023-07-14) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bernardine Apartments (CMFA, 2023-07-14) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>10705 Avalon Blvd Apartments (CMFA, 2024-02-02) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>820 MacArthur Apartments (CMFA, 2024-02-02) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4252 Crenshaw Apartments (CMFA, 2024-04-26) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Montessa Apartments (CMFA, 2024-04-26) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2330 3rd Street Apartments (CMFA, 2024-08-09) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Hillsdale Gardens Apartments (CMFA, 2024-08-30) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>6171 Mission Gorge Apartments (CMFA, 2024-09-20) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Horizon Apartments (CMFA, 2024-09-20) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Bella Vista Apartments (CMFA, 2025-01-10) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Electric Lofts Apartments (CMFA, 2025-01-31) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Meridian Apartments (CMFA, 2025-02-21) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>569 W 6th Apartments (CMFA, 2025-04-25) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>685 W 4th Apartments (CMFA, 2025-04-25) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Bella Vista at Hilltop Apartments (CMFA, 2025-05-30) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Chadwick Apartments (CMFA, 2025-05-30) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Bella Vista at Hilltop Apartments (CMFA, 2025-06-06) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Chadwick Apartments (CMFA, 2025-06-06) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Meridian Apartments (CMFA, 2025-07-18) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Meridian Apartments (CMFA, 2025-08-08) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Citrine Apartments (CMFA, 2025-08-29) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4228 Western Apartments (CMFA, 2025-10-24) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>4228 Western Ave Apartments (CMFA, 2025-11-07) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>12th Street Apartments (CMFA, 2026-01-09) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Del Norte Apartments (CMFA, 2026-04-17) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Terrace View Apartments (CMFA, 2026-06-12) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>The Heltsley Apartments FKA SoFi Redwood Park Apartments (CMFA, 2026-06-12) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Terrace View Apartments (CMFA, 2026-06-26) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>The Heltsley Apartments FKA SoFi Redwood Park Apartments (CMFA, 2026-06-26) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>new-grant</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Verdana Apartments (CSCDA, 2026-08-20) not in collaborator sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>investor_1: generated 'Oak Road' -&gt; manual 'Eleos Ventures, LLC'</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>entity: generated '2019 Ozone Affordable Housing – 820 MacArthur, LP' -&gt; manual '2019 Ozone Affordable Housing'</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>entity: generated 'OODB2, LP, a Washington Limited Partnership' -&gt; manual 'OODB2, LP'</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>entity: generated 'Affordable Housing Alliance II, Inc., d/b/a Integrity Housing, a Colorado nonprofit corporation' -&gt; manual 'Affordable Housing Alliance II, Inc. dba Integrity Housing'</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>investor_1: generated 'AOF / Pacific Affordable Housing Corp.' -&gt; manual 'AOF'</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>nonprofit_partner: generated 'AOF / Pacific Affordable Housing Corp.' -&gt; manual 'Pacific Affordable Housing Corp'</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>city: generated 'Los Angeles' -&gt; manual 'El Sobrante'</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>county: generated 'Los Angeles' -&gt; manual 'Contra Costa'</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>total_units: generated '24' -&gt; manual '52'</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>total_units: generated '22' -&gt; manual '72'</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>total_units: generated '24' -&gt; manual '48'</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>total_units: generated '65' -&gt; manual '165'</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>property_name: generated '2330 3rd Street Apartments' -&gt; manual '2330 E. 3rd Street Apartments'</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>investor_1: generated 'Ethos Real Estate' -&gt; manual 'Vistria Group'</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>nonprofit_partner: generated 'Step Forward Communities' -&gt; manual 'Step Forward Comminities'</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>total_units: generated '144' -&gt; manual '145'</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>total_units: generated '42' -&gt; manual '356'</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>investor_1: generated 'BRIDGE Housing Corporation' -&gt; manual 'Bridge Housing'</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>nonprofit_partner: generated 'BRIDGE Housing Corporation' -&gt; manual 'Bridge Housing'</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>entity: generated 'PREG 5150 ECR Los Altos, LP, a California limited partnership' -&gt; manual 'Prometheus Real Estate Group'</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>total_units: generated '29' -&gt; manual '196'</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>entity: generated '3 SIOF 1451 W MLK BLVD, LP' -&gt; manual '1451 W. MLK Boulevard Apartments'</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>investor_1: generated 'Vintage Housing Holdings, LLC / Kennedy Wilson' -&gt; manual 'Kennedy Wilson'</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>nonprofit_partner: generated 'Pacific Housing, Inc.' -&gt; manual 'Hearthstone Housing Foundation'</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>total_units: generated '8' -&gt; manual '1008'</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>total_units: generated '32' -&gt; manual '31'</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>city_cut: generated '4650.0' -&gt; manual '4500'</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>entity: generated '2 SIOF 10811 S Compton Ave, LP' -&gt; manual '10811 S. Compton Ave Apartments'</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>entity: generated 'SIOF 5 Properties, LP, a California limited partnership' -&gt; manual 'SIOF 5 Properties, LP, California limited partnership'</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>entity: generated '2 SIOF 685 W Fourth St, LP, a Delaware limited partnership' -&gt; manual '2 SIOF 685 W Fourth St, LP, Delaware limited partnership'</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>investor_1: generated 'Vintage Housing Holdings, LLC / Kennedy Wilson' -&gt; manual 'Vintage Housing Holdings'</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>total_units: generated '30' -&gt; manual '29'</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>investor_1: generated 'Belveron Partners' -&gt; manual 'Sack Capital Partners'</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>nonprofit_partner: generated 'Las Palmas Housing &amp; Development Corporation' -&gt; manual 'Las Palmas Housing &amp; Development Corp.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>investor_1: generated 'BRIDGE Housing Corporation' -&gt; manual 'BRIDGE Housing Corp.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>total_units: generated '24' -&gt; manual '42'</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>city: generated 'Sacramento' -&gt; manual 'Unincorporated'</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>property_name: generated 'Kinglsey Apartments' -&gt; manual 'Kingsley Apartments'</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>total_units: generated '69' -&gt; manual '68'</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>address: generated '5805 Charlotte Drive, San Jose, CA' -&gt; manual '5805 Charlotte Drive, San Jose, CA 95123'</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>total_units: generated '42' -&gt; manual '41'</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>property_name: generated 'Coliseum Connections Transit Village Apartments' -&gt; manual 'Coliseum Transit Village'</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>city: generated 'Santa Clara' -&gt; manual 'San Jose'</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>property_name: generated 'Coliseum Connections Transit Village Apartments' -&gt; manual 'Coliseum Connections'</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>property_name: generated 'The Langham Apartments' -&gt; manual 'Langham Apartments'</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>property_name: generated 'The Piccadilly Apartments' -&gt; manual 'Piccadilly Apartments'</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>total_units: generated '52' -&gt; manual '152'</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>entity: generated 'A limited partnership to be formed by Kairos Investment Management and Pacific Housing' -&gt; manual 'TBD LP'</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>entity: generated 'A limited partnership to be formed by Kairos Investment Management and Pacific Housing' -&gt; manual 'TBD LP'</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>city_cut: generated '15900.0' -&gt; manual '6300'</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>city: generated 'Long Beach' -&gt; manual 'Los Angeles'</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>total_units: generated '52' -&gt; manual '152'</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>entity: generated 'St. Anton Highlands LP' -&gt; manual 'St. Anton Highland, LP'</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>property_name: generated 'La Vista Apartments' -&gt; manual 'La Vista Apartment Homes'</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>total_units: generated '42' -&gt; manual '41'</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>address: generated '9750 Airport Blvd, Los Angeles, CA' -&gt; manual '9750 Airport Blvd, Westchester, CA 90045'</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>city_cut: generated '5550.0' -&gt; manual '5500'</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>address: generated '2625 Cullen Street, Los Angeles, CA' -&gt; manual '2625 Cullen St, Los Angeles, CA 90034'</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>address: generated '2481 South Sawtelle Blvd, Los Angeles, CA' -&gt; manual '2481 Sawtelle Blvd, Los Angeles, CA 90064'</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>property_name: generated 'Summerwood Apartment Homes' -&gt; manual 'Summerwood Apartments Homes Apartments'</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>entity: generated 'Standard Summerwood II LP' -&gt; manual 'Standard Properties'</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>investor_1: generated 'Standard Property Company, Inc.' -&gt; manual 'Standard Properties'</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>total_units: generated '50' -&gt; manual '49'</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>county: generated 'San Diego' -&gt; manual 'Los Angeles'</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>address: generated '1454 West Florence Avenue, Los Angeles, CA' -&gt; manual '1454 W Florence Ave, Los Angeles, CA 90047'</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>investor_1: generated 'Zenith Property Group LLC' -&gt; manual 'Red Stone Equity Partners'</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>term_years: generated '35' -&gt; manual '15'</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>term_years: generated '55' -&gt; manual '10'</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>address: generated '142 Fig Tree Lane, Martinez, CA' -&gt; manual '142 Fig Tree Lane, Martinez, CA 94553'</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>term_years: generated '15' -&gt; manual '10'</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>nonprofit_partner: generated 'The Foundation for Affordable Housing' -&gt; manual 'Foundation for Affordable Housing'</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>term_years: generated '10' -&gt; manual '15'</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>property_name: generated 'Hansen Village Apartments' -&gt; manual 'Hansen illage Apartments'</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>nonprofit_partner: generated 'The Foundation for Affordable Housing' -&gt; manual 'Foundation for Affordable Housing'</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>address: generated '11821 Foothill Blvd, Los Angeles, CA' -&gt; manual '11821 Foothill Blvd, Lake View Terrace, CA 91342'</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>address: generated '12091 Bayport Street, Garden Grove, CA' -&gt; manual '12091 Bayport St, Garden Grove, CA 92840'</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>address: generated '16077 Ashland Avenue, San Lorenzo' -&gt; manual '16077 Ashland Ave, San Lorenzo, CA 94580'</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>total_units: generated '35' -&gt; manual '34'</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>address: generated '511 N. Hoover Street, Los Angeles' -&gt; manual '511 N. Hoover Street, Los Angeles, California'</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>entity: generated 'Haven, LP' -&gt; manual 'Heven LP'</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>address: generated '6530 Independence Avenue, Los Angeles' -&gt; manual '6530 Independence Ave, Canoga Park, CA 91303'</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>address: generated '2075 West Jefferson Blvd., Los Angeles' -&gt; manual '2075 W Jefferson BlvdLos Angeles, CA 90018'</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>address: generated '5416 Jackson Street, North Highlands' -&gt; manual '5416 Jackson St, North Highlands, CA 95660'</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>address: generated '444 North Amelia Avenue, San Dimas' -&gt; manual '444 N Amelia Ave, San Dimas, CA 91773'</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>address: generated '220 47th Street, San Diego' -&gt; manual '220 47th St, San Diego, CA 92102'</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>nonprofit_partner: generated 'Bedford' -&gt; manual 'Bedford Affordable Housing Foundation'</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>address: generated '160 S. Virgil Avenue, Los Angeles' -&gt; manual '160 S Virgil Ave, Los Angeles, CA 90004'</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>address: generated '926 S. Kingsley Drive, Los Angeles, CA' -&gt; manual '926 S Kingsley Dr, Los Angeles, CA 90006'</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>term_years: generated '55' -&gt; manual '10'</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>address: generated '939 S. Kingsley Drive, Los Angeles, CA' -&gt; manual '939 S Kingsley Dr, Los Angeles, CA 90006'</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>address: generated '3950 W. Ingraham Street, Los Angeles, CA' -&gt; manual '3950 Ingraham St, San Diego, CA 92109'</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>total_units: generated '136' -&gt; manual '108'</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>address: generated '6985 S. Centinela Avenue, Los Angeles, CA' -&gt; manual '6985 S. Centinela Avenue, Los Angeles, CA 90045'</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>address: generated '1178 N. Edgemont Street, Los Angeles, CA' -&gt; manual '1178 N Edgemont St, Los Angeles, CA 90029'</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>entity: generated 'CG Bennington, LP and JSP Bennington, LP' -&gt; manual 'CG Bennington, LP / JSP Bennington, LP'</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>override-conflict</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>term_years: generated '30' -&gt; manual '55'</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>la-fetch-fallback</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>AIN 6020022027 has no current roll data; using manual value</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>AIN 6020022027 (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>la-fetch-fallback</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>AIN 5036031006 has no current roll data; using manual value</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>la-fetch-fallback</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>AIN 4262018026 has no current roll data; using manual value</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>la-fetch-fallback</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>AIN 6020022027 has no current roll data; using manual value</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>la-fetch-fallback</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>AIN 2125017014 has no current roll data; using manual value</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>AIN 41416654 (Alameda): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>AIN 41416654 (Alameda): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>AIN 5036031006 (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>AIN (none) (Santa Barbara): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>AIN (none) (Sacramento): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>AIN (none) (Contra Costa): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>AIN (none) (San Diego): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>AIN (none) (Sacramento): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>AIN (none) (San Diego): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>AIN (none) (Alameda): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>AIN (none) (Alameda): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>AIN (none) (Contra Costa): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>AIN (none) (San Diego): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>AIN 46745075 (Santa Clara): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>AIN 46745074 (Santa Clara): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>AIN 46745073 (Santa Clara): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>AIN (none) (Santa Clara): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>AIN (none) (Santa Cruz): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>AIN 128101150 (Solano): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>AIN 128101050 (Solano): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>AIN 128105060 (Solano): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>parcel-no-values</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>AIN (none) (Solano): no roll values from any source</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>missing-parcels</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Heritage Park Apartments Livermore: authorized, not dead, no parcel rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>shared-ain</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>143/147</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>AIN 41416654 assigned to multiple projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>shared-ain</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>182/76</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>AIN 5036031006 assigned to multiple projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>shared-ain</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>130/179</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>AIN 5080006008 assigned to multiple projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>shared-ain</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>126/173</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>AIN 5094005005 assigned to multiple projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>shared-ain</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>127/174</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>AIN 5094006003 assigned to multiple projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>shared-ain</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>122/165</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>AIN 5094017020 assigned to multiple projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>shared-ain</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>124/169</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>AIN 5094023025 assigned to multiple projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>shared-ain</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>128/175</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>AIN 5502019004 assigned to multiple projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>shared-ain</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>125/170</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>AIN 5503024012 assigned to multiple projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>shared-ain</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>129/177</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>AIN 5517005016 assigned to multiple projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>shared-ain</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>121/162</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>AIN 5518013024 assigned to multiple projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>shared-ain</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>123/168</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>AIN 5518020021 assigned to multiple projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>shared-ain</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>10/132</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>AIN 6020022027 assigned to multiple projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>shared-ain</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>152/181</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>AIN 7157012017 assigned to multiple projects</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -34477,7 +34477,7 @@
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="25" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -58019,14 +58019,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N329" t="inlineStr">
-        <is>
-          <t>7595</t>
-        </is>
-      </c>
-      <c r="R329" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K329" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L329" s="2" t="inlineStr">
+        <is>
+          <t>8875.0</t>
+        </is>
+      </c>
+      <c r="M329" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N329" s="2" t="inlineStr">
+        <is>
+          <t>8875.0</t>
+        </is>
+      </c>
+      <c r="O329" s="2" t="inlineStr">
+        <is>
+          <t>1569.0</t>
+        </is>
+      </c>
+      <c r="R329" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S329" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -58066,14 +58091,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N330" t="inlineStr">
-        <is>
-          <t>7606</t>
-        </is>
-      </c>
-      <c r="R330" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K330" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L330" s="2" t="inlineStr">
+        <is>
+          <t>8888.0</t>
+        </is>
+      </c>
+      <c r="M330" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N330" s="2" t="inlineStr">
+        <is>
+          <t>8888.0</t>
+        </is>
+      </c>
+      <c r="O330" s="2" t="inlineStr">
+        <is>
+          <t>1535.0</t>
+        </is>
+      </c>
+      <c r="R330" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S330" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -58113,14 +58163,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N331" t="inlineStr">
-        <is>
-          <t>7619</t>
-        </is>
-      </c>
-      <c r="R331" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K331" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L331" s="2" t="inlineStr">
+        <is>
+          <t>8903.0</t>
+        </is>
+      </c>
+      <c r="M331" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N331" s="2" t="inlineStr">
+        <is>
+          <t>8903.0</t>
+        </is>
+      </c>
+      <c r="O331" s="2" t="inlineStr">
+        <is>
+          <t>1514.0</t>
+        </is>
+      </c>
+      <c r="R331" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S331" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -58160,14 +58235,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N332" t="inlineStr">
-        <is>
-          <t>7631</t>
-        </is>
-      </c>
-      <c r="R332" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K332" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L332" s="2" t="inlineStr">
+        <is>
+          <t>8918.0</t>
+        </is>
+      </c>
+      <c r="M332" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N332" s="2" t="inlineStr">
+        <is>
+          <t>8918.0</t>
+        </is>
+      </c>
+      <c r="O332" s="2" t="inlineStr">
+        <is>
+          <t>1541.0</t>
+        </is>
+      </c>
+      <c r="R332" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S332" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -58207,14 +58307,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N333" t="inlineStr">
-        <is>
-          <t>30262</t>
-        </is>
-      </c>
-      <c r="R333" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K333" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L333" s="2" t="inlineStr">
+        <is>
+          <t>30867.0</t>
+        </is>
+      </c>
+      <c r="M333" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N333" s="2" t="inlineStr">
+        <is>
+          <t>30867.0</t>
+        </is>
+      </c>
+      <c r="O333" s="2" t="inlineStr">
+        <is>
+          <t>5457.0</t>
+        </is>
+      </c>
+      <c r="R333" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S333" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -58254,14 +58379,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N334" t="inlineStr">
-        <is>
-          <t>30426</t>
-        </is>
-      </c>
-      <c r="R334" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K334" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L334" s="2" t="inlineStr">
+        <is>
+          <t>31033.0</t>
+        </is>
+      </c>
+      <c r="M334" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N334" s="2" t="inlineStr">
+        <is>
+          <t>31033.0</t>
+        </is>
+      </c>
+      <c r="O334" s="2" t="inlineStr">
+        <is>
+          <t>5362.0</t>
+        </is>
+      </c>
+      <c r="R334" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S334" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -58301,14 +58451,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N335" t="inlineStr">
-        <is>
-          <t>31967</t>
-        </is>
-      </c>
-      <c r="R335" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K335" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L335" s="2" t="inlineStr">
+        <is>
+          <t>32605.0</t>
+        </is>
+      </c>
+      <c r="M335" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N335" s="2" t="inlineStr">
+        <is>
+          <t>32605.0</t>
+        </is>
+      </c>
+      <c r="O335" s="2" t="inlineStr">
+        <is>
+          <t>5546.0</t>
+        </is>
+      </c>
+      <c r="R335" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S335" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -58348,14 +58523,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N336" t="inlineStr">
-        <is>
-          <t>35714</t>
-        </is>
-      </c>
-      <c r="R336" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K336" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L336" s="2" t="inlineStr">
+        <is>
+          <t>36427.0</t>
+        </is>
+      </c>
+      <c r="M336" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N336" s="2" t="inlineStr">
+        <is>
+          <t>36427.0</t>
+        </is>
+      </c>
+      <c r="O336" s="2" t="inlineStr">
+        <is>
+          <t>6294.0</t>
+        </is>
+      </c>
+      <c r="R336" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S336" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -58395,14 +58595,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N337" t="inlineStr">
-        <is>
-          <t>40196</t>
-        </is>
-      </c>
-      <c r="R337" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K337" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L337" s="2" t="inlineStr">
+        <is>
+          <t>40997.0</t>
+        </is>
+      </c>
+      <c r="M337" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N337" s="2" t="inlineStr">
+        <is>
+          <t>40997.0</t>
+        </is>
+      </c>
+      <c r="O337" s="2" t="inlineStr">
+        <is>
+          <t>7248.0</t>
+        </is>
+      </c>
+      <c r="R337" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S337" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -58479,14 +58704,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N339" t="inlineStr">
-        <is>
-          <t>66586</t>
-        </is>
-      </c>
-      <c r="R339" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K339" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L339" s="2" t="inlineStr">
+        <is>
+          <t>67916.0</t>
+        </is>
+      </c>
+      <c r="M339" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N339" s="2" t="inlineStr">
+        <is>
+          <t>67916.0</t>
+        </is>
+      </c>
+      <c r="O339" s="2" t="inlineStr">
+        <is>
+          <t>11735.0</t>
+        </is>
+      </c>
+      <c r="R339" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S339" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -58526,14 +58776,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N340" t="inlineStr">
-        <is>
-          <t>61921</t>
-        </is>
-      </c>
-      <c r="R340" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K340" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L340" s="2" t="inlineStr">
+        <is>
+          <t>63157.0</t>
+        </is>
+      </c>
+      <c r="M340" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N340" s="2" t="inlineStr">
+        <is>
+          <t>63157.0</t>
+        </is>
+      </c>
+      <c r="O340" s="2" t="inlineStr">
+        <is>
+          <t>10743.0</t>
+        </is>
+      </c>
+      <c r="R340" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S340" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -58573,14 +58848,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N341" t="inlineStr">
-        <is>
-          <t>49211</t>
-        </is>
-      </c>
-      <c r="R341" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K341" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L341" s="2" t="inlineStr">
+        <is>
+          <t>50192.0</t>
+        </is>
+      </c>
+      <c r="M341" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N341" s="2" t="inlineStr">
+        <is>
+          <t>50192.0</t>
+        </is>
+      </c>
+      <c r="O341" s="2" t="inlineStr">
+        <is>
+          <t>8873.0</t>
+        </is>
+      </c>
+      <c r="R341" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S341" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -58620,14 +58920,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N342" t="inlineStr">
-        <is>
-          <t>99051</t>
-        </is>
-      </c>
-      <c r="R342" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K342" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L342" s="2" t="inlineStr">
+        <is>
+          <t>101032.0</t>
+        </is>
+      </c>
+      <c r="M342" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N342" s="2" t="inlineStr">
+        <is>
+          <t>101032.0</t>
+        </is>
+      </c>
+      <c r="O342" s="2" t="inlineStr">
+        <is>
+          <t>17458.0</t>
+        </is>
+      </c>
+      <c r="R342" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S342" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -58667,14 +58992,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N343" t="inlineStr">
-        <is>
-          <t>1360</t>
-        </is>
-      </c>
-      <c r="R343" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K343" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L343" s="2" t="inlineStr">
+        <is>
+          <t>51705.0</t>
+        </is>
+      </c>
+      <c r="M343" s="2" t="inlineStr">
+        <is>
+          <t>561000.0</t>
+        </is>
+      </c>
+      <c r="N343" s="2" t="inlineStr">
+        <is>
+          <t>612705.0</t>
+        </is>
+      </c>
+      <c r="O343" s="2" t="inlineStr">
+        <is>
+          <t>108006.0</t>
+        </is>
+      </c>
+      <c r="R343" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S343" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -58714,14 +59064,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N344" t="inlineStr">
-        <is>
-          <t>1201</t>
-        </is>
-      </c>
-      <c r="R344" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K344" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L344" s="2" t="inlineStr">
+        <is>
+          <t>50439.0</t>
+        </is>
+      </c>
+      <c r="M344" s="2" t="inlineStr">
+        <is>
+          <t>571000.0</t>
+        </is>
+      </c>
+      <c r="N344" s="2" t="inlineStr">
+        <is>
+          <t>621439.0</t>
+        </is>
+      </c>
+      <c r="O344" s="2" t="inlineStr">
+        <is>
+          <t>115237.0</t>
+        </is>
+      </c>
+      <c r="R344" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S344" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -58761,14 +59136,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N345" t="inlineStr">
-        <is>
-          <t>1201</t>
-        </is>
-      </c>
-      <c r="R345" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K345" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L345" s="2" t="inlineStr">
+        <is>
+          <t>50439.0</t>
+        </is>
+      </c>
+      <c r="M345" s="2" t="inlineStr">
+        <is>
+          <t>561000.0</t>
+        </is>
+      </c>
+      <c r="N345" s="2" t="inlineStr">
+        <is>
+          <t>611439.0</t>
+        </is>
+      </c>
+      <c r="O345" s="2" t="inlineStr">
+        <is>
+          <t>107787.0</t>
+        </is>
+      </c>
+      <c r="R345" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S345" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -58808,14 +59208,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N346" t="inlineStr">
-        <is>
-          <t>1202</t>
-        </is>
-      </c>
-      <c r="R346" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K346" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L346" s="2" t="inlineStr">
+        <is>
+          <t>50439.0</t>
+        </is>
+      </c>
+      <c r="M346" s="2" t="inlineStr">
+        <is>
+          <t>605000.0</t>
+        </is>
+      </c>
+      <c r="N346" s="2" t="inlineStr">
+        <is>
+          <t>655439.0</t>
+        </is>
+      </c>
+      <c r="O346" s="2" t="inlineStr">
+        <is>
+          <t>118205.0</t>
+        </is>
+      </c>
+      <c r="R346" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S346" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -58855,14 +59280,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N347" t="inlineStr">
-        <is>
-          <t>1202</t>
-        </is>
-      </c>
-      <c r="R347" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K347" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L347" s="2" t="inlineStr">
+        <is>
+          <t>9639.0</t>
+        </is>
+      </c>
+      <c r="M347" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N347" s="2" t="inlineStr">
+        <is>
+          <t>9639.0</t>
+        </is>
+      </c>
+      <c r="O347" s="2" t="inlineStr">
+        <is>
+          <t>1665.0</t>
+        </is>
+      </c>
+      <c r="R347" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S347" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -58902,14 +59352,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N348" t="inlineStr">
-        <is>
-          <t>1202</t>
-        </is>
-      </c>
-      <c r="R348" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K348" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L348" s="2" t="inlineStr">
+        <is>
+          <t>9639.0</t>
+        </is>
+      </c>
+      <c r="M348" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N348" s="2" t="inlineStr">
+        <is>
+          <t>9639.0</t>
+        </is>
+      </c>
+      <c r="O348" s="2" t="inlineStr">
+        <is>
+          <t>1704.0</t>
+        </is>
+      </c>
+      <c r="R348" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S348" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -58949,14 +59424,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N349" t="inlineStr">
-        <is>
-          <t>32653</t>
-        </is>
-      </c>
-      <c r="R349" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K349" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L349" s="2" t="inlineStr">
+        <is>
+          <t>33305.0</t>
+        </is>
+      </c>
+      <c r="M349" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N349" s="2" t="inlineStr">
+        <is>
+          <t>33305.0</t>
+        </is>
+      </c>
+      <c r="O349" s="2" t="inlineStr">
+        <is>
+          <t>5755.0</t>
+        </is>
+      </c>
+      <c r="R349" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S349" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -58996,14 +59496,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N350" t="inlineStr">
-        <is>
-          <t>32653</t>
-        </is>
-      </c>
-      <c r="R350" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K350" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L350" s="2" t="inlineStr">
+        <is>
+          <t>33305.0</t>
+        </is>
+      </c>
+      <c r="M350" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N350" s="2" t="inlineStr">
+        <is>
+          <t>33305.0</t>
+        </is>
+      </c>
+      <c r="O350" s="2" t="inlineStr">
+        <is>
+          <t>5888.0</t>
+        </is>
+      </c>
+      <c r="R350" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S350" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -59043,14 +59568,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N351" t="inlineStr">
-        <is>
-          <t>32697</t>
-        </is>
-      </c>
-      <c r="R351" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K351" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L351" s="2" t="inlineStr">
+        <is>
+          <t>33350.0</t>
+        </is>
+      </c>
+      <c r="M351" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N351" s="2" t="inlineStr">
+        <is>
+          <t>33350.0</t>
+        </is>
+      </c>
+      <c r="O351" s="2" t="inlineStr">
+        <is>
+          <t>5762.0</t>
+        </is>
+      </c>
+      <c r="R351" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S351" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -59090,14 +59640,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N352" t="inlineStr">
-        <is>
-          <t>32612</t>
-        </is>
-      </c>
-      <c r="R352" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K352" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L352" s="2" t="inlineStr">
+        <is>
+          <t>33263.0</t>
+        </is>
+      </c>
+      <c r="M352" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N352" s="2" t="inlineStr">
+        <is>
+          <t>33263.0</t>
+        </is>
+      </c>
+      <c r="O352" s="2" t="inlineStr">
+        <is>
+          <t>5658.0</t>
+        </is>
+      </c>
+      <c r="R352" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S352" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -59137,14 +59712,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N353" t="inlineStr">
-        <is>
-          <t>40431</t>
-        </is>
-      </c>
-      <c r="R353" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K353" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L353" s="2" t="inlineStr">
+        <is>
+          <t>41238.0</t>
+        </is>
+      </c>
+      <c r="M353" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N353" s="2" t="inlineStr">
+        <is>
+          <t>41238.0</t>
+        </is>
+      </c>
+      <c r="O353" s="2" t="inlineStr">
+        <is>
+          <t>7125.0</t>
+        </is>
+      </c>
+      <c r="R353" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S353" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -59184,14 +59784,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N354" t="inlineStr">
-        <is>
-          <t>47216</t>
-        </is>
-      </c>
-      <c r="R354" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K354" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L354" s="2" t="inlineStr">
+        <is>
+          <t>88958.0</t>
+        </is>
+      </c>
+      <c r="M354" s="2" t="inlineStr">
+        <is>
+          <t>561000.0</t>
+        </is>
+      </c>
+      <c r="N354" s="2" t="inlineStr">
+        <is>
+          <t>649958.0</t>
+        </is>
+      </c>
+      <c r="O354" s="2" t="inlineStr">
+        <is>
+          <t>114443.0</t>
+        </is>
+      </c>
+      <c r="R354" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S354" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -59231,14 +59856,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N355" t="inlineStr">
-        <is>
-          <t>29071</t>
-        </is>
-      </c>
-      <c r="R355" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K355" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L355" s="2" t="inlineStr">
+        <is>
+          <t>70451.0</t>
+        </is>
+      </c>
+      <c r="M355" s="2" t="inlineStr">
+        <is>
+          <t>605000.0</t>
+        </is>
+      </c>
+      <c r="N355" s="2" t="inlineStr">
+        <is>
+          <t>675451.0</t>
+        </is>
+      </c>
+      <c r="O355" s="2" t="inlineStr">
+        <is>
+          <t>448773.0</t>
+        </is>
+      </c>
+      <c r="R355" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S355" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -59278,14 +59928,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N356" t="inlineStr">
-        <is>
-          <t>29025</t>
-        </is>
-      </c>
-      <c r="R356" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K356" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L356" s="2" t="inlineStr">
+        <is>
+          <t>70404.0</t>
+        </is>
+      </c>
+      <c r="M356" s="2" t="inlineStr">
+        <is>
+          <t>561000.0</t>
+        </is>
+      </c>
+      <c r="N356" s="2" t="inlineStr">
+        <is>
+          <t>631404.0</t>
+        </is>
+      </c>
+      <c r="O356" s="2" t="inlineStr">
+        <is>
+          <t>111237.0</t>
+        </is>
+      </c>
+      <c r="R356" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S356" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -59325,14 +60000,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N357" t="inlineStr">
-        <is>
-          <t>29025</t>
-        </is>
-      </c>
-      <c r="R357" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K357" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L357" s="2" t="inlineStr">
+        <is>
+          <t>70404.0</t>
+        </is>
+      </c>
+      <c r="M357" s="2" t="inlineStr">
+        <is>
+          <t>605000.0</t>
+        </is>
+      </c>
+      <c r="N357" s="2" t="inlineStr">
+        <is>
+          <t>675404.0</t>
+        </is>
+      </c>
+      <c r="O357" s="2" t="inlineStr">
+        <is>
+          <t>121601.0</t>
+        </is>
+      </c>
+      <c r="R357" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S357" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -59372,14 +60072,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N358" t="inlineStr">
-        <is>
-          <t>29025</t>
-        </is>
-      </c>
-      <c r="R358" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K358" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L358" s="2" t="inlineStr">
+        <is>
+          <t>70404.0</t>
+        </is>
+      </c>
+      <c r="M358" s="2" t="inlineStr">
+        <is>
+          <t>561000.0</t>
+        </is>
+      </c>
+      <c r="N358" s="2" t="inlineStr">
+        <is>
+          <t>631404.0</t>
+        </is>
+      </c>
+      <c r="O358" s="2" t="inlineStr">
+        <is>
+          <t>111237.0</t>
+        </is>
+      </c>
+      <c r="R358" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S358" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -59419,14 +60144,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N359" t="inlineStr">
-        <is>
-          <t>7331</t>
-        </is>
-      </c>
-      <c r="R359" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K359" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L359" s="2" t="inlineStr">
+        <is>
+          <t>49366.0</t>
+        </is>
+      </c>
+      <c r="M359" s="2" t="inlineStr">
+        <is>
+          <t>571000.0</t>
+        </is>
+      </c>
+      <c r="N359" s="2" t="inlineStr">
+        <is>
+          <t>620366.0</t>
+        </is>
+      </c>
+      <c r="O359" s="2" t="inlineStr">
+        <is>
+          <t>113937.0</t>
+        </is>
+      </c>
+      <c r="R359" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S359" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -59466,14 +60216,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N360" t="inlineStr">
-        <is>
-          <t>7331</t>
-        </is>
-      </c>
-      <c r="R360" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K360" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L360" s="2" t="inlineStr">
+        <is>
+          <t>49366.0</t>
+        </is>
+      </c>
+      <c r="M360" s="2" t="inlineStr">
+        <is>
+          <t>561000.0</t>
+        </is>
+      </c>
+      <c r="N360" s="2" t="inlineStr">
+        <is>
+          <t>610366.0</t>
+        </is>
+      </c>
+      <c r="O360" s="2" t="inlineStr">
+        <is>
+          <t>107602.0</t>
+        </is>
+      </c>
+      <c r="R360" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S360" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -59513,14 +60288,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N361" t="inlineStr">
-        <is>
-          <t>6988</t>
-        </is>
-      </c>
-      <c r="R361" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K361" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L361" s="2" t="inlineStr">
+        <is>
+          <t>48965.0</t>
+        </is>
+      </c>
+      <c r="M361" s="2" t="inlineStr">
+        <is>
+          <t>605000.0</t>
+        </is>
+      </c>
+      <c r="N361" s="2" t="inlineStr">
+        <is>
+          <t>653965.0</t>
+        </is>
+      </c>
+      <c r="O361" s="2" t="inlineStr">
+        <is>
+          <t>117954.0</t>
+        </is>
+      </c>
+      <c r="R361" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S361" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -59560,14 +60360,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N362" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="R362" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K362" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L362" s="2" t="inlineStr">
+        <is>
+          <t>48965.0</t>
+        </is>
+      </c>
+      <c r="M362" s="2" t="inlineStr">
+        <is>
+          <t>561000.0</t>
+        </is>
+      </c>
+      <c r="N362" s="2" t="inlineStr">
+        <is>
+          <t>609965.0</t>
+        </is>
+      </c>
+      <c r="O362" s="2" t="inlineStr">
+        <is>
+          <t>107533.0</t>
+        </is>
+      </c>
+      <c r="R362" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S362" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -59607,14 +60432,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N363" t="inlineStr">
-        <is>
-          <t>1223</t>
-        </is>
-      </c>
-      <c r="R363" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K363" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L363" s="2" t="inlineStr">
+        <is>
+          <t>50603.0</t>
+        </is>
+      </c>
+      <c r="M363" s="2" t="inlineStr">
+        <is>
+          <t>571000.0</t>
+        </is>
+      </c>
+      <c r="N363" s="2" t="inlineStr">
+        <is>
+          <t>621603.0</t>
+        </is>
+      </c>
+      <c r="O363" s="2" t="inlineStr">
+        <is>
+          <t>115266.0</t>
+        </is>
+      </c>
+      <c r="R363" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S363" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -59654,14 +60504,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N364" t="inlineStr">
-        <is>
-          <t>1507</t>
-        </is>
-      </c>
-      <c r="R364" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K364" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L364" s="2" t="inlineStr">
+        <is>
+          <t>52887.0</t>
+        </is>
+      </c>
+      <c r="M364" s="2" t="inlineStr">
+        <is>
+          <t>561000.0</t>
+        </is>
+      </c>
+      <c r="N364" s="2" t="inlineStr">
+        <is>
+          <t>613887.0</t>
+        </is>
+      </c>
+      <c r="O364" s="2" t="inlineStr">
+        <is>
+          <t>390827.0</t>
+        </is>
+      </c>
+      <c r="R364" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S364" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -59701,14 +60576,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N365" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="R365" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K365" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L365" s="2" t="inlineStr">
+        <is>
+          <t>49635.0</t>
+        </is>
+      </c>
+      <c r="M365" s="2" t="inlineStr">
+        <is>
+          <t>571000.0</t>
+        </is>
+      </c>
+      <c r="N365" s="2" t="inlineStr">
+        <is>
+          <t>620635.0</t>
+        </is>
+      </c>
+      <c r="O365" s="2" t="inlineStr">
+        <is>
+          <t>115095.0</t>
+        </is>
+      </c>
+      <c r="R365" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S365" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -59748,14 +60648,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N366" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="R366" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K366" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L366" s="2" t="inlineStr">
+        <is>
+          <t>49635.0</t>
+        </is>
+      </c>
+      <c r="M366" s="2" t="inlineStr">
+        <is>
+          <t>561000.0</t>
+        </is>
+      </c>
+      <c r="N366" s="2" t="inlineStr">
+        <is>
+          <t>610635.0</t>
+        </is>
+      </c>
+      <c r="O366" s="2" t="inlineStr">
+        <is>
+          <t>107648.0</t>
+        </is>
+      </c>
+      <c r="R366" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S366" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -59795,14 +60720,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N367" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="R367" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K367" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L367" s="2" t="inlineStr">
+        <is>
+          <t>49635.0</t>
+        </is>
+      </c>
+      <c r="M367" s="2" t="inlineStr">
+        <is>
+          <t>605000.0</t>
+        </is>
+      </c>
+      <c r="N367" s="2" t="inlineStr">
+        <is>
+          <t>654635.0</t>
+        </is>
+      </c>
+      <c r="O367" s="2" t="inlineStr">
+        <is>
+          <t>434959.0</t>
+        </is>
+      </c>
+      <c r="R367" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S367" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -59842,14 +60792,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N368" t="inlineStr">
-        <is>
-          <t>1101</t>
-        </is>
-      </c>
-      <c r="R368" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K368" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L368" s="2" t="inlineStr">
+        <is>
+          <t>49635.0</t>
+        </is>
+      </c>
+      <c r="M368" s="2" t="inlineStr">
+        <is>
+          <t>561000.0</t>
+        </is>
+      </c>
+      <c r="N368" s="2" t="inlineStr">
+        <is>
+          <t>610635.0</t>
+        </is>
+      </c>
+      <c r="O368" s="2" t="inlineStr">
+        <is>
+          <t>107648.0</t>
+        </is>
+      </c>
+      <c r="R368" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S368" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -59889,14 +60864,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N369" t="inlineStr">
-        <is>
-          <t>29932</t>
-        </is>
-      </c>
-      <c r="R369" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K369" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L369" s="2" t="inlineStr">
+        <is>
+          <t>71329.0</t>
+        </is>
+      </c>
+      <c r="M369" s="2" t="inlineStr">
+        <is>
+          <t>571000.0</t>
+        </is>
+      </c>
+      <c r="N369" s="2" t="inlineStr">
+        <is>
+          <t>642329.0</t>
+        </is>
+      </c>
+      <c r="O369" s="2" t="inlineStr">
+        <is>
+          <t>118930.0</t>
+        </is>
+      </c>
+      <c r="R369" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S369" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -59936,14 +60936,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N370" t="inlineStr">
-        <is>
-          <t>29932</t>
-        </is>
-      </c>
-      <c r="R370" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K370" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L370" s="2" t="inlineStr">
+        <is>
+          <t>30529.0</t>
+        </is>
+      </c>
+      <c r="M370" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N370" s="2" t="inlineStr">
+        <is>
+          <t>30529.0</t>
+        </is>
+      </c>
+      <c r="O370" s="2" t="inlineStr">
+        <is>
+          <t>5275.0</t>
+        </is>
+      </c>
+      <c r="R370" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S370" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -59983,14 +61008,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N371" t="inlineStr">
-        <is>
-          <t>29932</t>
-        </is>
-      </c>
-      <c r="R371" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K371" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L371" s="2" t="inlineStr">
+        <is>
+          <t>30529.0</t>
+        </is>
+      </c>
+      <c r="M371" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N371" s="2" t="inlineStr">
+        <is>
+          <t>30529.0</t>
+        </is>
+      </c>
+      <c r="O371" s="2" t="inlineStr">
+        <is>
+          <t>5397.0</t>
+        </is>
+      </c>
+      <c r="R371" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S371" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -60030,14 +61080,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N372" t="inlineStr">
-        <is>
-          <t>55923</t>
-        </is>
-      </c>
-      <c r="R372" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K372" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L372" s="2" t="inlineStr">
+        <is>
+          <t>97840.0</t>
+        </is>
+      </c>
+      <c r="M372" s="2" t="inlineStr">
+        <is>
+          <t>561000.0</t>
+        </is>
+      </c>
+      <c r="N372" s="2" t="inlineStr">
+        <is>
+          <t>658840.0</t>
+        </is>
+      </c>
+      <c r="O372" s="2" t="inlineStr">
+        <is>
+          <t>419134.0</t>
+        </is>
+      </c>
+      <c r="R372" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S372" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -60077,14 +61152,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N373" t="inlineStr">
-        <is>
-          <t>47738</t>
-        </is>
-      </c>
-      <c r="R373" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K373" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L373" s="2" t="inlineStr">
+        <is>
+          <t>89491.0</t>
+        </is>
+      </c>
+      <c r="M373" s="2" t="inlineStr">
+        <is>
+          <t>572220.0</t>
+        </is>
+      </c>
+      <c r="N373" s="2" t="inlineStr">
+        <is>
+          <t>661711.0</t>
+        </is>
+      </c>
+      <c r="O373" s="2" t="inlineStr">
+        <is>
+          <t>116518.0</t>
+        </is>
+      </c>
+      <c r="R373" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S373" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -60124,14 +61224,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N374" t="inlineStr">
-        <is>
-          <t>27211</t>
-        </is>
-      </c>
-      <c r="R374" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K374" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L374" s="2" t="inlineStr">
+        <is>
+          <t>68555.0</t>
+        </is>
+      </c>
+      <c r="M374" s="2" t="inlineStr">
+        <is>
+          <t>582420.0</t>
+        </is>
+      </c>
+      <c r="N374" s="2" t="inlineStr">
+        <is>
+          <t>650975.0</t>
+        </is>
+      </c>
+      <c r="O374" s="2" t="inlineStr">
+        <is>
+          <t>351865.0</t>
+        </is>
+      </c>
+      <c r="R374" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S374" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -60171,14 +61296,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N375" t="inlineStr">
-        <is>
-          <t>27211</t>
-        </is>
-      </c>
-      <c r="R375" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K375" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L375" s="2" t="inlineStr">
+        <is>
+          <t>68555.0</t>
+        </is>
+      </c>
+      <c r="M375" s="2" t="inlineStr">
+        <is>
+          <t>617100.0</t>
+        </is>
+      </c>
+      <c r="N375" s="2" t="inlineStr">
+        <is>
+          <t>685655.0</t>
+        </is>
+      </c>
+      <c r="O375" s="2" t="inlineStr">
+        <is>
+          <t>123479.0</t>
+        </is>
+      </c>
+      <c r="R375" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S375" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -60218,14 +61368,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N376" t="inlineStr">
-        <is>
-          <t>27211</t>
-        </is>
-      </c>
-      <c r="R376" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K376" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L376" s="2" t="inlineStr">
+        <is>
+          <t>68555.0</t>
+        </is>
+      </c>
+      <c r="M376" s="2" t="inlineStr">
+        <is>
+          <t>572220.0</t>
+        </is>
+      </c>
+      <c r="N376" s="2" t="inlineStr">
+        <is>
+          <t>640775.0</t>
+        </is>
+      </c>
+      <c r="O376" s="2" t="inlineStr">
+        <is>
+          <t>112900.0</t>
+        </is>
+      </c>
+      <c r="R376" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S376" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -60265,14 +61440,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N377" t="inlineStr">
-        <is>
-          <t>6874</t>
-        </is>
-      </c>
-      <c r="R377" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K377" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L377" s="2" t="inlineStr">
+        <is>
+          <t>48832.0</t>
+        </is>
+      </c>
+      <c r="M377" s="2" t="inlineStr">
+        <is>
+          <t>582420.0</t>
+        </is>
+      </c>
+      <c r="N377" s="2" t="inlineStr">
+        <is>
+          <t>631252.0</t>
+        </is>
+      </c>
+      <c r="O377" s="2" t="inlineStr">
+        <is>
+          <t>341301.0</t>
+        </is>
+      </c>
+      <c r="R377" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S377" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -60312,14 +61512,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N378" t="inlineStr">
-        <is>
-          <t>6874</t>
-        </is>
-      </c>
-      <c r="R378" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K378" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L378" s="2" t="inlineStr">
+        <is>
+          <t>8032.0</t>
+        </is>
+      </c>
+      <c r="M378" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N378" s="2" t="inlineStr">
+        <is>
+          <t>8032.0</t>
+        </is>
+      </c>
+      <c r="O378" s="2" t="inlineStr">
+        <is>
+          <t>1366.0</t>
+        </is>
+      </c>
+      <c r="R378" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S378" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -60359,14 +61584,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N379" t="inlineStr">
-        <is>
-          <t>6874</t>
-        </is>
-      </c>
-      <c r="R379" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K379" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L379" s="2" t="inlineStr">
+        <is>
+          <t>48832.0</t>
+        </is>
+      </c>
+      <c r="M379" s="2" t="inlineStr">
+        <is>
+          <t>572220.0</t>
+        </is>
+      </c>
+      <c r="N379" s="2" t="inlineStr">
+        <is>
+          <t>621052.0</t>
+        </is>
+      </c>
+      <c r="O379" s="2" t="inlineStr">
+        <is>
+          <t>109492.0</t>
+        </is>
+      </c>
+      <c r="R379" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S379" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -60406,14 +61656,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N380" t="inlineStr">
-        <is>
-          <t>6874</t>
-        </is>
-      </c>
-      <c r="R380" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K380" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L380" s="2" t="inlineStr">
+        <is>
+          <t>48832.0</t>
+        </is>
+      </c>
+      <c r="M380" s="2" t="inlineStr">
+        <is>
+          <t>582420.0</t>
+        </is>
+      </c>
+      <c r="N380" s="2" t="inlineStr">
+        <is>
+          <t>631252.0</t>
+        </is>
+      </c>
+      <c r="O380" s="2" t="inlineStr">
+        <is>
+          <t>341301.0</t>
+        </is>
+      </c>
+      <c r="R380" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S380" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -60453,14 +61728,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N381" t="inlineStr">
-        <is>
-          <t>8329</t>
-        </is>
-      </c>
-      <c r="R381" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K381" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L381" s="2" t="inlineStr">
+        <is>
+          <t>50532.0</t>
+        </is>
+      </c>
+      <c r="M381" s="2" t="inlineStr">
+        <is>
+          <t>572220.0</t>
+        </is>
+      </c>
+      <c r="N381" s="2" t="inlineStr">
+        <is>
+          <t>622752.0</t>
+        </is>
+      </c>
+      <c r="O381" s="2" t="inlineStr">
+        <is>
+          <t>622752.0</t>
+        </is>
+      </c>
+      <c r="R381" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S381" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -60537,14 +61837,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N383" t="inlineStr">
-        <is>
-          <t>11538</t>
-        </is>
-      </c>
-      <c r="R383" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K383" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L383" s="2" t="inlineStr">
+        <is>
+          <t>54282.0</t>
+        </is>
+      </c>
+      <c r="M383" s="2" t="inlineStr">
+        <is>
+          <t>408000.0</t>
+        </is>
+      </c>
+      <c r="N383" s="2" t="inlineStr">
+        <is>
+          <t>462282.0</t>
+        </is>
+      </c>
+      <c r="O383" s="2" t="inlineStr">
+        <is>
+          <t>132718.0</t>
+        </is>
+      </c>
+      <c r="R383" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S383" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -60584,14 +61909,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N384" t="inlineStr">
-        <is>
-          <t>11625</t>
-        </is>
-      </c>
-      <c r="R384" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K384" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L384" s="2" t="inlineStr">
+        <is>
+          <t>54384.0</t>
+        </is>
+      </c>
+      <c r="M384" s="2" t="inlineStr">
+        <is>
+          <t>397800.0</t>
+        </is>
+      </c>
+      <c r="N384" s="2" t="inlineStr">
+        <is>
+          <t>452184.0</t>
+        </is>
+      </c>
+      <c r="O384" s="2" t="inlineStr">
+        <is>
+          <t>452184.0</t>
+        </is>
+      </c>
+      <c r="R384" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S384" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -60631,14 +61981,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N385" t="inlineStr">
-        <is>
-          <t>11618</t>
-        </is>
-      </c>
-      <c r="R385" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K385" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L385" s="2" t="inlineStr">
+        <is>
+          <t>13574.0</t>
+        </is>
+      </c>
+      <c r="M385" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N385" s="2" t="inlineStr">
+        <is>
+          <t>13574.0</t>
+        </is>
+      </c>
+      <c r="O385" s="2" t="inlineStr">
+        <is>
+          <t>3743.0</t>
+        </is>
+      </c>
+      <c r="R385" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S385" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -60678,14 +62053,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N386" t="inlineStr">
-        <is>
-          <t>11609</t>
-        </is>
-      </c>
-      <c r="R386" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K386" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L386" s="2" t="inlineStr">
+        <is>
+          <t>54364.0</t>
+        </is>
+      </c>
+      <c r="M386" s="2" t="inlineStr">
+        <is>
+          <t>397800.0</t>
+        </is>
+      </c>
+      <c r="N386" s="2" t="inlineStr">
+        <is>
+          <t>452164.0</t>
+        </is>
+      </c>
+      <c r="O386" s="2" t="inlineStr">
+        <is>
+          <t>161808.0</t>
+        </is>
+      </c>
+      <c r="R386" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S386" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -60725,14 +62125,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N387" t="inlineStr">
-        <is>
-          <t>11771</t>
-        </is>
-      </c>
-      <c r="R387" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K387" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L387" s="2" t="inlineStr">
+        <is>
+          <t>54554.0</t>
+        </is>
+      </c>
+      <c r="M387" s="2" t="inlineStr">
+        <is>
+          <t>408000.0</t>
+        </is>
+      </c>
+      <c r="N387" s="2" t="inlineStr">
+        <is>
+          <t>462554.0</t>
+        </is>
+      </c>
+      <c r="O387" s="2" t="inlineStr">
+        <is>
+          <t>132793.0</t>
+        </is>
+      </c>
+      <c r="R387" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S387" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -60772,14 +62197,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N388" t="inlineStr">
-        <is>
-          <t>56604</t>
-        </is>
-      </c>
-      <c r="R388" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K388" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L388" s="2" t="inlineStr">
+        <is>
+          <t>98534.0</t>
+        </is>
+      </c>
+      <c r="M388" s="2" t="inlineStr">
+        <is>
+          <t>572220.0</t>
+        </is>
+      </c>
+      <c r="N388" s="2" t="inlineStr">
+        <is>
+          <t>670754.0</t>
+        </is>
+      </c>
+      <c r="O388" s="2" t="inlineStr">
+        <is>
+          <t>362111.0</t>
+        </is>
+      </c>
+      <c r="R388" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S388" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -60819,14 +62269,39 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N389" t="inlineStr">
-        <is>
-          <t>60404</t>
-        </is>
-      </c>
-      <c r="R389" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K389" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L389" s="2" t="inlineStr">
+        <is>
+          <t>61611.0</t>
+        </is>
+      </c>
+      <c r="M389" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N389" s="2" t="inlineStr">
+        <is>
+          <t>61611.0</t>
+        </is>
+      </c>
+      <c r="O389" s="2" t="inlineStr">
+        <is>
+          <t>24570.0</t>
+        </is>
+      </c>
+      <c r="R389" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S389" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -60846,6 +62321,21 @@
           <t>Bennington Apartments</t>
         </is>
       </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>168150010</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>0168-150-010</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>2780 NORTH TEXAS STREET FAIRFIELD</t>
+        </is>
+      </c>
       <c r="G390" t="inlineStr">
         <is>
           <t>False</t>
@@ -60853,7 +62343,47 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>Single Real Property parcel at the project situs per Solano assessor portal search 2026-08-22 (other hits are business accounts)</t>
+        </is>
+      </c>
+      <c r="K390" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L390" s="2" t="inlineStr">
+        <is>
+          <t>5338692.0</t>
+        </is>
+      </c>
+      <c r="M390" s="2" t="inlineStr">
+        <is>
+          <t>23942991.0</t>
+        </is>
+      </c>
+      <c r="N390" s="2" t="inlineStr">
+        <is>
+          <t>29281683.0</t>
+        </is>
+      </c>
+      <c r="O390" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="R390" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S390" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -60925,7 +62455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C201"/>
+  <dimension ref="A1:C200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -63129,7 +64659,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>la-fetch-fallback</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -63139,7 +64669,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>AIN 6020022027 has no current roll data; using manual value</t>
+          <t>AIN 6020022027 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
@@ -63163,7 +64693,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>la-fetch-fallback</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -63173,14 +64703,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>AIN 5036031006 has no current roll data; using manual value</t>
+          <t>AIN 5036031006 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>la-fetch-fallback</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -63190,14 +64720,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AIN 4262018026 has no current roll data; using manual value</t>
+          <t>AIN 4262018026 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>la-fetch-fallback</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -63207,14 +64737,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>AIN 6020022027 has no current roll data; using manual value</t>
+          <t>AIN 6020022027 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>la-fetch-fallback</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -63224,7 +64754,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>AIN 2125017014 has no current roll data; using manual value</t>
+          <t>AIN 2125017014 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
@@ -64081,34 +65611,34 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>missing-parcels</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>238</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>AIN (none) (Solano): no roll values from any source</t>
+          <t>Heritage Park Apartments Livermore: authorized, not dead, no parcel rows</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>missing-parcels</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>143/147</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Heritage Park Apartments Livermore: authorized, not dead, no parcel rows</t>
+          <t>AIN 41416654 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -64120,12 +65650,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>143/147</t>
+          <t>182/76</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>AIN 41416654 assigned to multiple projects</t>
+          <t>AIN 5036031006 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -64137,12 +65667,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>182/76</t>
+          <t>130/179</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>AIN 5036031006 assigned to multiple projects</t>
+          <t>AIN 5080006008 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -64154,12 +65684,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>130/179</t>
+          <t>126/173</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>AIN 5080006008 assigned to multiple projects</t>
+          <t>AIN 5094005005 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -64171,12 +65701,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>126/173</t>
+          <t>127/174</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>AIN 5094005005 assigned to multiple projects</t>
+          <t>AIN 5094006003 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -64188,12 +65718,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>127/174</t>
+          <t>122/165</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>AIN 5094006003 assigned to multiple projects</t>
+          <t>AIN 5094017020 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -64205,12 +65735,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>122/165</t>
+          <t>124/169</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>AIN 5094017020 assigned to multiple projects</t>
+          <t>AIN 5094023025 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -64222,12 +65752,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>124/169</t>
+          <t>128/175</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>AIN 5094023025 assigned to multiple projects</t>
+          <t>AIN 5502019004 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -64239,12 +65769,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>128/175</t>
+          <t>125/170</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>AIN 5502019004 assigned to multiple projects</t>
+          <t>AIN 5503024012 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -64256,12 +65786,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>125/170</t>
+          <t>129/177</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>AIN 5503024012 assigned to multiple projects</t>
+          <t>AIN 5517005016 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -64273,12 +65803,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>129/177</t>
+          <t>121/162</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>AIN 5517005016 assigned to multiple projects</t>
+          <t>AIN 5518013024 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -64290,12 +65820,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>121/162</t>
+          <t>123/168</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>AIN 5518013024 assigned to multiple projects</t>
+          <t>AIN 5518020021 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -64307,12 +65837,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>123/168</t>
+          <t>10/132</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>AIN 5518020021 assigned to multiple projects</t>
+          <t>AIN 6020022027 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -64324,27 +65854,10 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>10/132</t>
+          <t>152/181</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
-        <is>
-          <t>AIN 6020022027 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>152/181</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
         <is>
           <t>AIN 7157012017 assigned to multiple projects</t>
         </is>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -34903,14 +34903,44 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>9316117</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2202858</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7489628</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>9692486</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>sandag-parcels</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -35844,14 +35874,44 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>32460480</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>9568699</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>24203182</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>33771881</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>sandag-parcels</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -40766,14 +40826,44 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>13158000</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>204000</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
         <is>
           <t>13362000</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>sandag-parcels</t>
+        </is>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -41172,14 +41262,44 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>53339453</t>
-        </is>
-      </c>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>18360000</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>50003178</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>68363178</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>sandag-parcels</t>
+        </is>
+      </c>
+      <c r="S83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -41219,14 +41339,44 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>5832864</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>2142762</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3925748</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>6068510</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>sandag-parcels</t>
+        </is>
+      </c>
+      <c r="S84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -46298,14 +46448,44 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>2804259</t>
-        </is>
-      </c>
-      <c r="R146" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>4462500</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>4462500</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  </t>
+        </is>
+      </c>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R146" s="2" t="inlineStr">
+        <is>
+          <t>sandag-parcels</t>
+        </is>
+      </c>
+      <c r="S146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -46345,14 +46525,44 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N147" t="inlineStr">
-        <is>
-          <t>30350548</t>
-        </is>
-      </c>
-      <c r="R147" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>23383000</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>10021000</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>33404000</t>
+        </is>
+      </c>
+      <c r="P147" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R147" s="2" t="inlineStr">
+        <is>
+          <t>sandag-parcels</t>
+        </is>
+      </c>
+      <c r="S147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -47831,14 +48041,44 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>51548563</t>
-        </is>
-      </c>
-      <c r="R165" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>30000000</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>43424100</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>73424100</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R165" s="2" t="inlineStr">
+        <is>
+          <t>sandag-parcels</t>
+        </is>
+      </c>
+      <c r="S165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -52860,14 +53100,44 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N227" t="inlineStr">
-        <is>
-          <t>12540125</t>
-        </is>
-      </c>
-      <c r="R227" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K227" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L227" s="2" t="inlineStr">
+        <is>
+          <t>5116369</t>
+        </is>
+      </c>
+      <c r="M227" s="2" t="inlineStr">
+        <is>
+          <t>7674557</t>
+        </is>
+      </c>
+      <c r="N227" s="2" t="inlineStr">
+        <is>
+          <t>12790926</t>
+        </is>
+      </c>
+      <c r="P227" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="Q227" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R227" s="2" t="inlineStr">
+        <is>
+          <t>sandag-parcels</t>
+        </is>
+      </c>
+      <c r="S227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -52907,14 +53177,44 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N228" t="inlineStr">
-        <is>
-          <t>41107952</t>
-        </is>
-      </c>
-      <c r="R228" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K228" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L228" s="2" t="inlineStr">
+        <is>
+          <t>20621754</t>
+        </is>
+      </c>
+      <c r="M228" s="2" t="inlineStr">
+        <is>
+          <t>21308356</t>
+        </is>
+      </c>
+      <c r="N228" s="2" t="inlineStr">
+        <is>
+          <t>41930110</t>
+        </is>
+      </c>
+      <c r="P228" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="Q228" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R228" s="2" t="inlineStr">
+        <is>
+          <t>sandag-parcels</t>
+        </is>
+      </c>
+      <c r="S228" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -52954,14 +53254,44 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N229" t="inlineStr">
-        <is>
-          <t>18982539</t>
-        </is>
-      </c>
-      <c r="R229" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K229" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L229" s="2" t="inlineStr">
+        <is>
+          <t>7937360</t>
+        </is>
+      </c>
+      <c r="M229" s="2" t="inlineStr">
+        <is>
+          <t>11424829</t>
+        </is>
+      </c>
+      <c r="N229" s="2" t="inlineStr">
+        <is>
+          <t>19362189</t>
+        </is>
+      </c>
+      <c r="P229" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="Q229" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R229" s="2" t="inlineStr">
+        <is>
+          <t>sandag-parcels</t>
+        </is>
+      </c>
+      <c r="S229" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -53001,14 +53331,44 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N230" t="inlineStr">
-        <is>
-          <t>12540125</t>
-        </is>
-      </c>
-      <c r="R230" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="K230" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L230" s="2" t="inlineStr">
+        <is>
+          <t>5116369</t>
+        </is>
+      </c>
+      <c r="M230" s="2" t="inlineStr">
+        <is>
+          <t>7674557</t>
+        </is>
+      </c>
+      <c r="N230" s="2" t="inlineStr">
+        <is>
+          <t>12790926</t>
+        </is>
+      </c>
+      <c r="P230" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="Q230" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R230" s="2" t="inlineStr">
+        <is>
+          <t>sandag-parcels</t>
+        </is>
+      </c>
+      <c r="S230" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -55776,19 +56136,49 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N265" t="inlineStr">
-        <is>
-          <t>49668778</t>
-        </is>
-      </c>
-      <c r="O265" t="inlineStr">
+      <c r="K265" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L265" s="2" t="inlineStr">
+        <is>
+          <t>30308100</t>
+        </is>
+      </c>
+      <c r="M265" s="2" t="inlineStr">
+        <is>
+          <t>20354053</t>
+        </is>
+      </c>
+      <c r="N265" s="2" t="inlineStr">
+        <is>
+          <t>50662153</t>
+        </is>
+      </c>
+      <c r="O265" s="2" t="inlineStr">
         <is>
           <t>49157189</t>
         </is>
       </c>
-      <c r="R265" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="P265" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="Q265" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R265" s="2" t="inlineStr">
+        <is>
+          <t>sandag-parcels</t>
+        </is>
+      </c>
+      <c r="S265" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -24937,6 +24937,11 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>6840 Baird Ave, Los Angeles, CA 91335</t>
+        </is>
+      </c>
       <c r="AD199" t="inlineStr">
         <is>
           <t>operative</t>
@@ -24954,7 +24959,7 @@
       </c>
       <c r="AH199" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; city_cut:collaborator-sheet</t>
+          <t>restricted_units:collaborator-sheet; city_cut:collaborator-sheet; address:manual-repo-edit</t>
         </is>
       </c>
     </row>
@@ -25527,6 +25532,11 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>6144 Hazelhurst Place, North Hollywood, CA 91606</t>
+        </is>
+      </c>
       <c r="W204" t="inlineStr">
         <is>
           <t>YES</t>
@@ -25549,7 +25559,7 @@
       </c>
       <c r="AH204" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:manual-repo-edit</t>
         </is>
       </c>
     </row>
@@ -27033,6 +27043,11 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>217 N. Park View Street, Los Angeles, CA 90026</t>
+        </is>
+      </c>
       <c r="W217" t="inlineStr">
         <is>
           <t>YES</t>
@@ -27055,7 +27070,7 @@
       </c>
       <c r="AH217" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:manual-repo-edit</t>
         </is>
       </c>
     </row>
@@ -36124,7 +36139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T392"/>
+  <dimension ref="A1:T394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42491,7 +42506,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4284000</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -59787,6 +59802,21 @@
           <t>Bluwater Crossing Apartments</t>
         </is>
       </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>2146500200</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>214-650-02-00</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>6790 EMBARCADERO LN CARLSBAD CA 92011</t>
+        </is>
+      </c>
       <c r="G279" t="inlineStr">
         <is>
           <t>False</t>
@@ -59794,7 +59824,52 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
+          <t>script-situs-match (2026-08-22)</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>Exact situs match, SANDAG; 66-unit apartment parcel</t>
+        </is>
+      </c>
+      <c r="K279" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L279" s="2" t="inlineStr">
+        <is>
+          <t>15568767</t>
+        </is>
+      </c>
+      <c r="M279" s="2" t="inlineStr">
+        <is>
+          <t>33766648</t>
+        </is>
+      </c>
+      <c r="N279" s="2" t="inlineStr">
+        <is>
+          <t>49335415</t>
+        </is>
+      </c>
+      <c r="P279" s="2" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Q279" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R279" s="2" t="inlineStr">
+        <is>
+          <t>sandag-parcels</t>
+        </is>
+      </c>
+      <c r="S279" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T279" t="inlineStr">
@@ -60216,6 +60291,21 @@
           <t>Guava Gardens Apartments</t>
         </is>
       </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>4701122500</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>470-112-25-00</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>5035 GUAVA AVE LA MESA CA 91942</t>
+        </is>
+      </c>
       <c r="G286" t="inlineStr">
         <is>
           <t>False</t>
@@ -60223,7 +60313,52 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
+          <t>script-situs-match (2026-08-22)</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>Exact situs match, SANDAG; 81-unit apartment parcel</t>
+        </is>
+      </c>
+      <c r="K286" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L286" s="2" t="inlineStr">
+        <is>
+          <t>2033407</t>
+        </is>
+      </c>
+      <c r="M286" s="2" t="inlineStr">
+        <is>
+          <t>3050116</t>
+        </is>
+      </c>
+      <c r="N286" s="2" t="inlineStr">
+        <is>
+          <t>5083523</t>
+        </is>
+      </c>
+      <c r="P286" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="Q286" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R286" s="2" t="inlineStr">
+        <is>
+          <t>sandag-parcels</t>
+        </is>
+      </c>
+      <c r="S286" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T286" t="inlineStr">
@@ -60248,6 +60383,21 @@
           <t>Park View by Angeleno Apartments</t>
         </is>
       </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>5157007028</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>5157-007-028</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>217 N PARK VIEW ST LOS ANGELES CA 90026</t>
+        </is>
+      </c>
       <c r="G287" t="inlineStr">
         <is>
           <t>False</t>
@@ -60255,7 +60405,57 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
+          <t>script-situs-match (2026-08-22)</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>Exact situs match, LA parcel API; use still "Single" (pre-development)</t>
+        </is>
+      </c>
+      <c r="K287" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L287" s="2" t="inlineStr">
+        <is>
+          <t>938400</t>
+        </is>
+      </c>
+      <c r="M287" s="2" t="inlineStr">
+        <is>
+          <t>234600</t>
+        </is>
+      </c>
+      <c r="N287" s="2" t="inlineStr">
+        <is>
+          <t>1173000</t>
+        </is>
+      </c>
+      <c r="O287" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P287" s="2" t="inlineStr">
+        <is>
+          <t>1911</t>
+        </is>
+      </c>
+      <c r="Q287" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="R287" s="2" t="inlineStr">
+        <is>
+          <t>la-county-api</t>
+        </is>
+      </c>
+      <c r="S287" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T287" t="inlineStr">
@@ -67511,6 +67711,200 @@
       <c r="T392" t="inlineStr">
         <is>
           <t>230</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Verdana Apartments</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>4441201300</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>444-120-13-00</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>438 CAMINO DEL RIO S SAN DIEGO CA 92108</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>script-situs-match (2026-08-22)</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>situs-match</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>Exact situs match, SANDAG; pre-development parcels per staff report address</t>
+        </is>
+      </c>
+      <c r="K393" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L393" s="2" t="inlineStr">
+        <is>
+          <t>2427182</t>
+        </is>
+      </c>
+      <c r="M393" s="2" t="inlineStr">
+        <is>
+          <t>1490976</t>
+        </is>
+      </c>
+      <c r="N393" s="2" t="inlineStr">
+        <is>
+          <t>3918158</t>
+        </is>
+      </c>
+      <c r="P393" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="Q393" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R393" s="2" t="inlineStr">
+        <is>
+          <t>sandag-parcels</t>
+        </is>
+      </c>
+      <c r="S393" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Verdana Apartments</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>4441201800</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>444-120-18-00</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>480 CAMINO DEL RIO S SAN DIEGO CA 92108</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>script-situs-match (2026-08-22)</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>situs-match</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>Exact situs match, SANDAG; pre-development parcels per staff report address</t>
+        </is>
+      </c>
+      <c r="K394" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L394" s="2" t="inlineStr">
+        <is>
+          <t>1884643</t>
+        </is>
+      </c>
+      <c r="M394" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N394" s="2" t="inlineStr">
+        <is>
+          <t>1884643</t>
+        </is>
+      </c>
+      <c r="P394" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  </t>
+        </is>
+      </c>
+      <c r="Q394" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R394" s="2" t="inlineStr">
+        <is>
+          <t>sandag-parcels</t>
+        </is>
+      </c>
+      <c r="S394" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="T394" t="inlineStr">
+        <is>
+          <t>369</t>
         </is>
       </c>
     </row>
@@ -67525,7 +67919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C187"/>
+  <dimension ref="A1:C183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -70074,12 +70468,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>213</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>AIN (none) (San Diego): no roll values from any source</t>
+          <t>AIN (none) (Sacramento): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70091,12 +70485,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>215</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>AIN (none) (Sacramento): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70108,7 +70502,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>221</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -70125,12 +70519,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>222</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>AIN (none) (San Diego): no roll values from any source</t>
+          <t>AIN (none) (Alameda): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70142,12 +70536,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>223</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN (none) (Alameda): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70159,12 +70553,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN (none) (Contra Costa): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70176,12 +70570,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>229</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>AIN (none) (Alameda): no roll values from any source</t>
+          <t>AIN (none) (San Diego): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70193,12 +70587,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>235</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>AIN (none) (Alameda): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70210,12 +70604,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>236</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>AIN (none) (Contra Costa): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70227,12 +70621,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>AIN (none) (San Diego): no roll values from any source</t>
+          <t>AIN 46745075 (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70244,12 +70638,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 46745074 (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70261,12 +70655,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 46745073 (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70278,12 +70672,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>198</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>AIN 46745075 (Santa Clara): no roll values from any source</t>
+          <t>AIN (none) (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70295,12 +70689,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>AIN 46745074 (Santa Clara): no roll values from any source</t>
+          <t>AIN (none) (Santa Cruz): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70312,12 +70706,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>AIN 46745073 (Santa Clara): no roll values from any source</t>
+          <t>AIN 128101150 (Solano): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70329,12 +70723,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>AIN (none) (Santa Clara): no roll values from any source</t>
+          <t>AIN 128101050 (Solano): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70346,97 +70740,97 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>AIN (none) (Santa Cruz): no roll values from any source</t>
+          <t>AIN 128105060 (Solano): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>missing-parcels</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>238</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>AIN 128101150 (Solano): no roll values from any source</t>
+          <t>Heritage Park Apartments Livermore (Alameda): operative authorization, not dead, no parcels anywhere in its property group</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>143/147</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>AIN 128101050 (Solano): no roll values from any source</t>
+          <t>AIN 41416654 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>182/76</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>AIN 128105060 (Solano): no roll values from any source</t>
+          <t>AIN 5036031006 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>missing-parcels</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>200/218</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Heritage Park Apartments Livermore (Alameda): operative authorization, not dead, no parcels anywhere in its property group</t>
+          <t>AIN 5040021006 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>missing-parcels</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>130/179</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Verdana Apartments (San Diego): operative authorization, not dead, no parcels anywhere in its property group</t>
+          <t>AIN 5080006008 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70448,12 +70842,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>143/147</t>
+          <t>126/173</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>AIN 41416654 assigned to multiple projects</t>
+          <t>AIN 5094005005 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70465,12 +70859,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>182/76</t>
+          <t>127/174</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>AIN 5036031006 assigned to multiple projects</t>
+          <t>AIN 5094006003 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70482,12 +70876,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>200/218</t>
+          <t>122/165</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>AIN 5040021006 assigned to multiple projects</t>
+          <t>AIN 5094017020 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70499,12 +70893,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>130/179</t>
+          <t>124/169</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>AIN 5080006008 assigned to multiple projects</t>
+          <t>AIN 5094023025 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70516,12 +70910,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>126/173</t>
+          <t>128/175</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>AIN 5094005005 assigned to multiple projects</t>
+          <t>AIN 5502019004 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70533,12 +70927,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>127/174</t>
+          <t>125/170</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>AIN 5094006003 assigned to multiple projects</t>
+          <t>AIN 5503024012 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70550,12 +70944,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>122/165</t>
+          <t>129/177</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>AIN 5094017020 assigned to multiple projects</t>
+          <t>AIN 5517005016 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70567,12 +70961,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>124/169</t>
+          <t>121/162</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>AIN 5094023025 assigned to multiple projects</t>
+          <t>AIN 5518013024 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70584,12 +70978,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>128/175</t>
+          <t>123/168</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>AIN 5502019004 assigned to multiple projects</t>
+          <t>AIN 5518020021 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70601,12 +70995,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>125/170</t>
+          <t>135/220</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>AIN 5503024012 assigned to multiple projects</t>
+          <t>AIN 5518026004 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70618,12 +71012,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>129/177</t>
+          <t>10/132</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>AIN 5517005016 assigned to multiple projects</t>
+          <t>AIN 6020022027 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70635,78 +71029,10 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>121/162</t>
+          <t>152/181</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
-        <is>
-          <t>AIN 5518013024 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>123/168</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>AIN 5518020021 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>135/220</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>AIN 5518026004 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>10/132</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>AIN 6020022027 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>152/181</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
         <is>
           <t>AIN 7157012017 assigned to multiple projects</t>
         </is>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -59454,6 +59454,21 @@
           <t>Baird Affordable Housing Apartments</t>
         </is>
       </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2126022021</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>2126-022-021</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>6838 BAIRD AVE LOS ANGELES CA 91335</t>
+        </is>
+      </c>
       <c r="G270" t="inlineStr">
         <is>
           <t>False</t>
@@ -59461,7 +59476,57 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>Drew 2026-08-22: project aligns to 6838 Baird Ave (no 6840 situs exists). Assessor unit counts not usable to disambiguate — proposed project may differ.</t>
+        </is>
+      </c>
+      <c r="K270" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L270" s="2" t="inlineStr">
+        <is>
+          <t>833472</t>
+        </is>
+      </c>
+      <c r="M270" s="2" t="inlineStr">
+        <is>
+          <t>552040</t>
+        </is>
+      </c>
+      <c r="N270" s="2" t="inlineStr">
+        <is>
+          <t>1385512</t>
+        </is>
+      </c>
+      <c r="O270" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P270" s="2" t="inlineStr">
+        <is>
+          <t>1952</t>
+        </is>
+      </c>
+      <c r="Q270" s="2" t="inlineStr">
+        <is>
+          <t>Two Units</t>
+        </is>
+      </c>
+      <c r="R270" s="2" t="inlineStr">
+        <is>
+          <t>la-county-api</t>
+        </is>
+      </c>
+      <c r="S270" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T270" t="inlineStr">
@@ -59642,6 +59707,21 @@
           <t>Hazelhurst Affordable Housing Apartments</t>
         </is>
       </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2338006014</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>2338-006-014</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>6142 HAZELHURST PL LOS ANGELES CA 91606</t>
+        </is>
+      </c>
       <c r="G274" t="inlineStr">
         <is>
           <t>False</t>
@@ -59649,7 +59729,57 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>Drew 2026-08-22: development parcel is 6142 (no 6144 situs exists). Assessor unit counts not usable to disambiguate — proposed project may differ.</t>
+        </is>
+      </c>
+      <c r="K274" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L274" s="2" t="inlineStr">
+        <is>
+          <t>688500</t>
+        </is>
+      </c>
+      <c r="M274" s="2" t="inlineStr">
+        <is>
+          <t>1224000</t>
+        </is>
+      </c>
+      <c r="N274" s="2" t="inlineStr">
+        <is>
+          <t>1912500</t>
+        </is>
+      </c>
+      <c r="O274" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P274" s="2" t="inlineStr">
+        <is>
+          <t>1952</t>
+        </is>
+      </c>
+      <c r="Q274" s="2" t="inlineStr">
+        <is>
+          <t>Two Units</t>
+        </is>
+      </c>
+      <c r="R274" s="2" t="inlineStr">
+        <is>
+          <t>la-county-api</t>
+        </is>
+      </c>
+      <c r="S274" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T274" t="inlineStr">
@@ -67919,7 +68049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C183"/>
+  <dimension ref="A1:C181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -70332,12 +70462,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN (none) (Santa Barbara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70349,12 +70479,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>203</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>AIN (none) (Santa Barbara): no roll values from any source</t>
+          <t>AIN (none) (Sacramento): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70366,12 +70496,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>205</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>AIN (none) (Sacramento): no roll values from any source</t>
+          <t>AIN (none) (Contra Costa): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70383,7 +70513,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>206</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -70400,12 +70530,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>207</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>AIN (none) (Contra Costa): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70417,7 +70547,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>208</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -70434,12 +70564,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>213</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN (none) (Sacramento): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70451,7 +70581,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>215</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -70468,12 +70598,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>221</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>AIN (none) (Sacramento): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70485,12 +70615,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>222</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN (none) (Alameda): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70502,12 +70632,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>223</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN (none) (Alameda): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70519,12 +70649,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>AIN (none) (Alameda): no roll values from any source</t>
+          <t>AIN (none) (Contra Costa): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70536,12 +70666,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>229</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>AIN (none) (Alameda): no roll values from any source</t>
+          <t>AIN (none) (San Diego): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70553,12 +70683,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>235</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>AIN (none) (Contra Costa): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70570,12 +70700,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>236</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>AIN (none) (San Diego): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70587,12 +70717,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 46745075 (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70604,12 +70734,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 46745074 (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70626,7 +70756,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>AIN 46745075 (Santa Clara): no roll values from any source</t>
+          <t>AIN 46745073 (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70638,12 +70768,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>198</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>AIN 46745074 (Santa Clara): no roll values from any source</t>
+          <t>AIN (none) (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70655,12 +70785,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>AIN 46745073 (Santa Clara): no roll values from any source</t>
+          <t>AIN (none) (Santa Cruz): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70672,12 +70802,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>AIN (none) (Santa Clara): no roll values from any source</t>
+          <t>AIN 128101150 (Solano): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70689,12 +70819,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>AIN (none) (Santa Cruz): no roll values from any source</t>
+          <t>AIN 128101050 (Solano): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70711,58 +70841,58 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>AIN 128101150 (Solano): no roll values from any source</t>
+          <t>AIN 128105060 (Solano): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>missing-parcels</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>238</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>AIN 128101050 (Solano): no roll values from any source</t>
+          <t>Heritage Park Apartments Livermore (Alameda): operative authorization, not dead, no parcels anywhere in its property group</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>143/147</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>AIN 128105060 (Solano): no roll values from any source</t>
+          <t>AIN 41416654 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>missing-parcels</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>182/76</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Heritage Park Apartments Livermore (Alameda): operative authorization, not dead, no parcels anywhere in its property group</t>
+          <t>AIN 5036031006 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70774,12 +70904,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>143/147</t>
+          <t>200/218</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>AIN 41416654 assigned to multiple projects</t>
+          <t>AIN 5040021006 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70791,12 +70921,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>182/76</t>
+          <t>130/179</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>AIN 5036031006 assigned to multiple projects</t>
+          <t>AIN 5080006008 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70808,12 +70938,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>200/218</t>
+          <t>126/173</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>AIN 5040021006 assigned to multiple projects</t>
+          <t>AIN 5094005005 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70825,12 +70955,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>130/179</t>
+          <t>127/174</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>AIN 5080006008 assigned to multiple projects</t>
+          <t>AIN 5094006003 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70842,12 +70972,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>126/173</t>
+          <t>122/165</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>AIN 5094005005 assigned to multiple projects</t>
+          <t>AIN 5094017020 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70859,12 +70989,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>127/174</t>
+          <t>124/169</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>AIN 5094006003 assigned to multiple projects</t>
+          <t>AIN 5094023025 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70876,12 +71006,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>122/165</t>
+          <t>128/175</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>AIN 5094017020 assigned to multiple projects</t>
+          <t>AIN 5502019004 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70893,12 +71023,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>124/169</t>
+          <t>125/170</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>AIN 5094023025 assigned to multiple projects</t>
+          <t>AIN 5503024012 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70910,12 +71040,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>128/175</t>
+          <t>129/177</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>AIN 5502019004 assigned to multiple projects</t>
+          <t>AIN 5517005016 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70927,12 +71057,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>125/170</t>
+          <t>121/162</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>AIN 5503024012 assigned to multiple projects</t>
+          <t>AIN 5518013024 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70944,12 +71074,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>129/177</t>
+          <t>123/168</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>AIN 5517005016 assigned to multiple projects</t>
+          <t>AIN 5518020021 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70961,12 +71091,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>121/162</t>
+          <t>135/220</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>AIN 5518013024 assigned to multiple projects</t>
+          <t>AIN 5518026004 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70978,12 +71108,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>123/168</t>
+          <t>10/132</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>AIN 5518020021 assigned to multiple projects</t>
+          <t>AIN 6020022027 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70995,44 +71125,10 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>135/220</t>
+          <t>152/181</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
-        <is>
-          <t>AIN 5518026004 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>10/132</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>AIN 6020022027 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>152/181</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
         <is>
           <t>AIN 7157012017 assigned to multiple projects</t>
         </is>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -36151,7 +36151,7 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
@@ -60389,6 +60389,21 @@
           <t>511 Hoover Street Apartments</t>
         </is>
       </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>5539028040</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>5539-028-040</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>511 N HOOVER ST (no county situs; AIN from assessor portal map)</t>
+        </is>
+      </c>
       <c r="G285" t="inlineStr">
         <is>
           <t>False</t>
@@ -60396,7 +60411,12 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>Drew 2026-08-22 via assessor portal map view; new construction, situs not yet keyed.</t>
         </is>
       </c>
       <c r="T285" t="inlineStr">
@@ -60886,6 +60906,21 @@
           <t>Banner Avenue Apartments</t>
         </is>
       </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>5534006026</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>5534-006-026</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>6219 BANNER AVE (no county situs; AIN from assessor portal map)</t>
+        </is>
+      </c>
       <c r="G291" t="inlineStr">
         <is>
           <t>False</t>
@@ -60893,7 +60928,57 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>Drew 2026-08-22 via assessor portal map view; Banner Ave parcels not situs-keyed.</t>
+        </is>
+      </c>
+      <c r="K291" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L291" s="2" t="inlineStr">
+        <is>
+          <t>3459330</t>
+        </is>
+      </c>
+      <c r="M291" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N291" s="2" t="inlineStr">
+        <is>
+          <t>3459330</t>
+        </is>
+      </c>
+      <c r="O291" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P291" s="2" t="inlineStr">
+        <is>
+          <t>0000</t>
+        </is>
+      </c>
+      <c r="Q291" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="R291" s="2" t="inlineStr">
+        <is>
+          <t>la-county-api</t>
+        </is>
+      </c>
+      <c r="S291" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T291" t="inlineStr">
@@ -61779,6 +61864,21 @@
           <t>3950 Ingraham Apartments</t>
         </is>
       </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>5092029007</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>5092-029-007</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>3950 INGRAHAM ST LOS ANGELES CA 90005</t>
+        </is>
+      </c>
       <c r="G305" t="inlineStr">
         <is>
           <t>False</t>
@@ -61786,7 +61886,52 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>Drew confirmed 2026-08-22: staff report "3950 W. Ingraham" has spurious W; single Ingraham St in LA. Pre-development "Four Units" lot.</t>
+        </is>
+      </c>
+      <c r="K305" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L305" s="2" t="inlineStr">
+        <is>
+          <t>1237872</t>
+        </is>
+      </c>
+      <c r="M305" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N305" s="2" t="inlineStr">
+        <is>
+          <t>1237872</t>
+        </is>
+      </c>
+      <c r="O305" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q305" s="2" t="inlineStr">
+        <is>
+          <t>Four Units (Any Combination)</t>
+        </is>
+      </c>
+      <c r="R305" s="2" t="inlineStr">
+        <is>
+          <t>la-county-api</t>
+        </is>
+      </c>
+      <c r="S305" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T305" t="inlineStr">
@@ -61811,6 +61956,21 @@
           <t>Park Playa Apartments</t>
         </is>
       </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>4211011047</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>4211-011-047</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>6985 S CENTINELA AVE (no county situs; AIN from assessor portal map)</t>
+        </is>
+      </c>
       <c r="G306" t="inlineStr">
         <is>
           <t>False</t>
@@ -61818,7 +61978,52 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>Drew 2026-08-22 via assessor portal map view; odd lot shape, best-fit parcel.</t>
+        </is>
+      </c>
+      <c r="K306" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L306" s="2" t="inlineStr">
+        <is>
+          <t>5234013</t>
+        </is>
+      </c>
+      <c r="M306" s="2" t="inlineStr">
+        <is>
+          <t>28443</t>
+        </is>
+      </c>
+      <c r="N306" s="2" t="inlineStr">
+        <is>
+          <t>5262456</t>
+        </is>
+      </c>
+      <c r="O306" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q306" s="2" t="inlineStr">
+        <is>
+          <t>Parking Lots (Commercial Use Properties)</t>
+        </is>
+      </c>
+      <c r="R306" s="2" t="inlineStr">
+        <is>
+          <t>la-county-api</t>
+        </is>
+      </c>
+      <c r="S306" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T306" t="inlineStr">
@@ -68049,7 +68254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C181"/>
+  <dimension ref="A1:C178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -70586,7 +70791,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 5539028040 (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70598,12 +70803,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>222</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN (none) (Alameda): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70615,7 +70820,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>223</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -70632,12 +70837,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>AIN (none) (Alameda): no roll values from any source</t>
+          <t>AIN (none) (Contra Costa): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70649,12 +70854,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>229</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>AIN (none) (Contra Costa): no roll values from any source</t>
+          <t>AIN (none) (San Diego): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70666,12 +70871,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>AIN (none) (San Diego): no roll values from any source</t>
+          <t>AIN 46745075 (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70683,12 +70888,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 46745074 (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70700,12 +70905,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 46745073 (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70717,12 +70922,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>198</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>AIN 46745075 (Santa Clara): no roll values from any source</t>
+          <t>AIN (none) (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70734,12 +70939,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>AIN 46745074 (Santa Clara): no roll values from any source</t>
+          <t>AIN (none) (Santa Cruz): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70751,12 +70956,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>AIN 46745073 (Santa Clara): no roll values from any source</t>
+          <t>AIN 128101150 (Solano): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70768,12 +70973,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>AIN (none) (Santa Clara): no roll values from any source</t>
+          <t>AIN 128101050 (Solano): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70785,80 +70990,80 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>AIN (none) (Santa Cruz): no roll values from any source</t>
+          <t>AIN 128105060 (Solano): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>missing-parcels</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>238</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>AIN 128101150 (Solano): no roll values from any source</t>
+          <t>Heritage Park Apartments Livermore (Alameda): operative authorization, not dead, no parcels anywhere in its property group</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>143/147</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>AIN 128101050 (Solano): no roll values from any source</t>
+          <t>AIN 41416654 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>182/76</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>AIN 128105060 (Solano): no roll values from any source</t>
+          <t>AIN 5036031006 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>missing-parcels</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>200/218</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Heritage Park Apartments Livermore (Alameda): operative authorization, not dead, no parcels anywhere in its property group</t>
+          <t>AIN 5040021006 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70870,12 +71075,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>143/147</t>
+          <t>130/179</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>AIN 41416654 assigned to multiple projects</t>
+          <t>AIN 5080006008 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70887,12 +71092,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>182/76</t>
+          <t>126/173</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>AIN 5036031006 assigned to multiple projects</t>
+          <t>AIN 5094005005 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70904,12 +71109,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>200/218</t>
+          <t>127/174</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>AIN 5040021006 assigned to multiple projects</t>
+          <t>AIN 5094006003 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70921,12 +71126,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>130/179</t>
+          <t>122/165</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>AIN 5080006008 assigned to multiple projects</t>
+          <t>AIN 5094017020 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70938,12 +71143,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>126/173</t>
+          <t>124/169</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>AIN 5094005005 assigned to multiple projects</t>
+          <t>AIN 5094023025 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70955,12 +71160,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>127/174</t>
+          <t>128/175</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>AIN 5094006003 assigned to multiple projects</t>
+          <t>AIN 5502019004 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70972,12 +71177,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>122/165</t>
+          <t>125/170</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>AIN 5094017020 assigned to multiple projects</t>
+          <t>AIN 5503024012 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -70989,12 +71194,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>124/169</t>
+          <t>129/177</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>AIN 5094023025 assigned to multiple projects</t>
+          <t>AIN 5517005016 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71006,12 +71211,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>128/175</t>
+          <t>121/162</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>AIN 5502019004 assigned to multiple projects</t>
+          <t>AIN 5518013024 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71023,12 +71228,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>125/170</t>
+          <t>123/168</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>AIN 5503024012 assigned to multiple projects</t>
+          <t>AIN 5518020021 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71040,12 +71245,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>129/177</t>
+          <t>135/220</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>AIN 5517005016 assigned to multiple projects</t>
+          <t>AIN 5518026004 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71057,12 +71262,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>121/162</t>
+          <t>10/132</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>AIN 5518013024 assigned to multiple projects</t>
+          <t>AIN 6020022027 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71074,61 +71279,10 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>123/168</t>
+          <t>152/181</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
-        <is>
-          <t>AIN 5518020021 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>135/220</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>AIN 5518026004 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>10/132</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>AIN 6020022027 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>152/181</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
         <is>
           <t>AIN 7157012017 assigned to multiple projects</t>
         </is>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -36139,7 +36139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T394"/>
+  <dimension ref="A1:T395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -36151,7 +36151,7 @@
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="38" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
@@ -54924,6 +54924,26 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
       <c r="T215" t="inlineStr">
         <is>
           <t>147</t>
@@ -59675,6 +59695,21 @@
           <t>Bent Tree Apartments</t>
         </is>
       </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>21900420330000</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>219-0042-033-0000</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>4350 GALBRATH DR SACRAMENTO CA 95842</t>
+        </is>
+      </c>
       <c r="G273" t="inlineStr">
         <is>
           <t>False</t>
@@ -59682,7 +59717,32 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>Drew 2026-08-22 via Sacramento assessor lookup</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>15693765</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>manual-repo-edit</t>
         </is>
       </c>
       <c r="T273" t="inlineStr">
@@ -60265,6 +60325,21 @@
           <t>Sierra Village</t>
         </is>
       </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>22800420320000</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>228-0042-032-0000</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>5416 JACKSON ST NORTH HIGHLANDS CA 95660</t>
+        </is>
+      </c>
       <c r="G283" t="inlineStr">
         <is>
           <t>False</t>
@@ -60272,7 +60347,32 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>Drew 2026-08-22 via Sacramento assessor lookup</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>8878476</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>manual-repo-edit</t>
         </is>
       </c>
       <c r="T283" t="inlineStr">
@@ -61003,6 +61103,21 @@
           <t>Bayfair Apartments</t>
         </is>
       </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>80C49562</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>80C-495-6-2</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>16077 ASHLAND AVE SAN LORENZO CA 94580</t>
+        </is>
+      </c>
       <c r="G292" t="inlineStr">
         <is>
           <t>False</t>
@@ -61010,7 +61125,32 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>Drew 2026-08-22 via Alameda assessor lookup</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>11141147</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>manual-repo-edit</t>
         </is>
       </c>
       <c r="T292" t="inlineStr">
@@ -61035,6 +61175,21 @@
           <t>2121 Wood St</t>
         </is>
       </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>1831016</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>18-310-16</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>2121 WOOD ST OAKLAND CA 94607</t>
+        </is>
+      </c>
       <c r="G293" t="inlineStr">
         <is>
           <t>False</t>
@@ -61042,7 +61197,32 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>Drew 2026-08-22 via Alameda assessor lookup</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>71934357</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>56403868</t>
+        </is>
+      </c>
+      <c r="R293" t="inlineStr">
+        <is>
+          <t>manual-repo-edit</t>
         </is>
       </c>
       <c r="T293" t="inlineStr">
@@ -63118,6 +63298,16 @@
           <t>La Posada Apartments</t>
         </is>
       </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>01125105</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>011-251-05</t>
+        </is>
+      </c>
       <c r="G327" t="inlineStr">
         <is>
           <t>False</t>
@@ -63125,7 +63315,32 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>Drew 2026-08-22 via Santa Cruz assessor lookup, 609 Frederick St</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>9776112</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R327" t="inlineStr">
+        <is>
+          <t>manual-repo-edit</t>
         </is>
       </c>
       <c r="T327" t="inlineStr">
@@ -68240,6 +68455,78 @@
       <c r="T394" t="inlineStr">
         <is>
           <t>369</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Alameda</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Heritage Park Apartments Livermore</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>9917523</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>99-175-23</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>900 E STANLEY BLVD LIVERMORE CA 94550</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>Drew 2026-08-22 via Alameda assessor lookup</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>47387387</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>19523603</t>
+        </is>
+      </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
+      <c r="T395" t="inlineStr">
+        <is>
+          <t>238</t>
         </is>
       </c>
     </row>
@@ -68254,7 +68541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C178"/>
+  <dimension ref="A1:C171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -70582,12 +70869,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>158</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>AIN 41416654 (Alameda): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70599,12 +70886,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>182</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 5036031006 (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70616,12 +70903,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>196</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>AIN 5036031006 (Los Angeles): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70633,7 +70920,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>197</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -70650,12 +70937,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN (none) (Santa Barbara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70667,12 +70954,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>205</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>AIN (none) (Santa Barbara): no roll values from any source</t>
+          <t>AIN (none) (Contra Costa): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70684,12 +70971,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>206</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>AIN (none) (Sacramento): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70701,12 +70988,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>207</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>AIN (none) (Contra Costa): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70718,7 +71005,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>208</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -70735,12 +71022,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>215</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 5539028040 (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70752,12 +71039,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN (none) (Contra Costa): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70769,12 +71056,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>229</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>AIN (none) (Sacramento): no roll values from any source</t>
+          <t>AIN (none) (San Diego): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70786,12 +71073,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>AIN 5539028040 (Los Angeles): no roll values from any source</t>
+          <t>AIN 46745075 (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70803,12 +71090,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>AIN (none) (Alameda): no roll values from any source</t>
+          <t>AIN 46745074 (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70820,12 +71107,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>AIN (none) (Alameda): no roll values from any source</t>
+          <t>AIN 46745073 (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70837,12 +71124,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>198</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>AIN (none) (Contra Costa): no roll values from any source</t>
+          <t>AIN (none) (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70854,12 +71141,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>AIN (none) (San Diego): no roll values from any source</t>
+          <t>AIN 128101150 (Solano): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70871,12 +71158,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>AIN 46745075 (Santa Clara): no roll values from any source</t>
+          <t>AIN 128101050 (Solano): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70888,131 +71175,131 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>AIN 46745074 (Santa Clara): no roll values from any source</t>
+          <t>AIN 128105060 (Solano): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>143/147</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>AIN 46745073 (Santa Clara): no roll values from any source</t>
+          <t>AIN 41416654 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>182/76</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>AIN (none) (Santa Clara): no roll values from any source</t>
+          <t>AIN 5036031006 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>200/218</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>AIN (none) (Santa Cruz): no roll values from any source</t>
+          <t>AIN 5040021006 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>130/179</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>AIN 128101150 (Solano): no roll values from any source</t>
+          <t>AIN 5080006008 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>126/173</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>AIN 128101050 (Solano): no roll values from any source</t>
+          <t>AIN 5094005005 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>127/174</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>AIN 128105060 (Solano): no roll values from any source</t>
+          <t>AIN 5094006003 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>missing-parcels</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>122/165</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Heritage Park Apartments Livermore (Alameda): operative authorization, not dead, no parcels anywhere in its property group</t>
+          <t>AIN 5094017020 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71024,12 +71311,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>143/147</t>
+          <t>124/169</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>AIN 41416654 assigned to multiple projects</t>
+          <t>AIN 5094023025 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71041,12 +71328,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>182/76</t>
+          <t>128/175</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>AIN 5036031006 assigned to multiple projects</t>
+          <t>AIN 5502019004 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71058,12 +71345,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>200/218</t>
+          <t>125/170</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>AIN 5040021006 assigned to multiple projects</t>
+          <t>AIN 5503024012 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71075,12 +71362,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>130/179</t>
+          <t>129/177</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>AIN 5080006008 assigned to multiple projects</t>
+          <t>AIN 5517005016 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71092,12 +71379,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>126/173</t>
+          <t>121/162</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>AIN 5094005005 assigned to multiple projects</t>
+          <t>AIN 5518013024 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71109,12 +71396,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>127/174</t>
+          <t>123/168</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>AIN 5094006003 assigned to multiple projects</t>
+          <t>AIN 5518020021 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71126,12 +71413,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>122/165</t>
+          <t>135/220</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>AIN 5094017020 assigned to multiple projects</t>
+          <t>AIN 5518026004 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71143,12 +71430,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>124/169</t>
+          <t>10/132</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>AIN 5094023025 assigned to multiple projects</t>
+          <t>AIN 6020022027 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71160,129 +71447,10 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>128/175</t>
+          <t>152/181</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
-        <is>
-          <t>AIN 5502019004 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>125/170</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>AIN 5503024012 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>129/177</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>AIN 5517005016 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>121/162</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>AIN 5518013024 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>123/168</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>AIN 5518020021 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>135/220</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>AIN 5518026004 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>10/132</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>AIN 6020022027 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>152/181</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
         <is>
           <t>AIN 7157012017 assigned to multiple projects</t>
         </is>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -36139,7 +36139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T395"/>
+  <dimension ref="A1:T393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -54522,12 +54522,17 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
           <t>collaborator-sheet</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Duplicate of project 147 row (same AIN, same property, re-authorized deal); marked redundant 2026-08-22</t>
         </is>
       </c>
       <c r="T208" t="inlineStr">
@@ -59851,17 +59856,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>206</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Contra Costa</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Del Norte Place Apartments</t>
+          <t>Elan River Village Apartments</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -59876,14 +59881,14 @@
       </c>
       <c r="T275" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>206</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>207</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -59893,7 +59898,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Elan River Village Apartments</t>
+          <t>Cullen Living Apartments</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -59908,14 +59913,14 @@
       </c>
       <c r="T276" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>207</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>208</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -59925,7 +59930,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Cullen Living Apartments</t>
+          <t>Sawtelle 2481 Apartments</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -59940,24 +59945,39 @@
       </c>
       <c r="T277" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>208</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>209</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Sawtelle 2481 Apartments</t>
+          <t>Bluwater Crossing Apartments</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>2146500200</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>214-650-02-00</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>6790 EMBARCADERO LN CARLSBAD CA 92011</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -59967,44 +59987,84 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
+          <t>script-situs-match (2026-08-22)</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>Exact situs match, SANDAG; 66-unit apartment parcel</t>
+        </is>
+      </c>
+      <c r="K278" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L278" s="2" t="inlineStr">
+        <is>
+          <t>15568767</t>
+        </is>
+      </c>
+      <c r="M278" s="2" t="inlineStr">
+        <is>
+          <t>33766648</t>
+        </is>
+      </c>
+      <c r="N278" s="2" t="inlineStr">
+        <is>
+          <t>49335415</t>
+        </is>
+      </c>
+      <c r="P278" s="2" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Q278" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R278" s="2" t="inlineStr">
+        <is>
+          <t>sandag-parcels</t>
+        </is>
+      </c>
+      <c r="S278" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T278" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>209</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>210</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Bluwater Crossing Apartments</t>
+          <t>California Place Apartments</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2146500200</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr">
-        <is>
-          <t>214-650-02-00</t>
+          <t>11700120210000</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>6790 EMBARCADERO LN CARLSBAD CA 92011</t>
+          <t>6633 VALLEY HI DR SACRAMENTO 95823</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -60014,84 +60074,54 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>script-situs-match (2026-08-22)</t>
-        </is>
-      </c>
-      <c r="J279" t="inlineStr">
-        <is>
-          <t>Exact situs match, SANDAG; 66-unit apartment parcel</t>
-        </is>
-      </c>
-      <c r="K279" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="L279" s="2" t="inlineStr">
-        <is>
-          <t>15568767</t>
-        </is>
-      </c>
-      <c r="M279" s="2" t="inlineStr">
-        <is>
-          <t>33766648</t>
-        </is>
-      </c>
-      <c r="N279" s="2" t="inlineStr">
-        <is>
-          <t>49335415</t>
-        </is>
-      </c>
-      <c r="P279" s="2" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="Q279" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R279" s="2" t="inlineStr">
-        <is>
-          <t>sandag-parcels</t>
-        </is>
-      </c>
-      <c r="S279" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
+          <t>collaborator-sheet</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>11438021</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>collaborator-sheet</t>
         </is>
       </c>
       <c r="T279" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>210</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>211</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>California Place Apartments</t>
+          <t>Haven Warner Center</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>11700120210000</t>
+          <t>2148026046</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>6633 VALLEY HI DR SACRAMENTO 95823</t>
+          <t>6530 INDEPENDENCE AVE LOS ANGELES CA 91303</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -60101,34 +60131,69 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
-        </is>
-      </c>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="N280" t="inlineStr">
-        <is>
-          <t>11438021</t>
-        </is>
-      </c>
-      <c r="R280" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+          <t>script-situs-match (2026-08-21)</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>Resolved by LA county situs/geocode search</t>
+        </is>
+      </c>
+      <c r="K280" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L280" s="2" t="inlineStr">
+        <is>
+          <t>20375193</t>
+        </is>
+      </c>
+      <c r="M280" s="2" t="inlineStr">
+        <is>
+          <t>36930038</t>
+        </is>
+      </c>
+      <c r="N280" s="2" t="inlineStr">
+        <is>
+          <t>57305231</t>
+        </is>
+      </c>
+      <c r="O280" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P280" s="2" t="inlineStr">
+        <is>
+          <t>1985</t>
+        </is>
+      </c>
+      <c r="Q280" s="2" t="inlineStr">
+        <is>
+          <t>Five or more apartments</t>
+        </is>
+      </c>
+      <c r="R280" s="2" t="inlineStr">
+        <is>
+          <t>la-county-api</t>
+        </is>
+      </c>
+      <c r="S280" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T280" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>211</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>212</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -60138,17 +60203,17 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Haven Warner Center</t>
+          <t>The Arlo</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2148026046</t>
+          <t>5052023039</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>6530 INDEPENDENCE AVE LOS ANGELES CA 91303</t>
+          <t>2075 W JEFFERSON BLVD LOS ANGELES CA 90018</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -60163,7 +60228,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Resolved by LA county situs/geocode search</t>
+          <t>Resolved by LA county situs/geocode search; use code "Restaurants" — pre-development roll</t>
         </is>
       </c>
       <c r="K281" s="2" t="inlineStr">
@@ -60173,17 +60238,17 @@
       </c>
       <c r="L281" s="2" t="inlineStr">
         <is>
-          <t>20375193</t>
+          <t>1144440</t>
         </is>
       </c>
       <c r="M281" s="2" t="inlineStr">
         <is>
-          <t>36930038</t>
+          <t>312120</t>
         </is>
       </c>
       <c r="N281" s="2" t="inlineStr">
         <is>
-          <t>57305231</t>
+          <t>1456560</t>
         </is>
       </c>
       <c r="O281" s="2" t="inlineStr">
@@ -60193,12 +60258,12 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
         <is>
-          <t>Five or more apartments</t>
+          <t>Restaurants, Cocktail Lounges</t>
         </is>
       </c>
       <c r="R281" s="2" t="inlineStr">
@@ -60213,34 +60278,39 @@
       </c>
       <c r="T281" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>212</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>The Arlo</t>
+          <t>Sierra Village</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>5052023039</t>
+          <t>22800420320000</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>228-0042-032-0000</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>2075 W JEFFERSON BLVD LOS ANGELES CA 90018</t>
+          <t>5416 JACKSON ST NORTH HIGHLANDS CA 95660</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -60250,94 +60320,64 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>script-situs-match (2026-08-21)</t>
+          <t>manual-repo-edit</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>Resolved by LA county situs/geocode search; use code "Restaurants" — pre-development roll</t>
-        </is>
-      </c>
-      <c r="K282" s="2" t="inlineStr">
+          <t>Drew 2026-08-22 via Sacramento assessor lookup</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="L282" s="2" t="inlineStr">
-        <is>
-          <t>1144440</t>
-        </is>
-      </c>
-      <c r="M282" s="2" t="inlineStr">
-        <is>
-          <t>312120</t>
-        </is>
-      </c>
-      <c r="N282" s="2" t="inlineStr">
-        <is>
-          <t>1456560</t>
-        </is>
-      </c>
-      <c r="O282" s="2" t="inlineStr">
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>8878476</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P282" s="2" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="Q282" s="2" t="inlineStr">
-        <is>
-          <t>Restaurants, Cocktail Lounges</t>
-        </is>
-      </c>
-      <c r="R282" s="2" t="inlineStr">
-        <is>
-          <t>la-county-api</t>
-        </is>
-      </c>
-      <c r="S282" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>manual-repo-edit</t>
         </is>
       </c>
       <c r="T282" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>213</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>214</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Sierra Village</t>
+          <t>Trails at San Dimas</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>22800420320000</t>
-        </is>
-      </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>228-0042-032-0000</t>
+          <t>8386006015</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>5416 JACKSON ST NORTH HIGHLANDS CA 95660</t>
+          <t>444 N AMELIA AVE SAN DIMAS CA 91773</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -60347,44 +60387,69 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>manual-repo-edit</t>
+          <t>script-situs-match (2026-08-21)</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Drew 2026-08-22 via Sacramento assessor lookup</t>
-        </is>
-      </c>
-      <c r="K283" t="inlineStr">
+          <t>Resolved by LA county situs/geocode search</t>
+        </is>
+      </c>
+      <c r="K283" s="2" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="N283" t="inlineStr">
-        <is>
-          <t>8878476</t>
-        </is>
-      </c>
-      <c r="O283" t="inlineStr">
+      <c r="L283" s="2" t="inlineStr">
+        <is>
+          <t>22187671</t>
+        </is>
+      </c>
+      <c r="M283" s="2" t="inlineStr">
+        <is>
+          <t>44750710</t>
+        </is>
+      </c>
+      <c r="N283" s="2" t="inlineStr">
+        <is>
+          <t>66938381</t>
+        </is>
+      </c>
+      <c r="O283" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R283" t="inlineStr">
-        <is>
-          <t>manual-repo-edit</t>
+      <c r="P283" s="2" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="Q283" s="2" t="inlineStr">
+        <is>
+          <t>Five or more apartments</t>
+        </is>
+      </c>
+      <c r="R283" s="2" t="inlineStr">
+        <is>
+          <t>la-county-api</t>
+        </is>
+      </c>
+      <c r="S283" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T283" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>214</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>215</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -60394,17 +60459,22 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Trails at San Dimas</t>
+          <t>511 Hoover Street Apartments</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>8386006015</t>
+          <t>5539028040</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>5539-028-040</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>444 N AMELIA AVE SAN DIMAS CA 91773</t>
+          <t>511 N HOOVER ST (no county situs; AIN from assessor portal map)</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -60414,94 +60484,49 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>script-situs-match (2026-08-21)</t>
+          <t>manual-repo-edit</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>Resolved by LA county situs/geocode search</t>
-        </is>
-      </c>
-      <c r="K284" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="L284" s="2" t="inlineStr">
-        <is>
-          <t>22187671</t>
-        </is>
-      </c>
-      <c r="M284" s="2" t="inlineStr">
-        <is>
-          <t>44750710</t>
-        </is>
-      </c>
-      <c r="N284" s="2" t="inlineStr">
-        <is>
-          <t>66938381</t>
-        </is>
-      </c>
-      <c r="O284" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P284" s="2" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="Q284" s="2" t="inlineStr">
-        <is>
-          <t>Five or more apartments</t>
-        </is>
-      </c>
-      <c r="R284" s="2" t="inlineStr">
-        <is>
-          <t>la-county-api</t>
-        </is>
-      </c>
-      <c r="S284" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
+          <t>Drew 2026-08-22 via assessor portal map view; new construction, situs not yet keyed.</t>
         </is>
       </c>
       <c r="T284" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>215</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>216</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>511 Hoover Street Apartments</t>
+          <t>Guava Gardens Apartments</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>5539028040</t>
+          <t>4701122500</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>5539-028-040</t>
+          <t>470-112-25-00</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>511 N HOOVER ST (no county situs; AIN from assessor portal map)</t>
+          <t>5035 GUAVA AVE LA MESA CA 91942</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -60511,49 +60536,89 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>manual-repo-edit</t>
+          <t>script-situs-match (2026-08-22)</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>Drew 2026-08-22 via assessor portal map view; new construction, situs not yet keyed.</t>
+          <t>Exact situs match, SANDAG; 81-unit apartment parcel</t>
+        </is>
+      </c>
+      <c r="K285" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L285" s="2" t="inlineStr">
+        <is>
+          <t>2033407</t>
+        </is>
+      </c>
+      <c r="M285" s="2" t="inlineStr">
+        <is>
+          <t>3050116</t>
+        </is>
+      </c>
+      <c r="N285" s="2" t="inlineStr">
+        <is>
+          <t>5083523</t>
+        </is>
+      </c>
+      <c r="P285" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="Q285" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R285" s="2" t="inlineStr">
+        <is>
+          <t>sandag-parcels</t>
+        </is>
+      </c>
+      <c r="S285" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T285" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>216</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>217</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Guava Gardens Apartments</t>
+          <t>Park View by Angeleno Apartments</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>4701122500</t>
+          <t>5157007028</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>470-112-25-00</t>
+          <t>5157-007-028</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>5035 GUAVA AVE LA MESA CA 91942</t>
+          <t>217 N PARK VIEW ST LOS ANGELES CA 90026</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -60568,7 +60633,7 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>Exact situs match, SANDAG; 81-unit apartment parcel</t>
+          <t>Exact situs match, LA parcel API; use still "Single" (pre-development)</t>
         </is>
       </c>
       <c r="K286" s="2" t="inlineStr">
@@ -60578,32 +60643,37 @@
       </c>
       <c r="L286" s="2" t="inlineStr">
         <is>
-          <t>2033407</t>
+          <t>938400</t>
         </is>
       </c>
       <c r="M286" s="2" t="inlineStr">
         <is>
-          <t>3050116</t>
+          <t>234600</t>
         </is>
       </c>
       <c r="N286" s="2" t="inlineStr">
         <is>
-          <t>5083523</t>
+          <t>1173000</t>
+        </is>
+      </c>
+      <c r="O286" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="R286" s="2" t="inlineStr">
         <is>
-          <t>sandag-parcels</t>
+          <t>la-county-api</t>
         </is>
       </c>
       <c r="S286" s="2" t="inlineStr">
@@ -60613,14 +60683,14 @@
       </c>
       <c r="T286" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>217</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>218</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -60630,22 +60700,17 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Park View by Angeleno Apartments</t>
+          <t>1408 Jefferson Blvd Apartments</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>5157007028</t>
-        </is>
-      </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>5157-007-028</t>
+          <t>5040021006</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>217 N PARK VIEW ST LOS ANGELES CA 90026</t>
+          <t>1408 W JEFFERSON BLVD LOS ANGELES CA 90007</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -60655,12 +60720,12 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>script-situs-match (2026-08-22)</t>
+          <t>script-situs-match (2026-08-21)</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>Exact situs match, LA parcel API; use still "Single" (pre-development)</t>
+          <t>Resolved by LA county situs/geocode search; DUPLICATE of project 200 (same AIN)</t>
         </is>
       </c>
       <c r="K287" s="2" t="inlineStr">
@@ -60670,17 +60735,17 @@
       </c>
       <c r="L287" s="2" t="inlineStr">
         <is>
-          <t>938400</t>
+          <t>1456560</t>
         </is>
       </c>
       <c r="M287" s="2" t="inlineStr">
         <is>
-          <t>234600</t>
+          <t>62424</t>
         </is>
       </c>
       <c r="N287" s="2" t="inlineStr">
         <is>
-          <t>1173000</t>
+          <t>1518984</t>
         </is>
       </c>
       <c r="O287" s="2" t="inlineStr">
@@ -60690,12 +60755,12 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Store Combination</t>
         </is>
       </c>
       <c r="R287" s="2" t="inlineStr">
@@ -60710,14 +60775,14 @@
       </c>
       <c r="T287" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>218</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>219</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -60727,17 +60792,17 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>1408 Jefferson Blvd Apartments</t>
+          <t>603 Mariposa Apartments</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>5040021006</t>
+          <t>5502031012</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>1408 W JEFFERSON BLVD LOS ANGELES CA 90007</t>
+          <t>603 S MARIPOSA AVE LOS ANGELES CA 90005</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -60752,7 +60817,7 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Resolved by LA county situs/geocode search; DUPLICATE of project 200 (same AIN)</t>
+          <t>Resolved by LA county situs/geocode search; use code "Restaurants" — pre-development roll</t>
         </is>
       </c>
       <c r="K288" s="2" t="inlineStr">
@@ -60762,17 +60827,17 @@
       </c>
       <c r="L288" s="2" t="inlineStr">
         <is>
-          <t>1456560</t>
+          <t>3974689</t>
         </is>
       </c>
       <c r="M288" s="2" t="inlineStr">
         <is>
-          <t>62424</t>
+          <t>684528</t>
         </is>
       </c>
       <c r="N288" s="2" t="inlineStr">
         <is>
-          <t>1518984</t>
+          <t>4659217</t>
         </is>
       </c>
       <c r="O288" s="2" t="inlineStr">
@@ -60782,12 +60847,12 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
         <is>
-          <t>Store Combination</t>
+          <t>Restaurants, Cocktail Lounges</t>
         </is>
       </c>
       <c r="R288" s="2" t="inlineStr">
@@ -60802,14 +60867,14 @@
       </c>
       <c r="T288" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>219</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>220</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -60819,17 +60884,17 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>603 Mariposa Apartments</t>
+          <t>236 Berendo Apartments</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>5502031012</t>
+          <t>5518026004</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>603 S MARIPOSA AVE LOS ANGELES CA 90005</t>
+          <t>236 N BERENDO ST LOS ANGELES CA 90004</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -60844,7 +60909,7 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Resolved by LA county situs/geocode search; use code "Restaurants" — pre-development roll</t>
+          <t>Resolved by LA county situs/geocode search; use code "Single" — pre-development roll</t>
         </is>
       </c>
       <c r="K289" s="2" t="inlineStr">
@@ -60854,17 +60919,17 @@
       </c>
       <c r="L289" s="2" t="inlineStr">
         <is>
-          <t>3974689</t>
+          <t>1040400</t>
         </is>
       </c>
       <c r="M289" s="2" t="inlineStr">
         <is>
-          <t>684528</t>
+          <t>374544</t>
         </is>
       </c>
       <c r="N289" s="2" t="inlineStr">
         <is>
-          <t>4659217</t>
+          <t>1414944</t>
         </is>
       </c>
       <c r="O289" s="2" t="inlineStr">
@@ -60874,12 +60939,12 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>1925</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
         <is>
-          <t>Restaurants, Cocktail Lounges</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="R289" s="2" t="inlineStr">
@@ -60894,14 +60959,14 @@
       </c>
       <c r="T289" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>220</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>221</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -60911,17 +60976,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>236 Berendo Apartments</t>
+          <t>Banner Avenue Apartments</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>5518026004</t>
+          <t>5534006026</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>5534-006-026</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>236 N BERENDO ST LOS ANGELES CA 90004</t>
+          <t>6219 BANNER AVE (no county situs; AIN from assessor portal map)</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -60931,12 +61001,12 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>script-situs-match (2026-08-21)</t>
+          <t>manual-repo-edit</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>Resolved by LA county situs/geocode search; use code "Single" — pre-development roll</t>
+          <t>Drew 2026-08-22 via assessor portal map view; Banner Ave parcels not situs-keyed.</t>
         </is>
       </c>
       <c r="K290" s="2" t="inlineStr">
@@ -60946,17 +61016,17 @@
       </c>
       <c r="L290" s="2" t="inlineStr">
         <is>
-          <t>1040400</t>
+          <t>3459330</t>
         </is>
       </c>
       <c r="M290" s="2" t="inlineStr">
         <is>
-          <t>374544</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N290" s="2" t="inlineStr">
         <is>
-          <t>1414944</t>
+          <t>3459330</t>
         </is>
       </c>
       <c r="O290" s="2" t="inlineStr">
@@ -60966,7 +61036,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>0000</t>
         </is>
       </c>
       <c r="Q290" s="2" t="inlineStr">
@@ -60986,39 +61056,39 @@
       </c>
       <c r="T290" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>221</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>222</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Alameda</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Banner Avenue Apartments</t>
+          <t>Bayfair Apartments</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>5534006026</t>
+          <t>80C49562</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>5534-006-026</t>
+          <t>80C-495-6-2</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>6219 BANNER AVE (no county situs; AIN from assessor portal map)</t>
+          <t>16077 ASHLAND AVE SAN LORENZO CA 94580</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -61033,64 +61103,39 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>Drew 2026-08-22 via assessor portal map view; Banner Ave parcels not situs-keyed.</t>
-        </is>
-      </c>
-      <c r="K291" s="2" t="inlineStr">
+          <t>Drew 2026-08-22 via Alameda assessor lookup</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="L291" s="2" t="inlineStr">
-        <is>
-          <t>3459330</t>
-        </is>
-      </c>
-      <c r="M291" s="2" t="inlineStr">
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>11141147</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N291" s="2" t="inlineStr">
-        <is>
-          <t>3459330</t>
-        </is>
-      </c>
-      <c r="O291" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P291" s="2" t="inlineStr">
-        <is>
-          <t>0000</t>
-        </is>
-      </c>
-      <c r="Q291" s="2" t="inlineStr">
-        <is>
-          <t>Single</t>
-        </is>
-      </c>
-      <c r="R291" s="2" t="inlineStr">
-        <is>
-          <t>la-county-api</t>
-        </is>
-      </c>
-      <c r="S291" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
+      <c r="R291" t="inlineStr">
+        <is>
+          <t>manual-repo-edit</t>
         </is>
       </c>
       <c r="T291" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>222</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>223</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -61100,22 +61145,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Bayfair Apartments</t>
+          <t>2121 Wood St</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>80C49562</t>
+          <t>1831016</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>80C-495-6-2</t>
+          <t>18-310-16</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>16077 ASHLAND AVE SAN LORENZO CA 94580</t>
+          <t>2121 WOOD ST OAKLAND CA 94607</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -61140,12 +61185,12 @@
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>11141147</t>
+          <t>71934357</t>
         </is>
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56403868</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -61155,39 +61200,34 @@
       </c>
       <c r="T292" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>223</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>224</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Alameda</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2121 Wood St</t>
+          <t>1454 Florence Apartments</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>1831016</t>
-        </is>
-      </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>18-310-16</t>
+          <t>6018007001</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>2121 WOOD ST OAKLAND CA 94607</t>
+          <t>1454 W FLORENCE AVE LOS ANGELES CA 90047</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -61197,64 +61237,79 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>manual-repo-edit</t>
+          <t>script-situs-match (2026-08-21)</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>Drew 2026-08-22 via Alameda assessor lookup</t>
-        </is>
-      </c>
-      <c r="K293" t="inlineStr">
+          <t>Resolved by LA county situs/geocode search; matched W Florence per address; use code pre-development</t>
+        </is>
+      </c>
+      <c r="K293" s="2" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="N293" t="inlineStr">
-        <is>
-          <t>71934357</t>
-        </is>
-      </c>
-      <c r="O293" t="inlineStr">
-        <is>
-          <t>56403868</t>
-        </is>
-      </c>
-      <c r="R293" t="inlineStr">
-        <is>
-          <t>manual-repo-edit</t>
+      <c r="L293" s="2" t="inlineStr">
+        <is>
+          <t>1224000</t>
+        </is>
+      </c>
+      <c r="M293" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N293" s="2" t="inlineStr">
+        <is>
+          <t>1224000</t>
+        </is>
+      </c>
+      <c r="O293" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P293" s="2" t="inlineStr">
+        <is>
+          <t>1932</t>
+        </is>
+      </c>
+      <c r="Q293" s="2" t="inlineStr">
+        <is>
+          <t>Auto, Recreation EQPT, Construction EQPT, Sales &amp; Service</t>
+        </is>
+      </c>
+      <c r="R293" s="2" t="inlineStr">
+        <is>
+          <t>la-county-api</t>
+        </is>
+      </c>
+      <c r="S293" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T293" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>224</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>226</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Contra Costa</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>1454 Florence Apartments</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>6018007001</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>1454 W FLORENCE AVE LOS ANGELES CA 90047</t>
+          <t>Maris at Martinez Apartments</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -61264,79 +61319,39 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>script-situs-match (2026-08-21)</t>
-        </is>
-      </c>
-      <c r="J294" t="inlineStr">
-        <is>
-          <t>Resolved by LA county situs/geocode search; matched W Florence per address; use code pre-development</t>
-        </is>
-      </c>
-      <c r="K294" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="L294" s="2" t="inlineStr">
-        <is>
-          <t>1224000</t>
-        </is>
-      </c>
-      <c r="M294" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N294" s="2" t="inlineStr">
-        <is>
-          <t>1224000</t>
-        </is>
-      </c>
-      <c r="O294" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P294" s="2" t="inlineStr">
-        <is>
-          <t>1932</t>
-        </is>
-      </c>
-      <c r="Q294" s="2" t="inlineStr">
-        <is>
-          <t>Auto, Recreation EQPT, Construction EQPT, Sales &amp; Service</t>
-        </is>
-      </c>
-      <c r="R294" s="2" t="inlineStr">
-        <is>
-          <t>la-county-api</t>
-        </is>
-      </c>
-      <c r="S294" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
+          <t>collaborator-sheet</t>
         </is>
       </c>
       <c r="T294" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>226</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>227</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Contra Costa</t>
+          <t>Sacramento</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Maris at Martinez Apartments</t>
+          <t>Westlake Apartments</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>3003300180000</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>1 SHOAL CT SACRAMENTO 95831</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -61349,36 +61364,51 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>41186542</t>
+        </is>
+      </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>collaborator-sheet</t>
+        </is>
+      </c>
       <c r="T295" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>227</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>228</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Sacramento</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Westlake Apartments</t>
+          <t>Colden Oaks Apartments</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>3003300180000</t>
+          <t>6053006052</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>1 SHOAL CT SACRAMENTO 95831</t>
+          <t>225 W COLDEN AVE LOS ANGELES CA 90003</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -61388,34 +61418,69 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
-        </is>
-      </c>
-      <c r="K296" t="inlineStr">
+          <t>script-situs-match (2026-08-21)</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>Resolved by LA county situs/geocode search</t>
+        </is>
+      </c>
+      <c r="K296" s="2" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="N296" t="inlineStr">
-        <is>
-          <t>41186542</t>
-        </is>
-      </c>
-      <c r="R296" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="L296" s="2" t="inlineStr">
+        <is>
+          <t>2000000</t>
+        </is>
+      </c>
+      <c r="M296" s="2" t="inlineStr">
+        <is>
+          <t>4000000</t>
+        </is>
+      </c>
+      <c r="N296" s="2" t="inlineStr">
+        <is>
+          <t>6000000</t>
+        </is>
+      </c>
+      <c r="O296" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P296" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q296" s="2" t="inlineStr">
+        <is>
+          <t>Five or more apartments</t>
+        </is>
+      </c>
+      <c r="R296" s="2" t="inlineStr">
+        <is>
+          <t>la-county-api</t>
+        </is>
+      </c>
+      <c r="S296" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T296" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>228</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>230</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -61425,17 +61490,17 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Colden Oaks Apartments</t>
+          <t>Hansen illage Apartments</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>6053006052</t>
+          <t>2530007014</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>225 W COLDEN AVE LOS ANGELES CA 90003</t>
+          <t>11821 FOOTHILL BLVD LOS ANGELES CA 91342</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -61450,7 +61515,7 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>Resolved by LA county situs/geocode search</t>
+          <t>Resolved by LA county situs/geocode search; two parcels share situs 11821 Foothill — multi-parcel</t>
         </is>
       </c>
       <c r="K297" s="2" t="inlineStr">
@@ -61460,17 +61525,17 @@
       </c>
       <c r="L297" s="2" t="inlineStr">
         <is>
-          <t>2000000</t>
+          <t>1768372</t>
         </is>
       </c>
       <c r="M297" s="2" t="inlineStr">
         <is>
-          <t>4000000</t>
+          <t>4763318</t>
         </is>
       </c>
       <c r="N297" s="2" t="inlineStr">
         <is>
-          <t>6000000</t>
+          <t>6531690</t>
         </is>
       </c>
       <c r="O297" s="2" t="inlineStr">
@@ -61480,7 +61545,7 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="Q297" s="2" t="inlineStr">
@@ -61500,24 +61565,34 @@
       </c>
       <c r="T297" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>230</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>231</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Creekside Villas Apartments</t>
+          <t>Violet on Virgil</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>5501017044</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>160 S VIRGIL AVE LOS ANGELES CA 90004</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -61527,39 +61602,89 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
+          <t>script-situs-match (2026-08-21)</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>Resolved by LA county situs/geocode search</t>
+        </is>
+      </c>
+      <c r="K298" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L298" s="2" t="inlineStr">
+        <is>
+          <t>18210958</t>
+        </is>
+      </c>
+      <c r="M298" s="2" t="inlineStr">
+        <is>
+          <t>30209370</t>
+        </is>
+      </c>
+      <c r="N298" s="2" t="inlineStr">
+        <is>
+          <t>48420328</t>
+        </is>
+      </c>
+      <c r="O298" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P298" s="2" t="inlineStr">
+        <is>
+          <t>1971</t>
+        </is>
+      </c>
+      <c r="Q298" s="2" t="inlineStr">
+        <is>
+          <t>Five or more apartments</t>
+        </is>
+      </c>
+      <c r="R298" s="2" t="inlineStr">
+        <is>
+          <t>la-county-api</t>
+        </is>
+      </c>
+      <c r="S298" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T298" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>231</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>232</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Hansen illage Apartments</t>
+          <t>Crystal View Apartments</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2530007014</t>
+          <t>23115127</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>11821 FOOTHILL BLVD LOS ANGELES CA 91342</t>
+          <t>12021 BAYPORT ST GARDEN GROVE 92840</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -61569,89 +61694,59 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>script-situs-match (2026-08-21)</t>
-        </is>
-      </c>
-      <c r="J299" t="inlineStr">
-        <is>
-          <t>Resolved by LA county situs/geocode search; two parcels share situs 11821 Foothill — multi-parcel</t>
-        </is>
-      </c>
-      <c r="K299" s="2" t="inlineStr">
+          <t>collaborator-sheet</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="L299" s="2" t="inlineStr">
-        <is>
-          <t>1768372</t>
-        </is>
-      </c>
-      <c r="M299" s="2" t="inlineStr">
-        <is>
-          <t>4763318</t>
-        </is>
-      </c>
-      <c r="N299" s="2" t="inlineStr">
-        <is>
-          <t>6531690</t>
-        </is>
-      </c>
-      <c r="O299" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P299" s="2" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
-      </c>
-      <c r="Q299" s="2" t="inlineStr">
-        <is>
-          <t>Five or more apartments</t>
-        </is>
-      </c>
-      <c r="R299" s="2" t="inlineStr">
-        <is>
-          <t>la-county-api</t>
-        </is>
-      </c>
-      <c r="S299" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>90133662</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>62106599</t>
+        </is>
+      </c>
+      <c r="R299" t="inlineStr">
+        <is>
+          <t>collaborator-sheet</t>
         </is>
       </c>
       <c r="T299" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>232</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>232</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Violet on Virgil</t>
+          <t>Crystal View Apartments</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>5501017044</t>
+          <t>23115128</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>160 S VIRGIL AVE LOS ANGELES CA 90004</t>
+          <t>12156 BAYPORT ST GARDEN GROVE 92840</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -61661,89 +61756,59 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>script-situs-match (2026-08-21)</t>
-        </is>
-      </c>
-      <c r="J300" t="inlineStr">
-        <is>
-          <t>Resolved by LA county situs/geocode search</t>
-        </is>
-      </c>
-      <c r="K300" s="2" t="inlineStr">
+          <t>collaborator-sheet</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="L300" s="2" t="inlineStr">
-        <is>
-          <t>18210958</t>
-        </is>
-      </c>
-      <c r="M300" s="2" t="inlineStr">
-        <is>
-          <t>30209370</t>
-        </is>
-      </c>
-      <c r="N300" s="2" t="inlineStr">
-        <is>
-          <t>48420328</t>
-        </is>
-      </c>
-      <c r="O300" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P300" s="2" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="Q300" s="2" t="inlineStr">
-        <is>
-          <t>Five or more apartments</t>
-        </is>
-      </c>
-      <c r="R300" s="2" t="inlineStr">
-        <is>
-          <t>la-county-api</t>
-        </is>
-      </c>
-      <c r="S300" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>30044551</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>20702197</t>
+        </is>
+      </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>collaborator-sheet</t>
         </is>
       </c>
       <c r="T300" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>232</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>233</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Crystal View Apartments</t>
+          <t>926 S. Kingsley Apartments</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>23115127</t>
+          <t>5093023058</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>12021 BAYPORT ST GARDEN GROVE 92840</t>
+          <t>926 S HARVARD BLVD LOS ANGELES CA 90006</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -61753,59 +61818,89 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
-        </is>
-      </c>
-      <c r="K301" t="inlineStr">
+          <t>script-finder-auto (2026-08-21)</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>Resolved by LA county situs/geocode search</t>
+        </is>
+      </c>
+      <c r="K301" s="2" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="N301" t="inlineStr">
-        <is>
-          <t>90133662</t>
-        </is>
-      </c>
-      <c r="O301" t="inlineStr">
-        <is>
-          <t>62106599</t>
-        </is>
-      </c>
-      <c r="R301" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="L301" s="2" t="inlineStr">
+        <is>
+          <t>1396325</t>
+        </is>
+      </c>
+      <c r="M301" s="2" t="inlineStr">
+        <is>
+          <t>587224</t>
+        </is>
+      </c>
+      <c r="N301" s="2" t="inlineStr">
+        <is>
+          <t>1983549</t>
+        </is>
+      </c>
+      <c r="O301" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P301" s="2" t="inlineStr">
+        <is>
+          <t>1914</t>
+        </is>
+      </c>
+      <c r="Q301" s="2" t="inlineStr">
+        <is>
+          <t>Five or more apartments</t>
+        </is>
+      </c>
+      <c r="R301" s="2" t="inlineStr">
+        <is>
+          <t>la-county-api</t>
+        </is>
+      </c>
+      <c r="S301" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T301" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>233</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>234</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Crystal View Apartments</t>
+          <t>939 S. Kingsley Apartments</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>23115128</t>
+          <t>5093023059</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>12156 BAYPORT ST GARDEN GROVE 92840</t>
+          <t>939 S KINGSLEY DR LOS ANGELES CA 90006</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -61815,39 +61910,69 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
-        </is>
-      </c>
-      <c r="K302" t="inlineStr">
+          <t>script-situs-match (2026-08-21)</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>Resolved by LA county situs/geocode search; use code "Single" — verify (value $6.2M suggests recent build)</t>
+        </is>
+      </c>
+      <c r="K302" s="2" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="N302" t="inlineStr">
-        <is>
-          <t>30044551</t>
-        </is>
-      </c>
-      <c r="O302" t="inlineStr">
-        <is>
-          <t>20702197</t>
-        </is>
-      </c>
-      <c r="R302" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+      <c r="L302" s="2" t="inlineStr">
+        <is>
+          <t>4800320</t>
+        </is>
+      </c>
+      <c r="M302" s="2" t="inlineStr">
+        <is>
+          <t>1382526</t>
+        </is>
+      </c>
+      <c r="N302" s="2" t="inlineStr">
+        <is>
+          <t>6182846</t>
+        </is>
+      </c>
+      <c r="O302" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P302" s="2" t="inlineStr">
+        <is>
+          <t>1913</t>
+        </is>
+      </c>
+      <c r="Q302" s="2" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+      <c r="R302" s="2" t="inlineStr">
+        <is>
+          <t>la-county-api</t>
+        </is>
+      </c>
+      <c r="S302" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T302" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>234</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>235</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -61857,17 +61982,22 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>926 S. Kingsley Apartments</t>
+          <t>3950 Ingraham Apartments</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>5093023058</t>
+          <t>5092029007</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>5092-029-007</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>926 S HARVARD BLVD LOS ANGELES CA 90006</t>
+          <t>3950 INGRAHAM ST LOS ANGELES CA 90005</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -61877,12 +62007,12 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>script-finder-auto (2026-08-21)</t>
+          <t>manual-repo-edit</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>Resolved by LA county situs/geocode search</t>
+          <t>Drew confirmed 2026-08-22: staff report "3950 W. Ingraham" has spurious W; single Ingraham St in LA. Pre-development "Four Units" lot.</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr">
@@ -61892,17 +62022,17 @@
       </c>
       <c r="L303" s="2" t="inlineStr">
         <is>
-          <t>1396325</t>
+          <t>1237872</t>
         </is>
       </c>
       <c r="M303" s="2" t="inlineStr">
         <is>
-          <t>587224</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N303" s="2" t="inlineStr">
         <is>
-          <t>1983549</t>
+          <t>1237872</t>
         </is>
       </c>
       <c r="O303" s="2" t="inlineStr">
@@ -61910,14 +62040,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="P303" s="2" t="inlineStr">
-        <is>
-          <t>1914</t>
-        </is>
-      </c>
       <c r="Q303" s="2" t="inlineStr">
         <is>
-          <t>Five or more apartments</t>
+          <t>Four Units (Any Combination)</t>
         </is>
       </c>
       <c r="R303" s="2" t="inlineStr">
@@ -61932,14 +62057,14 @@
       </c>
       <c r="T303" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>235</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>236</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -61949,17 +62074,22 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>939 S. Kingsley Apartments</t>
+          <t>Park Playa Apartments</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>5093023059</t>
+          <t>4211011047</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>4211-011-047</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>939 S KINGSLEY DR LOS ANGELES CA 90006</t>
+          <t>6985 S CENTINELA AVE (no county situs; AIN from assessor portal map)</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -61969,12 +62099,12 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>script-situs-match (2026-08-21)</t>
+          <t>manual-repo-edit</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>Resolved by LA county situs/geocode search; use code "Single" — verify (value $6.2M suggests recent build)</t>
+          <t>Drew 2026-08-22 via assessor portal map view; odd lot shape, best-fit parcel.</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr">
@@ -61984,17 +62114,17 @@
       </c>
       <c r="L304" s="2" t="inlineStr">
         <is>
-          <t>4800320</t>
+          <t>5234013</t>
         </is>
       </c>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>1382526</t>
+          <t>28443</t>
         </is>
       </c>
       <c r="N304" s="2" t="inlineStr">
         <is>
-          <t>6182846</t>
+          <t>5262456</t>
         </is>
       </c>
       <c r="O304" s="2" t="inlineStr">
@@ -62002,14 +62132,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="P304" s="2" t="inlineStr">
-        <is>
-          <t>1913</t>
-        </is>
-      </c>
       <c r="Q304" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Parking Lots (Commercial Use Properties)</t>
         </is>
       </c>
       <c r="R304" s="2" t="inlineStr">
@@ -62024,14 +62149,14 @@
       </c>
       <c r="T304" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>236</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>237</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -62041,22 +62166,17 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>3950 Ingraham Apartments</t>
+          <t>Edgemont by Angeleno</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>5092029007</t>
-        </is>
-      </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>5092-029-007</t>
+          <t>5540023002</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>3950 INGRAHAM ST LOS ANGELES CA 90005</t>
+          <t>1178 N HELIOTROPE DR LOS ANGELES CA 90029</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -62066,12 +62186,12 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>manual-repo-edit</t>
+          <t>script-finder-auto (2026-08-21)</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>Drew confirmed 2026-08-22: staff report "3950 W. Ingraham" has spurious W; single Ingraham St in LA. Pre-development "Four Units" lot.</t>
+          <t>Resolved by LA county situs/geocode search</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr">
@@ -62081,27 +62201,32 @@
       </c>
       <c r="L305" s="2" t="inlineStr">
         <is>
-          <t>1237872</t>
+          <t>271221</t>
         </is>
       </c>
       <c r="M305" s="2" t="inlineStr">
         <is>
+          <t>331491</t>
+        </is>
+      </c>
+      <c r="N305" s="2" t="inlineStr">
+        <is>
+          <t>602712</t>
+        </is>
+      </c>
+      <c r="O305" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N305" s="2" t="inlineStr">
-        <is>
-          <t>1237872</t>
-        </is>
-      </c>
-      <c r="O305" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="P305" s="2" t="inlineStr">
+        <is>
+          <t>1962</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
         <is>
-          <t>Four Units (Any Combination)</t>
+          <t>Five or more apartments</t>
         </is>
       </c>
       <c r="R305" s="2" t="inlineStr">
@@ -62116,39 +62241,34 @@
       </c>
       <c r="T305" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>237</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Park Playa Apartments</t>
+          <t>SoFi Los Gatos Creek Apartments</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>4211011047</t>
-        </is>
-      </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>4211-011-047</t>
+          <t>28424015</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>6985 S CENTINELA AVE (no county situs; AIN from assessor portal map)</t>
+          <t>2070 Southwest Ex, San Jose, CA 95128</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -62158,84 +62278,54 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>manual-repo-edit</t>
-        </is>
-      </c>
-      <c r="J306" t="inlineStr">
-        <is>
-          <t>Drew 2026-08-22 via assessor portal map view; odd lot shape, best-fit parcel.</t>
-        </is>
-      </c>
-      <c r="K306" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="L306" s="2" t="inlineStr">
-        <is>
-          <t>5234013</t>
-        </is>
-      </c>
-      <c r="M306" s="2" t="inlineStr">
-        <is>
-          <t>28443</t>
-        </is>
-      </c>
-      <c r="N306" s="2" t="inlineStr">
-        <is>
-          <t>5262456</t>
-        </is>
-      </c>
-      <c r="O306" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q306" s="2" t="inlineStr">
-        <is>
-          <t>Parking Lots (Commercial Use Properties)</t>
-        </is>
-      </c>
-      <c r="R306" s="2" t="inlineStr">
-        <is>
-          <t>la-county-api</t>
-        </is>
-      </c>
-      <c r="S306" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
+          <t>collaborator-sheet</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>36559633</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>18850147</t>
+        </is>
+      </c>
+      <c r="R306" t="inlineStr">
+        <is>
+          <t>collaborator-sheet</t>
         </is>
       </c>
       <c r="T306" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Edgemont by Angeleno</t>
+          <t>HARKEN APARTMENTS</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>5540023002</t>
+          <t>17004068</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>1178 N HELIOTROPE DR LOS ANGELES CA 90029</t>
+          <t>5150 EL CAMINO REAL LOS ALTOS CA</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -62245,69 +62335,29 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>script-finder-auto (2026-08-21)</t>
-        </is>
-      </c>
-      <c r="J307" t="inlineStr">
-        <is>
-          <t>Resolved by LA county situs/geocode search</t>
-        </is>
-      </c>
-      <c r="K307" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="L307" s="2" t="inlineStr">
-        <is>
-          <t>271221</t>
-        </is>
-      </c>
-      <c r="M307" s="2" t="inlineStr">
-        <is>
-          <t>331491</t>
-        </is>
-      </c>
-      <c r="N307" s="2" t="inlineStr">
-        <is>
-          <t>602712</t>
-        </is>
-      </c>
-      <c r="O307" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P307" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="Q307" s="2" t="inlineStr">
-        <is>
-          <t>Five or more apartments</t>
-        </is>
-      </c>
-      <c r="R307" s="2" t="inlineStr">
-        <is>
-          <t>la-county-api</t>
-        </is>
-      </c>
-      <c r="S307" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
+          <t>collaborator-sheet</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>32171358</t>
+        </is>
+      </c>
+      <c r="R307" t="inlineStr">
+        <is>
+          <t>collaborator-sheet</t>
         </is>
       </c>
       <c r="T307" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -62317,17 +62367,17 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>SoFi Los Gatos Creek Apartments</t>
+          <t>HARKEN APARTMENTS</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>28424015</t>
+          <t>17004069</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>2070 Southwest Ex, San Jose, CA 95128</t>
+          <t>5150 EL CAMINO REAL LOS ALTOS CA</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -62342,12 +62392,7 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>36559633</t>
-        </is>
-      </c>
-      <c r="O308" t="inlineStr">
-        <is>
-          <t>18850147</t>
+          <t>18766626</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -62357,14 +62402,14 @@
       </c>
       <c r="T308" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>89</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -62374,17 +62419,17 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>HARKEN APARTMENTS</t>
+          <t>LINQ Apartments</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>17004068</t>
+          <t>25404108</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>5150 EL CAMINO REAL LOS ALTOS CA</t>
+          <t>1700 NEWBURY PARK DR SAN JOSE CA 95133-1771</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -62399,7 +62444,7 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>32171358</t>
+          <t>113197044</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -62409,14 +62454,14 @@
       </c>
       <c r="T309" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>89</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>95</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -62426,17 +62471,17 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>HARKEN APARTMENTS</t>
+          <t>Fountain Park Apartments</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>17004069</t>
+          <t>37226016</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>5150 EL CAMINO REAL LOS ALTOS CA</t>
+          <t>1028 S De Anza Bl, San Jose, CA 95129</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -62451,7 +62496,7 @@
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>18766626</t>
+          <t>4853048</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -62461,14 +62506,14 @@
       </c>
       <c r="T310" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>95</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -62478,17 +62523,17 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>LINQ Apartments</t>
+          <t>Park Kiely Apartments</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>25404108</t>
+          <t>29640005</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>1700 NEWBURY PARK DR SAN JOSE CA 95133-1771</t>
+          <t>355 Kiely Bl, San Jose, CA 95129</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -62503,7 +62548,7 @@
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>113197044</t>
+          <t>129482004</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -62513,14 +62558,14 @@
       </c>
       <c r="T311" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -62530,17 +62575,17 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Fountain Park Apartments</t>
+          <t>Park Kiely Apartments</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>37226016</t>
+          <t>29640004</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>1028 S De Anza Bl, San Jose, CA 95129</t>
+          <t>4240 Albany Dr, San Jose, CA 95129</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -62555,7 +62600,7 @@
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>4853048</t>
+          <t>95469825</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -62565,7 +62610,7 @@
       </c>
       <c r="T312" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
     </row>
@@ -62587,12 +62632,12 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>29640005</t>
+          <t>29640003</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>355 Kiely Bl, San Jose, CA 95129</t>
+          <t>4280 Albany Dr, San Jose, CA 95129</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -62607,7 +62652,7 @@
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t>129482004</t>
+          <t>72364911</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -62624,7 +62669,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -62634,17 +62679,17 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Park Kiely Apartments</t>
+          <t>Ascent Apartments</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>29640004</t>
+          <t>70607013</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>4240 Albany Dr, San Jose, CA 95129</t>
+          <t>5805 CHARLOTTE DR SAN JOSE CA 95123-3619</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -62659,7 +62704,7 @@
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t>95469825</t>
+          <t>269608107</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -62669,14 +62714,14 @@
       </c>
       <c r="T314" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>136</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>138</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -62686,17 +62731,17 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Park Kiely Apartments</t>
+          <t>Montecito Apartments</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>29640003</t>
+          <t>21332022</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>4280 Albany Dr, San Jose, CA 95129</t>
+          <t>3765 TAMARACK LN SANTA CLARA CA 95051-2571</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -62711,7 +62756,7 @@
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>72364911</t>
+          <t>27979060</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -62721,14 +62766,14 @@
       </c>
       <c r="T315" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>138</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -62738,17 +62783,17 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Ascent Apartments</t>
+          <t>Thornbridge Apartments</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>70607013</t>
+          <t>68429011</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>5805 CHARLOTTE DR SAN JOSE CA 95123-3619</t>
+          <t>5150 Monterey Rd, San Jose, CA 95111</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -62763,7 +62808,12 @@
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>269608107</t>
+          <t>51700304</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>51700304</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -62773,14 +62823,14 @@
       </c>
       <c r="T316" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>139</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>139</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -62790,17 +62840,17 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Montecito Apartments</t>
+          <t>Thornbridge Apartments</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>21332022</t>
+          <t>68428078</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>3765 TAMARACK LN SANTA CLARA CA 95051-2571</t>
+          <t>70 Crocker Ct, San Jose, CA 95111</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -62815,7 +62865,12 @@
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>27979060</t>
+          <t>8396294</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>8396294</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -62825,14 +62880,14 @@
       </c>
       <c r="T317" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>139</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>140</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -62842,17 +62897,17 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Thornbridge Apartments</t>
+          <t>The Crossings Apartments</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>68429011</t>
+          <t>31342061</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>5150 Monterey Rd, San Jose, CA 95111</t>
+          <t>1180 LOCHINVAR AVE SUNNYVALE CA 94087-5100</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -62867,12 +62922,7 @@
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>51700304</t>
-        </is>
-      </c>
-      <c r="O318" t="inlineStr">
-        <is>
-          <t>51700304</t>
+          <t>70919811</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -62882,14 +62932,14 @@
       </c>
       <c r="T318" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>140</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>189</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -62899,17 +62949,22 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Thornbridge Apartments</t>
+          <t>The Colonnade Apartments</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>68428078</t>
+          <t>46745084</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>467-45-084</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>70 Crocker Ct, San Jose, CA 95111</t>
+          <t>201 S 4Th St</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -62924,12 +62979,7 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>8396294</t>
-        </is>
-      </c>
-      <c r="O319" t="inlineStr">
-        <is>
-          <t>8396294</t>
+          <t>31718046</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -62939,14 +62989,14 @@
       </c>
       <c r="T319" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>189</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>189</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -62956,17 +63006,22 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>The Crossings Apartments</t>
+          <t>The Colonnade Apartments</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>31342061</t>
+          <t>46745075</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>467-45-075</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>1180 LOCHINVAR AVE SUNNYVALE CA 94087-5100</t>
+          <t>115 E San Carlos</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -62979,19 +63034,9 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="N320" t="inlineStr">
-        <is>
-          <t>70919811</t>
-        </is>
-      </c>
-      <c r="R320" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
-        </is>
-      </c>
       <c r="T320" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>189</t>
         </is>
       </c>
     </row>
@@ -63013,17 +63058,17 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>46745084</t>
+          <t>46745074</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>467-45-084</t>
+          <t>467-45-074</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>201 S 4Th St</t>
+          <t>115 E San Carlos St</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -63032,16 +63077,6 @@
         </is>
       </c>
       <c r="H321" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
-        </is>
-      </c>
-      <c r="N321" t="inlineStr">
-        <is>
-          <t>31718046</t>
-        </is>
-      </c>
-      <c r="R321" t="inlineStr">
         <is>
           <t>collaborator-sheet</t>
         </is>
@@ -63070,17 +63105,17 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>46745075</t>
+          <t>46745073</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>467-45-075</t>
+          <t>467-45-073</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>115 E San Carlos</t>
+          <t>200 S 3Rd St</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -63102,7 +63137,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>191</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -63112,22 +63147,22 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>The Colonnade Apartments</t>
+          <t>Highland Gardens Apartments</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>46745074</t>
+          <t>15401034</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>467-45-074</t>
+          <t>154-01-034</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>115 E San Carlos St</t>
+          <t>234 Escuela Av</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -63140,16 +63175,26 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>104843965</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>collaborator-sheet</t>
+        </is>
+      </c>
       <c r="T323" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>191</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>198</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -63159,22 +63204,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>The Colonnade Apartments</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>46745073</t>
-        </is>
-      </c>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>467-45-073</t>
-        </is>
-      </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>200 S 3Rd St</t>
+          <t>220 Humboldt Ct. Apartments</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -63189,39 +63219,34 @@
       </c>
       <c r="T324" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>198</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>202</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Highland Gardens Apartments</t>
+          <t>La Posada Apartments</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>15401034</t>
+          <t>01125105</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>154-01-034</t>
-        </is>
-      </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>234 Escuela Av</t>
+          <t>011-251-05</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -63231,39 +63256,64 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>Drew 2026-08-22 via Santa Cruz assessor lookup, 609 Frederick St</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>2026</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t>104843965</t>
+          <t>9776112</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
+          <t>manual-repo-edit</t>
         </is>
       </c>
       <c r="T325" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>202</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Solano</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>220 Humboldt Ct. Apartments</t>
+          <t>Montessa Apartments</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>128101150</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>343 MOON RIVER PL VACAVILLE CA 95687</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -63278,34 +63328,34 @@
       </c>
       <c r="T326" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Solano</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>La Posada Apartments</t>
+          <t>Montessa Apartments</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>01125105</t>
-        </is>
-      </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>011-251-05</t>
+          <t>128101140</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>343 MOON RIVER PL VACAVILLE CA 95687</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -63315,37 +63365,47 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>manual-repo-edit</t>
-        </is>
-      </c>
-      <c r="J327" t="inlineStr">
-        <is>
-          <t>Drew 2026-08-22 via Santa Cruz assessor lookup, 609 Frederick St</t>
-        </is>
-      </c>
-      <c r="K327" t="inlineStr">
+          <t>collaborator-sheet</t>
+        </is>
+      </c>
+      <c r="K327" s="2" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="N327" t="inlineStr">
-        <is>
-          <t>9776112</t>
-        </is>
-      </c>
-      <c r="O327" t="inlineStr">
+      <c r="L327" s="2" t="inlineStr">
+        <is>
+          <t>8875.0</t>
+        </is>
+      </c>
+      <c r="M327" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="R327" t="inlineStr">
-        <is>
-          <t>manual-repo-edit</t>
+      <c r="N327" s="2" t="inlineStr">
+        <is>
+          <t>8875.0</t>
+        </is>
+      </c>
+      <c r="O327" s="2" t="inlineStr">
+        <is>
+          <t>1569.0</t>
+        </is>
+      </c>
+      <c r="R327" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S327" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T327" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -63367,7 +63427,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>128101150</t>
+          <t>128101130</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -63383,6 +63443,41 @@
       <c r="H328" t="inlineStr">
         <is>
           <t>collaborator-sheet</t>
+        </is>
+      </c>
+      <c r="K328" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L328" s="2" t="inlineStr">
+        <is>
+          <t>8888.0</t>
+        </is>
+      </c>
+      <c r="M328" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N328" s="2" t="inlineStr">
+        <is>
+          <t>8888.0</t>
+        </is>
+      </c>
+      <c r="O328" s="2" t="inlineStr">
+        <is>
+          <t>1535.0</t>
+        </is>
+      </c>
+      <c r="R328" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S328" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T328" t="inlineStr">
@@ -63409,7 +63504,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>128101140</t>
+          <t>128101120</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -63434,7 +63529,7 @@
       </c>
       <c r="L329" s="2" t="inlineStr">
         <is>
-          <t>8875.0</t>
+          <t>8903.0</t>
         </is>
       </c>
       <c r="M329" s="2" t="inlineStr">
@@ -63444,12 +63539,12 @@
       </c>
       <c r="N329" s="2" t="inlineStr">
         <is>
-          <t>8875.0</t>
+          <t>8903.0</t>
         </is>
       </c>
       <c r="O329" s="2" t="inlineStr">
         <is>
-          <t>1569.0</t>
+          <t>1514.0</t>
         </is>
       </c>
       <c r="R329" s="2" t="inlineStr">
@@ -63486,7 +63581,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>128101130</t>
+          <t>128101110</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -63511,7 +63606,7 @@
       </c>
       <c r="L330" s="2" t="inlineStr">
         <is>
-          <t>8888.0</t>
+          <t>8918.0</t>
         </is>
       </c>
       <c r="M330" s="2" t="inlineStr">
@@ -63521,12 +63616,12 @@
       </c>
       <c r="N330" s="2" t="inlineStr">
         <is>
-          <t>8888.0</t>
+          <t>8918.0</t>
         </is>
       </c>
       <c r="O330" s="2" t="inlineStr">
         <is>
-          <t>1535.0</t>
+          <t>1541.0</t>
         </is>
       </c>
       <c r="R330" s="2" t="inlineStr">
@@ -63563,7 +63658,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>128101120</t>
+          <t>128101100</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -63573,7 +63668,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -63588,7 +63683,7 @@
       </c>
       <c r="L331" s="2" t="inlineStr">
         <is>
-          <t>8903.0</t>
+          <t>30867.0</t>
         </is>
       </c>
       <c r="M331" s="2" t="inlineStr">
@@ -63598,12 +63693,12 @@
       </c>
       <c r="N331" s="2" t="inlineStr">
         <is>
-          <t>8903.0</t>
+          <t>30867.0</t>
         </is>
       </c>
       <c r="O331" s="2" t="inlineStr">
         <is>
-          <t>1514.0</t>
+          <t>5457.0</t>
         </is>
       </c>
       <c r="R331" s="2" t="inlineStr">
@@ -63640,7 +63735,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>128101110</t>
+          <t>128101090</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -63665,7 +63760,7 @@
       </c>
       <c r="L332" s="2" t="inlineStr">
         <is>
-          <t>8918.0</t>
+          <t>31033.0</t>
         </is>
       </c>
       <c r="M332" s="2" t="inlineStr">
@@ -63675,12 +63770,12 @@
       </c>
       <c r="N332" s="2" t="inlineStr">
         <is>
-          <t>8918.0</t>
+          <t>31033.0</t>
         </is>
       </c>
       <c r="O332" s="2" t="inlineStr">
         <is>
-          <t>1541.0</t>
+          <t>5362.0</t>
         </is>
       </c>
       <c r="R332" s="2" t="inlineStr">
@@ -63717,7 +63812,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>128101100</t>
+          <t>128101080</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -63727,7 +63822,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -63742,7 +63837,7 @@
       </c>
       <c r="L333" s="2" t="inlineStr">
         <is>
-          <t>30867.0</t>
+          <t>32605.0</t>
         </is>
       </c>
       <c r="M333" s="2" t="inlineStr">
@@ -63752,12 +63847,12 @@
       </c>
       <c r="N333" s="2" t="inlineStr">
         <is>
-          <t>30867.0</t>
+          <t>32605.0</t>
         </is>
       </c>
       <c r="O333" s="2" t="inlineStr">
         <is>
-          <t>5457.0</t>
+          <t>5546.0</t>
         </is>
       </c>
       <c r="R333" s="2" t="inlineStr">
@@ -63794,7 +63889,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>128101090</t>
+          <t>128101070</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -63819,7 +63914,7 @@
       </c>
       <c r="L334" s="2" t="inlineStr">
         <is>
-          <t>31033.0</t>
+          <t>36427.0</t>
         </is>
       </c>
       <c r="M334" s="2" t="inlineStr">
@@ -63829,12 +63924,12 @@
       </c>
       <c r="N334" s="2" t="inlineStr">
         <is>
-          <t>31033.0</t>
+          <t>36427.0</t>
         </is>
       </c>
       <c r="O334" s="2" t="inlineStr">
         <is>
-          <t>5362.0</t>
+          <t>6294.0</t>
         </is>
       </c>
       <c r="R334" s="2" t="inlineStr">
@@ -63871,7 +63966,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>128101080</t>
+          <t>128101060</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -63896,7 +63991,7 @@
       </c>
       <c r="L335" s="2" t="inlineStr">
         <is>
-          <t>32605.0</t>
+          <t>40997.0</t>
         </is>
       </c>
       <c r="M335" s="2" t="inlineStr">
@@ -63906,12 +64001,12 @@
       </c>
       <c r="N335" s="2" t="inlineStr">
         <is>
-          <t>32605.0</t>
+          <t>40997.0</t>
         </is>
       </c>
       <c r="O335" s="2" t="inlineStr">
         <is>
-          <t>5546.0</t>
+          <t>7248.0</t>
         </is>
       </c>
       <c r="R335" s="2" t="inlineStr">
@@ -63948,7 +64043,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>128101070</t>
+          <t>128101050</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -63964,41 +64059,6 @@
       <c r="H336" t="inlineStr">
         <is>
           <t>collaborator-sheet</t>
-        </is>
-      </c>
-      <c r="K336" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="L336" s="2" t="inlineStr">
-        <is>
-          <t>36427.0</t>
-        </is>
-      </c>
-      <c r="M336" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N336" s="2" t="inlineStr">
-        <is>
-          <t>36427.0</t>
-        </is>
-      </c>
-      <c r="O336" s="2" t="inlineStr">
-        <is>
-          <t>6294.0</t>
-        </is>
-      </c>
-      <c r="R336" s="2" t="inlineStr">
-        <is>
-          <t>solano-county-portal</t>
-        </is>
-      </c>
-      <c r="S336" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T336" t="inlineStr">
@@ -64025,7 +64085,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>128101060</t>
+          <t>128101040</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -64050,7 +64110,7 @@
       </c>
       <c r="L337" s="2" t="inlineStr">
         <is>
-          <t>40997.0</t>
+          <t>67916.0</t>
         </is>
       </c>
       <c r="M337" s="2" t="inlineStr">
@@ -64060,12 +64120,12 @@
       </c>
       <c r="N337" s="2" t="inlineStr">
         <is>
-          <t>40997.0</t>
+          <t>67916.0</t>
         </is>
       </c>
       <c r="O337" s="2" t="inlineStr">
         <is>
-          <t>7248.0</t>
+          <t>11735.0</t>
         </is>
       </c>
       <c r="R337" s="2" t="inlineStr">
@@ -64102,7 +64162,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>128101050</t>
+          <t>128101030</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -64118,6 +64178,41 @@
       <c r="H338" t="inlineStr">
         <is>
           <t>collaborator-sheet</t>
+        </is>
+      </c>
+      <c r="K338" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L338" s="2" t="inlineStr">
+        <is>
+          <t>63157.0</t>
+        </is>
+      </c>
+      <c r="M338" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N338" s="2" t="inlineStr">
+        <is>
+          <t>63157.0</t>
+        </is>
+      </c>
+      <c r="O338" s="2" t="inlineStr">
+        <is>
+          <t>10743.0</t>
+        </is>
+      </c>
+      <c r="R338" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S338" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T338" t="inlineStr">
@@ -64144,7 +64239,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>128101040</t>
+          <t>128101020</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -64169,7 +64264,7 @@
       </c>
       <c r="L339" s="2" t="inlineStr">
         <is>
-          <t>67916.0</t>
+          <t>50192.0</t>
         </is>
       </c>
       <c r="M339" s="2" t="inlineStr">
@@ -64179,12 +64274,12 @@
       </c>
       <c r="N339" s="2" t="inlineStr">
         <is>
-          <t>67916.0</t>
+          <t>50192.0</t>
         </is>
       </c>
       <c r="O339" s="2" t="inlineStr">
         <is>
-          <t>11735.0</t>
+          <t>8873.0</t>
         </is>
       </c>
       <c r="R339" s="2" t="inlineStr">
@@ -64221,7 +64316,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>128101030</t>
+          <t>128101010</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -64246,7 +64341,7 @@
       </c>
       <c r="L340" s="2" t="inlineStr">
         <is>
-          <t>63157.0</t>
+          <t>101032.0</t>
         </is>
       </c>
       <c r="M340" s="2" t="inlineStr">
@@ -64256,12 +64351,12 @@
       </c>
       <c r="N340" s="2" t="inlineStr">
         <is>
-          <t>63157.0</t>
+          <t>101032.0</t>
         </is>
       </c>
       <c r="O340" s="2" t="inlineStr">
         <is>
-          <t>10743.0</t>
+          <t>17458.0</t>
         </is>
       </c>
       <c r="R340" s="2" t="inlineStr">
@@ -64298,7 +64393,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>128101020</t>
+          <t>128102110</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -64323,22 +64418,22 @@
       </c>
       <c r="L341" s="2" t="inlineStr">
         <is>
-          <t>50192.0</t>
+          <t>51705.0</t>
         </is>
       </c>
       <c r="M341" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>561000.0</t>
         </is>
       </c>
       <c r="N341" s="2" t="inlineStr">
         <is>
-          <t>50192.0</t>
+          <t>612705.0</t>
         </is>
       </c>
       <c r="O341" s="2" t="inlineStr">
         <is>
-          <t>8873.0</t>
+          <t>108006.0</t>
         </is>
       </c>
       <c r="R341" s="2" t="inlineStr">
@@ -64375,7 +64470,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>128101010</t>
+          <t>128102100</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -64400,22 +64495,22 @@
       </c>
       <c r="L342" s="2" t="inlineStr">
         <is>
-          <t>101032.0</t>
+          <t>50439.0</t>
         </is>
       </c>
       <c r="M342" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>571000.0</t>
         </is>
       </c>
       <c r="N342" s="2" t="inlineStr">
         <is>
-          <t>101032.0</t>
+          <t>621439.0</t>
         </is>
       </c>
       <c r="O342" s="2" t="inlineStr">
         <is>
-          <t>17458.0</t>
+          <t>115237.0</t>
         </is>
       </c>
       <c r="R342" s="2" t="inlineStr">
@@ -64452,7 +64547,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>128102110</t>
+          <t>128102090</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -64477,7 +64572,7 @@
       </c>
       <c r="L343" s="2" t="inlineStr">
         <is>
-          <t>51705.0</t>
+          <t>50439.0</t>
         </is>
       </c>
       <c r="M343" s="2" t="inlineStr">
@@ -64487,12 +64582,12 @@
       </c>
       <c r="N343" s="2" t="inlineStr">
         <is>
-          <t>612705.0</t>
+          <t>611439.0</t>
         </is>
       </c>
       <c r="O343" s="2" t="inlineStr">
         <is>
-          <t>108006.0</t>
+          <t>107787.0</t>
         </is>
       </c>
       <c r="R343" s="2" t="inlineStr">
@@ -64529,7 +64624,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>128102100</t>
+          <t>128102080</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -64559,17 +64654,17 @@
       </c>
       <c r="M344" s="2" t="inlineStr">
         <is>
-          <t>571000.0</t>
+          <t>605000.0</t>
         </is>
       </c>
       <c r="N344" s="2" t="inlineStr">
         <is>
-          <t>621439.0</t>
+          <t>655439.0</t>
         </is>
       </c>
       <c r="O344" s="2" t="inlineStr">
         <is>
-          <t>115237.0</t>
+          <t>118205.0</t>
         </is>
       </c>
       <c r="R344" s="2" t="inlineStr">
@@ -64606,7 +64701,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>128102090</t>
+          <t>128102070</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -64631,22 +64726,22 @@
       </c>
       <c r="L345" s="2" t="inlineStr">
         <is>
-          <t>50439.0</t>
+          <t>9639.0</t>
         </is>
       </c>
       <c r="M345" s="2" t="inlineStr">
         <is>
-          <t>561000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N345" s="2" t="inlineStr">
         <is>
-          <t>611439.0</t>
+          <t>9639.0</t>
         </is>
       </c>
       <c r="O345" s="2" t="inlineStr">
         <is>
-          <t>107787.0</t>
+          <t>1665.0</t>
         </is>
       </c>
       <c r="R345" s="2" t="inlineStr">
@@ -64683,7 +64778,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>128102080</t>
+          <t>128102060</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -64708,22 +64803,22 @@
       </c>
       <c r="L346" s="2" t="inlineStr">
         <is>
-          <t>50439.0</t>
+          <t>9639.0</t>
         </is>
       </c>
       <c r="M346" s="2" t="inlineStr">
         <is>
-          <t>605000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N346" s="2" t="inlineStr">
         <is>
-          <t>655439.0</t>
+          <t>9639.0</t>
         </is>
       </c>
       <c r="O346" s="2" t="inlineStr">
         <is>
-          <t>118205.0</t>
+          <t>1704.0</t>
         </is>
       </c>
       <c r="R346" s="2" t="inlineStr">
@@ -64760,7 +64855,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>128102070</t>
+          <t>128102050</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -64785,7 +64880,7 @@
       </c>
       <c r="L347" s="2" t="inlineStr">
         <is>
-          <t>9639.0</t>
+          <t>33305.0</t>
         </is>
       </c>
       <c r="M347" s="2" t="inlineStr">
@@ -64795,12 +64890,12 @@
       </c>
       <c r="N347" s="2" t="inlineStr">
         <is>
-          <t>9639.0</t>
+          <t>33305.0</t>
         </is>
       </c>
       <c r="O347" s="2" t="inlineStr">
         <is>
-          <t>1665.0</t>
+          <t>5755.0</t>
         </is>
       </c>
       <c r="R347" s="2" t="inlineStr">
@@ -64837,7 +64932,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>128102060</t>
+          <t>128102040</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -64862,7 +64957,7 @@
       </c>
       <c r="L348" s="2" t="inlineStr">
         <is>
-          <t>9639.0</t>
+          <t>33305.0</t>
         </is>
       </c>
       <c r="M348" s="2" t="inlineStr">
@@ -64872,12 +64967,12 @@
       </c>
       <c r="N348" s="2" t="inlineStr">
         <is>
-          <t>9639.0</t>
+          <t>33305.0</t>
         </is>
       </c>
       <c r="O348" s="2" t="inlineStr">
         <is>
-          <t>1704.0</t>
+          <t>5888.0</t>
         </is>
       </c>
       <c r="R348" s="2" t="inlineStr">
@@ -64914,7 +65009,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>128102050</t>
+          <t>128102030</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -64939,7 +65034,7 @@
       </c>
       <c r="L349" s="2" t="inlineStr">
         <is>
-          <t>33305.0</t>
+          <t>33350.0</t>
         </is>
       </c>
       <c r="M349" s="2" t="inlineStr">
@@ -64949,12 +65044,12 @@
       </c>
       <c r="N349" s="2" t="inlineStr">
         <is>
-          <t>33305.0</t>
+          <t>33350.0</t>
         </is>
       </c>
       <c r="O349" s="2" t="inlineStr">
         <is>
-          <t>5755.0</t>
+          <t>5762.0</t>
         </is>
       </c>
       <c r="R349" s="2" t="inlineStr">
@@ -64991,7 +65086,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>128102040</t>
+          <t>128102020</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
@@ -65016,7 +65111,7 @@
       </c>
       <c r="L350" s="2" t="inlineStr">
         <is>
-          <t>33305.0</t>
+          <t>33263.0</t>
         </is>
       </c>
       <c r="M350" s="2" t="inlineStr">
@@ -65026,12 +65121,12 @@
       </c>
       <c r="N350" s="2" t="inlineStr">
         <is>
-          <t>33305.0</t>
+          <t>33263.0</t>
         </is>
       </c>
       <c r="O350" s="2" t="inlineStr">
         <is>
-          <t>5888.0</t>
+          <t>5658.0</t>
         </is>
       </c>
       <c r="R350" s="2" t="inlineStr">
@@ -65068,7 +65163,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>128102030</t>
+          <t>128102010</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -65093,7 +65188,7 @@
       </c>
       <c r="L351" s="2" t="inlineStr">
         <is>
-          <t>33350.0</t>
+          <t>41238.0</t>
         </is>
       </c>
       <c r="M351" s="2" t="inlineStr">
@@ -65103,12 +65198,12 @@
       </c>
       <c r="N351" s="2" t="inlineStr">
         <is>
-          <t>33350.0</t>
+          <t>41238.0</t>
         </is>
       </c>
       <c r="O351" s="2" t="inlineStr">
         <is>
-          <t>5762.0</t>
+          <t>7125.0</t>
         </is>
       </c>
       <c r="R351" s="2" t="inlineStr">
@@ -65145,7 +65240,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>128102020</t>
+          <t>128102210</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -65170,22 +65265,22 @@
       </c>
       <c r="L352" s="2" t="inlineStr">
         <is>
-          <t>33263.0</t>
+          <t>88958.0</t>
         </is>
       </c>
       <c r="M352" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>561000.0</t>
         </is>
       </c>
       <c r="N352" s="2" t="inlineStr">
         <is>
-          <t>33263.0</t>
+          <t>649958.0</t>
         </is>
       </c>
       <c r="O352" s="2" t="inlineStr">
         <is>
-          <t>5658.0</t>
+          <t>114443.0</t>
         </is>
       </c>
       <c r="R352" s="2" t="inlineStr">
@@ -65222,7 +65317,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>128102010</t>
+          <t>128102200</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -65247,22 +65342,22 @@
       </c>
       <c r="L353" s="2" t="inlineStr">
         <is>
-          <t>41238.0</t>
+          <t>70451.0</t>
         </is>
       </c>
       <c r="M353" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>605000.0</t>
         </is>
       </c>
       <c r="N353" s="2" t="inlineStr">
         <is>
-          <t>41238.0</t>
+          <t>675451.0</t>
         </is>
       </c>
       <c r="O353" s="2" t="inlineStr">
         <is>
-          <t>7125.0</t>
+          <t>448773.0</t>
         </is>
       </c>
       <c r="R353" s="2" t="inlineStr">
@@ -65299,7 +65394,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>128102210</t>
+          <t>128102190</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -65324,7 +65419,7 @@
       </c>
       <c r="L354" s="2" t="inlineStr">
         <is>
-          <t>88958.0</t>
+          <t>70404.0</t>
         </is>
       </c>
       <c r="M354" s="2" t="inlineStr">
@@ -65334,12 +65429,12 @@
       </c>
       <c r="N354" s="2" t="inlineStr">
         <is>
-          <t>649958.0</t>
+          <t>631404.0</t>
         </is>
       </c>
       <c r="O354" s="2" t="inlineStr">
         <is>
-          <t>114443.0</t>
+          <t>111237.0</t>
         </is>
       </c>
       <c r="R354" s="2" t="inlineStr">
@@ -65376,7 +65471,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>128102200</t>
+          <t>128102180</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -65401,7 +65496,7 @@
       </c>
       <c r="L355" s="2" t="inlineStr">
         <is>
-          <t>70451.0</t>
+          <t>70404.0</t>
         </is>
       </c>
       <c r="M355" s="2" t="inlineStr">
@@ -65411,12 +65506,12 @@
       </c>
       <c r="N355" s="2" t="inlineStr">
         <is>
-          <t>675451.0</t>
+          <t>675404.0</t>
         </is>
       </c>
       <c r="O355" s="2" t="inlineStr">
         <is>
-          <t>448773.0</t>
+          <t>121601.0</t>
         </is>
       </c>
       <c r="R355" s="2" t="inlineStr">
@@ -65453,7 +65548,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>128102190</t>
+          <t>128102170</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -65530,7 +65625,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>128102180</t>
+          <t>128102160</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -65555,22 +65650,22 @@
       </c>
       <c r="L357" s="2" t="inlineStr">
         <is>
-          <t>70404.0</t>
+          <t>49366.0</t>
         </is>
       </c>
       <c r="M357" s="2" t="inlineStr">
         <is>
-          <t>605000.0</t>
+          <t>571000.0</t>
         </is>
       </c>
       <c r="N357" s="2" t="inlineStr">
         <is>
-          <t>675404.0</t>
+          <t>620366.0</t>
         </is>
       </c>
       <c r="O357" s="2" t="inlineStr">
         <is>
-          <t>121601.0</t>
+          <t>113937.0</t>
         </is>
       </c>
       <c r="R357" s="2" t="inlineStr">
@@ -65607,7 +65702,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>128102170</t>
+          <t>128102150</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -65632,7 +65727,7 @@
       </c>
       <c r="L358" s="2" t="inlineStr">
         <is>
-          <t>70404.0</t>
+          <t>49366.0</t>
         </is>
       </c>
       <c r="M358" s="2" t="inlineStr">
@@ -65642,12 +65737,12 @@
       </c>
       <c r="N358" s="2" t="inlineStr">
         <is>
-          <t>631404.0</t>
+          <t>610366.0</t>
         </is>
       </c>
       <c r="O358" s="2" t="inlineStr">
         <is>
-          <t>111237.0</t>
+          <t>107602.0</t>
         </is>
       </c>
       <c r="R358" s="2" t="inlineStr">
@@ -65684,7 +65779,7 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>128102160</t>
+          <t>128102140</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -65709,22 +65804,22 @@
       </c>
       <c r="L359" s="2" t="inlineStr">
         <is>
-          <t>49366.0</t>
+          <t>48965.0</t>
         </is>
       </c>
       <c r="M359" s="2" t="inlineStr">
         <is>
-          <t>571000.0</t>
+          <t>605000.0</t>
         </is>
       </c>
       <c r="N359" s="2" t="inlineStr">
         <is>
-          <t>620366.0</t>
+          <t>653965.0</t>
         </is>
       </c>
       <c r="O359" s="2" t="inlineStr">
         <is>
-          <t>113937.0</t>
+          <t>117954.0</t>
         </is>
       </c>
       <c r="R359" s="2" t="inlineStr">
@@ -65761,7 +65856,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>128102150</t>
+          <t>128102130</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -65786,7 +65881,7 @@
       </c>
       <c r="L360" s="2" t="inlineStr">
         <is>
-          <t>49366.0</t>
+          <t>48965.0</t>
         </is>
       </c>
       <c r="M360" s="2" t="inlineStr">
@@ -65796,12 +65891,12 @@
       </c>
       <c r="N360" s="2" t="inlineStr">
         <is>
-          <t>610366.0</t>
+          <t>609965.0</t>
         </is>
       </c>
       <c r="O360" s="2" t="inlineStr">
         <is>
-          <t>107602.0</t>
+          <t>107533.0</t>
         </is>
       </c>
       <c r="R360" s="2" t="inlineStr">
@@ -65838,7 +65933,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>128102140</t>
+          <t>128102120</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -65863,22 +65958,22 @@
       </c>
       <c r="L361" s="2" t="inlineStr">
         <is>
-          <t>48965.0</t>
+          <t>50603.0</t>
         </is>
       </c>
       <c r="M361" s="2" t="inlineStr">
         <is>
-          <t>605000.0</t>
+          <t>571000.0</t>
         </is>
       </c>
       <c r="N361" s="2" t="inlineStr">
         <is>
-          <t>653965.0</t>
+          <t>621603.0</t>
         </is>
       </c>
       <c r="O361" s="2" t="inlineStr">
         <is>
-          <t>117954.0</t>
+          <t>115266.0</t>
         </is>
       </c>
       <c r="R361" s="2" t="inlineStr">
@@ -65915,7 +66010,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>128102130</t>
+          <t>128103090</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
@@ -65940,7 +66035,7 @@
       </c>
       <c r="L362" s="2" t="inlineStr">
         <is>
-          <t>48965.0</t>
+          <t>52887.0</t>
         </is>
       </c>
       <c r="M362" s="2" t="inlineStr">
@@ -65950,12 +66045,12 @@
       </c>
       <c r="N362" s="2" t="inlineStr">
         <is>
-          <t>609965.0</t>
+          <t>613887.0</t>
         </is>
       </c>
       <c r="O362" s="2" t="inlineStr">
         <is>
-          <t>107533.0</t>
+          <t>390827.0</t>
         </is>
       </c>
       <c r="R362" s="2" t="inlineStr">
@@ -65992,7 +66087,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>128102120</t>
+          <t>128103080</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -66017,7 +66112,7 @@
       </c>
       <c r="L363" s="2" t="inlineStr">
         <is>
-          <t>50603.0</t>
+          <t>49635.0</t>
         </is>
       </c>
       <c r="M363" s="2" t="inlineStr">
@@ -66027,12 +66122,12 @@
       </c>
       <c r="N363" s="2" t="inlineStr">
         <is>
-          <t>621603.0</t>
+          <t>620635.0</t>
         </is>
       </c>
       <c r="O363" s="2" t="inlineStr">
         <is>
-          <t>115266.0</t>
+          <t>115095.0</t>
         </is>
       </c>
       <c r="R363" s="2" t="inlineStr">
@@ -66069,7 +66164,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>128103090</t>
+          <t>128103070</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -66094,7 +66189,7 @@
       </c>
       <c r="L364" s="2" t="inlineStr">
         <is>
-          <t>52887.0</t>
+          <t>49635.0</t>
         </is>
       </c>
       <c r="M364" s="2" t="inlineStr">
@@ -66104,12 +66199,12 @@
       </c>
       <c r="N364" s="2" t="inlineStr">
         <is>
-          <t>613887.0</t>
+          <t>610635.0</t>
         </is>
       </c>
       <c r="O364" s="2" t="inlineStr">
         <is>
-          <t>390827.0</t>
+          <t>107648.0</t>
         </is>
       </c>
       <c r="R364" s="2" t="inlineStr">
@@ -66146,7 +66241,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>128103080</t>
+          <t>128103060</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
@@ -66176,17 +66271,17 @@
       </c>
       <c r="M365" s="2" t="inlineStr">
         <is>
-          <t>571000.0</t>
+          <t>605000.0</t>
         </is>
       </c>
       <c r="N365" s="2" t="inlineStr">
         <is>
-          <t>620635.0</t>
+          <t>654635.0</t>
         </is>
       </c>
       <c r="O365" s="2" t="inlineStr">
         <is>
-          <t>115095.0</t>
+          <t>434959.0</t>
         </is>
       </c>
       <c r="R365" s="2" t="inlineStr">
@@ -66223,7 +66318,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>128103070</t>
+          <t>128103050</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -66300,7 +66395,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>128103060</t>
+          <t>128103040</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -66325,22 +66420,22 @@
       </c>
       <c r="L367" s="2" t="inlineStr">
         <is>
-          <t>49635.0</t>
+          <t>71329.0</t>
         </is>
       </c>
       <c r="M367" s="2" t="inlineStr">
         <is>
-          <t>605000.0</t>
+          <t>571000.0</t>
         </is>
       </c>
       <c r="N367" s="2" t="inlineStr">
         <is>
-          <t>654635.0</t>
+          <t>642329.0</t>
         </is>
       </c>
       <c r="O367" s="2" t="inlineStr">
         <is>
-          <t>434959.0</t>
+          <t>118930.0</t>
         </is>
       </c>
       <c r="R367" s="2" t="inlineStr">
@@ -66377,7 +66472,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>128103050</t>
+          <t>128103030</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -66402,22 +66497,22 @@
       </c>
       <c r="L368" s="2" t="inlineStr">
         <is>
-          <t>49635.0</t>
+          <t>30529.0</t>
         </is>
       </c>
       <c r="M368" s="2" t="inlineStr">
         <is>
-          <t>561000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N368" s="2" t="inlineStr">
         <is>
-          <t>610635.0</t>
+          <t>30529.0</t>
         </is>
       </c>
       <c r="O368" s="2" t="inlineStr">
         <is>
-          <t>107648.0</t>
+          <t>5275.0</t>
         </is>
       </c>
       <c r="R368" s="2" t="inlineStr">
@@ -66454,7 +66549,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>128103040</t>
+          <t>128103020</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
@@ -66479,22 +66574,22 @@
       </c>
       <c r="L369" s="2" t="inlineStr">
         <is>
-          <t>71329.0</t>
+          <t>30529.0</t>
         </is>
       </c>
       <c r="M369" s="2" t="inlineStr">
         <is>
-          <t>571000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N369" s="2" t="inlineStr">
         <is>
-          <t>642329.0</t>
+          <t>30529.0</t>
         </is>
       </c>
       <c r="O369" s="2" t="inlineStr">
         <is>
-          <t>118930.0</t>
+          <t>5397.0</t>
         </is>
       </c>
       <c r="R369" s="2" t="inlineStr">
@@ -66531,7 +66626,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>128103030</t>
+          <t>128103010</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -66556,22 +66651,22 @@
       </c>
       <c r="L370" s="2" t="inlineStr">
         <is>
-          <t>30529.0</t>
+          <t>97840.0</t>
         </is>
       </c>
       <c r="M370" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>561000.0</t>
         </is>
       </c>
       <c r="N370" s="2" t="inlineStr">
         <is>
-          <t>30529.0</t>
+          <t>658840.0</t>
         </is>
       </c>
       <c r="O370" s="2" t="inlineStr">
         <is>
-          <t>5275.0</t>
+          <t>419134.0</t>
         </is>
       </c>
       <c r="R370" s="2" t="inlineStr">
@@ -66608,7 +66703,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>128103020</t>
+          <t>128103180</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -66633,22 +66728,22 @@
       </c>
       <c r="L371" s="2" t="inlineStr">
         <is>
-          <t>30529.0</t>
+          <t>89491.0</t>
         </is>
       </c>
       <c r="M371" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>572220.0</t>
         </is>
       </c>
       <c r="N371" s="2" t="inlineStr">
         <is>
-          <t>30529.0</t>
+          <t>661711.0</t>
         </is>
       </c>
       <c r="O371" s="2" t="inlineStr">
         <is>
-          <t>5397.0</t>
+          <t>116518.0</t>
         </is>
       </c>
       <c r="R371" s="2" t="inlineStr">
@@ -66685,7 +66780,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>128103010</t>
+          <t>128103170</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -66710,22 +66805,22 @@
       </c>
       <c r="L372" s="2" t="inlineStr">
         <is>
-          <t>97840.0</t>
+          <t>68555.0</t>
         </is>
       </c>
       <c r="M372" s="2" t="inlineStr">
         <is>
-          <t>561000.0</t>
+          <t>582420.0</t>
         </is>
       </c>
       <c r="N372" s="2" t="inlineStr">
         <is>
-          <t>658840.0</t>
+          <t>650975.0</t>
         </is>
       </c>
       <c r="O372" s="2" t="inlineStr">
         <is>
-          <t>419134.0</t>
+          <t>351865.0</t>
         </is>
       </c>
       <c r="R372" s="2" t="inlineStr">
@@ -66762,7 +66857,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>128103180</t>
+          <t>128103160</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
@@ -66787,22 +66882,22 @@
       </c>
       <c r="L373" s="2" t="inlineStr">
         <is>
-          <t>89491.0</t>
+          <t>68555.0</t>
         </is>
       </c>
       <c r="M373" s="2" t="inlineStr">
         <is>
-          <t>572220.0</t>
+          <t>617100.0</t>
         </is>
       </c>
       <c r="N373" s="2" t="inlineStr">
         <is>
-          <t>661711.0</t>
+          <t>685655.0</t>
         </is>
       </c>
       <c r="O373" s="2" t="inlineStr">
         <is>
-          <t>116518.0</t>
+          <t>123479.0</t>
         </is>
       </c>
       <c r="R373" s="2" t="inlineStr">
@@ -66839,7 +66934,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>128103170</t>
+          <t>128103150</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -66869,17 +66964,17 @@
       </c>
       <c r="M374" s="2" t="inlineStr">
         <is>
-          <t>582420.0</t>
+          <t>572220.0</t>
         </is>
       </c>
       <c r="N374" s="2" t="inlineStr">
         <is>
-          <t>650975.0</t>
+          <t>640775.0</t>
         </is>
       </c>
       <c r="O374" s="2" t="inlineStr">
         <is>
-          <t>351865.0</t>
+          <t>112900.0</t>
         </is>
       </c>
       <c r="R374" s="2" t="inlineStr">
@@ -66916,7 +67011,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>128103160</t>
+          <t>128103140</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -66941,22 +67036,22 @@
       </c>
       <c r="L375" s="2" t="inlineStr">
         <is>
-          <t>68555.0</t>
+          <t>48832.0</t>
         </is>
       </c>
       <c r="M375" s="2" t="inlineStr">
         <is>
-          <t>617100.0</t>
+          <t>582420.0</t>
         </is>
       </c>
       <c r="N375" s="2" t="inlineStr">
         <is>
-          <t>685655.0</t>
+          <t>631252.0</t>
         </is>
       </c>
       <c r="O375" s="2" t="inlineStr">
         <is>
-          <t>123479.0</t>
+          <t>341301.0</t>
         </is>
       </c>
       <c r="R375" s="2" t="inlineStr">
@@ -66993,7 +67088,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>128103150</t>
+          <t>128103130</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -67018,22 +67113,22 @@
       </c>
       <c r="L376" s="2" t="inlineStr">
         <is>
-          <t>68555.0</t>
+          <t>8032.0</t>
         </is>
       </c>
       <c r="M376" s="2" t="inlineStr">
         <is>
-          <t>572220.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N376" s="2" t="inlineStr">
         <is>
-          <t>640775.0</t>
+          <t>8032.0</t>
         </is>
       </c>
       <c r="O376" s="2" t="inlineStr">
         <is>
-          <t>112900.0</t>
+          <t>1366.0</t>
         </is>
       </c>
       <c r="R376" s="2" t="inlineStr">
@@ -67070,7 +67165,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>128103140</t>
+          <t>128103120</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -67100,17 +67195,17 @@
       </c>
       <c r="M377" s="2" t="inlineStr">
         <is>
-          <t>582420.0</t>
+          <t>572220.0</t>
         </is>
       </c>
       <c r="N377" s="2" t="inlineStr">
         <is>
-          <t>631252.0</t>
+          <t>621052.0</t>
         </is>
       </c>
       <c r="O377" s="2" t="inlineStr">
         <is>
-          <t>341301.0</t>
+          <t>109492.0</t>
         </is>
       </c>
       <c r="R377" s="2" t="inlineStr">
@@ -67147,7 +67242,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>128103130</t>
+          <t>128103110</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
@@ -67172,22 +67267,22 @@
       </c>
       <c r="L378" s="2" t="inlineStr">
         <is>
-          <t>8032.0</t>
+          <t>48832.0</t>
         </is>
       </c>
       <c r="M378" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>582420.0</t>
         </is>
       </c>
       <c r="N378" s="2" t="inlineStr">
         <is>
-          <t>8032.0</t>
+          <t>631252.0</t>
         </is>
       </c>
       <c r="O378" s="2" t="inlineStr">
         <is>
-          <t>1366.0</t>
+          <t>341301.0</t>
         </is>
       </c>
       <c r="R378" s="2" t="inlineStr">
@@ -67224,7 +67319,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>128103120</t>
+          <t>128103100</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -67249,7 +67344,7 @@
       </c>
       <c r="L379" s="2" t="inlineStr">
         <is>
-          <t>48832.0</t>
+          <t>50532.0</t>
         </is>
       </c>
       <c r="M379" s="2" t="inlineStr">
@@ -67259,12 +67354,12 @@
       </c>
       <c r="N379" s="2" t="inlineStr">
         <is>
-          <t>621052.0</t>
+          <t>622752.0</t>
         </is>
       </c>
       <c r="O379" s="2" t="inlineStr">
         <is>
-          <t>109492.0</t>
+          <t>622752.0</t>
         </is>
       </c>
       <c r="R379" s="2" t="inlineStr">
@@ -67301,7 +67396,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>128103110</t>
+          <t>128105060</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
@@ -67317,41 +67412,6 @@
       <c r="H380" t="inlineStr">
         <is>
           <t>collaborator-sheet</t>
-        </is>
-      </c>
-      <c r="K380" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="L380" s="2" t="inlineStr">
-        <is>
-          <t>48832.0</t>
-        </is>
-      </c>
-      <c r="M380" s="2" t="inlineStr">
-        <is>
-          <t>582420.0</t>
-        </is>
-      </c>
-      <c r="N380" s="2" t="inlineStr">
-        <is>
-          <t>631252.0</t>
-        </is>
-      </c>
-      <c r="O380" s="2" t="inlineStr">
-        <is>
-          <t>341301.0</t>
-        </is>
-      </c>
-      <c r="R380" s="2" t="inlineStr">
-        <is>
-          <t>solano-county-portal</t>
-        </is>
-      </c>
-      <c r="S380" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T380" t="inlineStr">
@@ -67378,7 +67438,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>128103100</t>
+          <t>128105050</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
@@ -67403,22 +67463,22 @@
       </c>
       <c r="L381" s="2" t="inlineStr">
         <is>
-          <t>50532.0</t>
+          <t>54282.0</t>
         </is>
       </c>
       <c r="M381" s="2" t="inlineStr">
         <is>
-          <t>572220.0</t>
+          <t>408000.0</t>
         </is>
       </c>
       <c r="N381" s="2" t="inlineStr">
         <is>
-          <t>622752.0</t>
+          <t>462282.0</t>
         </is>
       </c>
       <c r="O381" s="2" t="inlineStr">
         <is>
-          <t>622752.0</t>
+          <t>132718.0</t>
         </is>
       </c>
       <c r="R381" s="2" t="inlineStr">
@@ -67455,7 +67515,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>128105060</t>
+          <t>128105040</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
@@ -67471,6 +67531,41 @@
       <c r="H382" t="inlineStr">
         <is>
           <t>collaborator-sheet</t>
+        </is>
+      </c>
+      <c r="K382" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L382" s="2" t="inlineStr">
+        <is>
+          <t>54384.0</t>
+        </is>
+      </c>
+      <c r="M382" s="2" t="inlineStr">
+        <is>
+          <t>397800.0</t>
+        </is>
+      </c>
+      <c r="N382" s="2" t="inlineStr">
+        <is>
+          <t>452184.0</t>
+        </is>
+      </c>
+      <c r="O382" s="2" t="inlineStr">
+        <is>
+          <t>452184.0</t>
+        </is>
+      </c>
+      <c r="R382" s="2" t="inlineStr">
+        <is>
+          <t>solano-county-portal</t>
+        </is>
+      </c>
+      <c r="S382" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T382" t="inlineStr">
@@ -67497,7 +67592,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>128105050</t>
+          <t>128105030</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
@@ -67522,22 +67617,22 @@
       </c>
       <c r="L383" s="2" t="inlineStr">
         <is>
-          <t>54282.0</t>
+          <t>13574.0</t>
         </is>
       </c>
       <c r="M383" s="2" t="inlineStr">
         <is>
-          <t>408000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N383" s="2" t="inlineStr">
         <is>
-          <t>462282.0</t>
+          <t>13574.0</t>
         </is>
       </c>
       <c r="O383" s="2" t="inlineStr">
         <is>
-          <t>132718.0</t>
+          <t>3743.0</t>
         </is>
       </c>
       <c r="R383" s="2" t="inlineStr">
@@ -67574,7 +67669,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>128105040</t>
+          <t>128105020</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -67599,7 +67694,7 @@
       </c>
       <c r="L384" s="2" t="inlineStr">
         <is>
-          <t>54384.0</t>
+          <t>54364.0</t>
         </is>
       </c>
       <c r="M384" s="2" t="inlineStr">
@@ -67609,12 +67704,12 @@
       </c>
       <c r="N384" s="2" t="inlineStr">
         <is>
-          <t>452184.0</t>
+          <t>452164.0</t>
         </is>
       </c>
       <c r="O384" s="2" t="inlineStr">
         <is>
-          <t>452184.0</t>
+          <t>161808.0</t>
         </is>
       </c>
       <c r="R384" s="2" t="inlineStr">
@@ -67651,7 +67746,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>128105030</t>
+          <t>128105010</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -67676,22 +67771,22 @@
       </c>
       <c r="L385" s="2" t="inlineStr">
         <is>
-          <t>13574.0</t>
+          <t>54554.0</t>
         </is>
       </c>
       <c r="M385" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>408000.0</t>
         </is>
       </c>
       <c r="N385" s="2" t="inlineStr">
         <is>
-          <t>13574.0</t>
+          <t>462554.0</t>
         </is>
       </c>
       <c r="O385" s="2" t="inlineStr">
         <is>
-          <t>3743.0</t>
+          <t>132793.0</t>
         </is>
       </c>
       <c r="R385" s="2" t="inlineStr">
@@ -67728,7 +67823,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>128105020</t>
+          <t>128104020</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
@@ -67753,22 +67848,22 @@
       </c>
       <c r="L386" s="2" t="inlineStr">
         <is>
-          <t>54364.0</t>
+          <t>98534.0</t>
         </is>
       </c>
       <c r="M386" s="2" t="inlineStr">
         <is>
-          <t>397800.0</t>
+          <t>572220.0</t>
         </is>
       </c>
       <c r="N386" s="2" t="inlineStr">
         <is>
-          <t>452164.0</t>
+          <t>670754.0</t>
         </is>
       </c>
       <c r="O386" s="2" t="inlineStr">
         <is>
-          <t>161808.0</t>
+          <t>362111.0</t>
         </is>
       </c>
       <c r="R386" s="2" t="inlineStr">
@@ -67805,7 +67900,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>128105010</t>
+          <t>128104010</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
@@ -67830,22 +67925,22 @@
       </c>
       <c r="L387" s="2" t="inlineStr">
         <is>
-          <t>54554.0</t>
+          <t>61611.0</t>
         </is>
       </c>
       <c r="M387" s="2" t="inlineStr">
         <is>
-          <t>408000.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N387" s="2" t="inlineStr">
         <is>
-          <t>462554.0</t>
+          <t>61611.0</t>
         </is>
       </c>
       <c r="O387" s="2" t="inlineStr">
         <is>
-          <t>132793.0</t>
+          <t>24570.0</t>
         </is>
       </c>
       <c r="R387" s="2" t="inlineStr">
@@ -67867,7 +67962,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>225</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -67877,17 +67972,22 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Montessa Apartments</t>
+          <t>Bennington Apartments</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>128104020</t>
+          <t>168150010</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>0168-150-010</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>343 MOON RIVER PL VACAVILLE CA 95687</t>
+          <t>2780 NORTH TEXAS STREET FAIRFIELD</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
@@ -67897,7 +67997,12 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>Single Real Property parcel at the project situs per Solano assessor portal search 2026-08-22 (other hits are business accounts)</t>
         </is>
       </c>
       <c r="K388" s="2" t="inlineStr">
@@ -67907,22 +68012,22 @@
       </c>
       <c r="L388" s="2" t="inlineStr">
         <is>
-          <t>98534.0</t>
+          <t>5338692.0</t>
         </is>
       </c>
       <c r="M388" s="2" t="inlineStr">
         <is>
-          <t>572220.0</t>
+          <t>23942991.0</t>
         </is>
       </c>
       <c r="N388" s="2" t="inlineStr">
         <is>
-          <t>670754.0</t>
+          <t>29281683.0</t>
         </is>
       </c>
       <c r="O388" s="2" t="inlineStr">
         <is>
-          <t>362111.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="R388" s="2" t="inlineStr">
@@ -67937,34 +68042,39 @@
       </c>
       <c r="T388" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>225</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Solano</t>
+          <t>Sonoma</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Montessa Apartments</t>
+          <t>Citrine Apartments</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>128104010</t>
+          <t>89082034000</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>089-082-034-000</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>343 MOON RIVER PL VACAVILLE CA 95687</t>
+          <t>1260 GROVE ST HEALDSBURG CA 95448-4784</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
@@ -67977,76 +68087,51 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="K389" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="L389" s="2" t="inlineStr">
-        <is>
-          <t>61611.0</t>
-        </is>
-      </c>
-      <c r="M389" s="2" t="inlineStr">
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>10140095</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N389" s="2" t="inlineStr">
-        <is>
-          <t>61611.0</t>
-        </is>
-      </c>
-      <c r="O389" s="2" t="inlineStr">
-        <is>
-          <t>24570.0</t>
-        </is>
-      </c>
-      <c r="R389" s="2" t="inlineStr">
-        <is>
-          <t>solano-county-portal</t>
-        </is>
-      </c>
-      <c r="S389" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
+      <c r="R389" t="inlineStr">
+        <is>
+          <t>collaborator-sheet</t>
         </is>
       </c>
       <c r="T389" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>131</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>230</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Solano</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Bennington Apartments</t>
+          <t>Hansen illage Apartments</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>168150010</t>
-        </is>
-      </c>
-      <c r="E390" t="inlineStr">
-        <is>
-          <t>0168-150-010</t>
+          <t>2530007015</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>2780 NORTH TEXAS STREET FAIRFIELD</t>
+          <t>11821 FOOTHILL BLVD LOS ANGELES CA 91342</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
@@ -68056,12 +68141,17 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>manual-repo-edit</t>
+          <t>script-situs-match (2026-08-21)</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>Single Real Property parcel at the project situs per Solano assessor portal search 2026-08-22 (other hits are business accounts)</t>
+          <t>Resolved by LA county situs/geocode search; two parcels share situs 11821 Foothill — multi-parcel</t>
         </is>
       </c>
       <c r="K390" s="2" t="inlineStr">
@@ -68071,27 +68161,37 @@
       </c>
       <c r="L390" s="2" t="inlineStr">
         <is>
-          <t>5338692.0</t>
+          <t>942311</t>
         </is>
       </c>
       <c r="M390" s="2" t="inlineStr">
         <is>
-          <t>23942991.0</t>
+          <t>822380</t>
         </is>
       </c>
       <c r="N390" s="2" t="inlineStr">
         <is>
-          <t>29281683.0</t>
+          <t>1764691</t>
         </is>
       </c>
       <c r="O390" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P390" s="2" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="Q390" s="2" t="inlineStr">
+        <is>
+          <t>Five or more apartments</t>
         </is>
       </c>
       <c r="R390" s="2" t="inlineStr">
         <is>
-          <t>solano-county-portal</t>
+          <t>la-county-api</t>
         </is>
       </c>
       <c r="S390" s="2" t="inlineStr">
@@ -68101,39 +68201,39 @@
       </c>
       <c r="T390" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>230</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>369</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Sonoma</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Citrine Apartments</t>
+          <t>Verdana Apartments</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>89082034000</t>
+          <t>4441201300</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>089-082-034-000</t>
+          <t>444-120-13-00</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>1260 GROVE ST HEALDSBURG CA 95448-4784</t>
+          <t>438 CAMINO DEL RIO S SAN DIEGO CA 92108</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
@@ -68143,54 +68243,94 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
-        </is>
-      </c>
-      <c r="N391" t="inlineStr">
-        <is>
-          <t>10140095</t>
-        </is>
-      </c>
-      <c r="O391" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R391" t="inlineStr">
-        <is>
-          <t>collaborator-sheet</t>
+          <t>script-situs-match (2026-08-22)</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>situs-match</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>Exact situs match, SANDAG; pre-development parcels per staff report address</t>
+        </is>
+      </c>
+      <c r="K391" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L391" s="2" t="inlineStr">
+        <is>
+          <t>2427182</t>
+        </is>
+      </c>
+      <c r="M391" s="2" t="inlineStr">
+        <is>
+          <t>1490976</t>
+        </is>
+      </c>
+      <c r="N391" s="2" t="inlineStr">
+        <is>
+          <t>3918158</t>
+        </is>
+      </c>
+      <c r="P391" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="Q391" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R391" s="2" t="inlineStr">
+        <is>
+          <t>sandag-parcels</t>
+        </is>
+      </c>
+      <c r="S391" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="T391" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>369</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>369</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Hansen illage Apartments</t>
+          <t>Verdana Apartments</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2530007015</t>
+          <t>4441201800</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>444-120-18-00</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>11821 FOOTHILL BLVD LOS ANGELES CA 91342</t>
+          <t>480 CAMINO DEL RIO S SAN DIEGO CA 92108</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
@@ -68200,7 +68340,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>script-situs-match (2026-08-21)</t>
+          <t>script-situs-match (2026-08-22)</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -68210,7 +68350,7 @@
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>Resolved by LA county situs/geocode search; two parcels share situs 11821 Foothill — multi-parcel</t>
+          <t>Exact situs match, SANDAG; pre-development parcels per staff report address</t>
         </is>
       </c>
       <c r="K392" s="2" t="inlineStr">
@@ -68220,37 +68360,32 @@
       </c>
       <c r="L392" s="2" t="inlineStr">
         <is>
-          <t>942311</t>
+          <t>1884643</t>
         </is>
       </c>
       <c r="M392" s="2" t="inlineStr">
         <is>
-          <t>822380</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N392" s="2" t="inlineStr">
         <is>
-          <t>1764691</t>
-        </is>
-      </c>
-      <c r="O392" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>1884643</t>
         </is>
       </c>
       <c r="P392" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t xml:space="preserve">  </t>
         </is>
       </c>
       <c r="Q392" s="2" t="inlineStr">
         <is>
-          <t>Five or more apartments</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R392" s="2" t="inlineStr">
         <is>
-          <t>la-county-api</t>
+          <t>sandag-parcels</t>
         </is>
       </c>
       <c r="S392" s="2" t="inlineStr">
@@ -68260,39 +68395,39 @@
       </c>
       <c r="T392" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>369</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>238</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Alameda</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Verdana Apartments</t>
+          <t>Heritage Park Apartments Livermore</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>4441201300</t>
+          <t>9917523</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>444-120-13-00</t>
+          <t>99-175-23</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>438 CAMINO DEL RIO S SAN DIEGO CA 92108</t>
+          <t>900 E STANLEY BLVD LIVERMORE CA 94550</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
@@ -68302,229 +68437,35 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>script-situs-match (2026-08-22)</t>
-        </is>
-      </c>
-      <c r="I393" t="inlineStr">
-        <is>
-          <t>situs-match</t>
+          <t>manual-repo-edit</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>Exact situs match, SANDAG; pre-development parcels per staff report address</t>
-        </is>
-      </c>
-      <c r="K393" s="2" t="inlineStr">
+          <t>Drew 2026-08-22 via Alameda assessor lookup</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="L393" s="2" t="inlineStr">
-        <is>
-          <t>2427182</t>
-        </is>
-      </c>
-      <c r="M393" s="2" t="inlineStr">
-        <is>
-          <t>1490976</t>
-        </is>
-      </c>
-      <c r="N393" s="2" t="inlineStr">
-        <is>
-          <t>3918158</t>
-        </is>
-      </c>
-      <c r="P393" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="Q393" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R393" s="2" t="inlineStr">
-        <is>
-          <t>sandag-parcels</t>
-        </is>
-      </c>
-      <c r="S393" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>47387387</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>19523603</t>
+        </is>
+      </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>manual-repo-edit</t>
         </is>
       </c>
       <c r="T393" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>San Diego</t>
-        </is>
-      </c>
-      <c r="C394" t="inlineStr">
-        <is>
-          <t>Verdana Apartments</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>4441201800</t>
-        </is>
-      </c>
-      <c r="E394" t="inlineStr">
-        <is>
-          <t>444-120-18-00</t>
-        </is>
-      </c>
-      <c r="F394" t="inlineStr">
-        <is>
-          <t>480 CAMINO DEL RIO S SAN DIEGO CA 92108</t>
-        </is>
-      </c>
-      <c r="G394" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H394" t="inlineStr">
-        <is>
-          <t>script-situs-match (2026-08-22)</t>
-        </is>
-      </c>
-      <c r="I394" t="inlineStr">
-        <is>
-          <t>situs-match</t>
-        </is>
-      </c>
-      <c r="J394" t="inlineStr">
-        <is>
-          <t>Exact situs match, SANDAG; pre-development parcels per staff report address</t>
-        </is>
-      </c>
-      <c r="K394" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="L394" s="2" t="inlineStr">
-        <is>
-          <t>1884643</t>
-        </is>
-      </c>
-      <c r="M394" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N394" s="2" t="inlineStr">
-        <is>
-          <t>1884643</t>
-        </is>
-      </c>
-      <c r="P394" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  </t>
-        </is>
-      </c>
-      <c r="Q394" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R394" s="2" t="inlineStr">
-        <is>
-          <t>sandag-parcels</t>
-        </is>
-      </c>
-      <c r="S394" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="T394" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>Alameda</t>
-        </is>
-      </c>
-      <c r="C395" t="inlineStr">
-        <is>
-          <t>Heritage Park Apartments Livermore</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>9917523</t>
-        </is>
-      </c>
-      <c r="E395" t="inlineStr">
-        <is>
-          <t>99-175-23</t>
-        </is>
-      </c>
-      <c r="F395" t="inlineStr">
-        <is>
-          <t>900 E STANLEY BLVD LIVERMORE CA 94550</t>
-        </is>
-      </c>
-      <c r="G395" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H395" t="inlineStr">
-        <is>
-          <t>manual-repo-edit</t>
-        </is>
-      </c>
-      <c r="J395" t="inlineStr">
-        <is>
-          <t>Drew 2026-08-22 via Alameda assessor lookup</t>
-        </is>
-      </c>
-      <c r="K395" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="N395" t="inlineStr">
-        <is>
-          <t>47387387</t>
-        </is>
-      </c>
-      <c r="O395" t="inlineStr">
-        <is>
-          <t>19523603</t>
-        </is>
-      </c>
-      <c r="R395" t="inlineStr">
-        <is>
-          <t>manual-repo-edit</t>
-        </is>
-      </c>
-      <c r="T395" t="inlineStr">
         <is>
           <t>238</t>
         </is>
@@ -68541,7 +68482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C171"/>
+  <dimension ref="A1:C168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -70954,12 +70895,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>206</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>AIN (none) (Contra Costa): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -70971,7 +70912,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>207</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -70988,7 +70929,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>208</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -71005,12 +70946,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>215</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 5539028040 (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -71022,12 +70963,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>AIN 5539028040 (Los Angeles): no roll values from any source</t>
+          <t>AIN (none) (Contra Costa): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -71039,12 +70980,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>AIN (none) (Contra Costa): no roll values from any source</t>
+          <t>AIN 46745075 (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -71056,12 +70997,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>AIN (none) (San Diego): no roll values from any source</t>
+          <t>AIN 46745074 (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -71078,7 +71019,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>AIN 46745075 (Santa Clara): no roll values from any source</t>
+          <t>AIN 46745073 (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -71090,12 +71031,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>198</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>AIN 46745074 (Santa Clara): no roll values from any source</t>
+          <t>AIN (none) (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -71107,12 +71048,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>AIN 46745073 (Santa Clara): no roll values from any source</t>
+          <t>AIN 128101150 (Solano): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -71124,12 +71065,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>AIN (none) (Santa Clara): no roll values from any source</t>
+          <t>AIN 128101050 (Solano): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -71146,41 +71087,41 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>AIN 128101150 (Solano): no roll values from any source</t>
+          <t>AIN 128105060 (Solano): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>182/76</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>AIN 128101050 (Solano): no roll values from any source</t>
+          <t>AIN 5036031006 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>200/218</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>AIN 128105060 (Solano): no roll values from any source</t>
+          <t>AIN 5040021006 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71192,12 +71133,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>143/147</t>
+          <t>130/179</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>AIN 41416654 assigned to multiple projects</t>
+          <t>AIN 5080006008 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71209,12 +71150,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>182/76</t>
+          <t>126/173</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>AIN 5036031006 assigned to multiple projects</t>
+          <t>AIN 5094005005 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71226,12 +71167,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>200/218</t>
+          <t>127/174</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>AIN 5040021006 assigned to multiple projects</t>
+          <t>AIN 5094006003 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71243,12 +71184,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>130/179</t>
+          <t>122/165</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>AIN 5080006008 assigned to multiple projects</t>
+          <t>AIN 5094017020 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71260,12 +71201,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>126/173</t>
+          <t>124/169</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>AIN 5094005005 assigned to multiple projects</t>
+          <t>AIN 5094023025 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71277,12 +71218,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>127/174</t>
+          <t>128/175</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>AIN 5094006003 assigned to multiple projects</t>
+          <t>AIN 5502019004 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71294,12 +71235,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>122/165</t>
+          <t>125/170</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>AIN 5094017020 assigned to multiple projects</t>
+          <t>AIN 5503024012 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71311,12 +71252,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>124/169</t>
+          <t>129/177</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>AIN 5094023025 assigned to multiple projects</t>
+          <t>AIN 5517005016 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71328,12 +71269,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>128/175</t>
+          <t>121/162</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>AIN 5502019004 assigned to multiple projects</t>
+          <t>AIN 5518013024 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71345,12 +71286,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>125/170</t>
+          <t>123/168</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>AIN 5503024012 assigned to multiple projects</t>
+          <t>AIN 5518020021 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71362,12 +71303,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>129/177</t>
+          <t>135/220</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>AIN 5517005016 assigned to multiple projects</t>
+          <t>AIN 5518026004 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71379,12 +71320,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>121/162</t>
+          <t>10/132</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>AIN 5518013024 assigned to multiple projects</t>
+          <t>AIN 6020022027 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -71396,61 +71337,10 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>123/168</t>
+          <t>152/181</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
-        <is>
-          <t>AIN 5518020021 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>135/220</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>AIN 5518026004 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>10/132</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>AIN 6020022027 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>152/181</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
         <is>
           <t>AIN 7157012017 assigned to multiple projects</t>
         </is>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -63326,6 +63326,31 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>Government-owned common-area parcel (use code 9800, $0 values) — Drew via Solano GIS 2026-08-22</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R326" t="inlineStr">
+        <is>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
       <c r="T326" t="inlineStr">
         <is>
           <t>16</t>
@@ -64061,6 +64086,31 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>Government-owned common-area parcel (use code 9800, Government Owned=YS, no site address, $0 values) — Drew via Solano GIS 2026-08-22</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R336" t="inlineStr">
+        <is>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
       <c r="T336" t="inlineStr">
         <is>
           <t>16</t>
@@ -67412,6 +67462,31 @@
       <c r="H380" t="inlineStr">
         <is>
           <t>collaborator-sheet</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>Government-owned common-area parcel (use code 9800, $0 values) — Drew via Solano GIS 2026-08-22</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>manual-repo-edit</t>
         </is>
       </c>
       <c r="T380" t="inlineStr">
@@ -71043,7 +71118,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -71053,14 +71128,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>AIN 128101150 (Solano): no roll values from any source</t>
+          <t>AIN 128101150 (Solano) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -71070,14 +71145,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>AIN 128101050 (Solano): no roll values from any source</t>
+          <t>AIN 128101050 (Solano) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -71087,7 +71162,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>AIN 128105060 (Solano): no roll values from any source</t>
+          <t>AIN 128105060 (Solano) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -727,7 +727,7 @@
           <t>24</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -774,7 +774,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -901,7 +901,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>built:collaborator-sheet; scc_filed:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>built:collaborator-sheet; scc_filed:collaborator-sheet; investor_1:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
           <t>48</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>manual_status:collaborator-sheet; city:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+          <t>manual_status:collaborator-sheet; city:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
           <t>61</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>61</t>
         </is>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>leasing_link:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>leasing_link:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
           <t>147</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>147</t>
         </is>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1693,7 @@
           <t>227</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>227</t>
         </is>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>investor_2:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>investor_2:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
           <t>166</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>166</t>
         </is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; entity:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
           <t>66</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>investor_2:collaborator-sheet; manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>investor_2:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
           <t>89</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="R15" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>leasing_link:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>leasing_link:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
           <t>69</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>69</t>
         </is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>built:collaborator-sheet; manual_status:collaborator-sheet; entity:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>built:collaborator-sheet; manual_status:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
           <t>169</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; entity:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
           <t>111</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>111</t>
         </is>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
           <t>103</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>102</t>
         </is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>investor_2:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; city:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+          <t>investor_2:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; city:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
           <t>160</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>160</t>
         </is>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>investor_2:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>investor_2:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
           <t>58</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
           <t>52</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
           <t>225</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>225</t>
         </is>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>built:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>built:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
           <t>74</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>74</t>
         </is>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>scc_filed:collaborator-sheet; resolution:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>scc_filed:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3832,7 @@
           <t>93</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>93</t>
         </is>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>built:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>built:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
           <t>52</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; link:collaborator-sheet; scc_filed:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; link:collaborator-sheet; scc_filed:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
           <t>72</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>49</t>
         </is>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>scc_filed:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>scc_filed:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -4228,7 +4228,7 @@
           <t>48</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>scc_filed:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>scc_filed:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>built:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>built:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
           <t>165</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="R33" s="2" t="inlineStr">
         <is>
           <t>98</t>
         </is>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>built:collaborator-sheet; scc_filed:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>built:collaborator-sheet; scc_filed:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
           <t>79</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4868,7 @@
           <t>41</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>scc_filed:collaborator-sheet; city:collaborator-sheet; county:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+          <t>scc_filed:collaborator-sheet; city:collaborator-sheet; county:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -4985,7 +4985,7 @@
           <t>104</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="R36" s="2" t="inlineStr">
         <is>
           <t>104</t>
         </is>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>scc_filed:collaborator-sheet; city:collaborator-sheet; resolution:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+          <t>scc_filed:collaborator-sheet; city:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
           <t>80</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>80</t>
         </is>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>scc_filed:collaborator-sheet; resolution:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>scc_filed:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
           <t>53</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="R38" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
@@ -5272,7 +5272,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; property_name:collaborator-sheet; resolution:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; property_name:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
           <t>236</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="R39" s="2" t="inlineStr">
         <is>
           <t>236</t>
         </is>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
           <t>66</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="R40" s="2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; resolution:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5606,7 @@
           <t>68</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="R41" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; resolution:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
           <t>188</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="R42" s="2" t="inlineStr">
         <is>
           <t>111</t>
         </is>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5855,7 @@
           <t>90</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="R43" s="2" t="inlineStr">
         <is>
           <t>71</t>
         </is>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -5987,7 +5987,7 @@
           <t>99</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="R44" s="2" t="inlineStr">
         <is>
           <t>99</t>
         </is>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -6109,7 +6109,7 @@
           <t>41</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="R45" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; nonprofit_partner:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6241,7 @@
           <t>406</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="R46" s="2" t="inlineStr">
         <is>
           <t>406</t>
         </is>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
           <t>53</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="R47" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
           <t>488</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="R48" s="2" t="inlineStr">
         <is>
           <t>483</t>
         </is>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
           <t>697</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="R49" s="2" t="inlineStr">
         <is>
           <t>697</t>
         </is>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; scc_filed:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; scc_filed:collaborator-sheet; investor_1:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
           <t>162</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="R50" s="2" t="inlineStr">
         <is>
           <t>162</t>
         </is>
@@ -6796,7 +6796,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; property_name:collaborator-sheet; entity:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; property_name:collaborator-sheet; entity:collaborator-sheet; investor_1:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6871,7 @@
           <t>229</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="R51" s="2" t="inlineStr">
         <is>
           <t>229</t>
         </is>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -7008,7 +7008,7 @@
           <t>145</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="R52" s="2" t="inlineStr">
         <is>
           <t>144</t>
         </is>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; manual_status:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; manual_status:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -7140,7 +7140,7 @@
           <t>63</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="R53" s="2" t="inlineStr">
         <is>
           <t>62</t>
         </is>
@@ -7187,7 +7187,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; city:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; city:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -7267,7 +7267,7 @@
           <t>198</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="R54" s="2" t="inlineStr">
         <is>
           <t>198</t>
         </is>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; manual_status:collaborator-sheet; city:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; manual_status:collaborator-sheet; city:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
           <t>356</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="R55" s="2" t="inlineStr">
         <is>
           <t>144</t>
         </is>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; resolution:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; resolution:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -7521,7 +7521,7 @@
           <t>377</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="R56" s="2" t="inlineStr">
         <is>
           <t>151</t>
         </is>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -7648,7 +7648,7 @@
           <t>94</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="R57" s="2" t="inlineStr">
         <is>
           <t>71</t>
         </is>
@@ -7695,7 +7695,7 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>leasing_link:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>leasing_link:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
           <t>193</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="R58" s="2" t="inlineStr">
         <is>
           <t>193</t>
         </is>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; built:collaborator-sheet; acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; link:collaborator-sheet; leasing_link:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; built:collaborator-sheet; acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; link:collaborator-sheet; leasing_link:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -7927,7 +7927,7 @@
           <t>296</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="R59" s="2" t="inlineStr">
         <is>
           <t>296</t>
         </is>
@@ -7979,7 +7979,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
           <t>193</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="R60" s="2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -8106,7 +8106,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; city:collaborator-sheet; resolution:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; city:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
           <t>196</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="R61" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; entity:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; entity:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -8415,7 +8415,7 @@
           <t>116</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="R63" s="2" t="inlineStr">
         <is>
           <t>115</t>
         </is>
@@ -8467,7 +8467,7 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="R64" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
@@ -8584,7 +8584,7 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>scc_filed:collaborator-sheet; resolution:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+          <t>scc_filed:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8766,7 @@
           <t>272</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="R66" s="2" t="inlineStr">
         <is>
           <t>270</t>
         </is>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -8903,7 +8903,7 @@
           <t>13</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="R67" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -8945,7 +8945,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -9020,7 +9020,7 @@
           <t>169</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="R68" s="2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
@@ -9067,7 +9067,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -9142,7 +9142,7 @@
           <t>189</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="R69" s="2" t="inlineStr">
         <is>
           <t>189</t>
         </is>
@@ -9199,7 +9199,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -9279,7 +9279,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="R70" s="2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -9401,6 +9401,11 @@
           <t>122</t>
         </is>
       </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
           <t>20% at 60% AMI; 80% at 80% AMI</t>
@@ -9772,7 +9777,7 @@
           <t>189</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="R74" s="2" t="inlineStr">
         <is>
           <t>148</t>
         </is>
@@ -9824,7 +9829,7 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10036,7 @@
           <t>203</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="R76" s="2" t="inlineStr">
         <is>
           <t>203</t>
         </is>
@@ -10078,7 +10083,7 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10158,7 @@
           <t>50</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="R77" s="2" t="inlineStr">
         <is>
           <t>49</t>
         </is>
@@ -10200,7 +10205,7 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; entity:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -10275,7 +10280,7 @@
           <t>84</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="R78" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -10322,7 +10327,7 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10539,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr">
+      <c r="R80" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
@@ -10581,7 +10586,7 @@
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; entity:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10661,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="R81" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
@@ -10703,7 +10708,7 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -10900,7 +10905,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="R83" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
@@ -10947,7 +10952,7 @@
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11027,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="R84" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -11069,7 +11074,7 @@
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11149,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="R85" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -11191,7 +11196,7 @@
       </c>
       <c r="AH85" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -11266,7 +11271,7 @@
           <t>48</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="R86" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
@@ -11313,7 +11318,7 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; entity:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -11388,7 +11393,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="R87" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -11435,7 +11440,7 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; entity:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11520,7 @@
           <t>687</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr">
+      <c r="R88" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
@@ -11567,7 +11572,7 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; scc_filed:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; scc_filed:collaborator-sheet; investor_1:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -11642,7 +11647,7 @@
           <t>69</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr">
+      <c r="R89" s="2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
@@ -11689,7 +11694,7 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -11764,7 +11769,7 @@
           <t>230</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr">
+      <c r="R90" s="2" t="inlineStr">
         <is>
           <t>230</t>
         </is>
@@ -11811,7 +11816,7 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>acquisition_date:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>acquisition_date:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -11886,7 +11891,7 @@
           <t>84</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr">
+      <c r="R91" s="2" t="inlineStr">
         <is>
           <t>84</t>
         </is>
@@ -11933,7 +11938,7 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -12008,7 +12013,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr">
+      <c r="R92" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -12055,7 +12060,7 @@
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12135,7 @@
           <t>177</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr">
+      <c r="R93" s="2" t="inlineStr">
         <is>
           <t>177</t>
         </is>
@@ -12182,7 +12187,7 @@
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -12252,7 +12257,7 @@
           <t>148</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr">
+      <c r="R94" s="2" t="inlineStr">
         <is>
           <t>148</t>
         </is>
@@ -12299,7 +12304,7 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; resolution:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; resolution:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -12374,7 +12379,7 @@
           <t>183</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr">
+      <c r="R95" s="2" t="inlineStr">
         <is>
           <t>183</t>
         </is>
@@ -12431,7 +12436,7 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -12506,7 +12511,7 @@
           <t>164</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr">
+      <c r="R96" s="2" t="inlineStr">
         <is>
           <t>164</t>
         </is>
@@ -12563,7 +12568,7 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>investor_2:collaborator-sheet; acquisition_date:collaborator-sheet; link:collaborator-sheet; scc_filed:collaborator-sheet; resolution:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>investor_2:collaborator-sheet; acquisition_date:collaborator-sheet; link:collaborator-sheet; scc_filed:collaborator-sheet; resolution:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -12643,7 +12648,7 @@
           <t>948</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr">
+      <c r="R97" s="2" t="inlineStr">
         <is>
           <t>948</t>
         </is>
@@ -12705,7 +12710,7 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>investor_2:collaborator-sheet; built:collaborator-sheet; acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>investor_2:collaborator-sheet; built:collaborator-sheet; acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -12780,7 +12785,7 @@
           <t>112</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr">
+      <c r="R98" s="2" t="inlineStr">
         <is>
           <t>112</t>
         </is>
@@ -12827,7 +12832,7 @@
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -12907,7 +12912,7 @@
           <t>192</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr">
+      <c r="R99" s="2" t="inlineStr">
         <is>
           <t>192</t>
         </is>
@@ -12959,7 +12964,7 @@
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; leasing_link:collaborator-sheet; manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; leasing_link:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -13161,7 +13166,7 @@
           <t>72</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr">
+      <c r="R101" s="2" t="inlineStr">
         <is>
           <t>71</t>
         </is>
@@ -13213,7 +13218,7 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -13288,7 +13293,7 @@
           <t>73</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr">
+      <c r="R102" s="2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
@@ -13340,7 +13345,7 @@
       </c>
       <c r="AH102" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -13415,7 +13420,7 @@
           <t>53</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr">
+      <c r="R103" s="2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
@@ -13467,7 +13472,7 @@
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -13542,7 +13547,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr">
+      <c r="R104" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -13589,7 +13594,7 @@
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -13664,7 +13669,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr">
+      <c r="R105" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -13711,7 +13716,7 @@
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -13786,7 +13791,7 @@
           <t>49</t>
         </is>
       </c>
-      <c r="R106" t="inlineStr">
+      <c r="R106" s="2" t="inlineStr">
         <is>
           <t>49</t>
         </is>
@@ -13833,7 +13838,7 @@
       </c>
       <c r="AH106" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -13908,7 +13913,7 @@
           <t>48</t>
         </is>
       </c>
-      <c r="R107" t="inlineStr">
+      <c r="R107" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -13955,7 +13960,7 @@
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -14030,7 +14035,7 @@
           <t>43</t>
         </is>
       </c>
-      <c r="R108" t="inlineStr">
+      <c r="R108" s="2" t="inlineStr">
         <is>
           <t>43</t>
         </is>
@@ -14077,7 +14082,7 @@
       </c>
       <c r="AH108" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14157,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr">
+      <c r="R109" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
@@ -14199,7 +14204,7 @@
       </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -14274,7 +14279,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="R110" t="inlineStr">
+      <c r="R110" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
@@ -14321,7 +14326,7 @@
       </c>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -14630,7 +14635,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="R113" t="inlineStr">
+      <c r="R113" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -14677,7 +14682,7 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -14752,7 +14757,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr">
+      <c r="R114" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
@@ -14799,7 +14804,7 @@
       </c>
       <c r="AH114" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14879,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="R115" t="inlineStr">
+      <c r="R115" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -14921,7 +14926,7 @@
       </c>
       <c r="AH115" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -14996,7 +15001,7 @@
           <t>60</t>
         </is>
       </c>
-      <c r="R116" t="inlineStr">
+      <c r="R116" s="2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -15043,7 +15048,7 @@
       </c>
       <c r="AH116" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -15118,7 +15123,7 @@
           <t>73</t>
         </is>
       </c>
-      <c r="R117" t="inlineStr">
+      <c r="R117" s="2" t="inlineStr">
         <is>
           <t>73</t>
         </is>
@@ -15165,7 +15170,7 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -15240,7 +15245,7 @@
           <t>55</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr">
+      <c r="R118" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
@@ -15287,7 +15292,7 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -15362,7 +15367,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr">
+      <c r="R119" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -15409,7 +15414,7 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -15596,7 +15601,7 @@
           <t>272</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr">
+      <c r="R121" s="2" t="inlineStr">
         <is>
           <t>272</t>
         </is>
@@ -15648,7 +15653,7 @@
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; city:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; city:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -15845,7 +15850,7 @@
           <t>39</t>
         </is>
       </c>
-      <c r="R123" t="inlineStr">
+      <c r="R123" s="2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
@@ -15892,7 +15897,7 @@
       </c>
       <c r="AH123" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -15972,7 +15977,7 @@
           <t>48</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr">
+      <c r="R124" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -16019,7 +16024,7 @@
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -16099,7 +16104,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="R125" t="inlineStr">
+      <c r="R125" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -16146,7 +16151,7 @@
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -16226,7 +16231,7 @@
           <t>45</t>
         </is>
       </c>
-      <c r="R126" t="inlineStr">
+      <c r="R126" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
@@ -16273,7 +16278,7 @@
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; property_name:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; property_name:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -16353,7 +16358,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr">
+      <c r="R127" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -16400,7 +16405,7 @@
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -16480,7 +16485,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="R128" t="inlineStr">
+      <c r="R128" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -16527,7 +16532,7 @@
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -16607,7 +16612,7 @@
           <t>48</t>
         </is>
       </c>
-      <c r="R129" t="inlineStr">
+      <c r="R129" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -16654,7 +16659,7 @@
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -16734,7 +16739,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="R130" t="inlineStr">
+      <c r="R130" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
@@ -16781,7 +16786,7 @@
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -16861,7 +16866,7 @@
           <t>76</t>
         </is>
       </c>
-      <c r="R131" t="inlineStr">
+      <c r="R131" s="2" t="inlineStr">
         <is>
           <t>76</t>
         </is>
@@ -16908,7 +16913,7 @@
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -16983,7 +16988,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="R132" t="inlineStr">
+      <c r="R132" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -17030,7 +17035,7 @@
       </c>
       <c r="AH132" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -17105,7 +17110,7 @@
           <t>79</t>
         </is>
       </c>
-      <c r="R133" t="inlineStr">
+      <c r="R133" s="2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
@@ -17147,7 +17152,7 @@
       </c>
       <c r="AH133" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -17222,7 +17227,7 @@
           <t>68</t>
         </is>
       </c>
-      <c r="R134" t="inlineStr">
+      <c r="R134" s="2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
@@ -17269,7 +17274,7 @@
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -17349,7 +17354,7 @@
           <t>52</t>
         </is>
       </c>
-      <c r="R135" t="inlineStr">
+      <c r="R135" s="2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
@@ -17396,7 +17401,7 @@
       </c>
       <c r="AH135" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -17573,7 +17578,7 @@
           <t>41</t>
         </is>
       </c>
-      <c r="R137" t="inlineStr">
+      <c r="R137" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
@@ -17620,7 +17625,7 @@
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -17695,7 +17700,7 @@
           <t>114</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr">
+      <c r="R138" s="2" t="inlineStr">
         <is>
           <t>114</t>
         </is>
@@ -17747,7 +17752,7 @@
       </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; city:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; city:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -17822,7 +17827,7 @@
           <t>286</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr">
+      <c r="R139" s="2" t="inlineStr">
         <is>
           <t>286</t>
         </is>
@@ -17869,7 +17874,7 @@
       </c>
       <c r="AH139" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; nonprofit_partner:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17949,7 @@
           <t>148</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr">
+      <c r="R140" s="2" t="inlineStr">
         <is>
           <t>148</t>
         </is>
@@ -17991,7 +17996,7 @@
       </c>
       <c r="AH140" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -18061,7 +18066,7 @@
           <t>278</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr">
+      <c r="R141" s="2" t="inlineStr">
         <is>
           <t>278</t>
         </is>
@@ -18113,7 +18118,7 @@
       </c>
       <c r="AH141" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -18183,7 +18188,7 @@
           <t>116</t>
         </is>
       </c>
-      <c r="R142" t="inlineStr">
+      <c r="R142" s="2" t="inlineStr">
         <is>
           <t>116</t>
         </is>
@@ -18225,7 +18230,7 @@
       </c>
       <c r="AH142" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -18427,7 +18432,7 @@
           <t>460</t>
         </is>
       </c>
-      <c r="R144" t="inlineStr">
+      <c r="R144" s="2" t="inlineStr">
         <is>
           <t>460</t>
         </is>
@@ -18474,7 +18479,7 @@
       </c>
       <c r="AH144" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; property_name:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; property_name:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18549,7 @@
           <t>110</t>
         </is>
       </c>
-      <c r="R145" t="inlineStr">
+      <c r="R145" s="2" t="inlineStr">
         <is>
           <t>110</t>
         </is>
@@ -18591,7 +18596,7 @@
       </c>
       <c r="AH145" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -18925,7 +18930,7 @@
           <t>170</t>
         </is>
       </c>
-      <c r="R148" t="inlineStr">
+      <c r="R148" s="2" t="inlineStr">
         <is>
           <t>170</t>
         </is>
@@ -18977,7 +18982,7 @@
       </c>
       <c r="AH148" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -19057,7 +19062,7 @@
           <t>61</t>
         </is>
       </c>
-      <c r="R149" t="inlineStr">
+      <c r="R149" s="2" t="inlineStr">
         <is>
           <t>61</t>
         </is>
@@ -19104,7 +19109,7 @@
       </c>
       <c r="AH149" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -19184,7 +19189,7 @@
           <t>181</t>
         </is>
       </c>
-      <c r="R150" t="inlineStr">
+      <c r="R150" s="2" t="inlineStr">
         <is>
           <t>181</t>
         </is>
@@ -19231,7 +19236,7 @@
       </c>
       <c r="AH150" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; property_name:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; property_name:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -19311,7 +19316,7 @@
           <t>74</t>
         </is>
       </c>
-      <c r="R151" t="inlineStr">
+      <c r="R151" s="2" t="inlineStr">
         <is>
           <t>74</t>
         </is>
@@ -19358,7 +19363,7 @@
       </c>
       <c r="AH151" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; property_name:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; property_name:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -19433,7 +19438,7 @@
           <t>152</t>
         </is>
       </c>
-      <c r="R152" t="inlineStr">
+      <c r="R152" s="2" t="inlineStr">
         <is>
           <t>152</t>
         </is>
@@ -19480,7 +19485,7 @@
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -19555,7 +19560,7 @@
           <t>101</t>
         </is>
       </c>
-      <c r="R153" t="inlineStr">
+      <c r="R153" s="2" t="inlineStr">
         <is>
           <t>101</t>
         </is>
@@ -19607,7 +19612,7 @@
       </c>
       <c r="AH153" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -19682,7 +19687,7 @@
           <t>482</t>
         </is>
       </c>
-      <c r="R154" t="inlineStr">
+      <c r="R154" s="2" t="inlineStr">
         <is>
           <t>216</t>
         </is>
@@ -19729,7 +19734,7 @@
       </c>
       <c r="AH154" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -19804,7 +19809,7 @@
           <t>120</t>
         </is>
       </c>
-      <c r="R155" t="inlineStr">
+      <c r="R155" s="2" t="inlineStr">
         <is>
           <t>120</t>
         </is>
@@ -19856,7 +19861,7 @@
       </c>
       <c r="AH155" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; entity:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -19931,7 +19936,7 @@
           <t>170</t>
         </is>
       </c>
-      <c r="R156" t="inlineStr">
+      <c r="R156" s="2" t="inlineStr">
         <is>
           <t>170</t>
         </is>
@@ -19983,7 +19988,7 @@
       </c>
       <c r="AH156" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; entity:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -20150,7 +20155,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="R158" t="inlineStr">
+      <c r="R158" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
@@ -20192,7 +20197,7 @@
       </c>
       <c r="AH158" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; total_units:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -20267,7 +20272,7 @@
           <t>290</t>
         </is>
       </c>
-      <c r="R159" t="inlineStr">
+      <c r="R159" s="2" t="inlineStr">
         <is>
           <t>290</t>
         </is>
@@ -20309,7 +20314,7 @@
       </c>
       <c r="AH159" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -20389,7 +20394,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="R160" t="inlineStr">
+      <c r="R160" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -20436,7 +20441,7 @@
       </c>
       <c r="AH160" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -20511,7 +20516,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="R161" t="inlineStr">
+      <c r="R161" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -20553,7 +20558,7 @@
       </c>
       <c r="AH161" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -20735,7 +20740,7 @@
           <t>67</t>
         </is>
       </c>
-      <c r="R163" t="inlineStr">
+      <c r="R163" s="2" t="inlineStr">
         <is>
           <t>67</t>
         </is>
@@ -20777,7 +20782,7 @@
       </c>
       <c r="AH163" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -20852,7 +20857,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="R164" t="inlineStr">
+      <c r="R164" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -20894,7 +20899,7 @@
       </c>
       <c r="AH164" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -20969,7 +20974,7 @@
           <t>39</t>
         </is>
       </c>
-      <c r="R165" t="inlineStr">
+      <c r="R165" s="2" t="inlineStr">
         <is>
           <t>39</t>
         </is>
@@ -21011,7 +21016,7 @@
       </c>
       <c r="AH165" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -21086,7 +21091,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="R166" t="inlineStr">
+      <c r="R166" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -21128,7 +21133,7 @@
       </c>
       <c r="AH166" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -21203,7 +21208,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="R167" t="inlineStr">
+      <c r="R167" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
@@ -21245,7 +21250,7 @@
       </c>
       <c r="AH167" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -21320,7 +21325,7 @@
           <t>48</t>
         </is>
       </c>
-      <c r="R168" t="inlineStr">
+      <c r="R168" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -21362,7 +21367,7 @@
       </c>
       <c r="AH168" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -21437,7 +21442,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="R169" t="inlineStr">
+      <c r="R169" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -21479,7 +21484,7 @@
       </c>
       <c r="AH169" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -21554,7 +21559,7 @@
           <t>45</t>
         </is>
       </c>
-      <c r="R170" t="inlineStr">
+      <c r="R170" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
@@ -21596,7 +21601,7 @@
       </c>
       <c r="AH170" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -21671,7 +21676,7 @@
           <t>42</t>
         </is>
       </c>
-      <c r="R171" t="inlineStr">
+      <c r="R171" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
@@ -21713,7 +21718,7 @@
       </c>
       <c r="AH171" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+          <t>address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -21895,7 +21900,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="R173" t="inlineStr">
+      <c r="R173" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -21937,7 +21942,7 @@
       </c>
       <c r="AH173" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -22012,7 +22017,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="R174" t="inlineStr">
+      <c r="R174" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
@@ -22054,7 +22059,7 @@
       </c>
       <c r="AH174" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -22129,7 +22134,7 @@
           <t>48</t>
         </is>
       </c>
-      <c r="R175" t="inlineStr">
+      <c r="R175" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
@@ -22171,7 +22176,7 @@
       </c>
       <c r="AH175" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -22246,7 +22251,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="R176" t="inlineStr">
+      <c r="R176" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
@@ -22288,7 +22293,7 @@
       </c>
       <c r="AH176" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -22363,7 +22368,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="R177" t="inlineStr">
+      <c r="R177" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
@@ -22405,7 +22410,7 @@
       </c>
       <c r="AH177" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -22480,7 +22485,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="R178" t="inlineStr">
+      <c r="R178" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
@@ -22522,7 +22527,7 @@
       </c>
       <c r="AH178" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -22597,7 +22602,7 @@
           <t>76</t>
         </is>
       </c>
-      <c r="R179" t="inlineStr">
+      <c r="R179" s="2" t="inlineStr">
         <is>
           <t>76</t>
         </is>
@@ -22639,7 +22644,7 @@
       </c>
       <c r="AH179" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -22826,7 +22831,7 @@
           <t>152</t>
         </is>
       </c>
-      <c r="R181" t="inlineStr">
+      <c r="R181" s="2" t="inlineStr">
         <is>
           <t>152</t>
         </is>
@@ -22868,7 +22873,7 @@
       </c>
       <c r="AH181" t="inlineStr">
         <is>
-          <t>manual_status:collaborator-sheet; city:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>manual_status:collaborator-sheet; city:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -23080,7 +23085,7 @@
           <t>70</t>
         </is>
       </c>
-      <c r="R183" t="inlineStr">
+      <c r="R183" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
@@ -23122,7 +23127,7 @@
       </c>
       <c r="AH183" t="inlineStr">
         <is>
-          <t>manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23202,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="R184" t="inlineStr">
+      <c r="R184" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -23244,7 +23249,7 @@
       </c>
       <c r="AH184" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -23319,7 +23324,7 @@
           <t>39</t>
         </is>
       </c>
-      <c r="R185" t="inlineStr">
+      <c r="R185" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -23366,7 +23371,7 @@
       </c>
       <c r="AH185" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -23441,7 +23446,7 @@
           <t>70</t>
         </is>
       </c>
-      <c r="R186" t="inlineStr">
+      <c r="R186" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -23488,7 +23493,7 @@
       </c>
       <c r="AH186" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -23563,7 +23568,7 @@
           <t>232</t>
         </is>
       </c>
-      <c r="R187" t="inlineStr">
+      <c r="R187" s="2" t="inlineStr">
         <is>
           <t>232</t>
         </is>
@@ -23610,7 +23615,7 @@
       </c>
       <c r="AH187" t="inlineStr">
         <is>
-          <t>built:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -23680,7 +23685,7 @@
           <t>135</t>
         </is>
       </c>
-      <c r="R188" t="inlineStr">
+      <c r="R188" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
@@ -23722,7 +23727,7 @@
       </c>
       <c r="AH188" t="inlineStr">
         <is>
-          <t>manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -23792,7 +23797,7 @@
           <t>221</t>
         </is>
       </c>
-      <c r="R189" t="inlineStr">
+      <c r="R189" s="2" t="inlineStr">
         <is>
           <t>221</t>
         </is>
@@ -23844,7 +23849,7 @@
       </c>
       <c r="AH189" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -23919,7 +23924,7 @@
           <t>293</t>
         </is>
       </c>
-      <c r="R190" t="inlineStr">
+      <c r="R190" s="2" t="inlineStr">
         <is>
           <t>102</t>
         </is>
@@ -23966,7 +23971,7 @@
       </c>
       <c r="AH190" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; entity:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -24332,7 +24337,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="R194" t="inlineStr">
+      <c r="R194" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
@@ -24379,7 +24384,7 @@
       </c>
       <c r="AH194" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -24454,7 +24459,7 @@
           <t>41</t>
         </is>
       </c>
-      <c r="R195" t="inlineStr">
+      <c r="R195" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
@@ -24501,7 +24506,7 @@
       </c>
       <c r="AH195" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -24683,7 +24688,7 @@
           <t>100</t>
         </is>
       </c>
-      <c r="R197" t="inlineStr">
+      <c r="R197" s="2" t="inlineStr">
         <is>
           <t>100</t>
         </is>
@@ -24730,7 +24735,7 @@
       </c>
       <c r="AH197" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -24795,7 +24800,7 @@
           <t>264</t>
         </is>
       </c>
-      <c r="R198" t="inlineStr">
+      <c r="R198" s="2" t="inlineStr">
         <is>
           <t>264</t>
         </is>
@@ -24842,7 +24847,7 @@
       </c>
       <c r="AH198" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -24917,7 +24922,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="R199" t="inlineStr">
+      <c r="R199" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
@@ -24959,7 +24964,7 @@
       </c>
       <c r="AH199" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; city_cut:collaborator-sheet; address:manual-repo-edit</t>
+          <t>city_cut:collaborator-sheet; address:manual-repo-edit</t>
         </is>
       </c>
     </row>
@@ -25029,7 +25034,7 @@
           <t>70</t>
         </is>
       </c>
-      <c r="R200" t="inlineStr">
+      <c r="R200" s="2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
@@ -25071,7 +25076,7 @@
       </c>
       <c r="AH200" t="inlineStr">
         <is>
-          <t>resolution:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>resolution:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -25151,7 +25156,7 @@
           <t>197</t>
         </is>
       </c>
-      <c r="R201" t="inlineStr">
+      <c r="R201" s="2" t="inlineStr">
         <is>
           <t>80</t>
         </is>
@@ -25193,7 +25198,7 @@
       </c>
       <c r="AH201" t="inlineStr">
         <is>
-          <t>manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -25268,7 +25273,7 @@
           <t>150</t>
         </is>
       </c>
-      <c r="R202" t="inlineStr">
+      <c r="R202" s="2" t="inlineStr">
         <is>
           <t>150</t>
         </is>
@@ -25320,7 +25325,7 @@
       </c>
       <c r="AH202" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -25395,7 +25400,7 @@
           <t>208</t>
         </is>
       </c>
-      <c r="R203" t="inlineStr">
+      <c r="R203" s="2" t="inlineStr">
         <is>
           <t>208</t>
         </is>
@@ -25437,7 +25442,7 @@
       </c>
       <c r="AH203" t="inlineStr">
         <is>
-          <t>city:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+          <t>city:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -25512,7 +25517,7 @@
           <t>49</t>
         </is>
       </c>
-      <c r="R204" t="inlineStr">
+      <c r="R204" s="2" t="inlineStr">
         <is>
           <t>49</t>
         </is>
@@ -25559,7 +25564,7 @@
       </c>
       <c r="AH204" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:manual-repo-edit</t>
+          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:manual-repo-edit</t>
         </is>
       </c>
     </row>
@@ -25751,7 +25756,7 @@
           <t>123</t>
         </is>
       </c>
-      <c r="R206" t="inlineStr">
+      <c r="R206" s="2" t="inlineStr">
         <is>
           <t>123</t>
         </is>
@@ -25793,7 +25798,7 @@
       </c>
       <c r="AH206" t="inlineStr">
         <is>
-          <t>manual_status:collaborator-sheet; county:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>manual_status:collaborator-sheet; county:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26092,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="R209" t="inlineStr">
+      <c r="R209" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -26129,7 +26134,7 @@
       </c>
       <c r="AH209" t="inlineStr">
         <is>
-          <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; term_years:collaborator-sheet</t>
+          <t>investor_1:collaborator-sheet; address:collaborator-sheet; term_years:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -26204,7 +26209,7 @@
           <t>211</t>
         </is>
       </c>
-      <c r="R210" t="inlineStr">
+      <c r="R210" s="2" t="inlineStr">
         <is>
           <t>211</t>
         </is>
@@ -26241,7 +26246,7 @@
       </c>
       <c r="AH210" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; address:collaborator-sheet; term_years:collaborator-sheet</t>
+          <t>address:collaborator-sheet; term_years:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -26901,7 +26906,7 @@
           <t>81</t>
         </is>
       </c>
-      <c r="R216" t="inlineStr">
+      <c r="R216" s="2" t="inlineStr">
         <is>
           <t>81</t>
         </is>
@@ -26948,7 +26953,7 @@
       </c>
       <c r="AH216" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -27023,7 +27028,7 @@
           <t>34</t>
         </is>
       </c>
-      <c r="R217" t="inlineStr">
+      <c r="R217" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -27070,7 +27075,7 @@
       </c>
       <c r="AH217" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:manual-repo-edit</t>
+          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:manual-repo-edit</t>
         </is>
       </c>
     </row>
@@ -27257,7 +27262,7 @@
           <t>94</t>
         </is>
       </c>
-      <c r="R219" t="inlineStr">
+      <c r="R219" s="2" t="inlineStr">
         <is>
           <t>94</t>
         </is>
@@ -27304,7 +27309,7 @@
       </c>
       <c r="AH219" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -27491,7 +27496,7 @@
           <t>64</t>
         </is>
       </c>
-      <c r="R221" t="inlineStr">
+      <c r="R221" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
@@ -27538,7 +27543,7 @@
       </c>
       <c r="AH221" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27899,7 @@
           <t>132</t>
         </is>
       </c>
-      <c r="R225" t="inlineStr">
+      <c r="R225" s="2" t="inlineStr">
         <is>
           <t>132</t>
         </is>
@@ -27936,7 +27941,7 @@
       </c>
       <c r="AH225" t="inlineStr">
         <is>
-          <t>entity:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; term_years:collaborator-sheet</t>
+          <t>entity:collaborator-sheet; address:collaborator-sheet; term_years:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -28118,7 +28123,7 @@
           <t>148</t>
         </is>
       </c>
-      <c r="R227" t="inlineStr">
+      <c r="R227" s="2" t="inlineStr">
         <is>
           <t>148</t>
         </is>
@@ -28160,7 +28165,7 @@
       </c>
       <c r="AH227" t="inlineStr">
         <is>
-          <t>restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -29611,6 +29616,11 @@
           <t>69</t>
         </is>
       </c>
+      <c r="R241" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
       <c r="S241" s="2" t="inlineStr">
         <is>
           <t>78% at 80% AMI</t>
@@ -29785,6 +29795,11 @@
           <t>111</t>
         </is>
       </c>
+      <c r="R243" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="S243" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -29892,6 +29907,11 @@
           <t>169</t>
         </is>
       </c>
+      <c r="R244" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
       <c r="S244" s="2" t="inlineStr">
         <is>
           <t>34% at 80% AMI</t>
@@ -29994,6 +30014,11 @@
           <t>53</t>
         </is>
       </c>
+      <c r="R245" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="S245" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -30091,6 +30116,11 @@
           <t>697</t>
         </is>
       </c>
+      <c r="R246" s="2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
       <c r="S246" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -30193,6 +30223,11 @@
           <t>488</t>
         </is>
       </c>
+      <c r="R247" s="2" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
       <c r="S247" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -30300,6 +30335,11 @@
           <t>406</t>
         </is>
       </c>
+      <c r="R248" s="2" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
+      </c>
       <c r="S248" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -30392,6 +30432,11 @@
           <t>53</t>
         </is>
       </c>
+      <c r="R249" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
       <c r="S249" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -30484,6 +30529,11 @@
           <t>38</t>
         </is>
       </c>
+      <c r="R250" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
       <c r="S250" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -30581,6 +30631,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="R251" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="S251" s="2" t="inlineStr">
         <is>
           <t>at 80% AMI</t>
@@ -30673,6 +30728,11 @@
           <t>171</t>
         </is>
       </c>
+      <c r="R252" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
       <c r="S252" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -30760,6 +30820,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="R253" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
       <c r="S253" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -30862,6 +30927,11 @@
           <t>89</t>
         </is>
       </c>
+      <c r="R254" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="S254" s="2" t="inlineStr">
         <is>
           <t>10% at 60% AMI; 90% at 80% AMI</t>
@@ -30954,6 +31024,11 @@
           <t>156</t>
         </is>
       </c>
+      <c r="R255" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
       <c r="S255" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -31046,6 +31121,11 @@
           <t>84</t>
         </is>
       </c>
+      <c r="R256" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="S256" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -31138,6 +31218,11 @@
           <t>42</t>
         </is>
       </c>
+      <c r="R257" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="S257" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -31230,6 +31315,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="R258" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
       <c r="S258" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -31322,6 +31412,11 @@
           <t>188</t>
         </is>
       </c>
+      <c r="R259" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
       <c r="S259" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -31414,6 +31509,11 @@
           <t>250</t>
         </is>
       </c>
+      <c r="R260" s="2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
       <c r="S260" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -31516,6 +31616,11 @@
           <t>99</t>
         </is>
       </c>
+      <c r="R261" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
       <c r="S261" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -31603,6 +31708,11 @@
           <t>160</t>
         </is>
       </c>
+      <c r="R262" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
       <c r="S262" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -31695,6 +31805,11 @@
           <t>193</t>
         </is>
       </c>
+      <c r="R263" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
       <c r="S263" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -31787,6 +31902,11 @@
           <t>148</t>
         </is>
       </c>
+      <c r="R264" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
       <c r="S264" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -31879,6 +31999,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="R265" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="S265" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -31971,6 +32096,11 @@
           <t>96</t>
         </is>
       </c>
+      <c r="R266" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
       <c r="S266" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -32063,6 +32193,11 @@
           <t>250</t>
         </is>
       </c>
+      <c r="R267" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="S267" s="2" t="inlineStr">
         <is>
           <t>40% at 80% AMI</t>
@@ -32170,6 +32305,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="R268" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="S268" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -32277,6 +32417,11 @@
           <t>28</t>
         </is>
       </c>
+      <c r="R269" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="S269" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -32369,6 +32514,11 @@
           <t>615</t>
         </is>
       </c>
+      <c r="R270" s="2" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
       <c r="S270" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -32456,6 +32606,11 @@
           <t>Kingdom Development, Inc.</t>
         </is>
       </c>
+      <c r="R271" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
       <c r="S271" s="2" t="inlineStr">
         <is>
           <t>40% at 80% AMI</t>
@@ -32558,6 +32713,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="R272" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="S272" s="2" t="inlineStr">
         <is>
           <t>at 80% AMI</t>
@@ -32660,6 +32820,11 @@
           <t>687</t>
         </is>
       </c>
+      <c r="R273" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
       <c r="S273" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -32752,6 +32917,11 @@
           <t>69</t>
         </is>
       </c>
+      <c r="R274" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="S274" s="2" t="inlineStr">
         <is>
           <t>81% at 80% AMI</t>
@@ -32859,6 +33029,11 @@
           <t>8</t>
         </is>
       </c>
+      <c r="R275" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="S275" s="2" t="inlineStr">
         <is>
           <t>at 80% AMI</t>
@@ -32966,6 +33141,11 @@
           <t>687</t>
         </is>
       </c>
+      <c r="R276" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
       <c r="S276" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -33058,6 +33238,11 @@
           <t>302</t>
         </is>
       </c>
+      <c r="R277" s="2" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
       <c r="S277" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -33150,6 +33335,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="R278" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="S278" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -33252,6 +33442,11 @@
           <t>99</t>
         </is>
       </c>
+      <c r="R279" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
       <c r="S279" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -33344,6 +33539,11 @@
           <t>208</t>
         </is>
       </c>
+      <c r="R280" s="2" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
       <c r="S280" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -33436,6 +33636,11 @@
           <t>148</t>
         </is>
       </c>
+      <c r="R281" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
       <c r="S281" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -33528,6 +33733,11 @@
           <t>84</t>
         </is>
       </c>
+      <c r="R282" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
       <c r="S282" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -33630,6 +33840,11 @@
           <t>99</t>
         </is>
       </c>
+      <c r="R283" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
       <c r="S283" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -33727,6 +33942,11 @@
           <t>37</t>
         </is>
       </c>
+      <c r="R284" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="S284" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -33819,6 +34039,11 @@
           <t>90</t>
         </is>
       </c>
+      <c r="R285" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="S285" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -33993,6 +34218,11 @@
           <t>68</t>
         </is>
       </c>
+      <c r="R287" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="S287" s="2" t="inlineStr">
         <is>
           <t>21% at 80% AMI</t>
@@ -34085,6 +34315,11 @@
           <t>101</t>
         </is>
       </c>
+      <c r="R288" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="S288" s="2" t="inlineStr">
         <is>
           <t>40% at 80% AMI</t>
@@ -34187,6 +34422,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="R289" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="S289" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -34279,6 +34519,11 @@
           <t>206</t>
         </is>
       </c>
+      <c r="R290" s="2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
       <c r="S290" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -34371,6 +34616,11 @@
           <t>192</t>
         </is>
       </c>
+      <c r="R291" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
       <c r="S291" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -34525,6 +34775,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="R293" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="S293" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -34617,6 +34872,11 @@
           <t>5</t>
         </is>
       </c>
+      <c r="R294" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="S294" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -34709,6 +34969,11 @@
           <t>151</t>
         </is>
       </c>
+      <c r="R295" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
       <c r="S295" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -34883,6 +35148,11 @@
           <t>122</t>
         </is>
       </c>
+      <c r="R297" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="S297" s="2" t="inlineStr">
         <is>
           <t>20% at 60% AMI; 80% at 80% AMI</t>
@@ -34980,6 +35250,11 @@
           <t>112</t>
         </is>
       </c>
+      <c r="R298" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="S298" s="2" t="inlineStr">
         <is>
           <t>20% at 60% AMI; 80% at 80% AMI</t>
@@ -35072,6 +35347,11 @@
           <t>99</t>
         </is>
       </c>
+      <c r="R299" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
       <c r="S299" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -35164,6 +35444,11 @@
           <t>88</t>
         </is>
       </c>
+      <c r="R300" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
       <c r="S300" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -35261,6 +35546,11 @@
           <t>122</t>
         </is>
       </c>
+      <c r="R301" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="S301" s="2" t="inlineStr">
         <is>
           <t>20% at 60% AMI; 80% at 80% AMI</t>
@@ -35358,6 +35648,11 @@
           <t>112</t>
         </is>
       </c>
+      <c r="R302" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="S302" s="2" t="inlineStr">
         <is>
           <t>20% at 60% AMI; 80% at 80% AMI</t>
@@ -35450,6 +35745,11 @@
           <t>164</t>
         </is>
       </c>
+      <c r="R303" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
       <c r="S303" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -35542,6 +35842,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="R304" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="S304" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -35619,6 +35924,11 @@
           <t>128</t>
         </is>
       </c>
+      <c r="R305" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
       <c r="S305" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -35702,6 +36012,11 @@
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="R306" s="2" t="inlineStr">
         <is>
           <t>148</t>
         </is>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -466,7 +466,7 @@
     <col width="38" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="35" customWidth="1" min="19" max="19"/>
+    <col width="38" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="17" customWidth="1" min="22" max="22"/>
@@ -1984,9 +1984,9 @@
           <t>820 MacArthur Apartments</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2019 Ozone Affordable Housing</t>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2019 Ozone Affordable Housing – 820 MacArthur, LP</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -2532,9 +2532,9 @@
           <t>Premiere Hollywood Apartments</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>OODB2, LP</t>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>OODB2, LP, a Washington Limited Partnership</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>built:collaborator-sheet; manual_status:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
+          <t>built:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -2669,9 +2669,9 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Affordable Housing Alliance II, Inc. dba Integrity Housing</t>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Affordable Housing Alliance II, Inc., d/b/a Integrity Housing, a Colorado nonprofit corporation</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -3003,21 +3003,21 @@
           <t>2-CMFA-Minutes-06-07-24.pdf</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>AOF</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>Pacific Affordable Housing Corp.</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>Pacific Affordable Housing Corp</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Pacific Affordable Housing Corp</t>
-        </is>
-      </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
           <t>103</t>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>investor_2:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; city:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+          <t>built:collaborator-sheet; scc_filed:collaborator-sheet; city:collaborator-sheet; nonprofit_partner:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -6556,9 +6556,9 @@
           <t>Eleos Ventures, LLC</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>Step Forward Comminities</t>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>Step Forward Communities</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; nonprofit_partner:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -7186,9 +7186,9 @@
           <t>CMFA</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Summerwood Apartments Homes Apartments</t>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Summerwood Apartment Homes</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; property_name:collaborator-sheet; entity:collaborator-sheet; investor_1:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; entity:collaborator-sheet; investor_1:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -8210,14 +8210,14 @@
           <t>CMFA-Minutes-12-13-2024.pdf</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>Bridge Housing</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>Bridge Housing</t>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>BRIDGE Housing Corporation</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>BRIDGE Housing Corporation</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>leasing_link:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; address:collaborator-sheet</t>
+          <t>leasing_link:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -12068,9 +12068,9 @@
           <t>569 W. 6th Street. Apartments</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>SIOF 5 Properties, LP, California limited partnership</t>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>SIOF 5 Properties, LP, a California limited partnership</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -12200,9 +12200,9 @@
           <t>685 W. 4th St Apartments</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>2 SIOF 685 W Fourth St, LP, Delaware limited partnership</t>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>2 SIOF 685 W Fourth St, LP, a Delaware limited partnership</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -12387,12 +12387,12 @@
           <t>2-CMFA-Minutes-06-27-2025.pdf</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>Vintage Housing Holdings</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr">
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>Vintage Housing Holdings, LLC</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr">
         <is>
           <t>Kennedy Wilson</t>
         </is>
@@ -12454,7 +12454,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; scc_filed:collaborator-sheet; investor_1:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -13189,16 +13189,16 @@
           <t>2-CMFA-Minutes-08-08-25.pdf</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr">
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>BRIDGE Housing Corporation</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
         <is>
           <t>BRIDGE Housing Corp.</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>BRIDGE Housing Corp.</t>
-        </is>
-      </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
           <t>148</t>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; resolution:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; resolution:collaborator-sheet; nonprofit_partner:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -13468,9 +13468,9 @@
           <t>Belveron Partners</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>Las Palmas Housing &amp; Development Corp.</t>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>Las Palmas Housing &amp; Development Corporation</t>
         </is>
       </c>
       <c r="T96" s="2" t="inlineStr">
@@ -13530,7 +13530,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>investor_2:collaborator-sheet; acquisition_date:collaborator-sheet; link:collaborator-sheet; scc_filed:collaborator-sheet; resolution:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; address:collaborator-sheet</t>
+          <t>investor_2:collaborator-sheet; acquisition_date:collaborator-sheet; link:collaborator-sheet; scc_filed:collaborator-sheet; resolution:collaborator-sheet; investor_1:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -18853,9 +18853,9 @@
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>5805 Charlotte Drive, San Jose, CA 95123</t>
+      <c r="Z136" s="2" t="inlineStr">
+        <is>
+          <t>5805 Charlotte Drive, San Jose, CA</t>
         </is>
       </c>
       <c r="AA136" s="2" t="inlineStr">
@@ -18870,7 +18870,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -19667,9 +19667,9 @@
           <t>CMFA</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Coliseum Transit Village</t>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Coliseum Connections Transit Village Apartments</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -19789,7 +19789,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; property_name:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -20195,9 +20195,9 @@
           <t>CMFA</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Coliseum Connections</t>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Coliseum Connections Transit Village Apartments</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; manual_status:collaborator-sheet; property_name:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -20616,9 +20616,9 @@
           <t>CMFA</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Langham Apartments</t>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>The Langham Apartments</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; property_name:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -20753,9 +20753,9 @@
           <t>CMFA</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Piccadilly Apartments</t>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>The Piccadilly Apartments</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -20875,7 +20875,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; property_name:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -25761,9 +25761,9 @@
           <t>Highlands Point Apartments</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>St. Anton Highland, LP</t>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>St. Anton Highlands LP</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -25873,7 +25873,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -27945,9 +27945,9 @@
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="Z207" t="inlineStr">
-        <is>
-          <t>2625 Cullen St, Los Angeles, CA 90034</t>
+      <c r="Z207" s="2" t="inlineStr">
+        <is>
+          <t>2625 Cullen Street, Los Angeles, CA</t>
         </is>
       </c>
       <c r="AA207" s="2" t="inlineStr">
@@ -27962,7 +27962,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>manual_status:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>manual_status:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -28682,9 +28682,9 @@
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="Z213" t="inlineStr">
-        <is>
-          <t>5416 Jackson St, North Highlands, CA 95660</t>
+      <c r="Z213" s="2" t="inlineStr">
+        <is>
+          <t>5416 Jackson Street, North Highlands</t>
         </is>
       </c>
       <c r="AA213" s="2" t="inlineStr">
@@ -28699,7 +28699,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>city:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>city:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -28804,9 +28804,9 @@
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="Z214" t="inlineStr">
-        <is>
-          <t>444 N Amelia Ave, San Dimas, CA 91773</t>
+      <c r="Z214" s="2" t="inlineStr">
+        <is>
+          <t>444 North Amelia Avenue, San Dimas</t>
         </is>
       </c>
       <c r="AA214" s="2" t="inlineStr">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -28936,9 +28936,9 @@
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="Z215" t="inlineStr">
-        <is>
-          <t>511 N. Hoover Street, Los Angeles, California</t>
+      <c r="Z215" s="2" t="inlineStr">
+        <is>
+          <t>511 N. Hoover Street, Los Angeles</t>
         </is>
       </c>
       <c r="AA215" s="2" t="inlineStr">
@@ -28963,7 +28963,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; link:collaborator-sheet; resolution:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; link:collaborator-sheet; resolution:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -29840,9 +29840,9 @@
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="Z222" t="inlineStr">
-        <is>
-          <t>16077 Ashland Ave, San Lorenzo, CA 94580</t>
+      <c r="Z222" s="2" t="inlineStr">
+        <is>
+          <t>16077 Ashland Avenue, San Lorenzo</t>
         </is>
       </c>
       <c r="AA222" s="2" t="inlineStr">
@@ -29857,7 +29857,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>city:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>city:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -30019,9 +30019,9 @@
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>1454 W Florence Ave, Los Angeles, CA 90047</t>
+      <c r="Z224" s="2" t="inlineStr">
+        <is>
+          <t>1454 West Florence Avenue, Los Angeles, CA</t>
         </is>
       </c>
       <c r="AA224" s="2" t="inlineStr">
@@ -30041,7 +30041,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -30061,9 +30061,9 @@
           <t>Bennington Apartments</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>CG Bennington, LP / JSP Bennington, LP</t>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>CG Bennington, LP and JSP Bennington, LP</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -30158,7 +30158,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>entity:collaborator-sheet; address:collaborator-sheet; term_years:collaborator-sheet</t>
+          <t>address:collaborator-sheet; term_years:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -30263,9 +30263,9 @@
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="Z226" t="inlineStr">
-        <is>
-          <t>142 Fig Tree Lane, Martinez, CA 94553</t>
+      <c r="Z226" s="2" t="inlineStr">
+        <is>
+          <t>142 Fig Tree Lane, Martinez, CA</t>
         </is>
       </c>
       <c r="AA226" s="2" t="inlineStr">
@@ -30280,7 +30280,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>manual_status:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; term_years:collaborator-sheet</t>
+          <t>manual_status:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; term_years:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -30467,9 +30467,9 @@
           <t>Positive Investments, Inc.</t>
         </is>
       </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>Foundation for Affordable Housing</t>
+      <c r="S228" s="2" t="inlineStr">
+        <is>
+          <t>The Foundation for Affordable Housing</t>
         </is>
       </c>
       <c r="T228" s="2" t="inlineStr">
@@ -30514,7 +30514,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; term_years:collaborator-sheet</t>
+          <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet; term_years:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -30619,9 +30619,9 @@
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="Z229" t="inlineStr">
-        <is>
-          <t>220 47th St, San Diego, CA 92102</t>
+      <c r="Z229" s="2" t="inlineStr">
+        <is>
+          <t>220 47th Street, San Diego</t>
         </is>
       </c>
       <c r="AA229" s="2" t="inlineStr">
@@ -30636,7 +30636,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -30651,9 +30651,9 @@
           <t>CSCDA</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Hansen illage Apartments</t>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>Hansen Village Apartments</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -30706,9 +30706,9 @@
           <t>Positive Investments, Inc.</t>
         </is>
       </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>Foundation for Affordable Housing</t>
+      <c r="S230" s="2" t="inlineStr">
+        <is>
+          <t>The Foundation for Affordable Housing</t>
         </is>
       </c>
       <c r="T230" s="2" t="inlineStr">
@@ -30758,7 +30758,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; property_name:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -30863,9 +30863,9 @@
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="Z231" t="inlineStr">
-        <is>
-          <t>160 S Virgil Ave, Los Angeles, CA 90004</t>
+      <c r="Z231" s="2" t="inlineStr">
+        <is>
+          <t>160 S. Virgil Avenue, Los Angeles</t>
         </is>
       </c>
       <c r="AA231" s="2" t="inlineStr">
@@ -30880,7 +30880,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -30980,9 +30980,9 @@
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="Z232" t="inlineStr">
-        <is>
-          <t>12091 Bayport St, Garden Grove, CA 92840</t>
+      <c r="Z232" s="2" t="inlineStr">
+        <is>
+          <t>12091 Bayport Street, Garden Grove, CA</t>
         </is>
       </c>
       <c r="AA232" s="2" t="inlineStr">
@@ -31007,7 +31007,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; link:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; link:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -31112,9 +31112,9 @@
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="Z233" t="inlineStr">
-        <is>
-          <t>926 S Kingsley Dr, Los Angeles, CA 90006</t>
+      <c r="Z233" s="2" t="inlineStr">
+        <is>
+          <t>926 S. Kingsley Drive, Los Angeles, CA</t>
         </is>
       </c>
       <c r="AA233" s="2" t="inlineStr">
@@ -31129,7 +31129,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; term_years:collaborator-sheet</t>
+          <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet; term_years:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -31234,9 +31234,9 @@
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="Z234" t="inlineStr">
-        <is>
-          <t>939 S Kingsley Dr, Los Angeles, CA 90006</t>
+      <c r="Z234" s="2" t="inlineStr">
+        <is>
+          <t>939 S. Kingsley Drive, Los Angeles, CA</t>
         </is>
       </c>
       <c r="AA234" s="2" t="inlineStr">
@@ -31251,7 +31251,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -31478,9 +31478,9 @@
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="Z236" t="inlineStr">
-        <is>
-          <t>6985 S. Centinela Avenue, Los Angeles, CA 90045</t>
+      <c r="Z236" s="2" t="inlineStr">
+        <is>
+          <t>6985 S. Centinela Avenue, Los Angeles, CA</t>
         </is>
       </c>
       <c r="AA236" s="2" t="inlineStr">
@@ -31500,7 +31500,7 @@
       </c>
       <c r="AJ236" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -31605,9 +31605,9 @@
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="Z237" t="inlineStr">
-        <is>
-          <t>1178 N Edgemont St, Los Angeles, CA 90029</t>
+      <c r="Z237" s="2" t="inlineStr">
+        <is>
+          <t>1178 N. Edgemont Street, Los Angeles, CA</t>
         </is>
       </c>
       <c r="AA237" s="2" t="inlineStr">
@@ -31622,7 +31622,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -35377,7 +35377,12 @@
       </c>
       <c r="Q272" s="2" t="inlineStr">
         <is>
-          <t>Vintage Housing Holdings, LLC / Kennedy Wilson</t>
+          <t>Vintage Housing Holdings, LLC</t>
+        </is>
+      </c>
+      <c r="R272" s="2" t="inlineStr">
+        <is>
+          <t>Kennedy Wilson</t>
         </is>
       </c>
       <c r="S272" s="2" t="inlineStr">
@@ -35494,7 +35499,12 @@
       </c>
       <c r="Q273" s="2" t="inlineStr">
         <is>
-          <t>Vintage Housing Holdings, LLC / Kennedy Wilson</t>
+          <t>Vintage Housing Holdings, LLC</t>
+        </is>
+      </c>
+      <c r="R273" s="2" t="inlineStr">
+        <is>
+          <t>Kennedy Wilson</t>
         </is>
       </c>
       <c r="S273" s="2" t="inlineStr">
@@ -35723,7 +35733,12 @@
       </c>
       <c r="Q275" s="2" t="inlineStr">
         <is>
-          <t>Vintage Housing Holdings, LLC / Kennedy Wilson</t>
+          <t>Vintage Housing Holdings, LLC</t>
+        </is>
+      </c>
+      <c r="R275" s="2" t="inlineStr">
+        <is>
+          <t>Kennedy Wilson</t>
         </is>
       </c>
       <c r="S275" s="2" t="inlineStr">
@@ -35845,7 +35860,12 @@
       </c>
       <c r="Q276" s="2" t="inlineStr">
         <is>
-          <t>Vintage Housing Holdings, LLC / Kennedy Wilson</t>
+          <t>Vintage Housing Holdings, LLC</t>
+        </is>
+      </c>
+      <c r="R276" s="2" t="inlineStr">
+        <is>
+          <t>Kennedy Wilson</t>
         </is>
       </c>
       <c r="S276" s="2" t="inlineStr">
@@ -72484,7 +72504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C168"/>
+  <dimension ref="A1:C131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -73078,12 +73098,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>entity: generated '2019 Ozone Affordable Housing – 820 MacArthur, LP' -&gt; manual '2019 Ozone Affordable Housing'</t>
+          <t>nonprofit_partner: generated 'AOF / Pacific Affordable Housing Corp.' -&gt; manual 'Pacific Affordable Housing Corp'</t>
         </is>
       </c>
     </row>
@@ -73095,12 +73115,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>entity: generated 'OODB2, LP, a Washington Limited Partnership' -&gt; manual 'OODB2, LP'</t>
+          <t>city: generated 'Los Angeles' -&gt; manual 'El Sobrante'</t>
         </is>
       </c>
     </row>
@@ -73112,12 +73132,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>entity: generated 'Affordable Housing Alliance II, Inc., d/b/a Integrity Housing, a Colorado nonprofit corporation' -&gt; manual 'Affordable Housing Alliance II, Inc. dba Integrity Housing'</t>
+          <t>county: generated 'Los Angeles' -&gt; manual 'Contra Costa'</t>
         </is>
       </c>
     </row>
@@ -73129,12 +73149,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>investor_1: generated 'AOF / Pacific Affordable Housing Corp.' -&gt; manual 'AOF'</t>
+          <t>total_units: generated '24' -&gt; manual '52'</t>
         </is>
       </c>
     </row>
@@ -73146,12 +73166,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>nonprofit_partner: generated 'AOF / Pacific Affordable Housing Corp.' -&gt; manual 'Pacific Affordable Housing Corp'</t>
+          <t>total_units: generated '22' -&gt; manual '72'</t>
         </is>
       </c>
     </row>
@@ -73163,12 +73183,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>city: generated 'Los Angeles' -&gt; manual 'El Sobrante'</t>
+          <t>total_units: generated '24' -&gt; manual '48'</t>
         </is>
       </c>
     </row>
@@ -73180,12 +73200,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>county: generated 'Los Angeles' -&gt; manual 'Contra Costa'</t>
+          <t>total_units: generated '65' -&gt; manual '165'</t>
         </is>
       </c>
     </row>
@@ -73197,12 +73217,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>total_units: generated '24' -&gt; manual '52'</t>
+          <t>property_name: generated '2330 3rd Street Apartments' -&gt; manual '2330 E. 3rd Street Apartments'</t>
         </is>
       </c>
     </row>
@@ -73214,12 +73234,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>total_units: generated '22' -&gt; manual '72'</t>
+          <t>investor_1: generated 'Ethos Real Estate' -&gt; manual 'Vistria Group'</t>
         </is>
       </c>
     </row>
@@ -73231,12 +73251,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>total_units: generated '24' -&gt; manual '48'</t>
+          <t>total_units: generated '144' -&gt; manual '145'</t>
         </is>
       </c>
     </row>
@@ -73248,12 +73268,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>total_units: generated '65' -&gt; manual '165'</t>
+          <t>total_units: generated '42' -&gt; manual '356'</t>
         </is>
       </c>
     </row>
@@ -73265,12 +73285,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>property_name: generated '2330 3rd Street Apartments' -&gt; manual '2330 E. 3rd Street Apartments'</t>
+          <t>entity: generated 'PREG 5150 ECR Los Altos, LP, a California limited partnership' -&gt; manual 'Prometheus Real Estate Group'</t>
         </is>
       </c>
     </row>
@@ -73282,12 +73302,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>investor_1: generated 'Ethos Real Estate' -&gt; manual 'Vistria Group'</t>
+          <t>total_units: generated '29' -&gt; manual '196'</t>
         </is>
       </c>
     </row>
@@ -73299,12 +73319,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>nonprofit_partner: generated 'Step Forward Communities' -&gt; manual 'Step Forward Comminities'</t>
+          <t>entity: generated '3 SIOF 1451 W MLK BLVD, LP' -&gt; manual '1451 W. MLK Boulevard Apartments'</t>
         </is>
       </c>
     </row>
@@ -73316,12 +73336,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>total_units: generated '144' -&gt; manual '145'</t>
+          <t>investor_1: generated 'Vintage Housing Holdings, LLC' -&gt; manual 'Kennedy Wilson'</t>
         </is>
       </c>
     </row>
@@ -73333,12 +73353,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>total_units: generated '42' -&gt; manual '356'</t>
+          <t>nonprofit_partner: generated 'Pacific Housing, Inc.' -&gt; manual 'Hearthstone Housing Foundation'</t>
         </is>
       </c>
     </row>
@@ -73350,12 +73370,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>investor_1: generated 'BRIDGE Housing Corporation' -&gt; manual 'Bridge Housing'</t>
+          <t>total_units: generated '8' -&gt; manual '1008'</t>
         </is>
       </c>
     </row>
@@ -73367,12 +73387,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>nonprofit_partner: generated 'BRIDGE Housing Corporation' -&gt; manual 'Bridge Housing'</t>
+          <t>total_units: generated '32' -&gt; manual '31'</t>
         </is>
       </c>
     </row>
@@ -73384,12 +73404,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>entity: generated 'PREG 5150 ECR Los Altos, LP, a California limited partnership' -&gt; manual 'Prometheus Real Estate Group'</t>
+          <t>city_cut: generated '4650.0' -&gt; manual '4500'</t>
         </is>
       </c>
     </row>
@@ -73401,12 +73421,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>79</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>total_units: generated '29' -&gt; manual '196'</t>
+          <t>entity: generated '2 SIOF 10811 S Compton Ave, LP' -&gt; manual '10811 S. Compton Ave Apartments'</t>
         </is>
       </c>
     </row>
@@ -73418,12 +73438,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>158</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>entity: generated '3 SIOF 1451 W MLK BLVD, LP' -&gt; manual '1451 W. MLK Boulevard Apartments'</t>
+          <t>total_units: generated '30' -&gt; manual '29'</t>
         </is>
       </c>
     </row>
@@ -73435,12 +73455,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>95</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>investor_1: generated 'Vintage Housing Holdings, LLC / Kennedy Wilson' -&gt; manual 'Kennedy Wilson'</t>
+          <t>investor_1: generated 'Belveron Partners' -&gt; manual 'Sack Capital Partners'</t>
         </is>
       </c>
     </row>
@@ -73452,12 +73472,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>110</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>nonprofit_partner: generated 'Pacific Housing, Inc.' -&gt; manual 'Hearthstone Housing Foundation'</t>
+          <t>total_units: generated '24' -&gt; manual '42'</t>
         </is>
       </c>
     </row>
@@ -73469,12 +73489,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>120</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>total_units: generated '8' -&gt; manual '1008'</t>
+          <t>city: generated 'Sacramento' -&gt; manual 'Unincorporated'</t>
         </is>
       </c>
     </row>
@@ -73486,12 +73506,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>125</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>total_units: generated '32' -&gt; manual '31'</t>
+          <t>property_name: generated 'Kinglsey Apartments' -&gt; manual 'Kingsley Apartments'</t>
         </is>
       </c>
     </row>
@@ -73503,12 +73523,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>134</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>city_cut: generated '4650.0' -&gt; manual '4500'</t>
+          <t>total_units: generated '69' -&gt; manual '68'</t>
         </is>
       </c>
     </row>
@@ -73520,12 +73540,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>137</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>entity: generated '2 SIOF 10811 S Compton Ave, LP' -&gt; manual '10811 S. Compton Ave Apartments'</t>
+          <t>total_units: generated '42' -&gt; manual '41'</t>
         </is>
       </c>
     </row>
@@ -73537,12 +73557,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>138</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>entity: generated 'SIOF 5 Properties, LP, a California limited partnership' -&gt; manual 'SIOF 5 Properties, LP, California limited partnership'</t>
+          <t>city: generated 'Santa Clara' -&gt; manual 'San Jose'</t>
         </is>
       </c>
     </row>
@@ -73554,12 +73574,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>152</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>entity: generated '2 SIOF 685 W Fourth St, LP, a Delaware limited partnership' -&gt; manual '2 SIOF 685 W Fourth St, LP, Delaware limited partnership'</t>
+          <t>total_units: generated '52' -&gt; manual '152'</t>
         </is>
       </c>
     </row>
@@ -73571,12 +73591,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>155</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>investor_1: generated 'Vintage Housing Holdings, LLC / Kennedy Wilson' -&gt; manual 'Vintage Housing Holdings'</t>
+          <t>entity: generated 'A limited partnership to be formed by Kairos Investment Management and Pacific Housing' -&gt; manual 'TBD LP'</t>
         </is>
       </c>
     </row>
@@ -73588,12 +73608,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>156</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>total_units: generated '30' -&gt; manual '29'</t>
+          <t>entity: generated 'A limited partnership to be formed by Kairos Investment Management and Pacific Housing' -&gt; manual 'TBD LP'</t>
         </is>
       </c>
     </row>
@@ -73605,12 +73625,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>171</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>investor_1: generated 'Belveron Partners' -&gt; manual 'Sack Capital Partners'</t>
+          <t>city_cut: generated '15900.0' -&gt; manual '6300'</t>
         </is>
       </c>
     </row>
@@ -73622,12 +73642,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>181</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>nonprofit_partner: generated 'Las Palmas Housing &amp; Development Corporation' -&gt; manual 'Las Palmas Housing &amp; Development Corp.'</t>
+          <t>city: generated 'Long Beach' -&gt; manual 'Los Angeles'</t>
         </is>
       </c>
     </row>
@@ -73639,12 +73659,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>181</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>investor_1: generated 'BRIDGE Housing Corporation' -&gt; manual 'BRIDGE Housing Corp.'</t>
+          <t>total_units: generated '52' -&gt; manual '152'</t>
         </is>
       </c>
     </row>
@@ -73656,12 +73676,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>144</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>total_units: generated '24' -&gt; manual '42'</t>
+          <t>property_name: generated 'La Vista Apartments' -&gt; manual 'La Vista Apartment Homes'</t>
         </is>
       </c>
     </row>
@@ -73673,12 +73693,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>195</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>city: generated 'Sacramento' -&gt; manual 'Unincorporated'</t>
+          <t>total_units: generated '42' -&gt; manual '41'</t>
         </is>
       </c>
     </row>
@@ -73690,12 +73710,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>196</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>property_name: generated 'Kinglsey Apartments' -&gt; manual 'Kingsley Apartments'</t>
+          <t>address: generated '9750 Airport Blvd, Los Angeles, CA' -&gt; manual '9750 Airport Blvd, Westchester, CA 90045'</t>
         </is>
       </c>
     </row>
@@ -73707,12 +73727,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>199</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>total_units: generated '69' -&gt; manual '68'</t>
+          <t>city_cut: generated '5550.0' -&gt; manual '5500'</t>
         </is>
       </c>
     </row>
@@ -73724,12 +73744,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>208</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>address: generated '5805 Charlotte Drive, San Jose, CA' -&gt; manual '5805 Charlotte Drive, San Jose, CA 95123'</t>
+          <t>address: generated '2481 South Sawtelle Blvd, Los Angeles, CA' -&gt; manual '2481 Sawtelle Blvd, Los Angeles, CA 90064'</t>
         </is>
       </c>
     </row>
@@ -73741,12 +73761,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>total_units: generated '42' -&gt; manual '41'</t>
+          <t>entity: generated 'Standard Summerwood II LP' -&gt; manual 'Standard Properties'</t>
         </is>
       </c>
     </row>
@@ -73758,12 +73778,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>49</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>property_name: generated 'Coliseum Connections Transit Village Apartments' -&gt; manual 'Coliseum Transit Village'</t>
+          <t>investor_1: generated 'Standard Property Company, Inc.' -&gt; manual 'Standard Properties'</t>
         </is>
       </c>
     </row>
@@ -73775,12 +73795,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>204</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>city: generated 'Santa Clara' -&gt; manual 'San Jose'</t>
+          <t>total_units: generated '50' -&gt; manual '49'</t>
         </is>
       </c>
     </row>
@@ -73792,12 +73812,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>206</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>property_name: generated 'Coliseum Connections Transit Village Apartments' -&gt; manual 'Coliseum Connections'</t>
+          <t>county: generated 'San Diego' -&gt; manual 'Los Angeles'</t>
         </is>
       </c>
     </row>
@@ -73809,12 +73829,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>209</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>property_name: generated 'The Langham Apartments' -&gt; manual 'Langham Apartments'</t>
+          <t>investor_1: generated 'Zenith Property Group LLC' -&gt; manual 'Red Stone Equity Partners'</t>
         </is>
       </c>
     </row>
@@ -73826,12 +73846,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>209</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>property_name: generated 'The Piccadilly Apartments' -&gt; manual 'Piccadilly Apartments'</t>
+          <t>term_years: generated '35' -&gt; manual '15'</t>
         </is>
       </c>
     </row>
@@ -73843,12 +73863,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>210</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>total_units: generated '52' -&gt; manual '152'</t>
+          <t>term_years: generated '55' -&gt; manual '10'</t>
         </is>
       </c>
     </row>
@@ -73860,12 +73880,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>entity: generated 'A limited partnership to be formed by Kairos Investment Management and Pacific Housing' -&gt; manual 'TBD LP'</t>
+          <t>term_years: generated '15' -&gt; manual '10'</t>
         </is>
       </c>
     </row>
@@ -73877,12 +73897,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>228</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>entity: generated 'A limited partnership to be formed by Kairos Investment Management and Pacific Housing' -&gt; manual 'TBD LP'</t>
+          <t>term_years: generated '10' -&gt; manual '15'</t>
         </is>
       </c>
     </row>
@@ -73894,12 +73914,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>230</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>city_cut: generated '15900.0' -&gt; manual '6300'</t>
+          <t>address: generated '11821 Foothill Blvd, Los Angeles, CA' -&gt; manual '11821 Foothill Blvd, Lake View Terrace, CA 91342'</t>
         </is>
       </c>
     </row>
@@ -73911,12 +73931,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>217</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>city: generated 'Long Beach' -&gt; manual 'Los Angeles'</t>
+          <t>total_units: generated '35' -&gt; manual '34'</t>
         </is>
       </c>
     </row>
@@ -73928,12 +73948,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>211</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>total_units: generated '52' -&gt; manual '152'</t>
+          <t>entity: generated 'Haven, LP' -&gt; manual 'Heven LP'</t>
         </is>
       </c>
     </row>
@@ -73945,12 +73965,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>211</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>entity: generated 'St. Anton Highlands LP' -&gt; manual 'St. Anton Highland, LP'</t>
+          <t>address: generated '6530 Independence Avenue, Los Angeles' -&gt; manual '6530 Independence Ave, Canoga Park, CA 91303'</t>
         </is>
       </c>
     </row>
@@ -73962,12 +73982,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>212</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>property_name: generated 'La Vista Apartments' -&gt; manual 'La Vista Apartment Homes'</t>
+          <t>address: generated '2075 West Jefferson Blvd., Los Angeles' -&gt; manual '2075 W Jefferson BlvdLos Angeles, CA 90018'</t>
         </is>
       </c>
     </row>
@@ -73979,12 +73999,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>231</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>total_units: generated '42' -&gt; manual '41'</t>
+          <t>nonprofit_partner: generated 'Bedford' -&gt; manual 'Bedford Affordable Housing Foundation'</t>
         </is>
       </c>
     </row>
@@ -73996,12 +74016,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>233</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>address: generated '9750 Airport Blvd, Los Angeles, CA' -&gt; manual '9750 Airport Blvd, Westchester, CA 90045'</t>
+          <t>term_years: generated '55' -&gt; manual '10'</t>
         </is>
       </c>
     </row>
@@ -74013,12 +74033,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>235</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>city_cut: generated '5550.0' -&gt; manual '5500'</t>
+          <t>address: generated '3950 W. Ingraham Street, Los Angeles, CA' -&gt; manual '3950 Ingraham St, San Diego, CA 92109'</t>
         </is>
       </c>
     </row>
@@ -74030,12 +74050,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>236</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>address: generated '2625 Cullen Street, Los Angeles, CA' -&gt; manual '2625 Cullen St, Los Angeles, CA 90034'</t>
+          <t>total_units: generated '136' -&gt; manual '108'</t>
         </is>
       </c>
     </row>
@@ -74047,1302 +74067,673 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>225</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>address: generated '2481 South Sawtelle Blvd, Los Angeles, CA' -&gt; manual '2481 Sawtelle Blvd, Los Angeles, CA 90064'</t>
+          <t>term_years: generated '30' -&gt; manual '55'</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>property_name: generated 'Summerwood Apartment Homes' -&gt; manual 'Summerwood Apartments Homes Apartments'</t>
+          <t>AIN 6020022027 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>entity: generated 'Standard Summerwood II LP' -&gt; manual 'Standard Properties'</t>
+          <t>AIN 6020022027 (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>investor_1: generated 'Standard Property Company, Inc.' -&gt; manual 'Standard Properties'</t>
+          <t>AIN 5036031006 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>total_units: generated '50' -&gt; manual '49'</t>
+          <t>AIN 4262018026 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>132</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>county: generated 'San Diego' -&gt; manual 'Los Angeles'</t>
+          <t>AIN 6020022027 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>137</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>address: generated '1454 West Florence Avenue, Los Angeles, CA' -&gt; manual '1454 W Florence Ave, Los Angeles, CA 90047'</t>
+          <t>AIN 2125017014 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>143</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>investor_1: generated 'Zenith Property Group LLC' -&gt; manual 'Red Stone Equity Partners'</t>
+          <t>AIN 41416654 (Alameda): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>158</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>term_years: generated '35' -&gt; manual '15'</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>182</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>term_years: generated '55' -&gt; manual '10'</t>
+          <t>AIN 5036031006 (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>196</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>address: generated '142 Fig Tree Lane, Martinez, CA' -&gt; manual '142 Fig Tree Lane, Martinez, CA 94553'</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>197</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>term_years: generated '15' -&gt; manual '10'</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>nonprofit_partner: generated 'The Foundation for Affordable Housing' -&gt; manual 'Foundation for Affordable Housing'</t>
+          <t>AIN (none) (Santa Barbara): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>206</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>term_years: generated '10' -&gt; manual '15'</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>207</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>property_name: generated 'Hansen Village Apartments' -&gt; manual 'Hansen illage Apartments'</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>208</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>nonprofit_partner: generated 'The Foundation for Affordable Housing' -&gt; manual 'Foundation for Affordable Housing'</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>215</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>address: generated '11821 Foothill Blvd, Los Angeles, CA' -&gt; manual '11821 Foothill Blvd, Lake View Terrace, CA 91342'</t>
+          <t>AIN 5539028040 (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>address: generated '12091 Bayport Street, Garden Grove, CA' -&gt; manual '12091 Bayport St, Garden Grove, CA 92840'</t>
+          <t>AIN (none) (Contra Costa): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>address: generated '16077 Ashland Avenue, San Lorenzo' -&gt; manual '16077 Ashland Ave, San Lorenzo, CA 94580'</t>
+          <t>AIN 46745075 (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>total_units: generated '35' -&gt; manual '34'</t>
+          <t>AIN 46745074 (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>address: generated '511 N. Hoover Street, Los Angeles' -&gt; manual '511 N. Hoover Street, Los Angeles, California'</t>
+          <t>AIN 46745073 (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>198</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>entity: generated 'Haven, LP' -&gt; manual 'Heven LP'</t>
+          <t>AIN (none) (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>address: generated '6530 Independence Avenue, Los Angeles' -&gt; manual '6530 Independence Ave, Canoga Park, CA 91303'</t>
+          <t>AIN 128101150 (Solano) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>address: generated '2075 West Jefferson Blvd., Los Angeles' -&gt; manual '2075 W Jefferson BlvdLos Angeles, CA 90018'</t>
+          <t>AIN 128101050 (Solano) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>address: generated '5416 Jackson Street, North Highlands' -&gt; manual '5416 Jackson St, North Highlands, CA 95660'</t>
+          <t>AIN 128105060 (Solano) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>182/76</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>address: generated '444 North Amelia Avenue, San Dimas' -&gt; manual '444 N Amelia Ave, San Dimas, CA 91773'</t>
+          <t>AIN 5036031006 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>200/218</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>address: generated '220 47th Street, San Diego' -&gt; manual '220 47th St, San Diego, CA 92102'</t>
+          <t>AIN 5040021006 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>130/179</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>nonprofit_partner: generated 'Bedford' -&gt; manual 'Bedford Affordable Housing Foundation'</t>
+          <t>AIN 5080006008 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>126/173</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>address: generated '160 S. Virgil Avenue, Los Angeles' -&gt; manual '160 S Virgil Ave, Los Angeles, CA 90004'</t>
+          <t>AIN 5094005005 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>127/174</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>address: generated '926 S. Kingsley Drive, Los Angeles, CA' -&gt; manual '926 S Kingsley Dr, Los Angeles, CA 90006'</t>
+          <t>AIN 5094006003 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>122/165</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>term_years: generated '55' -&gt; manual '10'</t>
+          <t>AIN 5094017020 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>124/169</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>address: generated '939 S. Kingsley Drive, Los Angeles, CA' -&gt; manual '939 S Kingsley Dr, Los Angeles, CA 90006'</t>
+          <t>AIN 5094023025 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>128/175</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>address: generated '3950 W. Ingraham Street, Los Angeles, CA' -&gt; manual '3950 Ingraham St, San Diego, CA 92109'</t>
+          <t>AIN 5502019004 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>125/170</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>total_units: generated '136' -&gt; manual '108'</t>
+          <t>AIN 5503024012 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>129/177</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>address: generated '6985 S. Centinela Avenue, Los Angeles, CA' -&gt; manual '6985 S. Centinela Avenue, Los Angeles, CA 90045'</t>
+          <t>AIN 5517005016 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>121/162</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>address: generated '1178 N. Edgemont Street, Los Angeles, CA' -&gt; manual '1178 N Edgemont St, Los Angeles, CA 90029'</t>
+          <t>AIN 5518013024 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>123/168</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>entity: generated 'CG Bennington, LP and JSP Bennington, LP' -&gt; manual 'CG Bennington, LP / JSP Bennington, LP'</t>
+          <t>AIN 5518020021 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>135/220</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>term_years: generated '30' -&gt; manual '55'</t>
+          <t>AIN 5518026004 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>10/132</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>AIN 6020022027 (Los Angeles) has no current roll data; using manual value</t>
+          <t>AIN 6020022027 assigned to multiple projects</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>shared-ain</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>152/181</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
-        <is>
-          <t>AIN 6020022027 (Los Angeles): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>fetch-fallback</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>AIN 5036031006 (Los Angeles) has no current roll data; using manual value</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>fetch-fallback</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>AIN 4262018026 (Los Angeles) has no current roll data; using manual value</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>fetch-fallback</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>AIN 6020022027 (Los Angeles) has no current roll data; using manual value</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>fetch-fallback</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>AIN 2125017014 (Los Angeles) has no current roll data; using manual value</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>AIN 41416654 (Alameda): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>AIN 5036031006 (Los Angeles): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>AIN (none) (Santa Barbara): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>AIN 5539028040 (Los Angeles): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>AIN (none) (Contra Costa): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>AIN 46745075 (Santa Clara): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>AIN 46745074 (Santa Clara): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>AIN 46745073 (Santa Clara): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>AIN (none) (Santa Clara): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>fetch-fallback</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>AIN 128101150 (Solano) has no current roll data; using manual value</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>fetch-fallback</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>AIN 128101050 (Solano) has no current roll data; using manual value</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>fetch-fallback</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>AIN 128105060 (Solano) has no current roll data; using manual value</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>182/76</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>AIN 5036031006 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>200/218</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>AIN 5040021006 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>130/179</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>AIN 5080006008 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>126/173</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>AIN 5094005005 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>127/174</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>AIN 5094006003 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>122/165</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>AIN 5094017020 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>124/169</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>AIN 5094023025 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>128/175</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>AIN 5502019004 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>125/170</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>AIN 5503024012 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>129/177</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>AIN 5517005016 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>121/162</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>AIN 5518013024 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>123/168</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>AIN 5518020021 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>135/220</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>AIN 5518026004 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>10/132</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>AIN 6020022027 assigned to multiple projects</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>shared-ain</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>152/181</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
         <is>
           <t>AIN 7157012017 assigned to multiple projects</t>
         </is>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ307"/>
+  <dimension ref="A1:AL307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -483,7 +483,9 @@
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
     <col width="12" customWidth="1" min="35" max="35"/>
-    <col width="38" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="38" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -659,10 +661,20 @@
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
+          <t>scc_number</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>scc_issue_date</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>row_source</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>field_overrides</t>
         </is>
@@ -779,24 +791,29 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>1136 S. Alvarado Street, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AH2" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>12657</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>2023-11-30</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>generated</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -911,9 +928,9 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>2025 New Jersey St, Los Angeles, CA</t>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>2025 New Jersey St., Los Angeles, CA</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -921,19 +938,29 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AH3" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AI3" s="2" t="inlineStr">
+        <is>
+          <t>12635</t>
+        </is>
+      </c>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>built:collaborator-sheet; scc_filed:collaborator-sheet; investor_1:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>built:collaborator-sheet; investor_1:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -1053,19 +1080,29 @@
           <t>660 Mariposa Ave., Mountain View, CA</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AH4" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>10889</t>
+        </is>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>2024-01-11</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -1175,19 +1212,29 @@
           <t>363 E. Gilbert St., San Bernardino, CA</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AH5" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AI5" s="2" t="inlineStr">
+        <is>
+          <t>12700</t>
+        </is>
+      </c>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-08</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>scc_filed:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -1297,19 +1344,29 @@
           <t>840 17th St, San Diego, CA 92101</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AH6" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AI6" s="2" t="inlineStr">
+        <is>
+          <t>12670</t>
+        </is>
+      </c>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>2023-12-21</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>scc_filed:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1491,12 @@
           <t>381 Turk St., San Francisco, CA</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; city:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -1566,12 +1623,12 @@
           <t>https://www.townhomesongadingapts.com/</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>leasing_link:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -1693,19 +1750,29 @@
           <t>1317 S. Grand St, Los Angeles, CA 90015</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AH9" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AI9" s="2" t="inlineStr">
+        <is>
+          <t>13827</t>
+        </is>
+      </c>
+      <c r="AJ9" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -1830,12 +1897,12 @@
           <t>1411 Flower St, Los Angeles, CA 90015</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>investor_2:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -1952,19 +2019,29 @@
           <t>7518 S. Hoover, Los Angeles, CA 90044</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AH11" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AI11" s="2" t="inlineStr">
+        <is>
+          <t>14953</t>
+        </is>
+      </c>
+      <c r="AJ11" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>investor_2:collaborator-sheet; scc_filed:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>investor_2:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -2089,17 +2166,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AK12" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -2216,24 +2288,34 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>801-809 Waterloo Street, Los Angeles, CA</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>801-809 Waterloo Street, CA</t>
+        </is>
+      </c>
+      <c r="AH13" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AI13" s="2" t="inlineStr">
+        <is>
+          <t>15023</t>
+        </is>
+      </c>
+      <c r="AJ13" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-16</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>restricted_units:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -2363,12 +2445,12 @@
           <t>275 Turk St, San Francisco, CA</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
+      <c r="AK14" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ14" t="inlineStr">
+      <c r="AL14" t="inlineStr">
         <is>
           <t>investor_2:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -2500,19 +2582,29 @@
           <t>https://www.electriclofts.com/</t>
         </is>
       </c>
-      <c r="AH15" t="inlineStr">
+      <c r="AH15" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
+      <c r="AI15" s="2" t="inlineStr">
+        <is>
+          <t>15324</t>
+        </is>
+      </c>
+      <c r="AJ15" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>leasing_link:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>leasing_link:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -2642,12 +2734,12 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AK16" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
+      <c r="AL16" t="inlineStr">
         <is>
           <t>built:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -2774,12 +2866,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
+      <c r="AK17" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
+      <c r="AL17" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -2916,19 +3008,29 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="AH18" t="inlineStr">
+      <c r="AH18" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
+      <c r="AI18" s="2" t="inlineStr">
+        <is>
+          <t>14929</t>
+        </is>
+      </c>
+      <c r="AJ18" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -3058,19 +3160,29 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="AH19" t="inlineStr">
+      <c r="AH19" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
+      <c r="AI19" s="2" t="inlineStr">
+        <is>
+          <t>14935</t>
+        </is>
+      </c>
+      <c r="AJ19" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>built:collaborator-sheet; scc_filed:collaborator-sheet; city:collaborator-sheet; nonprofit_partner:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>built:collaborator-sheet; city:collaborator-sheet; nonprofit_partner:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -3200,19 +3312,29 @@
           <t>1969</t>
         </is>
       </c>
-      <c r="AH20" t="inlineStr">
+      <c r="AH20" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
+      <c r="AI20" s="2" t="inlineStr">
+        <is>
+          <t>14928</t>
+        </is>
+      </c>
+      <c r="AJ20" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>investor_2:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>investor_2:collaborator-sheet; built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -3342,19 +3464,29 @@
           <t>2024-06-28</t>
         </is>
       </c>
-      <c r="AH21" t="inlineStr">
+      <c r="AH21" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
+      <c r="AI21" s="2" t="inlineStr">
+        <is>
+          <t>14877</t>
+        </is>
+      </c>
+      <c r="AJ21" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -3484,19 +3616,29 @@
           <t>2024-06-13</t>
         </is>
       </c>
-      <c r="AH22" t="inlineStr">
+      <c r="AH22" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
+      <c r="AI22" s="2" t="inlineStr">
+        <is>
+          <t>14877</t>
+        </is>
+      </c>
+      <c r="AJ22" s="2" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -3621,19 +3763,29 @@
           <t>1989</t>
         </is>
       </c>
-      <c r="AH23" t="inlineStr">
+      <c r="AH23" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
+      <c r="AI23" s="2" t="inlineStr">
+        <is>
+          <t>14906</t>
+        </is>
+      </c>
+      <c r="AJ23" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-21</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>built:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -3748,9 +3900,9 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>445 N. Avalon Boulevard, Los Angeles, CA</t>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>445 N Avalon Blvd</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3758,14 +3910,14 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
+      <c r="AK24" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -3880,19 +4032,29 @@
           <t>4209 S Western Ave, Los Angeles, CA 90062</t>
         </is>
       </c>
-      <c r="AH25" t="inlineStr">
+      <c r="AH25" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
+      <c r="AI25" s="2" t="inlineStr">
+        <is>
+          <t>14952</t>
+        </is>
+      </c>
+      <c r="AJ25" s="2" t="inlineStr">
+        <is>
+          <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>scc_filed:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>resolution:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -4007,19 +4169,29 @@
           <t>1130 W Martin Luther King Jr Blvd, Los Angeles, CA 90037</t>
         </is>
       </c>
-      <c r="AH26" t="inlineStr">
+      <c r="AH26" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
+      <c r="AI26" s="2" t="inlineStr">
+        <is>
+          <t>14954</t>
+        </is>
+      </c>
+      <c r="AJ26" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-02</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -4144,19 +4316,29 @@
           <t>1987</t>
         </is>
       </c>
-      <c r="AH27" t="inlineStr">
+      <c r="AH27" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
+      <c r="AI27" s="2" t="inlineStr">
+        <is>
+          <t>15006</t>
+        </is>
+      </c>
+      <c r="AJ27" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-03</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>built:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -4301,19 +4483,29 @@
           <t>https://www.1422on6th.com/</t>
         </is>
       </c>
-      <c r="AH28" t="inlineStr">
+      <c r="AH28" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
+      <c r="AI28" s="2" t="inlineStr">
+        <is>
+          <t>14975</t>
+        </is>
+      </c>
+      <c r="AJ28" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; link:collaborator-sheet; scc_filed:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; link:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -4433,19 +4625,29 @@
           <t>1422-1432 7th, Santa Monica, CA</t>
         </is>
       </c>
-      <c r="AH29" t="inlineStr">
+      <c r="AH29" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
+      <c r="AI29" s="2" t="inlineStr">
+        <is>
+          <t>14977</t>
+        </is>
+      </c>
+      <c r="AJ29" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>scc_filed:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -4565,19 +4767,29 @@
           <t>1423-1425 6th, Santa Monica, CA</t>
         </is>
       </c>
-      <c r="AH30" t="inlineStr">
+      <c r="AH30" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
+      <c r="AI30" s="2" t="inlineStr">
+        <is>
+          <t>14984</t>
+        </is>
+      </c>
+      <c r="AJ30" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-23</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>scc_filed:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -4702,19 +4914,29 @@
           <t>2004</t>
         </is>
       </c>
-      <c r="AH31" t="inlineStr">
+      <c r="AH31" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
+      <c r="AI31" s="2" t="inlineStr">
+        <is>
+          <t>14983</t>
+        </is>
+      </c>
+      <c r="AJ31" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-29</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>built:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -4844,19 +5066,29 @@
           <t>2024-09-12</t>
         </is>
       </c>
-      <c r="AH32" t="inlineStr">
+      <c r="AH32" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
+      <c r="AI32" s="2" t="inlineStr">
+        <is>
+          <t>14985</t>
+        </is>
+      </c>
+      <c r="AJ32" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-17</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -4981,19 +5213,29 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="AH33" t="inlineStr">
+      <c r="AH33" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI33" t="inlineStr">
+      <c r="AI33" s="2" t="inlineStr">
+        <is>
+          <t>14980</t>
+        </is>
+      </c>
+      <c r="AJ33" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>built:collaborator-sheet; scc_filed:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>built:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -5128,12 +5370,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI34" t="inlineStr">
+      <c r="AK34" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ34" t="inlineStr">
+      <c r="AL34" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -5255,19 +5497,29 @@
           <t>4481 Appian Way, El Sobrante, CA 94803</t>
         </is>
       </c>
-      <c r="AH35" t="inlineStr">
+      <c r="AH35" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr">
+      <c r="AI35" s="2" t="inlineStr">
+        <is>
+          <t>15050</t>
+        </is>
+      </c>
+      <c r="AJ35" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>scc_filed:collaborator-sheet; city:collaborator-sheet; county:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>city:collaborator-sheet; county:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -5382,19 +5634,29 @@
           <t>4930 Polk St, North Highlands, CA 95660</t>
         </is>
       </c>
-      <c r="AH36" t="inlineStr">
+      <c r="AH36" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI36" t="inlineStr">
+      <c r="AI36" s="2" t="inlineStr">
+        <is>
+          <t>15049</t>
+        </is>
+      </c>
+      <c r="AJ36" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>scc_filed:collaborator-sheet; city:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>city:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -5504,25 +5766,34 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>9301 – 9609 Crenshaw
-Blvd, Inglewood, CA</t>
-        </is>
-      </c>
-      <c r="AH37" t="inlineStr">
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>9301 – 9609 Crenshaw</t>
+        </is>
+      </c>
+      <c r="AH37" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI37" t="inlineStr">
+      <c r="AI37" s="2" t="inlineStr">
+        <is>
+          <t>15124</t>
+        </is>
+      </c>
+      <c r="AJ37" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>scc_filed:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>resolution:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -5642,19 +5913,29 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AH38" t="inlineStr">
+      <c r="AH38" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI38" t="inlineStr">
+      <c r="AI38" s="2" t="inlineStr">
+        <is>
+          <t>15139</t>
+        </is>
+      </c>
+      <c r="AJ38" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; property_name:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; property_name:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -5784,19 +6065,29 @@
           <t>1965</t>
         </is>
       </c>
-      <c r="AH39" t="inlineStr">
+      <c r="AH39" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI39" t="inlineStr">
+      <c r="AI39" s="2" t="inlineStr">
+        <is>
+          <t>15055</t>
+        </is>
+      </c>
+      <c r="AJ39" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-06</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -5916,19 +6207,29 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AH40" t="inlineStr">
+      <c r="AH40" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI40" t="inlineStr">
+      <c r="AI40" s="2" t="inlineStr">
+        <is>
+          <t>15215</t>
+        </is>
+      </c>
+      <c r="AJ40" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -6058,12 +6359,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI41" t="inlineStr">
+      <c r="AK41" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ41" t="inlineStr">
+      <c r="AL41" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -6190,12 +6491,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI42" t="inlineStr">
+      <c r="AK42" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ42" t="inlineStr">
+      <c r="AL42" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -6327,12 +6628,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI43" t="inlineStr">
+      <c r="AK43" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ43" t="inlineStr">
+      <c r="AL43" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -6469,12 +6770,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI44" t="inlineStr">
+      <c r="AK44" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ44" t="inlineStr">
+      <c r="AL44" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -6601,19 +6902,29 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AH45" t="inlineStr">
+      <c r="AH45" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI45" t="inlineStr">
+      <c r="AI45" s="2" t="inlineStr">
+        <is>
+          <t>15180</t>
+        </is>
+      </c>
+      <c r="AJ45" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -6743,19 +7054,29 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AH46" t="inlineStr">
+      <c r="AH46" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI46" t="inlineStr">
+      <c r="AI46" s="2" t="inlineStr">
+        <is>
+          <t>14961</t>
+        </is>
+      </c>
+      <c r="AJ46" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -6885,12 +7206,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI47" t="inlineStr">
+      <c r="AK47" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ47" t="inlineStr">
+      <c r="AL47" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -7017,19 +7338,29 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AH48" t="inlineStr">
+      <c r="AH48" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI48" t="inlineStr">
+      <c r="AI48" s="2" t="inlineStr">
+        <is>
+          <t>15001</t>
+        </is>
+      </c>
+      <c r="AJ48" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -7159,17 +7490,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
+      <c r="AK49" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ49" t="inlineStr">
+      <c r="AL49" t="inlineStr">
         <is>
           <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; scc_filed:collaborator-sheet; investor_1:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -7291,12 +7617,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI50" t="inlineStr">
+      <c r="AK50" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ50" t="inlineStr">
+      <c r="AL50" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; entity:collaborator-sheet; investor_1:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -7423,19 +7749,29 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AH51" t="inlineStr">
+      <c r="AH51" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI51" t="inlineStr">
+      <c r="AI51" s="2" t="inlineStr">
+        <is>
+          <t>15201</t>
+        </is>
+      </c>
+      <c r="AJ51" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -7575,12 +7911,12 @@
           <t>1984</t>
         </is>
       </c>
-      <c r="AI52" t="inlineStr">
+      <c r="AK52" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ52" t="inlineStr">
+      <c r="AL52" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet; manual_status:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -7712,12 +8048,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI53" t="inlineStr">
+      <c r="AK53" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ53" t="inlineStr">
+      <c r="AL53" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; city:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -7854,12 +8190,12 @@
           <t>1973/1991</t>
         </is>
       </c>
-      <c r="AI54" t="inlineStr">
+      <c r="AK54" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ54" t="inlineStr">
+      <c r="AL54" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet; manual_status:collaborator-sheet; city:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -7971,9 +8307,9 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>5601 North Paramount Boulevard, Long Beach, Los Angeles</t>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5601 North Paramount Boulevard</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
@@ -7981,19 +8317,29 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AH55" t="inlineStr">
+      <c r="AH55" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI55" t="inlineStr">
+      <c r="AI55" s="2" t="inlineStr">
+        <is>
+          <t>15075</t>
+        </is>
+      </c>
+      <c r="AJ55" s="2" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; resolution:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; resolution:collaborator-sheet; total_units:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -8113,9 +8459,9 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>1457 N Main St, Los Angeles, CA 90012</t>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>1457 North Main Street, Los Angeles, CA</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
@@ -8123,19 +8469,29 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AH56" t="inlineStr">
+      <c r="AH56" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI56" t="inlineStr">
+      <c r="AI56" s="2" t="inlineStr">
+        <is>
+          <t>15083</t>
+        </is>
+      </c>
+      <c r="AJ56" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -8260,12 +8616,12 @@
           <t>https://bridgehousing.com/properties/viewpoint/</t>
         </is>
       </c>
-      <c r="AI57" t="inlineStr">
+      <c r="AK57" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ57" t="inlineStr">
+      <c r="AL57" t="inlineStr">
         <is>
           <t>leasing_link:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -8422,19 +8778,29 @@
           <t>https://www.losgatoslandingapts.com/</t>
         </is>
       </c>
-      <c r="AH58" t="inlineStr">
+      <c r="AH58" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI58" t="inlineStr">
+      <c r="AI58" s="2" t="inlineStr">
+        <is>
+          <t>15099</t>
+        </is>
+      </c>
+      <c r="AJ58" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; built:collaborator-sheet; acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; link:collaborator-sheet; leasing_link:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; built:collaborator-sheet; acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; link:collaborator-sheet; leasing_link:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -8559,17 +8925,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
+      <c r="AK59" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ59" t="inlineStr">
+      <c r="AL59" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -8696,19 +9057,29 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="AH60" t="inlineStr">
+      <c r="AH60" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI60" t="inlineStr">
+      <c r="AI60" s="2" t="inlineStr">
+        <is>
+          <t>15117</t>
+        </is>
+      </c>
+      <c r="AJ60" s="2" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; city:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; city:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -8833,12 +9204,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI61" t="inlineStr">
+      <c r="AK61" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ61" t="inlineStr">
+      <c r="AL61" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; entity:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -8955,12 +9326,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI62" t="inlineStr">
+      <c r="AK62" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ62" t="inlineStr">
+      <c r="AL62" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; resolution:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -9087,19 +9458,29 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AH63" t="inlineStr">
+      <c r="AH63" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI63" t="inlineStr">
+      <c r="AI63" s="2" t="inlineStr">
+        <is>
+          <t>15288</t>
+        </is>
+      </c>
+      <c r="AJ63" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -9214,19 +9595,29 @@
           <t>3081 N Main St, Walnut Creek, CA 94597</t>
         </is>
       </c>
-      <c r="AH64" t="inlineStr">
+      <c r="AH64" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI64" t="inlineStr">
+      <c r="AI64" s="2" t="inlineStr">
+        <is>
+          <t>15409</t>
+        </is>
+      </c>
+      <c r="AJ64" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>scc_filed:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>resolution:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -9336,12 +9727,12 @@
           <t>333 Douglas St, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI65" t="inlineStr">
+      <c r="AK65" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ65" t="inlineStr">
+      <c r="AL65" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; resolution:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -9458,9 +9849,9 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>7777 Valley View Street, La Palma, CA</t>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>7777 Valley View Street</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
@@ -9473,19 +9864,29 @@
           <t>1978</t>
         </is>
       </c>
-      <c r="AH66" t="inlineStr">
+      <c r="AH66" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI66" t="inlineStr">
+      <c r="AI66" s="2" t="inlineStr">
+        <is>
+          <t>5381</t>
+        </is>
+      </c>
+      <c r="AJ66" s="2" t="inlineStr">
+        <is>
+          <t>2012-02-08</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -9610,12 +10011,12 @@
           <t>920 S. Gramercy Place, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI67" t="inlineStr">
+      <c r="AK67" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ67" t="inlineStr">
+      <c r="AL67" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -9732,24 +10133,29 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="Z68" s="2" t="inlineStr">
         <is>
           <t>1250 S. Euclid St., Anaheim, CA</t>
         </is>
       </c>
-      <c r="AH68" t="inlineStr">
+      <c r="AH68" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI68" t="inlineStr">
+      <c r="AI68" s="2" t="inlineStr">
+        <is>
+          <t>15295</t>
+        </is>
+      </c>
+      <c r="AJ68" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
         <is>
           <t>generated</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -9879,19 +10285,29 @@
           <t>1964</t>
         </is>
       </c>
-      <c r="AH69" t="inlineStr">
+      <c r="AH69" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI69" t="inlineStr">
+      <c r="AI69" s="2" t="inlineStr">
+        <is>
+          <t>15230</t>
+        </is>
+      </c>
+      <c r="AJ69" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL69" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -10016,12 +10432,12 @@
           <t>10535 Lindley Ave, Granada Hills, CA 91326</t>
         </is>
       </c>
-      <c r="AI70" t="inlineStr">
+      <c r="AK70" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ70" t="inlineStr">
+      <c r="AL70" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -10148,12 +10564,12 @@
           <t>26 Terrace View Ct, Daly City, CA 94015</t>
         </is>
       </c>
-      <c r="AI71" t="inlineStr">
+      <c r="AK71" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ71" t="inlineStr">
+      <c r="AL71" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -10285,12 +10701,12 @@
           <t>https://www.theheltsley.com/</t>
         </is>
       </c>
-      <c r="AI72" t="inlineStr">
+      <c r="AK72" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ72" t="inlineStr">
+      <c r="AL72" t="inlineStr">
         <is>
           <t>acquisition_date:collaborator-sheet; leasing_link:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -10427,12 +10843,12 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="AI73" t="inlineStr">
+      <c r="AK73" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ73" t="inlineStr">
+      <c r="AL73" t="inlineStr">
         <is>
           <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; built:collaborator-sheet; city:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -10559,19 +10975,29 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AH74" t="inlineStr">
+      <c r="AH74" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI74" t="inlineStr">
+      <c r="AI74" s="2" t="inlineStr">
+        <is>
+          <t>15352</t>
+        </is>
+      </c>
+      <c r="AJ74" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL74" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -10696,17 +11122,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
+      <c r="AK75" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ75" t="inlineStr">
+      <c r="AL75" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -10838,12 +11259,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI76" t="inlineStr">
+      <c r="AK76" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ76" t="inlineStr">
+      <c r="AL76" t="inlineStr">
         <is>
           <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -10970,12 +11391,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI77" t="inlineStr">
+      <c r="AK77" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ77" t="inlineStr">
+      <c r="AL77" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -11102,12 +11523,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI78" t="inlineStr">
+      <c r="AK78" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ78" t="inlineStr">
+      <c r="AL78" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -11244,19 +11665,29 @@
           <t>https://www.cmfa-ca.com/wp-content/uploads/2025/01/CMFA-Staff-Reports-01-10-25.pdf</t>
         </is>
       </c>
-      <c r="AH79" t="inlineStr">
+      <c r="AH79" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI79" t="inlineStr">
+      <c r="AI79" s="2" t="inlineStr">
+        <is>
+          <t>15252</t>
+        </is>
+      </c>
+      <c r="AJ79" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; link:collaborator-sheet; scc_filed:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL79" t="inlineStr">
+        <is>
+          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; link:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -11381,12 +11812,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI80" t="inlineStr">
+      <c r="AK80" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ80" t="inlineStr">
+      <c r="AL80" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -11513,12 +11944,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI81" t="inlineStr">
+      <c r="AK81" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ81" t="inlineStr">
+      <c r="AL81" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -11645,12 +12076,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI82" t="inlineStr">
+      <c r="AK82" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ82" t="inlineStr">
+      <c r="AL82" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -11777,12 +12208,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI83" t="inlineStr">
+      <c r="AK83" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ83" t="inlineStr">
+      <c r="AL83" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -11909,12 +12340,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI84" t="inlineStr">
+      <c r="AK84" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ84" t="inlineStr">
+      <c r="AL84" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -12041,12 +12472,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI85" t="inlineStr">
+      <c r="AK85" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ85" t="inlineStr">
+      <c r="AL85" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -12173,12 +12604,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI86" t="inlineStr">
+      <c r="AK86" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ86" t="inlineStr">
+      <c r="AL86" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -12305,12 +12736,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI87" t="inlineStr">
+      <c r="AK87" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ87" t="inlineStr">
+      <c r="AL87" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -12442,19 +12873,29 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AH88" t="inlineStr">
+      <c r="AH88" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI88" t="inlineStr">
+      <c r="AI88" s="2" t="inlineStr">
+        <is>
+          <t>15376</t>
+        </is>
+      </c>
+      <c r="AJ88" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL88" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -12579,12 +13020,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI89" t="inlineStr">
+      <c r="AK89" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ89" t="inlineStr">
+      <c r="AL89" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -12711,12 +13152,12 @@
           <t>2025-09-03</t>
         </is>
       </c>
-      <c r="AI90" t="inlineStr">
+      <c r="AK90" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ90" t="inlineStr">
+      <c r="AL90" t="inlineStr">
         <is>
           <t>acquisition_date:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -12843,12 +13284,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI91" t="inlineStr">
+      <c r="AK91" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ91" t="inlineStr">
+      <c r="AL91" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -12975,12 +13416,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI92" t="inlineStr">
+      <c r="AK92" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ92" t="inlineStr">
+      <c r="AL92" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -13107,19 +13548,29 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AH93" t="inlineStr">
+      <c r="AH93" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI93" t="inlineStr">
+      <c r="AI93" s="2" t="inlineStr">
+        <is>
+          <t>15354</t>
+        </is>
+      </c>
+      <c r="AJ93" s="2" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL93" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -13239,12 +13690,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI94" t="inlineStr">
+      <c r="AK94" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ94" t="inlineStr">
+      <c r="AL94" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; resolution:collaborator-sheet; nonprofit_partner:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -13376,19 +13827,29 @@
           <t>1981</t>
         </is>
       </c>
-      <c r="AH95" t="inlineStr">
+      <c r="AH95" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI95" t="inlineStr">
+      <c r="AI95" s="2" t="inlineStr">
+        <is>
+          <t>15328</t>
+        </is>
+      </c>
+      <c r="AJ95" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL95" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -13518,19 +13979,29 @@
           <t>https://rebusinessonline.com/sack-properties-belveron-partners-buy-164-unit-multifamily-property-in-san-jose-california/</t>
         </is>
       </c>
-      <c r="AH96" t="inlineStr">
+      <c r="AH96" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI96" t="inlineStr">
+      <c r="AI96" s="2" t="inlineStr">
+        <is>
+          <t>15311</t>
+        </is>
+      </c>
+      <c r="AJ96" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>investor_2:collaborator-sheet; acquisition_date:collaborator-sheet; link:collaborator-sheet; scc_filed:collaborator-sheet; resolution:collaborator-sheet; investor_1:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL96" t="inlineStr">
+        <is>
+          <t>investor_2:collaborator-sheet; acquisition_date:collaborator-sheet; link:collaborator-sheet; resolution:collaborator-sheet; investor_1:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -13670,19 +14141,29 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AH97" t="inlineStr">
+      <c r="AH97" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI97" t="inlineStr">
+      <c r="AI97" s="2" t="inlineStr">
+        <is>
+          <t>15323</t>
+        </is>
+      </c>
+      <c r="AJ97" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>investor_2:collaborator-sheet; built:collaborator-sheet; acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL97" t="inlineStr">
+        <is>
+          <t>investor_2:collaborator-sheet; built:collaborator-sheet; acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -13807,12 +14288,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI98" t="inlineStr">
+      <c r="AK98" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ98" t="inlineStr">
+      <c r="AL98" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -13949,12 +14430,12 @@
           <t>https://www.camdenvillageapts.com/</t>
         </is>
       </c>
-      <c r="AI99" t="inlineStr">
+      <c r="AK99" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ99" t="inlineStr">
+      <c r="AL99" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; leasing_link:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -14081,19 +14562,29 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AH100" t="inlineStr">
+      <c r="AH100" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI100" t="inlineStr">
+      <c r="AI100" s="2" t="inlineStr">
+        <is>
+          <t>15404</t>
+        </is>
+      </c>
+      <c r="AJ100" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL100" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -14218,19 +14709,29 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AH101" t="inlineStr">
+      <c r="AH101" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI101" t="inlineStr">
+      <c r="AI101" s="2" t="inlineStr">
+        <is>
+          <t>15405</t>
+        </is>
+      </c>
+      <c r="AJ101" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL101" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -14355,19 +14856,29 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AH102" t="inlineStr">
+      <c r="AH102" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI102" t="inlineStr">
+      <c r="AI102" s="2" t="inlineStr">
+        <is>
+          <t>15406</t>
+        </is>
+      </c>
+      <c r="AJ102" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL102" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -14492,19 +15003,29 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AH103" t="inlineStr">
+      <c r="AH103" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI103" t="inlineStr">
+      <c r="AI103" s="2" t="inlineStr">
+        <is>
+          <t>15403</t>
+        </is>
+      </c>
+      <c r="AJ103" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL103" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -14629,12 +15150,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI104" t="inlineStr">
+      <c r="AK104" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ104" t="inlineStr">
+      <c r="AL104" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -14761,12 +15282,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI105" t="inlineStr">
+      <c r="AK105" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ105" t="inlineStr">
+      <c r="AL105" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -14893,12 +15414,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI106" t="inlineStr">
+      <c r="AK106" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ106" t="inlineStr">
+      <c r="AL106" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -15025,12 +15546,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI107" t="inlineStr">
+      <c r="AK107" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ107" t="inlineStr">
+      <c r="AL107" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -15157,12 +15678,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI108" t="inlineStr">
+      <c r="AK108" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ108" t="inlineStr">
+      <c r="AL108" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -15289,12 +15810,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI109" t="inlineStr">
+      <c r="AK109" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ109" t="inlineStr">
+      <c r="AL109" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -15421,12 +15942,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI110" t="inlineStr">
+      <c r="AK110" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ110" t="inlineStr">
+      <c r="AL110" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -15553,12 +16074,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI111" t="inlineStr">
+      <c r="AK111" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ111" t="inlineStr">
+      <c r="AL111" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -15675,12 +16196,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI112" t="inlineStr">
+      <c r="AK112" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ112" t="inlineStr">
+      <c r="AL112" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -15807,12 +16328,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI113" t="inlineStr">
+      <c r="AK113" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ113" t="inlineStr">
+      <c r="AL113" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -15939,12 +16460,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI114" t="inlineStr">
+      <c r="AK114" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ114" t="inlineStr">
+      <c r="AL114" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -16071,12 +16592,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI115" t="inlineStr">
+      <c r="AK115" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ115" t="inlineStr">
+      <c r="AL115" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -16203,12 +16724,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI116" t="inlineStr">
+      <c r="AK116" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ116" t="inlineStr">
+      <c r="AL116" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -16335,12 +16856,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI117" t="inlineStr">
+      <c r="AK117" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ117" t="inlineStr">
+      <c r="AL117" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -16467,12 +16988,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI118" t="inlineStr">
+      <c r="AK118" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ118" t="inlineStr">
+      <c r="AL118" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -16599,12 +17120,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI119" t="inlineStr">
+      <c r="AK119" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ119" t="inlineStr">
+      <c r="AL119" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -16721,12 +17242,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI120" t="inlineStr">
+      <c r="AK120" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ120" t="inlineStr">
+      <c r="AL120" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -16853,19 +17374,29 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AH121" t="inlineStr">
+      <c r="AH121" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI121" t="inlineStr">
+      <c r="AI121" s="2" t="inlineStr">
+        <is>
+          <t>15388</t>
+        </is>
+      </c>
+      <c r="AJ121" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; city:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+      <c r="AL121" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; city:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -16985,12 +17516,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI122" t="inlineStr">
+      <c r="AK122" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ122" t="inlineStr">
+      <c r="AL122" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -17122,12 +17653,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI123" t="inlineStr">
+      <c r="AK123" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ123" t="inlineStr">
+      <c r="AL123" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -17259,12 +17790,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI124" t="inlineStr">
+      <c r="AK124" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ124" t="inlineStr">
+      <c r="AL124" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -17396,12 +17927,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI125" t="inlineStr">
+      <c r="AK125" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ125" t="inlineStr">
+      <c r="AL125" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -17533,12 +18064,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI126" t="inlineStr">
+      <c r="AK126" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ126" t="inlineStr">
+      <c r="AL126" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; property_name:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -17670,12 +18201,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI127" t="inlineStr">
+      <c r="AK127" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ127" t="inlineStr">
+      <c r="AL127" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -17807,12 +18338,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI128" t="inlineStr">
+      <c r="AK128" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ128" t="inlineStr">
+      <c r="AL128" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -17944,12 +18475,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI129" t="inlineStr">
+      <c r="AK129" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ129" t="inlineStr">
+      <c r="AL129" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -18081,12 +18612,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI130" t="inlineStr">
+      <c r="AK130" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ130" t="inlineStr">
+      <c r="AL130" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -18218,12 +18749,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI131" t="inlineStr">
+      <c r="AK131" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ131" t="inlineStr">
+      <c r="AL131" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -18350,12 +18881,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI132" t="inlineStr">
+      <c r="AK132" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ132" t="inlineStr">
+      <c r="AL132" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -18477,12 +19008,12 @@
           <t>7524 S. Hoover St, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI133" t="inlineStr">
+      <c r="AK133" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ133" t="inlineStr">
+      <c r="AL133" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -18609,12 +19140,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI134" t="inlineStr">
+      <c r="AK134" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ134" t="inlineStr">
+      <c r="AL134" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -18746,12 +19277,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI135" t="inlineStr">
+      <c r="AK135" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ135" t="inlineStr">
+      <c r="AL135" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -18863,12 +19394,12 @@
           <t>December, 2025</t>
         </is>
       </c>
-      <c r="AI136" t="inlineStr">
+      <c r="AK136" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ136" t="inlineStr">
+      <c r="AL136" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -18990,12 +19521,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI137" t="inlineStr">
+      <c r="AK137" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ137" t="inlineStr">
+      <c r="AL137" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -19122,19 +19653,29 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AH138" t="inlineStr">
+      <c r="AH138" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI138" t="inlineStr">
+      <c r="AI138" s="2" t="inlineStr">
+        <is>
+          <t>15461</t>
+        </is>
+      </c>
+      <c r="AJ138" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; city:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL138" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; city:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -19259,12 +19800,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI139" t="inlineStr">
+      <c r="AK139" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ139" t="inlineStr">
+      <c r="AL139" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; nonprofit_partner:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -19391,12 +19932,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI140" t="inlineStr">
+      <c r="AK140" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ140" t="inlineStr">
+      <c r="AL140" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -19523,12 +20064,12 @@
           <t>1984</t>
         </is>
       </c>
-      <c r="AI141" t="inlineStr">
+      <c r="AK141" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ141" t="inlineStr">
+      <c r="AL141" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -19645,12 +20186,12 @@
           <t>9033 Ramsgate Avenue, Westchester, CA</t>
         </is>
       </c>
-      <c r="AI142" t="inlineStr">
+      <c r="AK142" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ142" t="inlineStr">
+      <c r="AL142" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -19777,19 +20318,29 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AH143" t="inlineStr">
+      <c r="AH143" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI143" t="inlineStr">
+      <c r="AI143" s="2" t="inlineStr">
+        <is>
+          <t>7474</t>
+        </is>
+      </c>
+      <c r="AJ143" s="2" t="inlineStr">
+        <is>
+          <t>2018-10-12</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL143" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -19914,12 +20465,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI144" t="inlineStr">
+      <c r="AK144" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ144" t="inlineStr">
+      <c r="AL144" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; property_name:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -20041,12 +20592,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI145" t="inlineStr">
+      <c r="AK145" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ145" t="inlineStr">
+      <c r="AL145" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -20173,12 +20724,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI146" t="inlineStr">
+      <c r="AK146" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ146" t="inlineStr">
+      <c r="AL146" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -20310,19 +20861,29 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AH147" t="inlineStr">
+      <c r="AH147" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AI147" t="inlineStr">
+      <c r="AI147" s="2" t="inlineStr">
+        <is>
+          <t>7474</t>
+        </is>
+      </c>
+      <c r="AJ147" s="2" t="inlineStr">
+        <is>
+          <t>2018-10-12</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ147" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL147" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -20442,9 +21003,9 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>2424 Wilshire Blvd, Los Angeles, CA 90057</t>
+      <c r="Z148" s="2" t="inlineStr">
+        <is>
+          <t>2424 Wilshire</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
@@ -20457,14 +21018,14 @@
           <t>1929</t>
         </is>
       </c>
-      <c r="AI148" t="inlineStr">
+      <c r="AK148" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
+      <c r="AL148" t="inlineStr">
+        <is>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; manual_status:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -20594,12 +21155,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI149" t="inlineStr">
+      <c r="AK149" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ149" t="inlineStr">
+      <c r="AL149" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -20731,12 +21292,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI150" t="inlineStr">
+      <c r="AK150" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ150" t="inlineStr">
+      <c r="AL150" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -20868,12 +21429,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI151" t="inlineStr">
+      <c r="AK151" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ151" t="inlineStr">
+      <c r="AL151" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -21000,12 +21561,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI152" t="inlineStr">
+      <c r="AK152" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ152" t="inlineStr">
+      <c r="AL152" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -21137,12 +21698,12 @@
           <t>1990</t>
         </is>
       </c>
-      <c r="AI153" t="inlineStr">
+      <c r="AK153" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ153" t="inlineStr">
+      <c r="AL153" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -21269,12 +21830,12 @@
           <t>NO/YES</t>
         </is>
       </c>
-      <c r="AI154" t="inlineStr">
+      <c r="AK154" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ154" t="inlineStr">
+      <c r="AL154" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -21406,12 +21967,12 @@
           <t>1974</t>
         </is>
       </c>
-      <c r="AI155" t="inlineStr">
+      <c r="AK155" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ155" t="inlineStr">
+      <c r="AL155" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -21543,12 +22104,12 @@
           <t>1969</t>
         </is>
       </c>
-      <c r="AI156" t="inlineStr">
+      <c r="AK156" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ156" t="inlineStr">
+      <c r="AL156" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -21640,12 +22201,12 @@
           <t>439 West El Norte Parkway / 1045 Morning View Drive, Escondido, CA</t>
         </is>
       </c>
-      <c r="AI157" t="inlineStr">
+      <c r="AK157" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ157" t="inlineStr">
+      <c r="AL157" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -21767,17 +22328,22 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
+      <c r="Z158" s="2" t="inlineStr">
+        <is>
+          <t>452 square feet that were designed to support independent living and housing stability. Every unit will include a private bathroom, kitchen</t>
+        </is>
+      </c>
       <c r="AB158" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AI158" t="inlineStr">
+      <c r="AK158" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ158" t="inlineStr">
+      <c r="AL158" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; total_units:collaborator-sheet</t>
         </is>
@@ -21899,12 +22465,12 @@
           <t>1141 N. Vermont Avenue, Los Angeles, CA 90029</t>
         </is>
       </c>
-      <c r="AI159" t="inlineStr">
+      <c r="AK159" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ159" t="inlineStr">
+      <c r="AL159" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -22036,12 +22602,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI160" t="inlineStr">
+      <c r="AK160" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ160" t="inlineStr">
+      <c r="AL160" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -22163,12 +22729,12 @@
           <t>2933 W. 8th Street, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI161" t="inlineStr">
+      <c r="AK161" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ161" t="inlineStr">
+      <c r="AL161" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -22280,12 +22846,12 @@
           <t>130 S. Alexandria Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI162" t="inlineStr">
+      <c r="AK162" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ162" t="inlineStr">
+      <c r="AL162" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -22407,12 +22973,12 @@
           <t>437 N. Ardmore Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI163" t="inlineStr">
+      <c r="AK163" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ163" t="inlineStr">
+      <c r="AL163" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -22534,12 +23100,12 @@
           <t>249 S. Ave 55, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI164" t="inlineStr">
+      <c r="AK164" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ164" t="inlineStr">
+      <c r="AL164" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -22661,12 +23227,12 @@
           <t>861 Fedora Street, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI165" t="inlineStr">
+      <c r="AK165" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ165" t="inlineStr">
+      <c r="AL165" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -22788,12 +23354,12 @@
           <t>516 N. Harvard Boulevard, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI166" t="inlineStr">
+      <c r="AK166" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ166" t="inlineStr">
+      <c r="AL166" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -22915,12 +23481,12 @@
           <t>5200 Hollywood Boulevard, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI167" t="inlineStr">
+      <c r="AK167" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ167" t="inlineStr">
+      <c r="AL167" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -23042,12 +23608,12 @@
           <t>200 S. Kenmore Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI168" t="inlineStr">
+      <c r="AK168" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ168" t="inlineStr">
+      <c r="AL168" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -23169,12 +23735,12 @@
           <t>915 S. Kenmore Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI169" t="inlineStr">
+      <c r="AK169" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ169" t="inlineStr">
+      <c r="AL169" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -23296,12 +23862,12 @@
           <t>530 Kingsley Drive, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI170" t="inlineStr">
+      <c r="AK170" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ170" t="inlineStr">
+      <c r="AL170" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -23423,12 +23989,12 @@
           <t>5406 Lexington Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI171" t="inlineStr">
+      <c r="AK171" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ171" t="inlineStr">
+      <c r="AL171" t="inlineStr">
         <is>
           <t>address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -23540,12 +24106,12 @@
           <t>410 S. Manhattan Place / 509 S. Manhattan Place, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI172" t="inlineStr">
+      <c r="AK172" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ172" t="inlineStr">
+      <c r="AL172" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -23667,12 +24233,12 @@
           <t>727 S. Mariposa Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI173" t="inlineStr">
+      <c r="AK173" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ173" t="inlineStr">
+      <c r="AL173" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -23794,12 +24360,12 @@
           <t>750-752 S. Mariposa Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI174" t="inlineStr">
+      <c r="AK174" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ174" t="inlineStr">
+      <c r="AL174" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -23921,12 +24487,12 @@
           <t>520 S. Mariposa Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI175" t="inlineStr">
+      <c r="AK175" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ175" t="inlineStr">
+      <c r="AL175" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -24048,12 +24614,12 @@
           <t>5635 Monte Vista Street, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI176" t="inlineStr">
+      <c r="AK176" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ176" t="inlineStr">
+      <c r="AL176" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -24175,12 +24741,12 @@
           <t>207 S. Oxford St, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI177" t="inlineStr">
+      <c r="AK177" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ177" t="inlineStr">
+      <c r="AL177" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -24302,12 +24868,12 @@
           <t>300 W. Avenue 37, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI178" t="inlineStr">
+      <c r="AK178" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ178" t="inlineStr">
+      <c r="AL178" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -24429,12 +24995,12 @@
           <t>1057 S. Western Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI179" t="inlineStr">
+      <c r="AK179" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ179" t="inlineStr">
+      <c r="AL179" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -24546,12 +25112,12 @@
           <t>132 S. Westmoreland Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI180" t="inlineStr">
+      <c r="AK180" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ180" t="inlineStr">
+      <c r="AL180" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -24678,12 +25244,12 @@
           <t>5565 &amp; 5575 Ackerfield Avenue, Long Beach, CA</t>
         </is>
       </c>
-      <c r="AI181" t="inlineStr">
+      <c r="AK181" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ181" t="inlineStr">
+      <c r="AL181" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; city:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -24820,12 +25386,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI182" t="inlineStr">
+      <c r="AK182" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ182" t="inlineStr">
+      <c r="AL182" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -24952,12 +25518,12 @@
           <t>4256 Whittier Blvd Apartments, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AI183" t="inlineStr">
+      <c r="AK183" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ183" t="inlineStr">
+      <c r="AL183" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -25084,12 +25650,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI184" t="inlineStr">
+      <c r="AK184" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ184" t="inlineStr">
+      <c r="AL184" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -25216,12 +25782,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI185" t="inlineStr">
+      <c r="AK185" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ185" t="inlineStr">
+      <c r="AL185" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -25348,12 +25914,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI186" t="inlineStr">
+      <c r="AK186" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ186" t="inlineStr">
+      <c r="AL186" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -25480,12 +26046,12 @@
           <t>1987</t>
         </is>
       </c>
-      <c r="AI187" t="inlineStr">
+      <c r="AK187" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ187" t="inlineStr">
+      <c r="AL187" t="inlineStr">
         <is>
           <t>built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -25602,12 +26168,12 @@
           <t>11720 San Pablo Ave, El Cerrito, CA 94530</t>
         </is>
       </c>
-      <c r="AI188" t="inlineStr">
+      <c r="AK188" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ188" t="inlineStr">
+      <c r="AL188" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -25734,12 +26300,12 @@
           <t>1987</t>
         </is>
       </c>
-      <c r="AI189" t="inlineStr">
+      <c r="AK189" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ189" t="inlineStr">
+      <c r="AL189" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -25866,12 +26432,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI190" t="inlineStr">
+      <c r="AK190" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ190" t="inlineStr">
+      <c r="AL190" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -25978,12 +26544,12 @@
           <t>February, 2026</t>
         </is>
       </c>
-      <c r="AI191" t="inlineStr">
+      <c r="AK191" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ191" t="inlineStr">
+      <c r="AL191" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -26077,10 +26643,20 @@
       </c>
       <c r="AI192" t="inlineStr">
         <is>
+          <t>11145</t>
+        </is>
+      </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>2022-12-02</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="AJ192" t="inlineStr">
+      <c r="AL192" t="inlineStr">
         <is>
           <t>*:collaborator-sheet</t>
         </is>
@@ -26167,12 +26743,27 @@
           <t>2549 E. Valley Parkway, Escondido, CA 92027</t>
         </is>
       </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="AI193" t="inlineStr">
         <is>
+          <t>11150</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>2022-12-02</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="AJ193" t="inlineStr">
+      <c r="AL193" t="inlineStr">
         <is>
           <t>*:collaborator-sheet</t>
         </is>
@@ -26299,12 +26890,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI194" t="inlineStr">
+      <c r="AK194" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ194" t="inlineStr">
+      <c r="AL194" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -26431,12 +27022,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI195" t="inlineStr">
+      <c r="AK195" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ195" t="inlineStr">
+      <c r="AL195" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -26553,12 +27144,12 @@
           <t>March, 2026</t>
         </is>
       </c>
-      <c r="AI196" t="inlineStr">
+      <c r="AK196" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ196" t="inlineStr">
+      <c r="AL196" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -26680,12 +27271,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI197" t="inlineStr">
+      <c r="AK197" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ197" t="inlineStr">
+      <c r="AL197" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -26802,12 +27393,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI198" t="inlineStr">
+      <c r="AK198" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ198" t="inlineStr">
+      <c r="AL198" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -26929,12 +27520,12 @@
           <t>6840 Baird Ave, Los Angeles, CA 91335</t>
         </is>
       </c>
-      <c r="AI199" t="inlineStr">
+      <c r="AK199" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ199" t="inlineStr">
+      <c r="AL199" t="inlineStr">
         <is>
           <t>city_cut:collaborator-sheet; address:manual-repo-edit</t>
         </is>
@@ -27051,12 +27642,12 @@
           <t>1408 W Jefferson Blvd, Los Angeles, CA 90007</t>
         </is>
       </c>
-      <c r="AI200" t="inlineStr">
+      <c r="AK200" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ200" t="inlineStr">
+      <c r="AL200" t="inlineStr">
         <is>
           <t>resolution:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -27183,12 +27774,12 @@
           <t>1311 W Battles Rd, Santa Maria, CA 93458</t>
         </is>
       </c>
-      <c r="AI201" t="inlineStr">
+      <c r="AK201" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ201" t="inlineStr">
+      <c r="AL201" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -27320,12 +27911,12 @@
           <t>1980</t>
         </is>
       </c>
-      <c r="AI202" t="inlineStr">
+      <c r="AK202" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ202" t="inlineStr">
+      <c r="AL202" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -27447,12 +28038,12 @@
           <t>4350 Galbrath Dr, Sacramento, CA 95842</t>
         </is>
       </c>
-      <c r="AI203" t="inlineStr">
+      <c r="AK203" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ203" t="inlineStr">
+      <c r="AL203" t="inlineStr">
         <is>
           <t>city:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -27579,12 +28170,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI204" t="inlineStr">
+      <c r="AK204" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ204" t="inlineStr">
+      <c r="AL204" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:manual-repo-edit</t>
         </is>
@@ -27701,12 +28292,12 @@
           <t>June, 2026</t>
         </is>
       </c>
-      <c r="AI205" t="inlineStr">
+      <c r="AK205" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ205" t="inlineStr">
+      <c r="AL205" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -27833,12 +28424,12 @@
           <t>1845 N Broadway, Escondido, CA 92026</t>
         </is>
       </c>
-      <c r="AI206" t="inlineStr">
+      <c r="AK206" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ206" t="inlineStr">
+      <c r="AL206" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; county:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -27955,12 +28546,12 @@
           <t>April, 2026</t>
         </is>
       </c>
-      <c r="AI207" t="inlineStr">
+      <c r="AK207" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ207" t="inlineStr">
+      <c r="AL207" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -28072,12 +28663,12 @@
           <t>April, 2026</t>
         </is>
       </c>
-      <c r="AI208" t="inlineStr">
+      <c r="AK208" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ208" t="inlineStr">
+      <c r="AL208" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -28199,12 +28790,12 @@
           <t>6790 Embarcadero Ln, Carlsbad, CA 92011</t>
         </is>
       </c>
-      <c r="AI209" t="inlineStr">
+      <c r="AK209" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ209" t="inlineStr">
+      <c r="AL209" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; address:collaborator-sheet; term_years:collaborator-sheet</t>
         </is>
@@ -28316,19 +28907,19 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="Z210" t="inlineStr">
-        <is>
-          <t>6633 Valley Hi Drive, Sacramento, CA</t>
-        </is>
-      </c>
-      <c r="AI210" t="inlineStr">
+      <c r="Z210" s="2" t="inlineStr">
+        <is>
+          <t>6633 Valley Hi</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ210" t="inlineStr">
-        <is>
-          <t>address:collaborator-sheet; term_years:collaborator-sheet</t>
+      <c r="AL210" t="inlineStr">
+        <is>
+          <t>term_years:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -28443,12 +29034,12 @@
           <t>August, 2026</t>
         </is>
       </c>
-      <c r="AI211" t="inlineStr">
+      <c r="AK211" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ211" t="inlineStr">
+      <c r="AL211" t="inlineStr">
         <is>
           <t>entity:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -28570,12 +29161,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI212" t="inlineStr">
+      <c r="AK212" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ212" t="inlineStr">
+      <c r="AL212" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -28692,12 +29283,12 @@
           <t>September, 2026</t>
         </is>
       </c>
-      <c r="AI213" t="inlineStr">
+      <c r="AK213" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ213" t="inlineStr">
+      <c r="AL213" t="inlineStr">
         <is>
           <t>city:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -28819,12 +29410,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI214" t="inlineStr">
+      <c r="AK214" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ214" t="inlineStr">
+      <c r="AL214" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -28956,12 +29547,12 @@
           <t>https://cscda.org/wp-content/uploads/2026/06/CSCDA-Agenda-Packet-7.2.26.pdf</t>
         </is>
       </c>
-      <c r="AI215" t="inlineStr">
+      <c r="AK215" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ215" t="inlineStr">
+      <c r="AL215" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; link:collaborator-sheet; resolution:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -29088,12 +29679,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI216" t="inlineStr">
+      <c r="AK216" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ216" t="inlineStr">
+      <c r="AL216" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -29220,12 +29811,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI217" t="inlineStr">
+      <c r="AK217" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ217" t="inlineStr">
+      <c r="AL217" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:manual-repo-edit</t>
         </is>
@@ -29342,12 +29933,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI218" t="inlineStr">
+      <c r="AK218" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ218" t="inlineStr">
+      <c r="AL218" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -29474,12 +30065,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI219" t="inlineStr">
+      <c r="AK219" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ219" t="inlineStr">
+      <c r="AL219" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -29596,12 +30187,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI220" t="inlineStr">
+      <c r="AK220" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ220" t="inlineStr">
+      <c r="AL220" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -29728,12 +30319,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI221" t="inlineStr">
+      <c r="AK221" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ221" t="inlineStr">
+      <c r="AL221" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -29850,12 +30441,12 @@
           <t>July, 2026</t>
         </is>
       </c>
-      <c r="AI222" t="inlineStr">
+      <c r="AK222" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ222" t="inlineStr">
+      <c r="AL222" t="inlineStr">
         <is>
           <t>city:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -29907,17 +30498,12 @@
           <t>2121 WOOD ST OAKLAND 94607</t>
         </is>
       </c>
-      <c r="AH223" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AI223" t="inlineStr">
+      <c r="AK223" t="inlineStr">
         <is>
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="AJ223" t="inlineStr">
+      <c r="AL223" t="inlineStr">
         <is>
           <t>*:collaborator-sheet</t>
         </is>
@@ -30034,12 +30620,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI224" t="inlineStr">
+      <c r="AK224" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ224" t="inlineStr">
+      <c r="AL224" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -30151,12 +30737,12 @@
           <t>2780 N Texas St, Fairfield, CA 94533</t>
         </is>
       </c>
-      <c r="AI225" t="inlineStr">
+      <c r="AK225" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ225" t="inlineStr">
+      <c r="AL225" t="inlineStr">
         <is>
           <t>address:collaborator-sheet; term_years:collaborator-sheet</t>
         </is>
@@ -30273,12 +30859,12 @@
           <t>July, 2026</t>
         </is>
       </c>
-      <c r="AI226" t="inlineStr">
+      <c r="AK226" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ226" t="inlineStr">
+      <c r="AL226" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; term_years:collaborator-sheet</t>
         </is>
@@ -30390,12 +30976,12 @@
           <t>1 Shoal Ct, Sacramento, CA 95831</t>
         </is>
       </c>
-      <c r="AI227" t="inlineStr">
+      <c r="AK227" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ227" t="inlineStr">
+      <c r="AL227" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -30507,12 +31093,12 @@
           <t>June, 2026</t>
         </is>
       </c>
-      <c r="AI228" t="inlineStr">
+      <c r="AK228" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ228" t="inlineStr">
+      <c r="AL228" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet; term_years:collaborator-sheet</t>
         </is>
@@ -30629,12 +31215,12 @@
           <t>September, 2026</t>
         </is>
       </c>
-      <c r="AI229" t="inlineStr">
+      <c r="AK229" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ229" t="inlineStr">
+      <c r="AL229" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -30751,12 +31337,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="AI230" t="inlineStr">
+      <c r="AK230" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ230" t="inlineStr">
+      <c r="AL230" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -30873,12 +31459,12 @@
           <t>September, 2026</t>
         </is>
       </c>
-      <c r="AI231" t="inlineStr">
+      <c r="AK231" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ231" t="inlineStr">
+      <c r="AL231" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -31000,12 +31586,12 @@
           <t>https://vistria.com/vistria-real-estate-acquires-orange-county-apartment-community/</t>
         </is>
       </c>
-      <c r="AI232" t="inlineStr">
+      <c r="AK232" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ232" t="inlineStr">
+      <c r="AL232" t="inlineStr">
         <is>
           <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; link:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -31122,12 +31708,12 @@
           <t>September, 2026</t>
         </is>
       </c>
-      <c r="AI233" t="inlineStr">
+      <c r="AK233" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ233" t="inlineStr">
+      <c r="AL233" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet; term_years:collaborator-sheet</t>
         </is>
@@ -31244,12 +31830,12 @@
           <t>September, 2026</t>
         </is>
       </c>
-      <c r="AI234" t="inlineStr">
+      <c r="AK234" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ234" t="inlineStr">
+      <c r="AL234" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -31366,12 +31952,12 @@
           <t>September, 2026</t>
         </is>
       </c>
-      <c r="AI235" t="inlineStr">
+      <c r="AK235" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ235" t="inlineStr">
+      <c r="AL235" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -31493,12 +32079,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="AI236" t="inlineStr">
+      <c r="AK236" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ236" t="inlineStr">
+      <c r="AL236" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -31615,12 +32201,12 @@
           <t>August, 2026</t>
         </is>
       </c>
-      <c r="AI237" t="inlineStr">
+      <c r="AK237" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AJ237" t="inlineStr">
+      <c r="AL237" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -31719,10 +32305,20 @@
       </c>
       <c r="AI238" t="inlineStr">
         <is>
+          <t>11142</t>
+        </is>
+      </c>
+      <c r="AJ238" t="inlineStr">
+        <is>
+          <t>2022-12-08</t>
+        </is>
+      </c>
+      <c r="AK238" t="inlineStr">
+        <is>
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="AJ238" t="inlineStr">
+      <c r="AL238" t="inlineStr">
         <is>
           <t>*:collaborator-sheet</t>
         </is>
@@ -31804,7 +32400,22 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI239" t="inlineStr">
+      <c r="AH239" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI239" s="2" t="inlineStr">
+        <is>
+          <t>12635</t>
+        </is>
+      </c>
+      <c r="AJ239" s="2" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AK239" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -31886,7 +32497,22 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI240" t="inlineStr">
+      <c r="AH240" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI240" s="2" t="inlineStr">
+        <is>
+          <t>12700</t>
+        </is>
+      </c>
+      <c r="AJ240" s="2" t="inlineStr">
+        <is>
+          <t>2024-02-08</t>
+        </is>
+      </c>
+      <c r="AK240" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -32008,7 +32634,22 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI241" t="inlineStr">
+      <c r="AH241" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI241" s="2" t="inlineStr">
+        <is>
+          <t>14852</t>
+        </is>
+      </c>
+      <c r="AJ241" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AK241" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -32090,7 +32731,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI242" t="inlineStr">
+      <c r="AK242" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -32207,7 +32848,27 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI243" t="inlineStr">
+      <c r="Z243" s="2" t="inlineStr">
+        <is>
+          <t>45 units restricted and 66 market-rate units, including</t>
+        </is>
+      </c>
+      <c r="AH243" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI243" s="2" t="inlineStr">
+        <is>
+          <t>14929</t>
+        </is>
+      </c>
+      <c r="AJ243" s="2" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AK243" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -32329,7 +32990,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI244" t="inlineStr">
+      <c r="AK244" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -32446,7 +33107,22 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI245" t="inlineStr">
+      <c r="AH245" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI245" s="2" t="inlineStr">
+        <is>
+          <t>15139</t>
+        </is>
+      </c>
+      <c r="AJ245" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AK245" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -32558,7 +33234,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI246" t="inlineStr">
+      <c r="AK246" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -32675,7 +33351,27 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI247" t="inlineStr">
+      <c r="Z247" s="2" t="inlineStr">
+        <is>
+          <t>5 levels of Type III construction, consisting of</t>
+        </is>
+      </c>
+      <c r="AH247" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI247" s="2" t="inlineStr">
+        <is>
+          <t>15001</t>
+        </is>
+      </c>
+      <c r="AJ247" s="2" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AK247" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -32797,7 +33493,27 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI248" t="inlineStr">
+      <c r="Z248" s="2" t="inlineStr">
+        <is>
+          <t>5 and State Highway 55 and is close to the Downtown Santa Ana and Irvine Business complexes, which are two large employment hubs in the area</t>
+        </is>
+      </c>
+      <c r="AH248" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI248" s="2" t="inlineStr">
+        <is>
+          <t>14961</t>
+        </is>
+      </c>
+      <c r="AJ248" s="2" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AK248" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -32904,7 +33620,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI249" t="inlineStr">
+      <c r="AK249" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -33006,7 +33722,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI250" t="inlineStr">
+      <c r="AK250" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -33123,7 +33839,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI251" t="inlineStr">
+      <c r="AK251" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -33225,7 +33941,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI252" t="inlineStr">
+      <c r="Z252" s="2" t="inlineStr">
+        <is>
+          <t>700 square feet. Amenities at the property include a rooftop sky deck with barbeque area and fireplace, fully equipped fitness center</t>
+        </is>
+      </c>
+      <c r="AK252" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -33332,7 +34053,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI253" t="inlineStr">
+      <c r="Z253" s="2" t="inlineStr">
+        <is>
+          <t>1301-1307 N. Cherokee Avenue in</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -33449,7 +34175,22 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI254" t="inlineStr">
+      <c r="AH254" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI254" s="2" t="inlineStr">
+        <is>
+          <t>15324</t>
+        </is>
+      </c>
+      <c r="AJ254" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -33556,7 +34297,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI255" t="inlineStr">
+      <c r="AK255" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -33663,7 +34404,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI256" t="inlineStr">
+      <c r="AK256" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -33770,7 +34511,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI257" t="inlineStr">
+      <c r="Z257" s="2" t="inlineStr">
+        <is>
+          <t>501 S. Burlington Avenue Apartments project is a three-story,</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -33877,7 +34623,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI258" t="inlineStr">
+      <c r="Z258" s="2" t="inlineStr">
+        <is>
+          <t>625 S. Burlington Avenue Apartments project is a four-story,</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -33984,7 +34735,22 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI259" t="inlineStr">
+      <c r="AH259" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI259" s="2" t="inlineStr">
+        <is>
+          <t>5435</t>
+        </is>
+      </c>
+      <c r="AJ259" s="2" t="inlineStr">
+        <is>
+          <t>2012-03-27</t>
+        </is>
+      </c>
+      <c r="AK259" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -34091,7 +34857,22 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI260" t="inlineStr">
+      <c r="AH260" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI260" s="2" t="inlineStr">
+        <is>
+          <t>6702</t>
+        </is>
+      </c>
+      <c r="AJ260" s="2" t="inlineStr">
+        <is>
+          <t>2016-01-26</t>
+        </is>
+      </c>
+      <c r="AK260" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -34203,7 +34984,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI261" t="inlineStr">
+      <c r="Z261" s="2" t="inlineStr">
+        <is>
+          <t>2022 and are sized to offset the electricity needs of all common areas. The grant for this project will create 99 units of affordable housing in</t>
+        </is>
+      </c>
+      <c r="AK261" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -34310,7 +35096,22 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI262" t="inlineStr">
+      <c r="AH262" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI262" s="2" t="inlineStr">
+        <is>
+          <t>6330</t>
+        </is>
+      </c>
+      <c r="AJ262" s="2" t="inlineStr">
+        <is>
+          <t>2014-12-29</t>
+        </is>
+      </c>
+      <c r="AK262" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -34417,7 +35218,22 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI263" t="inlineStr">
+      <c r="AH263" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI263" s="2" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="AJ263" s="2" t="inlineStr">
+        <is>
+          <t>2012-03-28</t>
+        </is>
+      </c>
+      <c r="AK263" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -34524,7 +35340,22 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI264" t="inlineStr">
+      <c r="AH264" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI264" s="2" t="inlineStr">
+        <is>
+          <t>5935</t>
+        </is>
+      </c>
+      <c r="AJ264" s="2" t="inlineStr">
+        <is>
+          <t>2014-02-18</t>
+        </is>
+      </c>
+      <c r="AK264" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -34631,7 +35462,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI265" t="inlineStr">
+      <c r="AK265" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -34738,7 +35569,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI266" t="inlineStr">
+      <c r="AK266" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -34845,7 +35676,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI267" t="inlineStr">
+      <c r="AK267" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -34967,7 +35798,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI268" t="inlineStr">
+      <c r="AK268" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -35089,7 +35920,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI269" t="inlineStr">
+      <c r="AK269" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -35196,7 +36027,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI270" t="inlineStr">
+      <c r="AK270" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -35298,7 +36129,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI271" t="inlineStr">
+      <c r="Z271" s="2" t="inlineStr">
+        <is>
+          <t>229 of which are designated as affordable housing for residents earning at or below 80% of</t>
+        </is>
+      </c>
+      <c r="AK271" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -35420,7 +36256,22 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI272" t="inlineStr">
+      <c r="AH272" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI272" s="2" t="inlineStr">
+        <is>
+          <t>15252</t>
+        </is>
+      </c>
+      <c r="AJ272" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AK272" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -35542,7 +36393,22 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI273" t="inlineStr">
+      <c r="AH273" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI273" s="2" t="inlineStr">
+        <is>
+          <t>15376</t>
+        </is>
+      </c>
+      <c r="AJ273" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AK273" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -35649,7 +36515,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI274" t="inlineStr">
+      <c r="Z274" s="2" t="inlineStr">
+        <is>
+          <t>17188 Chatsworth St. Apartments, is a new construction</t>
+        </is>
+      </c>
+      <c r="AK274" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -35776,7 +36647,22 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI275" t="inlineStr">
+      <c r="AH275" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI275" s="2" t="inlineStr">
+        <is>
+          <t>15252</t>
+        </is>
+      </c>
+      <c r="AJ275" s="2" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AK275" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -35903,7 +36789,22 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI276" t="inlineStr">
+      <c r="AH276" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI276" s="2" t="inlineStr">
+        <is>
+          <t>15376</t>
+        </is>
+      </c>
+      <c r="AJ276" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AK276" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -36010,7 +36911,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI277" t="inlineStr">
+      <c r="Z277" s="2" t="inlineStr">
+        <is>
+          <t>160 S Virgil Ave</t>
+        </is>
+      </c>
+      <c r="AK277" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -36117,7 +37023,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI278" t="inlineStr">
+      <c r="Z278" s="2" t="inlineStr">
+        <is>
+          <t>236 Berendo Street Apartments project is a proposed new construction of a 5-story,</t>
+        </is>
+      </c>
+      <c r="AK278" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -36234,7 +37145,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI279" t="inlineStr">
+      <c r="Z279" s="2" t="inlineStr">
+        <is>
+          <t>2022 and are sized to offset the electricity needs of all common areas. The grant for this project will create 99 units of affordable housing in</t>
+        </is>
+      </c>
+      <c r="AK279" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -36341,7 +37257,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI280" t="inlineStr">
+      <c r="AK280" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -36448,7 +37364,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI281" t="inlineStr">
+      <c r="AK281" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -36555,7 +37471,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI282" t="inlineStr">
+      <c r="AK282" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -36667,7 +37583,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI283" t="inlineStr">
+      <c r="Z283" s="2" t="inlineStr">
+        <is>
+          <t>2022 and are sized to offset the electricity needs of all common areas. The grant for this project will create 99 units of affordable housing in</t>
+        </is>
+      </c>
+      <c r="AK283" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -36784,7 +37705,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI284" t="inlineStr">
+      <c r="Z284" s="2" t="inlineStr">
+        <is>
+          <t>1 mile north of the historic Healdsburg Plaza</t>
+        </is>
+      </c>
+      <c r="AK284" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -36891,7 +37817,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI285" t="inlineStr">
+      <c r="AK285" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -36973,7 +37899,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI286" t="inlineStr">
+      <c r="AK286" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -37090,7 +38016,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI287" t="inlineStr">
+      <c r="AK287" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -37197,7 +38123,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI288" t="inlineStr">
+      <c r="AK288" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -37314,7 +38240,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI289" t="inlineStr">
+      <c r="Z289" s="2" t="inlineStr">
+        <is>
+          <t>3048</t>
+        </is>
+      </c>
+      <c r="AK289" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -37421,7 +38352,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI290" t="inlineStr">
+      <c r="Z290" s="2" t="inlineStr">
+        <is>
+          <t>4440</t>
+        </is>
+      </c>
+      <c r="AK290" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -37528,7 +38464,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI291" t="inlineStr">
+      <c r="AK291" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -37600,7 +38536,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI292" t="inlineStr">
+      <c r="AK292" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -37707,7 +38643,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI293" t="inlineStr">
+      <c r="Z293" s="2" t="inlineStr">
+        <is>
+          <t>3601 Fernwood</t>
+        </is>
+      </c>
+      <c r="AK293" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -37814,7 +38755,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI294" t="inlineStr">
+      <c r="Z294" s="2" t="inlineStr">
+        <is>
+          <t>119 East Johnson</t>
+        </is>
+      </c>
+      <c r="AK294" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -37921,7 +38867,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI295" t="inlineStr">
+      <c r="Z295" s="2" t="inlineStr">
+        <is>
+          <t>24650 Amador Street in Hayward, CA</t>
+        </is>
+      </c>
+      <c r="AK295" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -38003,7 +38954,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI296" t="inlineStr">
+      <c r="AK296" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -38120,7 +39071,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI297" t="inlineStr">
+      <c r="Z297" s="2" t="inlineStr">
+        <is>
+          <t>79 acres. The unit mix consists of 4 studios,</t>
+        </is>
+      </c>
+      <c r="AK297" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -38232,7 +39188,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI298" t="inlineStr">
+      <c r="Z298" s="2" t="inlineStr">
+        <is>
+          <t>81 acres. The unit mix consists of 5 studios,</t>
+        </is>
+      </c>
+      <c r="AK298" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -38339,7 +39300,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI299" t="inlineStr">
+      <c r="Z299" s="2" t="inlineStr">
+        <is>
+          <t>6754 Valjean Ave, Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="AK299" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -38446,7 +39412,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI300" t="inlineStr">
+      <c r="Z300" s="2" t="inlineStr">
+        <is>
+          <t>7408 S. Figueroa St., Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="AK300" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -38558,7 +39529,12 @@
           <t>Charitable Affordable Housing Grant for an Affordable Rental Housing Facility Located in the City of Daly City, San Mateo County, California</t>
         </is>
       </c>
-      <c r="AI301" t="inlineStr">
+      <c r="Z301" s="2" t="inlineStr">
+        <is>
+          <t>79 acres. The unit mix consists of 4 studios,</t>
+        </is>
+      </c>
+      <c r="AK301" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -38670,7 +39646,12 @@
           <t>Charitable Affordable Housing Grant for an Affordable Rental Housing Facility Located in the City of Redwood City, San Mateo County, California</t>
         </is>
       </c>
-      <c r="AI302" t="inlineStr">
+      <c r="Z302" s="2" t="inlineStr">
+        <is>
+          <t>81 acres. The unit mix consists of 5 studios,</t>
+        </is>
+      </c>
+      <c r="AK302" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -38777,7 +39758,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI303" t="inlineStr">
+      <c r="Z303" s="2" t="inlineStr">
+        <is>
+          <t>12534 San Fernando Rd, Los Angeles, CA</t>
+        </is>
+      </c>
+      <c r="AK303" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -38884,7 +39870,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI304" t="inlineStr">
+      <c r="Z304" s="2" t="inlineStr">
+        <is>
+          <t>1248–1254 North Cherokee Avenue in</t>
+        </is>
+      </c>
+      <c r="AK304" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -38971,7 +39962,12 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI305" t="inlineStr">
+      <c r="Z305" s="2" t="inlineStr">
+        <is>
+          <t>8513 Paradise Valley Road in the unincorporated community of Spring Valley in San Diego</t>
+        </is>
+      </c>
+      <c r="AK305" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -39073,7 +40069,7 @@
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AI306" t="inlineStr">
+      <c r="AK306" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -39165,7 +40161,7 @@
           <t>October, 2026</t>
         </is>
       </c>
-      <c r="AI307" t="inlineStr">
+      <c r="AK307" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -72504,7 +73500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C131"/>
+  <dimension ref="A1:C136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -74079,24 +75075,24 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AIN 6020022027 (Los Angeles) has no current roll data; using manual value</t>
+          <t>entity '381 Turk Street Associates, a California' ~ SCC LP '421 Turk Street Associates, L.P.' (#3326, San Francisco, score 92)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -74106,58 +75102,58 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AIN 6020022027 (Los Angeles): no roll values from any source</t>
+          <t>entity 'BIF NON OZ 7524 S HOOVER ST, LP' ~ SCC LP 'BIF NON OZ 7518 S Hoover St, LP' (#14953, Los Angeles, score 93)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AIN 5036031006 (Los Angeles) has no current roll data; using manual value</t>
+          <t>entity 'BIF NON OZ 4228 WESTERN AVE, LP' ~ SCC LP 'BIF NON OZ 4209 Western Ave, LP' (#14952, Los Angeles, score 93)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>122</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AIN 4262018026 (Los Angeles) has no current roll data; using manual value</t>
+          <t>entity '861 Fedora LLLP' ~ SCC LP '836 Fedora L.P.' (#1594, Los Angeles, score 90)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>165</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AIN 6020022027 (Los Angeles) has no current roll data; using manual value</t>
+          <t>entity '861 Fedora LLLP' ~ SCC LP '836 Fedora L.P.' (#1594, Los Angeles, score 90)</t>
         </is>
       </c>
     </row>
@@ -74169,12 +75165,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>AIN 2125017014 (Los Angeles) has no current roll data; using manual value</t>
+          <t>AIN 6020022027 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
@@ -74186,80 +75182,80 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AIN 41416654 (Alameda): no roll values from any source</t>
+          <t>AIN 6020022027 (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 5036031006 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AIN 5036031006 (Los Angeles): no roll values from any source</t>
+          <t>AIN 4262018026 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>132</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 6020022027 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>137</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 2125017014 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
@@ -74271,12 +75267,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>143</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AIN (none) (Santa Barbara): no roll values from any source</t>
+          <t>AIN 41416654 (Alameda): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -74288,7 +75284,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>158</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -74305,12 +75301,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>182</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 5036031006 (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -74322,7 +75318,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>196</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -74339,12 +75335,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>197</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AIN 5539028040 (Los Angeles): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -74356,12 +75352,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AIN (none) (Contra Costa): no roll values from any source</t>
+          <t>AIN (none) (Santa Barbara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -74373,12 +75369,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>206</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AIN 46745075 (Santa Clara): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -74390,12 +75386,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>207</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>AIN 46745074 (Santa Clara): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -74407,12 +75403,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>208</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AIN 46745073 (Santa Clara): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -74424,148 +75420,148 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>215</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>AIN (none) (Santa Clara): no roll values from any source</t>
+          <t>AIN 5539028040 (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AIN 128101150 (Solano) has no current roll data; using manual value</t>
+          <t>AIN (none) (Contra Costa): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>AIN 128101050 (Solano) has no current roll data; using manual value</t>
+          <t>AIN 46745075 (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AIN 128105060 (Solano) has no current roll data; using manual value</t>
+          <t>AIN 46745074 (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>shared-ain</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>182/76</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AIN 5036031006 assigned to multiple projects</t>
+          <t>AIN 46745073 (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>shared-ain</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>200/218</t>
+          <t>198</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AIN 5040021006 assigned to multiple projects</t>
+          <t>AIN (none) (Santa Clara): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>shared-ain</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>130/179</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>AIN 5080006008 assigned to multiple projects</t>
+          <t>AIN 128101150 (Solano) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>shared-ain</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>126/173</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>AIN 5094005005 assigned to multiple projects</t>
+          <t>AIN 128101050 (Solano) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>shared-ain</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>127/174</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>AIN 5094006003 assigned to multiple projects</t>
+          <t>AIN 128105060 (Solano) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
@@ -74577,12 +75573,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>122/165</t>
+          <t>182/76</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>AIN 5094017020 assigned to multiple projects</t>
+          <t>AIN 5036031006 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -74594,12 +75590,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>124/169</t>
+          <t>200/218</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>AIN 5094023025 assigned to multiple projects</t>
+          <t>AIN 5040021006 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -74611,12 +75607,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>128/175</t>
+          <t>130/179</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AIN 5502019004 assigned to multiple projects</t>
+          <t>AIN 5080006008 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -74628,12 +75624,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>125/170</t>
+          <t>126/173</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>AIN 5503024012 assigned to multiple projects</t>
+          <t>AIN 5094005005 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -74645,12 +75641,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>129/177</t>
+          <t>127/174</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AIN 5517005016 assigned to multiple projects</t>
+          <t>AIN 5094006003 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -74662,12 +75658,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>121/162</t>
+          <t>122/165</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>AIN 5518013024 assigned to multiple projects</t>
+          <t>AIN 5094017020 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -74679,12 +75675,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>123/168</t>
+          <t>124/169</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>AIN 5518020021 assigned to multiple projects</t>
+          <t>AIN 5094023025 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -74696,12 +75692,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>135/220</t>
+          <t>128/175</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>AIN 5518026004 assigned to multiple projects</t>
+          <t>AIN 5502019004 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -74713,12 +75709,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>10/132</t>
+          <t>125/170</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>AIN 6020022027 assigned to multiple projects</t>
+          <t>AIN 5503024012 assigned to multiple projects</t>
         </is>
       </c>
     </row>
@@ -74730,10 +75726,95 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
+          <t>129/177</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>AIN 5517005016 assigned to multiple projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>shared-ain</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>121/162</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>AIN 5518013024 assigned to multiple projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>shared-ain</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>123/168</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>AIN 5518020021 assigned to multiple projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>shared-ain</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>135/220</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>AIN 5518026004 assigned to multiple projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>shared-ain</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>10/132</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>AIN 6020022027 assigned to multiple projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>shared-ain</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
           <t>152/181</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>AIN 7157012017 assigned to multiple projects</t>
         </is>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -7522,9 +7522,9 @@
           <t>Summerwood Apartment Homes</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Standard Properties</t>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Standard Summerwood II LP</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -7572,9 +7572,9 @@
           <t>2-CMFA-Minutes-04-17-26.pdf</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Standard Properties</t>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>Standard Property Company, Inc.</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; entity:collaborator-sheet; investor_1:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -9104,66 +9104,81 @@
           <t>Harken Apartments</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>PREG 5150 ECR Los Altos, LP, a California limited partnership</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Los Altos</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Santa Clara</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>25-065</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>authorize</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>operative</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>15167</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-04</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr">
+        <is>
+          <t>1-CMFA-Agenda-1-31-2025.pdf</t>
+        </is>
+      </c>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>CMFA-Staff-Report-01-31-25.pdf</t>
+        </is>
+      </c>
+      <c r="S61" s="3" t="inlineStr">
+        <is>
+          <t>2-CMFA-Minutes-1-31-2025.pdf</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr">
         <is>
           <t>Prometheus Real Estate Group</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Los Altos</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>Santa Clara</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>25-065</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>authorize</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>operative</t>
-        </is>
-      </c>
-      <c r="Q61" s="3" t="inlineStr">
-        <is>
-          <t>1-CMFA-Agenda-1-31-2025.pdf</t>
-        </is>
-      </c>
-      <c r="R61" s="3" t="inlineStr">
-        <is>
-          <t>CMFA-Staff-Report-01-31-25.pdf</t>
-        </is>
-      </c>
-      <c r="S61" s="3" t="inlineStr">
-        <is>
-          <t>2-CMFA-Minutes-1-31-2025.pdf</t>
-        </is>
-      </c>
-      <c r="T61" s="2" t="inlineStr">
-        <is>
-          <t>Prometheus Real Estate Group</t>
-        </is>
-      </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
           <t>Hearthstone Housing Foundation</t>
@@ -9216,7 +9231,7 @@
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; entity:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -11717,9 +11732,9 @@
           <t>10811 S. Compton Ave Apartments</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>10811 S. Compton Ave Apartments</t>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>2 SIOF 10811 S Compton Ave, LP</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -11829,7 +11844,7 @@
       </c>
       <c r="AL80" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -19563,9 +19578,9 @@
           <t>Flag VII Montecito, L.P.</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>San Jose</t>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -19685,7 +19700,7 @@
       </c>
       <c r="AL138" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; city:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -25154,16 +25169,16 @@
           <t>Ackerfield 2 LP</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Long Beach</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>Los Angeles</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
-        </is>
-      </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
           <t>26-039</t>
@@ -25261,7 +25276,7 @@
       </c>
       <c r="AL181" t="inlineStr">
         <is>
-          <t>manual_status:collaborator-sheet; city:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>manual_status:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -28807,9 +28822,9 @@
           <t>Haven Warner Center</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>Heven LP</t>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Haven, LP</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -28909,7 +28924,7 @@
       </c>
       <c r="AL210" t="inlineStr">
         <is>
-          <t>entity:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -29014,9 +29029,9 @@
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>2075 W Jefferson BlvdLos Angeles, CA 90018</t>
+      <c r="AC211" s="2" t="inlineStr">
+        <is>
+          <t>2075 West Jefferson Blvd., Los Angeles</t>
         </is>
       </c>
       <c r="AD211" s="2" t="inlineStr">
@@ -29036,7 +29051,7 @@
       </c>
       <c r="AL211" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -31810,9 +31825,9 @@
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>3950 Ingraham St, San Diego, CA 92109</t>
+      <c r="AC234" s="2" t="inlineStr">
+        <is>
+          <t>3950 W. Ingraham Street, Los Angeles, CA</t>
         </is>
       </c>
       <c r="AD234" s="2" t="inlineStr">
@@ -31827,7 +31842,7 @@
       </c>
       <c r="AL234" t="inlineStr">
         <is>
-          <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -73052,7 +73067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C110"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -73629,12 +73644,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>nonprofit_partner: generated 'AOF / Pacific Affordable Housing Corp.' -&gt; manual 'Pacific Affordable Housing Corp'</t>
+          <t>total_units: generated '24' -&gt; manual '52'</t>
         </is>
       </c>
     </row>
@@ -73646,12 +73661,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>city: generated 'Los Angeles' -&gt; manual 'El Sobrante'</t>
+          <t>total_units: generated '22' -&gt; manual '72'</t>
         </is>
       </c>
     </row>
@@ -73663,12 +73678,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>county: generated 'Los Angeles' -&gt; manual 'Contra Costa'</t>
+          <t>total_units: generated '24' -&gt; manual '48'</t>
         </is>
       </c>
     </row>
@@ -73680,12 +73695,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>total_units: generated '24' -&gt; manual '52'</t>
+          <t>total_units: generated '65' -&gt; manual '165'</t>
         </is>
       </c>
     </row>
@@ -73697,12 +73712,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>total_units: generated '22' -&gt; manual '72'</t>
+          <t>investor_1: generated 'Ethos Real Estate' -&gt; manual 'Vistria Group'</t>
         </is>
       </c>
     </row>
@@ -73714,12 +73729,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>total_units: generated '24' -&gt; manual '48'</t>
+          <t>total_units: generated '144' -&gt; manual '145'</t>
         </is>
       </c>
     </row>
@@ -73731,12 +73746,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>total_units: generated '65' -&gt; manual '165'</t>
+          <t>total_units: generated '42' -&gt; manual '356'</t>
         </is>
       </c>
     </row>
@@ -73748,12 +73763,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>property_name: generated '2330 3rd Street Apartments' -&gt; manual '2330 E. 3rd Street Apartments'</t>
+          <t>total_units: generated '29' -&gt; manual '196'</t>
         </is>
       </c>
     </row>
@@ -73765,12 +73780,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>investor_1: generated 'Ethos Real Estate' -&gt; manual 'Vistria Group'</t>
+          <t>investor_1: generated 'Vintage Housing Holdings, LLC' -&gt; manual 'Kennedy Wilson'</t>
         </is>
       </c>
     </row>
@@ -73782,12 +73797,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>total_units: generated '144' -&gt; manual '145'</t>
+          <t>nonprofit_partner: generated 'Pacific Housing, Inc.' -&gt; manual 'Hearthstone Housing Foundation'</t>
         </is>
       </c>
     </row>
@@ -73799,12 +73814,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>total_units: generated '42' -&gt; manual '356'</t>
+          <t>total_units: generated '8' -&gt; manual '1008'</t>
         </is>
       </c>
     </row>
@@ -73816,12 +73831,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>entity: generated 'PREG 5150 ECR Los Altos, LP, a California limited partnership' -&gt; manual 'Prometheus Real Estate Group'</t>
+          <t>total_units: generated '32' -&gt; manual '31'</t>
         </is>
       </c>
     </row>
@@ -73833,12 +73848,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>total_units: generated '29' -&gt; manual '196'</t>
+          <t>city_cut: generated '4650.0' -&gt; manual '4500'</t>
         </is>
       </c>
     </row>
@@ -73850,12 +73865,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>158</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>investor_1: generated 'Vintage Housing Holdings, LLC' -&gt; manual 'Kennedy Wilson'</t>
+          <t>total_units: generated '30' -&gt; manual '29'</t>
         </is>
       </c>
     </row>
@@ -73867,12 +73882,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>95</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>nonprofit_partner: generated 'Pacific Housing, Inc.' -&gt; manual 'Hearthstone Housing Foundation'</t>
+          <t>investor_1: generated 'Belveron Partners' -&gt; manual 'Sack Capital Partners'</t>
         </is>
       </c>
     </row>
@@ -73884,12 +73899,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>110</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>total_units: generated '8' -&gt; manual '1008'</t>
+          <t>total_units: generated '24' -&gt; manual '42'</t>
         </is>
       </c>
     </row>
@@ -73901,12 +73916,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>134</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>total_units: generated '32' -&gt; manual '31'</t>
+          <t>total_units: generated '69' -&gt; manual '68'</t>
         </is>
       </c>
     </row>
@@ -73918,12 +73933,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>137</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>city_cut: generated '4650.0' -&gt; manual '4500'</t>
+          <t>total_units: generated '42' -&gt; manual '41'</t>
         </is>
       </c>
     </row>
@@ -73935,12 +73950,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>152</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>entity: generated '2 SIOF 10811 S Compton Ave, LP' -&gt; manual '10811 S. Compton Ave Apartments'</t>
+          <t>total_units: generated '52' -&gt; manual '152'</t>
         </is>
       </c>
     </row>
@@ -73952,12 +73967,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>155</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>total_units: generated '30' -&gt; manual '29'</t>
+          <t>entity: generated 'A limited partnership to be formed by Kairos Investment Management and Pacific Housing' -&gt; manual 'TBD LP'</t>
         </is>
       </c>
     </row>
@@ -73969,12 +73984,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>156</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>investor_1: generated 'Belveron Partners' -&gt; manual 'Sack Capital Partners'</t>
+          <t>entity: generated 'A limited partnership to be formed by Kairos Investment Management and Pacific Housing' -&gt; manual 'TBD LP'</t>
         </is>
       </c>
     </row>
@@ -73986,12 +74001,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>171</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>total_units: generated '24' -&gt; manual '42'</t>
+          <t>city_cut: generated '15900.0' -&gt; manual '6300'</t>
         </is>
       </c>
     </row>
@@ -74003,12 +74018,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>181</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>city: generated 'Sacramento' -&gt; manual 'Unincorporated'</t>
+          <t>total_units: generated '52' -&gt; manual '152'</t>
         </is>
       </c>
     </row>
@@ -74020,12 +74035,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>195</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>property_name: generated 'Kinglsey Apartments' -&gt; manual 'Kingsley Apartments'</t>
+          <t>total_units: generated '42' -&gt; manual '41'</t>
         </is>
       </c>
     </row>
@@ -74037,12 +74052,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>199</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>total_units: generated '69' -&gt; manual '68'</t>
+          <t>city_cut: generated '5550.0' -&gt; manual '5500'</t>
         </is>
       </c>
     </row>
@@ -74054,12 +74069,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>204</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>total_units: generated '42' -&gt; manual '41'</t>
+          <t>total_units: generated '50' -&gt; manual '49'</t>
         </is>
       </c>
     </row>
@@ -74071,12 +74086,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>206</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>city: generated 'Santa Clara' -&gt; manual 'San Jose'</t>
+          <t>county: generated 'San Diego' -&gt; manual 'Los Angeles'</t>
         </is>
       </c>
     </row>
@@ -74088,12 +74103,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>209</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>total_units: generated '52' -&gt; manual '152'</t>
+          <t>investor_1: generated 'Zenith Property Group LLC' -&gt; manual 'Red Stone Equity Partners'</t>
         </is>
       </c>
     </row>
@@ -74105,12 +74120,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>209</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>entity: generated 'A limited partnership to be formed by Kairos Investment Management and Pacific Housing' -&gt; manual 'TBD LP'</t>
+          <t>term_years: generated '35' -&gt; manual '15'</t>
         </is>
       </c>
     </row>
@@ -74122,12 +74137,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>210</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>entity: generated 'A limited partnership to be formed by Kairos Investment Management and Pacific Housing' -&gt; manual 'TBD LP'</t>
+          <t>term_years: generated '55' -&gt; manual '10'</t>
         </is>
       </c>
     </row>
@@ -74139,12 +74154,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>city_cut: generated '15900.0' -&gt; manual '6300'</t>
+          <t>term_years: generated '15' -&gt; manual '10'</t>
         </is>
       </c>
     </row>
@@ -74156,12 +74171,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>228</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>city: generated 'Long Beach' -&gt; manual 'Los Angeles'</t>
+          <t>term_years: generated '10' -&gt; manual '15'</t>
         </is>
       </c>
     </row>
@@ -74173,12 +74188,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>217</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>total_units: generated '52' -&gt; manual '152'</t>
+          <t>total_units: generated '35' -&gt; manual '34'</t>
         </is>
       </c>
     </row>
@@ -74190,12 +74205,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>233</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>property_name: generated 'La Vista Apartments' -&gt; manual 'La Vista Apartment Homes'</t>
+          <t>term_years: generated '55' -&gt; manual '10'</t>
         </is>
       </c>
     </row>
@@ -74207,12 +74222,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>236</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>total_units: generated '42' -&gt; manual '41'</t>
+          <t>total_units: generated '136' -&gt; manual '108'</t>
         </is>
       </c>
     </row>
@@ -74224,707 +74239,350 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>225</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>address: generated '9750 Airport Blvd, Los Angeles, CA' -&gt; manual '9750 Airport Blvd, Westchester, CA 90045'</t>
+          <t>term_years: generated '30' -&gt; manual '55'</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>city_cut: generated '5550.0' -&gt; manual '5500'</t>
+          <t>entity '381 Turk Street Associates, a California' ~ SCC LP '421 Turk Street Associates, L.P.' (#3326, San Francisco, score 92)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>address: generated '2481 South Sawtelle Blvd, Los Angeles, CA' -&gt; manual '2481 Sawtelle Blvd, Los Angeles, CA 90064'</t>
+          <t>entity 'BIF NON OZ 7524 S HOOVER ST, LP' ~ SCC LP 'BIF NON OZ 7518 S Hoover St, LP' (#14953, Los Angeles, score 93)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>entity: generated 'Standard Summerwood II LP' -&gt; manual 'Standard Properties'</t>
+          <t>entity 'BIF NON OZ 4228 WESTERN AVE, LP' ~ SCC LP 'BIF NON OZ 4209 Western Ave, LP' (#14952, Los Angeles, score 93)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>122</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>investor_1: generated 'Standard Property Company, Inc.' -&gt; manual 'Standard Properties'</t>
+          <t>entity '861 Fedora LLLP' ~ SCC LP '836 Fedora L.P.' (#1594, Los Angeles, score 90)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>165</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>total_units: generated '50' -&gt; manual '49'</t>
+          <t>entity '861 Fedora LLLP' ~ SCC LP '836 Fedora L.P.' (#1594, Los Angeles, score 90)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>county: generated 'San Diego' -&gt; manual 'Los Angeles'</t>
+          <t>AIN 5036031006 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>investor_1: generated 'Zenith Property Group LLC' -&gt; manual 'Red Stone Equity Partners'</t>
+          <t>AIN 4262018026 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>132</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>term_years: generated '35' -&gt; manual '15'</t>
+          <t>AIN 6020022027 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>137</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>term_years: generated '55' -&gt; manual '10'</t>
+          <t>AIN 2125017014 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>158</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>term_years: generated '15' -&gt; manual '10'</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>196</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>term_years: generated '10' -&gt; manual '15'</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>address: generated '11821 Foothill Blvd, Los Angeles, CA' -&gt; manual '11821 Foothill Blvd, Lake View Terrace, CA 91342'</t>
+          <t>AIN (none) (Santa Barbara): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>206</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>total_units: generated '35' -&gt; manual '34'</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>207</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>entity: generated 'Haven, LP' -&gt; manual 'Heven LP'</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>208</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>address: generated '6530 Independence Avenue, Los Angeles' -&gt; manual '6530 Independence Ave, Canoga Park, CA 91303'</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>215</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>address: generated '2075 West Jefferson Blvd., Los Angeles' -&gt; manual '2075 W Jefferson BlvdLos Angeles, CA 90018'</t>
+          <t>AIN 5539028040 (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>nonprofit_partner: generated 'Bedford' -&gt; manual 'Bedford Affordable Housing Foundation'</t>
+          <t>AIN (none) (Contra Costa): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>term_years: generated '55' -&gt; manual '10'</t>
+          <t>AIN 128101150 (Solano) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>address: generated '3950 W. Ingraham Street, Los Angeles, CA' -&gt; manual '3950 Ingraham St, San Diego, CA 92109'</t>
+          <t>AIN 128101050 (Solano) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
-        <is>
-          <t>total_units: generated '136' -&gt; manual '108'</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>override-conflict</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>term_years: generated '30' -&gt; manual '55'</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>scc-possible-match</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>entity '381 Turk Street Associates, a California' ~ SCC LP '421 Turk Street Associates, L.P.' (#3326, San Francisco, score 92)</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>scc-possible-match</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>entity 'BIF NON OZ 7524 S HOOVER ST, LP' ~ SCC LP 'BIF NON OZ 7518 S Hoover St, LP' (#14953, Los Angeles, score 93)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>scc-possible-match</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>entity 'BIF NON OZ 4228 WESTERN AVE, LP' ~ SCC LP 'BIF NON OZ 4209 Western Ave, LP' (#14952, Los Angeles, score 93)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>scc-possible-match</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>entity '861 Fedora LLLP' ~ SCC LP '836 Fedora L.P.' (#1594, Los Angeles, score 90)</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>scc-possible-match</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>entity '861 Fedora LLLP' ~ SCC LP '836 Fedora L.P.' (#1594, Los Angeles, score 90)</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>fetch-fallback</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>AIN 5036031006 (Los Angeles) has no current roll data; using manual value</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>fetch-fallback</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>AIN 4262018026 (Los Angeles) has no current roll data; using manual value</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>fetch-fallback</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>AIN 6020022027 (Los Angeles) has no current roll data; using manual value</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>fetch-fallback</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>AIN 2125017014 (Los Angeles) has no current roll data; using manual value</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>AIN (none) (Santa Barbara): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>AIN 5539028040 (Los Angeles): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>AIN (none) (Contra Costa): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>fetch-fallback</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>AIN 128101150 (Solano) has no current roll data; using manual value</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>fetch-fallback</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>AIN 128101050 (Solano) has no current roll data; using manual value</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>fetch-fallback</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
         <is>
           <t>AIN 128105060 (Solano) has no current roll data; using manual value</t>
         </is>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -73067,10 +73067,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
   </cols>
@@ -74585,6 +74585,261 @@
       <c r="C89" t="inlineStr">
         <is>
           <t>AIN 128105060 (Solano) has no current roll data; using manual value</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>assignment-mismatch</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Park Wilshire Apartments: grant city 'Los Angeles' appears in no assigned parcel's situs</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>assignment-mismatch</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Seaport Village Apartments: no assigned parcel's situs matches address '5601 North Paramount Boulevard' (e.g. 7157031001: 2697 E 56TH WAY LONG BEACH CA 90805; 7157031002: 2687 E 56TH WAY LONG BEACH CA 90805)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>assignment-mismatch</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>569 W. 6th Street. Apartments: grant city 'Los Angeles' appears in no assigned parcel's situs</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>possible-missing-parcel</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Alvarado Streets Apartments: parcel 5136019023 shares situs '1136 S ALVARADO ST LOS ANGELES CA 90006' (Auto, Recreation EQPT, C, $1,039,983) but is not assigned to any project</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>possible-missing-parcel</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Market Street Village Apartmen: parcel 5351441600 shares situs '699 14TH SD' (31, $15,300,000) but is not assigned to any project</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>possible-missing-parcel</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Alexandria II Apartments: parcel 5518012036 shares situs '130 N ALEXANDRIA AVE APT 0104 LOS ANGELES CA 90004' (Five or more apartments, $7,015,185) but is not assigned to any project</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>possible-missing-parcel</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Kenmore II Apartments: parcel 5518018011 shares situs '200 N KENMORE AVE LOS ANGELES CA 90004' (Five or more apartments, $452,268) but is not assigned to any project</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>units-undercount</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>The Waterloo Apartments: county records 5 units on assigned parcels vs 154 in the grant — parcels may be missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>units-undercount</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Candlewood North Apartments: county records 68 units on assigned parcels vs 189 in the grant — parcels may be missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>units-undercount</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Kenmore I Apartments: county records 24 units on assigned parcels vs 42 in the grant — parcels may be missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>units-undercount</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>The Hive Apartments: county records 50 units on assigned parcels vs 152 in the grant — parcels may be missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>units-undercount</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1723 Corinth Apartments: county records 10 units on assigned parcels vs 41 in the grant — parcels may be missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>units-undercount</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Violet on Virgil: county records 159 units on assigned parcels vs 302 in the grant — parcels may be missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>units-undercount</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>926 S. Kingsley Apartments: county records 1 units on assigned parcels vs 136 in the grant — parcels may be missing</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>units-undercount</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Edgemont by Angeleno: county records 8 units on assigned parcels vs 34 in the grant — parcels may be missing</t>
         </is>
       </c>
     </row>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -40962,7 +40962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T389"/>
+  <dimension ref="A1:U389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -40985,6 +40985,7 @@
     <col width="22" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -41088,6 +41089,11 @@
           <t>operative_project_id</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>assignment_check</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -41105,12 +41111,12 @@
           <t>Alvarado Streets Apartments</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>5136019013</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>5136-019-013</t>
         </is>
@@ -41188,6 +41194,11 @@
       <c r="T2" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -41207,12 +41218,12 @@
           <t>2025 New Jersey Apartments</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>5183001017</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>5183-001-017</t>
         </is>
@@ -41280,6 +41291,11 @@
       <c r="T3" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -41339,6 +41355,11 @@
           <t>3</t>
         </is>
       </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -41396,6 +41417,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -41414,7 +41440,7 @@
 Apartments</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>5343602100</t>
         </is>
@@ -41477,6 +41503,11 @@
       <c r="T6" t="inlineStr">
         <is>
           <t>5</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -41531,6 +41562,11 @@
           <t>6</t>
         </is>
       </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -41593,6 +41629,11 @@
           <t>7</t>
         </is>
       </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -41610,12 +41651,12 @@
           <t>1317 S. Grand Apartments</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>5134017037</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>5134-017-037</t>
         </is>
@@ -41693,6 +41734,11 @@
       <c r="T9" t="inlineStr">
         <is>
           <t>8</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -41712,12 +41758,12 @@
           <t>1411 S. Flower Apartments</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>5134009025</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>5134-009-025</t>
         </is>
@@ -41795,6 +41841,11 @@
       <c r="T10" t="inlineStr">
         <is>
           <t>9</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -41956,6 +42007,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -41973,12 +42029,12 @@
           <t>The Waterloo Apartments</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>5402028023</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>5402-028-023</t>
         </is>
@@ -42051,6 +42107,11 @@
       <c r="T13" t="inlineStr">
         <is>
           <t>12</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -42105,6 +42166,11 @@
           <t>13</t>
         </is>
       </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -42162,6 +42228,11 @@
           <t>316</t>
         </is>
       </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -42179,12 +42250,12 @@
           <t>Premiere Hollywood Apartments</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>5547013021</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>5547-013-021</t>
         </is>
@@ -42257,6 +42328,11 @@
       <c r="T16" t="inlineStr">
         <is>
           <t>15</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -42276,12 +42352,12 @@
           <t>4252 Crenshaw Apartments</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>5024017036</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>5024-017-036</t>
         </is>
@@ -42354,6 +42430,11 @@
       <c r="T17" t="inlineStr">
         <is>
           <t>17</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -42373,7 +42454,7 @@
           <t>Fallbrook Trail Apartments</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>1043514700</t>
         </is>
@@ -42436,6 +42517,11 @@
       <c r="T18" t="inlineStr">
         <is>
           <t>18</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -42490,6 +42576,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -42542,6 +42633,11 @@
           <t>19</t>
         </is>
       </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -42559,12 +42655,12 @@
           <t>Pinetree Terrace Apartments</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>2102015045</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>2102-015-045</t>
         </is>
@@ -42637,6 +42733,11 @@
       <c r="T21" t="inlineStr">
         <is>
           <t>20</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -42656,12 +42757,12 @@
           <t>Windmere Court Apartments</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>2119001222</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>2119-001-222</t>
         </is>
@@ -42734,6 +42835,11 @@
       <c r="T22" t="inlineStr">
         <is>
           <t>21</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -42753,12 +42859,12 @@
           <t>Seville Gardens Apartments</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>6320011041</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>6320-011-041</t>
         </is>
@@ -42831,6 +42937,11 @@
       <c r="T23" t="inlineStr">
         <is>
           <t>22</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -42850,12 +42961,12 @@
           <t>Harbour Residences Apartments</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>7418014021</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>7418-014-021</t>
         </is>
@@ -42923,6 +43034,11 @@
       <c r="T24" t="inlineStr">
         <is>
           <t>23</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -42942,12 +43058,12 @@
           <t>4209 Western Avenue Apartments</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>5021028002</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>5021-028-002</t>
         </is>
@@ -43020,6 +43136,11 @@
       <c r="T25" t="inlineStr">
         <is>
           <t>24</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -43039,12 +43160,12 @@
           <t>1130 Martin Luther King Jr. Blvd Apartments</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>5020017007</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>5020-017-007</t>
         </is>
@@ -43117,6 +43238,11 @@
       <c r="T26" t="inlineStr">
         <is>
           <t>25</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -43136,12 +43262,12 @@
           <t>Harbor Terrace Apartments</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>7455002027</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>7455-002-027</t>
         </is>
@@ -43214,6 +43340,11 @@
       <c r="T27" t="inlineStr">
         <is>
           <t>26</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -43233,12 +43364,12 @@
           <t>Santa Monica Portfolio A Apartments</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>4291019007</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>4291-019-007</t>
         </is>
@@ -43316,6 +43447,11 @@
       <c r="T28" t="inlineStr">
         <is>
           <t>27</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -43335,12 +43471,12 @@
           <t>Santa Monica Portfolio A Apartments</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>4291019006</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>4291-019-006</t>
         </is>
@@ -43418,6 +43554,11 @@
       <c r="T29" t="inlineStr">
         <is>
           <t>27</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -43437,12 +43578,12 @@
           <t>Santa Monica Portfolio B Apartments</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>4291020005</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>4291-020-005</t>
         </is>
@@ -43520,6 +43661,11 @@
       <c r="T30" t="inlineStr">
         <is>
           <t>28</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -43539,12 +43685,12 @@
           <t>Santa Monica Portfolio B Apartments</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>4291020006</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>4291-020-006</t>
         </is>
@@ -43622,6 +43768,11 @@
       <c r="T31" t="inlineStr">
         <is>
           <t>28</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -43641,12 +43792,12 @@
           <t>Santa Monica Portfolio B Apartments</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>4291020007</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>4291-020-007</t>
         </is>
@@ -43724,6 +43875,11 @@
       <c r="T32" t="inlineStr">
         <is>
           <t>28</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -43743,12 +43899,12 @@
           <t>Santa Monica Portfolio C Apartments</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>4291020018</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>4291-020-018</t>
         </is>
@@ -43826,6 +43982,11 @@
       <c r="T33" t="inlineStr">
         <is>
           <t>29</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -43845,12 +44006,12 @@
           <t>Santa Monica Portfolio C Apartments</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>4291020019</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>4291-020-019</t>
         </is>
@@ -43928,6 +44089,11 @@
       <c r="T34" t="inlineStr">
         <is>
           <t>29</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -43947,12 +44113,12 @@
           <t>Santa Monica Portfolio D Apartments</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>4291024007</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>4291-024-007</t>
         </is>
@@ -44025,6 +44191,11 @@
       <c r="T35" t="inlineStr">
         <is>
           <t>30</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -44044,12 +44215,12 @@
           <t>Santa Monica Portfolio E Apartments</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>4291022015</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>4291-022-015</t>
         </is>
@@ -44122,6 +44293,11 @@
       <c r="T36" t="inlineStr">
         <is>
           <t>31</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -44141,12 +44317,12 @@
           <t>Santa Monica Portfolio F Apartments</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>4275024005</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>4275-024-005</t>
         </is>
@@ -44224,6 +44400,11 @@
       <c r="T37" t="inlineStr">
         <is>
           <t>32</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -44243,12 +44424,12 @@
           <t>Santa Monica Portfolio F Apartments</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>4275024015</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>4275-024-015</t>
         </is>
@@ -44326,6 +44507,11 @@
       <c r="T38" t="inlineStr">
         <is>
           <t>32</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -44442,6 +44628,11 @@
           <t>34</t>
         </is>
       </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -44504,6 +44695,11 @@
           <t>35</t>
         </is>
       </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -44521,12 +44717,12 @@
           <t>Stadium Village Apartments</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>4025014001</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>4025-014-001</t>
         </is>
@@ -44604,6 +44800,11 @@
       <c r="T42" t="inlineStr">
         <is>
           <t>36</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -44623,12 +44824,12 @@
           <t>Stadium Village Apartments</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>4025014002</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>4025-014-002</t>
         </is>
@@ -44706,6 +44907,11 @@
       <c r="T43" t="inlineStr">
         <is>
           <t>36</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -44725,12 +44931,12 @@
           <t>Stadium Village Apartments</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>4025014003</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>4025-014-003</t>
         </is>
@@ -44808,6 +45014,11 @@
       <c r="T44" t="inlineStr">
         <is>
           <t>36</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -44827,12 +45038,12 @@
           <t>Stadium Village Apartments</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>4025014004</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>4025-014-004</t>
         </is>
@@ -44910,6 +45121,11 @@
       <c r="T45" t="inlineStr">
         <is>
           <t>36</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -44929,12 +45145,12 @@
           <t>Stadium Village Apartments</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>4025014005</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>4025-014-005</t>
         </is>
@@ -45012,6 +45228,11 @@
       <c r="T46" t="inlineStr">
         <is>
           <t>36</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -45031,12 +45252,12 @@
           <t>Stadium Village Apartments</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>4025014006</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>4025-014-006</t>
         </is>
@@ -45114,6 +45335,11 @@
       <c r="T47" t="inlineStr">
         <is>
           <t>36</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -45133,12 +45359,12 @@
           <t>Stadium Village Apartments</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>4025014007</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>4025-014-007</t>
         </is>
@@ -45216,6 +45442,11 @@
       <c r="T48" t="inlineStr">
         <is>
           <t>36</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -45235,12 +45466,12 @@
           <t>Stadium Village Apartments</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>4025014008</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>4025-014-008</t>
         </is>
@@ -45318,6 +45549,11 @@
       <c r="T49" t="inlineStr">
         <is>
           <t>36</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -45337,12 +45573,12 @@
           <t>Stadium Village Apartments</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>4025014009</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>4025-014-009</t>
         </is>
@@ -45420,6 +45656,11 @@
       <c r="T50" t="inlineStr">
         <is>
           <t>36</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -45439,12 +45680,12 @@
           <t>Stadium Village Apartments</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>4025014010</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>4025-014-010</t>
         </is>
@@ -45522,6 +45763,11 @@
       <c r="T51" t="inlineStr">
         <is>
           <t>36</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -45541,12 +45787,12 @@
           <t>Stadium Village Apartments</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>4025014011</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>4025-014-011</t>
         </is>
@@ -45624,6 +45870,11 @@
       <c r="T52" t="inlineStr">
         <is>
           <t>36</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -45643,12 +45894,12 @@
           <t>Stadium Village Apartments</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>4025014012</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>4025-014-012</t>
         </is>
@@ -45726,6 +45977,11 @@
       <c r="T53" t="inlineStr">
         <is>
           <t>36</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -45745,12 +46001,12 @@
           <t>Stadium Village Apartments</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>4025014013</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>4025-014-013</t>
         </is>
@@ -45828,6 +46084,11 @@
       <c r="T54" t="inlineStr">
         <is>
           <t>36</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -45847,12 +46108,12 @@
           <t>Stadium Village Apartments</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>4025014014</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>4025-014-014</t>
         </is>
@@ -45930,6 +46191,11 @@
       <c r="T55" t="inlineStr">
         <is>
           <t>36</t>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -45949,12 +46215,12 @@
           <t>Stadium Village Apartments</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>4025014015</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>4025-014-015</t>
         </is>
@@ -46032,6 +46298,11 @@
       <c r="T56" t="inlineStr">
         <is>
           <t>36</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -46051,12 +46322,12 @@
           <t>Stadium Village Apartments</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>4025014016</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>4025-014-016</t>
         </is>
@@ -46134,6 +46405,11 @@
       <c r="T57" t="inlineStr">
         <is>
           <t>36</t>
+        </is>
+      </c>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -46153,12 +46429,12 @@
           <t>Stadium Village Apartments</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>4025014017</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>4025-014-017</t>
         </is>
@@ -46236,6 +46512,11 @@
       <c r="T58" t="inlineStr">
         <is>
           <t>36</t>
+        </is>
+      </c>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -46255,12 +46536,12 @@
           <t>Stadium Village Apartments</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>4025014018</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>4025-014-018</t>
         </is>
@@ -46338,6 +46619,11 @@
       <c r="T59" t="inlineStr">
         <is>
           <t>36</t>
+        </is>
+      </c>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -46357,12 +46643,12 @@
           <t>Stadium Village Apartments</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>4025015001</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>4025-015-001</t>
         </is>
@@ -46440,6 +46726,11 @@
       <c r="T60" t="inlineStr">
         <is>
           <t>36</t>
+        </is>
+      </c>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -46459,12 +46750,12 @@
           <t>Stadium Village Apartments</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>4025015002</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>4025-015-002</t>
         </is>
@@ -46542,6 +46833,11 @@
       <c r="T61" t="inlineStr">
         <is>
           <t>36</t>
+        </is>
+      </c>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -46561,12 +46857,12 @@
           <t>2330 E. 3rd Street Apartments</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>5183013023</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>5183-013-023</t>
         </is>
@@ -46639,6 +46935,11 @@
       <c r="T62" t="inlineStr">
         <is>
           <t>37</t>
+        </is>
+      </c>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -46658,12 +46959,12 @@
           <t>Marquee Apartments</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>2321001019</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>2321-001-019</t>
         </is>
@@ -46736,6 +47037,11 @@
       <c r="T63" t="inlineStr">
         <is>
           <t>38</t>
+        </is>
+      </c>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -46755,12 +47061,12 @@
           <t>6200 S. Broadway Apartments</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>6005021032</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>6005-021-032</t>
         </is>
@@ -46833,6 +47139,11 @@
       <c r="T64" t="inlineStr">
         <is>
           <t>39</t>
+        </is>
+      </c>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -46852,12 +47163,12 @@
           <t>4228 Western Ave. Apartments</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>5021009036</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>5021-009-036</t>
         </is>
@@ -46930,6 +47241,11 @@
       <c r="T65" t="inlineStr">
         <is>
           <t>349</t>
+        </is>
+      </c>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -46949,12 +47265,12 @@
           <t>4327 S. Vermont Apartments</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>5020025039</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>5020-025-039</t>
         </is>
@@ -47027,6 +47343,11 @@
       <c r="T66" t="inlineStr">
         <is>
           <t>41</t>
+        </is>
+      </c>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -47046,12 +47367,12 @@
           <t>2023 Imperial Apartments</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>6083001009</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>6083-001-009</t>
         </is>
@@ -47124,6 +47445,11 @@
       <c r="T67" t="inlineStr">
         <is>
           <t>42</t>
+        </is>
+      </c>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -47178,6 +47504,11 @@
           <t>323</t>
         </is>
       </c>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -47195,12 +47526,12 @@
           <t>Soto Apartments</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>5180001024</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>5180-001-024</t>
         </is>
@@ -47278,6 +47609,11 @@
       <c r="T69" t="inlineStr">
         <is>
           <t>44</t>
+        </is>
+      </c>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -47332,6 +47668,11 @@
           <t>45</t>
         </is>
       </c>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -47384,6 +47725,11 @@
           <t>45</t>
         </is>
       </c>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -47401,12 +47747,12 @@
           <t>4752 Main Street Apartments</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>5109003014</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>5109-003-014</t>
         </is>
@@ -47484,6 +47830,11 @@
       <c r="T72" t="inlineStr">
         <is>
           <t>46</t>
+        </is>
+      </c>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -47503,12 +47854,12 @@
           <t>4752 Main Street Apartments</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>5109003001</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>5109-003-001</t>
         </is>
@@ -47586,6 +47937,11 @@
       <c r="T73" t="inlineStr">
         <is>
           <t>46</t>
+        </is>
+      </c>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -47605,7 +47961,7 @@
           <t>6171 Mission Gorge Apartments</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>4610304300</t>
         </is>
@@ -47668,6 +48024,11 @@
       <c r="T74" t="inlineStr">
         <is>
           <t>47</t>
+        </is>
+      </c>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -47727,6 +48088,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -47784,6 +48150,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -47841,6 +48212,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -47898,6 +48274,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -47955,6 +48336,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -48012,6 +48398,11 @@
           <t>48</t>
         </is>
       </c>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -48064,6 +48455,11 @@
           <t>49</t>
         </is>
       </c>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -48081,7 +48477,7 @@
           <t>Market Street Village Apartments</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>5351441500</t>
         </is>
@@ -48144,6 +48540,11 @@
       <c r="T82" t="inlineStr">
         <is>
           <t>50</t>
+        </is>
+      </c>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -48163,7 +48564,7 @@
           <t>Creekside Villas Apartments</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>5473131800</t>
         </is>
@@ -48226,6 +48627,11 @@
       <c r="T83" t="inlineStr">
         <is>
           <t>229</t>
+        </is>
+      </c>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -48280,6 +48686,11 @@
           <t>52</t>
         </is>
       </c>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -48332,6 +48743,11 @@
           <t>53</t>
         </is>
       </c>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -48434,6 +48850,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -48536,6 +48957,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -48638,6 +49064,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -48740,6 +49171,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -48842,6 +49278,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -48944,6 +49385,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -49046,6 +49492,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -49148,6 +49599,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -49250,6 +49706,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -49352,6 +49813,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -49454,6 +49920,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -49556,6 +50027,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -49658,6 +50134,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -49760,6 +50241,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -49862,6 +50348,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -49964,6 +50455,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -50066,6 +50562,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -50168,6 +50669,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -50270,6 +50776,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -50372,6 +50883,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -50474,6 +50990,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -50576,6 +51097,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -50678,6 +51204,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -50780,6 +51311,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U109" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -50882,6 +51418,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U110" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -50984,6 +51525,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U111" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -51086,6 +51632,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U112" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -51188,6 +51739,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U113" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -51290,6 +51846,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U114" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -51392,6 +51953,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U115" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -51494,6 +52060,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U116" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -51596,6 +52167,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U117" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -51698,6 +52274,11 @@
           <t>54</t>
         </is>
       </c>
+      <c r="U118" s="2" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -51715,12 +52296,12 @@
           <t>1457 Main Street Apartments</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>5409005030</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>5409-005-030</t>
         </is>
@@ -51788,6 +52369,11 @@
       <c r="T119" t="inlineStr">
         <is>
           <t>55</t>
+        </is>
+      </c>
+      <c r="U119" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -51847,6 +52433,11 @@
           <t>56</t>
         </is>
       </c>
+      <c r="U120" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -51864,12 +52455,12 @@
           <t>Chaparral Apartments</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>3004004033</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>3004-004-033</t>
         </is>
@@ -51942,6 +52533,11 @@
       <c r="T121" t="inlineStr">
         <is>
           <t>58</t>
+        </is>
+      </c>
+      <c r="U121" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -51996,6 +52592,11 @@
           <t>59</t>
         </is>
       </c>
+      <c r="U122" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -52013,12 +52614,12 @@
           <t>11422 Broadway Apartments</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>6087002036</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>6087-002-036</t>
         </is>
@@ -52091,6 +52692,11 @@
       <c r="T123" t="inlineStr">
         <is>
           <t>61</t>
+        </is>
+      </c>
+      <c r="U123" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -52180,6 +52786,11 @@
           <t>62</t>
         </is>
       </c>
+      <c r="U124" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -52232,6 +52843,11 @@
           <t>63</t>
         </is>
       </c>
+      <c r="U125" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -52249,12 +52865,12 @@
           <t>333 Douglas Apartments</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>5160009020</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>5160-009-020</t>
         </is>
@@ -52327,6 +52943,11 @@
       <c r="T126" t="inlineStr">
         <is>
           <t>64</t>
+        </is>
+      </c>
+      <c r="U126" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -52386,6 +53007,11 @@
           <t>65</t>
         </is>
       </c>
+      <c r="U127" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -52403,12 +53029,12 @@
           <t>The Eaves Apartments</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>5092023021</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>5092-023-021</t>
         </is>
@@ -52481,6 +53107,11 @@
       <c r="T128" t="inlineStr">
         <is>
           <t>66</t>
+        </is>
+      </c>
+      <c r="U128" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -52535,6 +53166,11 @@
           <t>67</t>
         </is>
       </c>
+      <c r="U129" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -52552,12 +53188,12 @@
           <t>Candlewood North Apartments</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>2764001013</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>2764-001-013</t>
         </is>
@@ -52630,6 +53266,11 @@
       <c r="T130" t="inlineStr">
         <is>
           <t>68</t>
+        </is>
+      </c>
+      <c r="U130" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -52649,12 +53290,12 @@
           <t>Lindley Parc Apartments</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>2731008014</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>2731-008-014</t>
         </is>
@@ -52727,6 +53368,11 @@
       <c r="T131" t="inlineStr">
         <is>
           <t>69</t>
+        </is>
+      </c>
+      <c r="U131" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -52781,6 +53427,11 @@
           <t>359</t>
         </is>
       </c>
+      <c r="U132" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -52833,6 +53484,11 @@
           <t>359</t>
         </is>
       </c>
+      <c r="U133" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -52885,6 +53541,11 @@
           <t>359</t>
         </is>
       </c>
+      <c r="U134" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -52937,6 +53598,11 @@
           <t>359</t>
         </is>
       </c>
+      <c r="U135" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -52989,6 +53655,11 @@
           <t>359</t>
         </is>
       </c>
+      <c r="U136" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -53041,6 +53712,11 @@
           <t>359</t>
         </is>
       </c>
+      <c r="U137" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -53093,6 +53769,11 @@
           <t>359</t>
         </is>
       </c>
+      <c r="U138" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -53145,6 +53826,11 @@
           <t>359</t>
         </is>
       </c>
+      <c r="U139" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -53197,6 +53883,11 @@
           <t>71</t>
         </is>
       </c>
+      <c r="U140" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -53259,6 +53950,11 @@
           <t>72</t>
         </is>
       </c>
+      <c r="U141" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -53361,6 +54057,11 @@
           <t>73</t>
         </is>
       </c>
+      <c r="U142" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -53378,12 +54079,12 @@
           <t>1540 W Court Apartments</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>5159020010</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>5159-020-010</t>
         </is>
@@ -53461,6 +54162,11 @@
       <c r="T143" t="inlineStr">
         <is>
           <t>73</t>
+        </is>
+      </c>
+      <c r="U143" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -53480,12 +54186,12 @@
           <t>1540 W Court Apartments</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>5159020009</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>5159-020-009</t>
         </is>
@@ -53563,6 +54269,11 @@
       <c r="T144" t="inlineStr">
         <is>
           <t>73</t>
+        </is>
+      </c>
+      <c r="U144" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -53582,7 +54293,7 @@
           <t>Sol Haus Apartments</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>5484004400</t>
         </is>
@@ -53645,6 +54356,11 @@
       <c r="T145" t="inlineStr">
         <is>
           <t>74</t>
+        </is>
+      </c>
+      <c r="U145" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -53664,7 +54380,7 @@
           <t>Palmilla Apartments</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>4635902700</t>
         </is>
@@ -53727,6 +54443,11 @@
       <c r="T146" t="inlineStr">
         <is>
           <t>75</t>
+        </is>
+      </c>
+      <c r="U146" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -53806,6 +54527,11 @@
           <t>76</t>
         </is>
       </c>
+      <c r="U147" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -53823,12 +54549,12 @@
           <t>11630 S. Main Street Apartments</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>6083010040</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>6083-010-040</t>
         </is>
@@ -53901,6 +54627,11 @@
       <c r="T148" t="inlineStr">
         <is>
           <t>77</t>
+        </is>
+      </c>
+      <c r="U148" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -53955,6 +54686,11 @@
           <t>78</t>
         </is>
       </c>
+      <c r="U149" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -53972,12 +54708,12 @@
           <t>10811 S. Compton Ave Apartments</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>6070003041</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>6070-003-041</t>
         </is>
@@ -54055,6 +54791,11 @@
       <c r="T150" t="inlineStr">
         <is>
           <t>79</t>
+        </is>
+      </c>
+      <c r="U150" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -54074,12 +54815,12 @@
           <t>4101 Somerset Dr. Apartments</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>5032015003</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>5032-015-003</t>
         </is>
@@ -54152,6 +54893,11 @@
       <c r="T151" t="inlineStr">
         <is>
           <t>80</t>
+        </is>
+      </c>
+      <c r="U151" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -54171,12 +54917,12 @@
           <t>321 E. Florence Apartments</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>6011008052</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>6011-008-052</t>
         </is>
@@ -54249,6 +54995,11 @@
       <c r="T152" t="inlineStr">
         <is>
           <t>81</t>
+        </is>
+      </c>
+      <c r="U152" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -54268,12 +55019,12 @@
           <t>9300 Compton Ave. Apartments</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>6048022067</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>6048-022-067</t>
         </is>
@@ -54341,6 +55092,11 @@
       <c r="T153" t="inlineStr">
         <is>
           <t>82</t>
+        </is>
+      </c>
+      <c r="U153" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -54360,12 +55116,12 @@
           <t>6401 S. Avalon Blvd. Apartments</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>6006018001</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>6006-018-001</t>
         </is>
@@ -54433,6 +55189,11 @@
       <c r="T154" t="inlineStr">
         <is>
           <t>83</t>
+        </is>
+      </c>
+      <c r="U154" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -54452,12 +55213,12 @@
           <t>9515 Compton Ave. Apartments</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>6048004025</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>6048-004-025</t>
         </is>
@@ -54525,6 +55286,11 @@
       <c r="T155" t="inlineStr">
         <is>
           <t>84</t>
+        </is>
+      </c>
+      <c r="U155" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -54544,12 +55310,12 @@
           <t>569 W. 6th Street Apartments</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>7451037031</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>7451-037-031</t>
         </is>
@@ -54622,6 +55388,11 @@
       <c r="T156" t="inlineStr">
         <is>
           <t>85</t>
+        </is>
+      </c>
+      <c r="U156" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -54641,12 +55412,12 @@
           <t>685 W. 4th St Apartments</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>7451026002</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>7451-026-002</t>
         </is>
@@ -54719,6 +55490,11 @@
       <c r="T157" t="inlineStr">
         <is>
           <t>86</t>
+        </is>
+      </c>
+      <c r="U157" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -54738,12 +55514,12 @@
           <t>Chadwick Apartments</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>5501013028</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>5501-013-028</t>
         </is>
@@ -54816,6 +55592,11 @@
       <c r="T158" t="inlineStr">
         <is>
           <t>87</t>
+        </is>
+      </c>
+      <c r="U158" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -54835,12 +55616,12 @@
           <t>Chatsworth Apartments</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>2695003030</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>2695-003-030</t>
         </is>
@@ -54913,6 +55694,11 @@
       <c r="T159" t="inlineStr">
         <is>
           <t>88</t>
+        </is>
+      </c>
+      <c r="U159" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -54932,12 +55718,12 @@
           <t>Pacific Trails Apartments</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>8630009026</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>8630-009-026</t>
         </is>
@@ -55010,6 +55796,11 @@
       <c r="T160" t="inlineStr">
         <is>
           <t>90</t>
+        </is>
+      </c>
+      <c r="U160" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -55029,12 +55820,12 @@
           <t>Huston Affordable Housing Apartments</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>2421011010</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>2421-011-010</t>
         </is>
@@ -55107,6 +55898,11 @@
       <c r="T161" t="inlineStr">
         <is>
           <t>91</t>
+        </is>
+      </c>
+      <c r="U161" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -55126,12 +55922,12 @@
           <t>The Parker Apartments</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>8576001024</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>8576-001-024</t>
         </is>
@@ -55204,6 +56000,11 @@
       <c r="T162" t="inlineStr">
         <is>
           <t>92</t>
+        </is>
+      </c>
+      <c r="U162" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -55258,6 +56059,11 @@
           <t>93</t>
         </is>
       </c>
+      <c r="U163" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -55275,7 +56081,7 @@
           <t>Canyon Villa Apartment Homes</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>6390806100</t>
         </is>
@@ -55338,6 +56144,11 @@
       <c r="T164" t="inlineStr">
         <is>
           <t>94</t>
+        </is>
+      </c>
+      <c r="U164" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -55357,12 +56168,12 @@
           <t>Azusa Gardens Apartments</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>8608030071</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>8608-030-071</t>
         </is>
@@ -55435,6 +56246,11 @@
       <c r="T165" t="inlineStr">
         <is>
           <t>97</t>
+        </is>
+      </c>
+      <c r="U165" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -55499,6 +56315,11 @@
           <t>98</t>
         </is>
       </c>
+      <c r="U166" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -55571,6 +56392,11 @@
           <t>99</t>
         </is>
       </c>
+      <c r="U167" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -55588,12 +56414,12 @@
           <t>Passo Centinela I Apartments</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>4231018020</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>4231-018-020</t>
         </is>
@@ -55666,6 +56492,11 @@
       <c r="T168" t="inlineStr">
         <is>
           <t>100</t>
+        </is>
+      </c>
+      <c r="U168" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -55685,12 +56516,12 @@
           <t>Passo Centinela II Apartments</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>4221007056</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>4221-007-056</t>
         </is>
@@ -55758,6 +56589,11 @@
       <c r="T169" t="inlineStr">
         <is>
           <t>101</t>
+        </is>
+      </c>
+      <c r="U169" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -55777,12 +56613,12 @@
           <t>Passo Stoner Apartments</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr">
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>4262016011</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>4262-016-011</t>
         </is>
@@ -55855,6 +56691,11 @@
       <c r="T170" t="inlineStr">
         <is>
           <t>102</t>
+        </is>
+      </c>
+      <c r="U170" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -55874,12 +56715,12 @@
           <t>4th Street Apartments</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>5183012030</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>5183-012-030</t>
         </is>
@@ -55952,6 +56793,11 @@
       <c r="T171" t="inlineStr">
         <is>
           <t>103</t>
+        </is>
+      </c>
+      <c r="U171" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -55971,12 +56817,12 @@
           <t>Alexandria I Apartments</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>5518008009</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>5518-008-009</t>
         </is>
@@ -56049,6 +56895,11 @@
       <c r="T172" t="inlineStr">
         <is>
           <t>104</t>
+        </is>
+      </c>
+      <c r="U172" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -56068,12 +56919,12 @@
           <t>Ashby Apartments</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>5093017031</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>5093-017-031</t>
         </is>
@@ -56146,6 +56997,11 @@
       <c r="T173" t="inlineStr">
         <is>
           <t>105</t>
+        </is>
+      </c>
+      <c r="U173" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -56165,12 +57021,12 @@
           <t>Catalina Apartments</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>5502011009</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>5502-011-009</t>
         </is>
@@ -56243,6 +57099,11 @@
       <c r="T174" t="inlineStr">
         <is>
           <t>106</t>
+        </is>
+      </c>
+      <c r="U174" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -56262,12 +57123,12 @@
           <t>Edgemont Apartments</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>5518013007</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>5518-013-007</t>
         </is>
@@ -56340,6 +57201,11 @@
       <c r="T175" t="inlineStr">
         <is>
           <t>107</t>
+        </is>
+      </c>
+      <c r="U175" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -56359,12 +57225,12 @@
           <t>Gramercy Apartments</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>5081032007</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>5081-032-007</t>
         </is>
@@ -56437,6 +57303,11 @@
       <c r="T176" t="inlineStr">
         <is>
           <t>108</t>
+        </is>
+      </c>
+      <c r="U176" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -56456,12 +57327,12 @@
           <t>Irolo Apartments</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>5094021028</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>5094-021-028</t>
         </is>
@@ -56534,6 +57405,11 @@
       <c r="T177" t="inlineStr">
         <is>
           <t>109</t>
+        </is>
+      </c>
+      <c r="U177" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -56553,12 +57429,12 @@
           <t>Kenmore I Apartments</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>5094023030</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>5094-023-030</t>
         </is>
@@ -56631,6 +57507,11 @@
       <c r="T178" t="inlineStr">
         <is>
           <t>110</t>
+        </is>
+      </c>
+      <c r="U178" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -56650,12 +57531,12 @@
           <t>Manhattan III Apartments</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>5503015016</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>5503-015-016</t>
         </is>
@@ -56728,6 +57609,11 @@
       <c r="T179" t="inlineStr">
         <is>
           <t>111</t>
+        </is>
+      </c>
+      <c r="U179" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -56747,12 +57633,12 @@
           <t>Mariposa II Apartments</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>5518008014</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>5518-008-014</t>
         </is>
@@ -56825,6 +57711,11 @@
       <c r="T180" t="inlineStr">
         <is>
           <t>112</t>
+        </is>
+      </c>
+      <c r="U180" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -56844,12 +57735,12 @@
           <t>Normandie Apartments</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>5094004004</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>5094-004-004</t>
         </is>
@@ -56922,6 +57813,11 @@
       <c r="T181" t="inlineStr">
         <is>
           <t>113</t>
+        </is>
+      </c>
+      <c r="U181" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -56941,12 +57837,12 @@
           <t>Norton Apartments</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>5081006014</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>5081-006-014</t>
         </is>
@@ -57019,6 +57915,11 @@
       <c r="T182" t="inlineStr">
         <is>
           <t>114</t>
+        </is>
+      </c>
+      <c r="U182" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -57038,12 +57939,12 @@
           <t>Oxford I Apartments</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>5080008006</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>5080-008-006</t>
         </is>
@@ -57121,6 +58022,11 @@
       <c r="T183" t="inlineStr">
         <is>
           <t>115</t>
+        </is>
+      </c>
+      <c r="U183" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -57140,12 +58046,12 @@
           <t>Oxford I Apartments</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>5080008007</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>5080-008-007</t>
         </is>
@@ -57223,6 +58129,11 @@
       <c r="T184" t="inlineStr">
         <is>
           <t>115</t>
+        </is>
+      </c>
+      <c r="U184" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -57242,12 +58153,12 @@
           <t>Oxford I Apartments</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>5080008008</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>5080-008-008</t>
         </is>
@@ -57325,6 +58236,11 @@
       <c r="T185" t="inlineStr">
         <is>
           <t>115</t>
+        </is>
+      </c>
+      <c r="U185" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -57344,12 +58260,12 @@
           <t>Oxford III Apartments</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>5080015003</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>5080-015-003</t>
         </is>
@@ -57422,6 +58338,11 @@
       <c r="T186" t="inlineStr">
         <is>
           <t>116</t>
+        </is>
+      </c>
+      <c r="U186" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -57441,12 +58362,12 @@
           <t>Seven Lions Apartments</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>5518027010</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>5518-027-010</t>
         </is>
@@ -57519,6 +58440,11 @@
       <c r="T187" t="inlineStr">
         <is>
           <t>117</t>
+        </is>
+      </c>
+      <c r="U187" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -57538,12 +58464,12 @@
           <t>St. Andrews I Apartments</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>5504029006</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>5504-029-006</t>
         </is>
@@ -57616,6 +58542,11 @@
       <c r="T188" t="inlineStr">
         <is>
           <t>118</t>
+        </is>
+      </c>
+      <c r="U188" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -57635,12 +58566,12 @@
           <t>St. Andrews II Apartments</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
+      <c r="D189" s="2" t="inlineStr">
         <is>
           <t>5503017013</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
+      <c r="E189" s="2" t="inlineStr">
         <is>
           <t>5503-017-013</t>
         </is>
@@ -57713,6 +58644,11 @@
       <c r="T189" t="inlineStr">
         <is>
           <t>119</t>
+        </is>
+      </c>
+      <c r="U189" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -57777,6 +58713,11 @@
           <t>120</t>
         </is>
       </c>
+      <c r="U190" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -57794,12 +58735,12 @@
           <t>Alexandria II Apartments</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
+      <c r="D191" s="2" t="inlineStr">
         <is>
           <t>5518013024</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
+      <c r="E191" s="2" t="inlineStr">
         <is>
           <t>5518-013-024</t>
         </is>
@@ -57872,6 +58813,11 @@
       <c r="T191" t="inlineStr">
         <is>
           <t>162</t>
+        </is>
+      </c>
+      <c r="U191" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -57891,12 +58837,12 @@
           <t>Fedora Apartments</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr">
+      <c r="D192" s="2" t="inlineStr">
         <is>
           <t>5094017020</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
+      <c r="E192" s="2" t="inlineStr">
         <is>
           <t>5094-017-020</t>
         </is>
@@ -57969,6 +58915,11 @@
       <c r="T192" t="inlineStr">
         <is>
           <t>165</t>
+        </is>
+      </c>
+      <c r="U192" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -57988,12 +58939,12 @@
           <t>Kenmore II Apartments</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>5518020021</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
+      <c r="E193" s="2" t="inlineStr">
         <is>
           <t>5518-020-021</t>
         </is>
@@ -58066,6 +59017,11 @@
       <c r="T193" t="inlineStr">
         <is>
           <t>168</t>
+        </is>
+      </c>
+      <c r="U193" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -58085,12 +59041,12 @@
           <t>Kenmore III Apartments</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
+      <c r="D194" s="2" t="inlineStr">
         <is>
           <t>5094023025</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
+      <c r="E194" s="2" t="inlineStr">
         <is>
           <t>5094-023-025</t>
         </is>
@@ -58163,6 +59119,11 @@
       <c r="T194" t="inlineStr">
         <is>
           <t>169</t>
+        </is>
+      </c>
+      <c r="U194" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -58182,12 +59143,12 @@
           <t>Kingsley Apartments</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
+      <c r="D195" s="2" t="inlineStr">
         <is>
           <t>5503024012</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
+      <c r="E195" s="2" t="inlineStr">
         <is>
           <t>5503-024-012</t>
         </is>
@@ -58260,6 +59221,11 @@
       <c r="T195" t="inlineStr">
         <is>
           <t>170</t>
+        </is>
+      </c>
+      <c r="U195" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -58279,12 +59245,12 @@
           <t>Mariposa I Apartments</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
+      <c r="D196" s="2" t="inlineStr">
         <is>
           <t>5094005005</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr">
+      <c r="E196" s="2" t="inlineStr">
         <is>
           <t>5094-005-005</t>
         </is>
@@ -58357,6 +59323,11 @@
       <c r="T196" t="inlineStr">
         <is>
           <t>173</t>
+        </is>
+      </c>
+      <c r="U196" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -58376,12 +59347,12 @@
           <t>Mariposa III Apartments</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
+      <c r="D197" s="2" t="inlineStr">
         <is>
           <t>5094006003</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
+      <c r="E197" s="2" t="inlineStr">
         <is>
           <t>5094-006-003</t>
         </is>
@@ -58454,6 +59425,11 @@
       <c r="T197" t="inlineStr">
         <is>
           <t>174</t>
+        </is>
+      </c>
+      <c r="U197" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -58473,12 +59449,12 @@
           <t>Mariposa IV Apartments</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
+      <c r="D198" s="2" t="inlineStr">
         <is>
           <t>5502019004</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
+      <c r="E198" s="2" t="inlineStr">
         <is>
           <t>5502-019-004</t>
         </is>
@@ -58551,6 +59527,11 @@
       <c r="T198" t="inlineStr">
         <is>
           <t>175</t>
+        </is>
+      </c>
+      <c r="U198" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -58570,12 +59551,12 @@
           <t>Oxford II Apartments</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
+      <c r="D199" s="2" t="inlineStr">
         <is>
           <t>5517005016</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
         <is>
           <t>5517-005-016</t>
         </is>
@@ -58648,6 +59629,11 @@
       <c r="T199" t="inlineStr">
         <is>
           <t>177</t>
+        </is>
+      </c>
+      <c r="U199" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -58667,12 +59653,12 @@
           <t>Western Apartments</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>5080006008</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>5080-006-008</t>
         </is>
@@ -58745,6 +59731,11 @@
       <c r="T200" t="inlineStr">
         <is>
           <t>179</t>
+        </is>
+      </c>
+      <c r="U200" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -58824,6 +59815,11 @@
           <t>132</t>
         </is>
       </c>
+      <c r="U201" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -58841,12 +59837,12 @@
           <t>10705 Avalon Blvd Apartments</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>6063029029</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>6063-029-029</t>
         </is>
@@ -58919,6 +59915,11 @@
       <c r="T202" t="inlineStr">
         <is>
           <t>134</t>
+        </is>
+      </c>
+      <c r="U202" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -58938,12 +59939,12 @@
           <t>236 Berendo Apartments</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>5518026004</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>5518-026-004</t>
         </is>
@@ -59016,6 +60017,11 @@
       <c r="T203" t="inlineStr">
         <is>
           <t>220</t>
+        </is>
+      </c>
+      <c r="U203" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -59090,6 +60096,11 @@
           <t>137</t>
         </is>
       </c>
+      <c r="U204" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -59142,6 +60153,11 @@
           <t>141</t>
         </is>
       </c>
+      <c r="U205" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -59159,12 +60175,12 @@
           <t>9033 Ramsgate Apartments</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>4125011053</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>4125-011-053</t>
         </is>
@@ -59242,6 +60258,11 @@
       <c r="T206" t="inlineStr">
         <is>
           <t>142</t>
+        </is>
+      </c>
+      <c r="U206" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -59343,6 +60364,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="U208" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -59395,6 +60421,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="U209" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -59447,6 +60478,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="U210" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -59499,6 +60535,11 @@
           <t>144</t>
         </is>
       </c>
+      <c r="U211" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -59563,12 +60604,12 @@
           <t>San Pedro Apartments</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>6022014002</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
+      <c r="E213" s="2" t="inlineStr">
         <is>
           <t>6022-014-002</t>
         </is>
@@ -59641,6 +60682,11 @@
       <c r="T213" t="inlineStr">
         <is>
           <t>146</t>
+        </is>
+      </c>
+      <c r="U213" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -59705,6 +60751,11 @@
           <t>147</t>
         </is>
       </c>
+      <c r="U214" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -59722,12 +60773,12 @@
           <t>Park Wilshire Apartments</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr">
+      <c r="D215" s="2" t="inlineStr">
         <is>
           <t>4276017047</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr">
+      <c r="E215" s="2" t="inlineStr">
         <is>
           <t>4276-017-047</t>
         </is>
@@ -59800,6 +60851,11 @@
       <c r="T215" t="inlineStr">
         <is>
           <t>148</t>
+        </is>
+      </c>
+      <c r="U215" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -59819,12 +60875,12 @@
           <t>Sir Francis Drake Villa Apartments</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
+      <c r="D216" s="2" t="inlineStr">
         <is>
           <t>5093010009</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr">
+      <c r="E216" s="2" t="inlineStr">
         <is>
           <t>5093-010-009</t>
         </is>
@@ -59897,6 +60953,11 @@
       <c r="T216" t="inlineStr">
         <is>
           <t>149</t>
+        </is>
+      </c>
+      <c r="U216" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -59916,12 +60977,12 @@
           <t>Langham Apartments</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
+      <c r="D217" s="2" t="inlineStr">
         <is>
           <t>5094004007</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
+      <c r="E217" s="2" t="inlineStr">
         <is>
           <t>5094-004-007</t>
         </is>
@@ -59994,6 +61055,11 @@
       <c r="T217" t="inlineStr">
         <is>
           <t>150</t>
+        </is>
+      </c>
+      <c r="U217" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -60013,12 +61079,12 @@
           <t>Piccadilly Apartments</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>5094002004</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
+      <c r="E218" s="2" t="inlineStr">
         <is>
           <t>5094-002-004</t>
         </is>
@@ -60091,6 +61157,11 @@
       <c r="T218" t="inlineStr">
         <is>
           <t>151</t>
+        </is>
+      </c>
+      <c r="U218" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -60110,12 +61181,12 @@
           <t>The Hive at Ackerfield Apartments</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="D219" s="2" t="inlineStr">
         <is>
           <t>7157012023</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
+      <c r="E219" s="2" t="inlineStr">
         <is>
           <t>7157-012-023</t>
         </is>
@@ -60193,6 +61264,11 @@
       <c r="T219" t="inlineStr">
         <is>
           <t>181</t>
+        </is>
+      </c>
+      <c r="U219" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -60212,12 +61288,12 @@
           <t>Hawaiian Terrace Senior Apartments</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D220" s="2" t="inlineStr">
         <is>
           <t>7075020011</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>7075-020-011</t>
         </is>
@@ -60295,6 +61371,11 @@
       <c r="T220" t="inlineStr">
         <is>
           <t>153</t>
+        </is>
+      </c>
+      <c r="U220" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -60314,12 +61395,12 @@
           <t>Hawaiian Terrace Senior Apartments</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="D221" s="2" t="inlineStr">
         <is>
           <t>7075020012</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>7075-020-012</t>
         </is>
@@ -60392,6 +61473,11 @@
       <c r="T221" t="inlineStr">
         <is>
           <t>153</t>
+        </is>
+      </c>
+      <c r="U221" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -60446,6 +61532,11 @@
           <t>154</t>
         </is>
       </c>
+      <c r="U222" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -60498,6 +61589,11 @@
           <t>155</t>
         </is>
       </c>
+      <c r="U223" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -60550,6 +61646,11 @@
           <t>156</t>
         </is>
       </c>
+      <c r="U224" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -60567,7 +61668,7 @@
           <t>Hendrix and Hadley Apartments</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
+      <c r="D225" s="2" t="inlineStr">
         <is>
           <t>2262031000</t>
         </is>
@@ -60630,6 +61731,11 @@
       <c r="T225" t="inlineStr">
         <is>
           <t>157</t>
+        </is>
+      </c>
+      <c r="U225" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -60649,7 +61755,7 @@
           <t>Hendrix and Hadley Apartments</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
+      <c r="D226" s="2" t="inlineStr">
         <is>
           <t>2280732000</t>
         </is>
@@ -60712,6 +61818,11 @@
       <c r="T226" t="inlineStr">
         <is>
           <t>157</t>
+        </is>
+      </c>
+      <c r="U226" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -60731,7 +61842,7 @@
           <t>Hendrix and Hadley Apartments</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="D227" s="2" t="inlineStr">
         <is>
           <t>2262030200</t>
         </is>
@@ -60794,6 +61905,11 @@
       <c r="T227" t="inlineStr">
         <is>
           <t>157</t>
+        </is>
+      </c>
+      <c r="U227" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -60813,7 +61929,7 @@
           <t>Hendrix and Hadley Apartments</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
+      <c r="D228" s="2" t="inlineStr">
         <is>
           <t>2262110300</t>
         </is>
@@ -60876,6 +61992,11 @@
       <c r="T228" t="inlineStr">
         <is>
           <t>157</t>
+        </is>
+      </c>
+      <c r="U228" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -60922,7 +62043,7 @@
           <t>1141 N. Vermont Avenue Apartments</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr">
+      <c r="D230" s="2" t="inlineStr">
         <is>
           <t>5540019012</t>
         </is>
@@ -60990,6 +62111,11 @@
       <c r="T230" t="inlineStr">
         <is>
           <t>159</t>
+        </is>
+      </c>
+      <c r="U230" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -61009,12 +62135,12 @@
           <t>12th Street Apartments</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr">
+      <c r="D231" s="2" t="inlineStr">
         <is>
           <t>5080011007</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
+      <c r="E231" s="2" t="inlineStr">
         <is>
           <t>5080-011-007</t>
         </is>
@@ -61092,6 +62218,11 @@
       <c r="T231" t="inlineStr">
         <is>
           <t>351</t>
+        </is>
+      </c>
+      <c r="U231" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -61111,12 +62242,12 @@
           <t>8th Street Apartments</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr">
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>5077018006</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
+      <c r="E232" s="2" t="inlineStr">
         <is>
           <t>5077-018-006</t>
         </is>
@@ -61184,6 +62315,11 @@
       <c r="T232" t="inlineStr">
         <is>
           <t>161</t>
+        </is>
+      </c>
+      <c r="U232" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -61203,12 +62339,12 @@
           <t>Alexandria II Apartments</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr">
+      <c r="D233" s="2" t="inlineStr">
         <is>
           <t>5518013024</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
+      <c r="E233" s="2" t="inlineStr">
         <is>
           <t>5518-013-024</t>
         </is>
@@ -61276,6 +62412,11 @@
       <c r="T233" t="inlineStr">
         <is>
           <t>162</t>
+        </is>
+      </c>
+      <c r="U233" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -61295,12 +62436,12 @@
           <t>Ardmore Apartments</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr">
+      <c r="D234" s="2" t="inlineStr">
         <is>
           <t>5521023008</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
+      <c r="E234" s="2" t="inlineStr">
         <is>
           <t>5521-023-008</t>
         </is>
@@ -61368,6 +62509,11 @@
       <c r="T234" t="inlineStr">
         <is>
           <t>163</t>
+        </is>
+      </c>
+      <c r="U234" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -61387,12 +62533,12 @@
           <t>Avalon Apartments</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
+      <c r="D235" s="2" t="inlineStr">
         <is>
           <t>5468028027</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
+      <c r="E235" s="2" t="inlineStr">
         <is>
           <t>5468-028-027</t>
         </is>
@@ -61460,6 +62606,11 @@
       <c r="T235" t="inlineStr">
         <is>
           <t>164</t>
+        </is>
+      </c>
+      <c r="U235" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -61479,12 +62630,12 @@
           <t>Fedora Apartments</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
+      <c r="D236" s="2" t="inlineStr">
         <is>
           <t>5094017020</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>5094-017-020</t>
         </is>
@@ -61552,6 +62703,11 @@
       <c r="T236" t="inlineStr">
         <is>
           <t>165</t>
+        </is>
+      </c>
+      <c r="U236" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -61571,12 +62727,12 @@
           <t>Harvard Apartments</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr">
+      <c r="D237" s="2" t="inlineStr">
         <is>
           <t>5521010010</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t>5521-010-010</t>
         </is>
@@ -61644,6 +62800,11 @@
       <c r="T237" t="inlineStr">
         <is>
           <t>166</t>
+        </is>
+      </c>
+      <c r="U237" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -61663,12 +62824,12 @@
           <t>Hollywood Apartments</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
+      <c r="D238" s="2" t="inlineStr">
         <is>
           <t>5544016002</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
+      <c r="E238" s="2" t="inlineStr">
         <is>
           <t>5544-016-002</t>
         </is>
@@ -61736,6 +62897,11 @@
       <c r="T238" t="inlineStr">
         <is>
           <t>167</t>
+        </is>
+      </c>
+      <c r="U238" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -61755,12 +62921,12 @@
           <t>Kenmore II Apartments</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
+      <c r="D239" s="2" t="inlineStr">
         <is>
           <t>5518020021</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>5518-020-021</t>
         </is>
@@ -61828,6 +62994,11 @@
       <c r="T239" t="inlineStr">
         <is>
           <t>168</t>
+        </is>
+      </c>
+      <c r="U239" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -61847,12 +63018,12 @@
           <t>Kenmore III Apartments</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr">
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>5094023025</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>5094-023-025</t>
         </is>
@@ -61920,6 +63091,11 @@
       <c r="T240" t="inlineStr">
         <is>
           <t>169</t>
+        </is>
+      </c>
+      <c r="U240" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -61939,12 +63115,12 @@
           <t>Kinglsey Apartments</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr">
+      <c r="D241" s="2" t="inlineStr">
         <is>
           <t>5503024012</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr">
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>5503-024-012</t>
         </is>
@@ -62012,6 +63188,11 @@
       <c r="T241" t="inlineStr">
         <is>
           <t>170</t>
+        </is>
+      </c>
+      <c r="U241" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -62031,12 +63212,12 @@
           <t>Lexington Apartments</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
+      <c r="D242" s="2" t="inlineStr">
         <is>
           <t>5537006002</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
+      <c r="E242" s="2" t="inlineStr">
         <is>
           <t>5537-006-002</t>
         </is>
@@ -62104,6 +63285,11 @@
       <c r="T242" t="inlineStr">
         <is>
           <t>171</t>
+        </is>
+      </c>
+      <c r="U242" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -62123,12 +63309,12 @@
           <t>Manhattan I &amp; II Apartments</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr">
+      <c r="D243" s="2" t="inlineStr">
         <is>
           <t>5503015019</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr">
+      <c r="E243" s="2" t="inlineStr">
         <is>
           <t>5503-015-019</t>
         </is>
@@ -62196,6 +63382,11 @@
       <c r="T243" t="inlineStr">
         <is>
           <t>172</t>
+        </is>
+      </c>
+      <c r="U243" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -62215,12 +63406,12 @@
           <t>Manhattan I &amp; II Apartments</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr">
+      <c r="D244" s="2" t="inlineStr">
         <is>
           <t>5503017019</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr">
+      <c r="E244" s="2" t="inlineStr">
         <is>
           <t>5503-017-019</t>
         </is>
@@ -62288,6 +63479,11 @@
       <c r="T244" t="inlineStr">
         <is>
           <t>172</t>
+        </is>
+      </c>
+      <c r="U244" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -62307,12 +63503,12 @@
           <t>Mariposa I Apartments</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr">
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t>5094005005</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
         <is>
           <t>5094-005-005</t>
         </is>
@@ -62380,6 +63576,11 @@
       <c r="T245" t="inlineStr">
         <is>
           <t>173</t>
+        </is>
+      </c>
+      <c r="U245" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -62399,12 +63600,12 @@
           <t>Mariposa III Apartments</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr">
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>5094006003</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>5094-006-003</t>
         </is>
@@ -62472,6 +63673,11 @@
       <c r="T246" t="inlineStr">
         <is>
           <t>174</t>
+        </is>
+      </c>
+      <c r="U246" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -62491,12 +63697,12 @@
           <t>Mariposa IV Apartments</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
+      <c r="D247" s="2" t="inlineStr">
         <is>
           <t>5502019004</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>5502-019-004</t>
         </is>
@@ -62564,6 +63770,11 @@
       <c r="T247" t="inlineStr">
         <is>
           <t>175</t>
+        </is>
+      </c>
+      <c r="U247" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -62583,12 +63794,12 @@
           <t>Monte Vista Apartments</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr">
+      <c r="D248" s="2" t="inlineStr">
         <is>
           <t>5469032001</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr">
+      <c r="E248" s="2" t="inlineStr">
         <is>
           <t>5469-032-001</t>
         </is>
@@ -62656,6 +63867,11 @@
       <c r="T248" t="inlineStr">
         <is>
           <t>176</t>
+        </is>
+      </c>
+      <c r="U248" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -62675,12 +63891,12 @@
           <t>Oxford II Apartments</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr">
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>5517005016</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>5517-005-016</t>
         </is>
@@ -62748,6 +63964,11 @@
       <c r="T249" t="inlineStr">
         <is>
           <t>177</t>
+        </is>
+      </c>
+      <c r="U249" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -62767,12 +63988,12 @@
           <t>Parkview Apartments</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr">
+      <c r="D250" s="2" t="inlineStr">
         <is>
           <t>5446002044</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr">
+      <c r="E250" s="2" t="inlineStr">
         <is>
           <t>5446-002-044</t>
         </is>
@@ -62840,6 +64061,11 @@
       <c r="T250" t="inlineStr">
         <is>
           <t>178</t>
+        </is>
+      </c>
+      <c r="U250" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -62859,12 +64085,12 @@
           <t>Western Apartments</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr">
+      <c r="D251" s="2" t="inlineStr">
         <is>
           <t>5080006008</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>5080-006-008</t>
         </is>
@@ -62932,6 +64158,11 @@
       <c r="T251" t="inlineStr">
         <is>
           <t>179</t>
+        </is>
+      </c>
+      <c r="U251" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -62951,12 +64182,12 @@
           <t>Westmoreland Apartments</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr">
+      <c r="D252" s="2" t="inlineStr">
         <is>
           <t>5501016008</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
+      <c r="E252" s="2" t="inlineStr">
         <is>
           <t>5501-016-008</t>
         </is>
@@ -63024,6 +64255,11 @@
       <c r="T252" t="inlineStr">
         <is>
           <t>180</t>
+        </is>
+      </c>
+      <c r="U252" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -63043,12 +64279,12 @@
           <t>The Hive Apartments</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr">
+      <c r="D253" s="2" t="inlineStr">
         <is>
           <t>7157012017</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
+      <c r="E253" s="2" t="inlineStr">
         <is>
           <t>7157-012-017</t>
         </is>
@@ -63116,6 +64352,11 @@
       <c r="T253" t="inlineStr">
         <is>
           <t>181</t>
+        </is>
+      </c>
+      <c r="U253" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -63135,12 +64376,12 @@
           <t>4256 Whittier Blvd Apartments</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
+      <c r="D254" s="2" t="inlineStr">
         <is>
           <t>5236016054</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
+      <c r="E254" s="2" t="inlineStr">
         <is>
           <t>5236-016-054</t>
         </is>
@@ -63208,6 +64449,11 @@
       <c r="T254" t="inlineStr">
         <is>
           <t>183</t>
+        </is>
+      </c>
+      <c r="U254" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -63227,12 +64473,12 @@
           <t>225 W 25th Apartments</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
+      <c r="D255" s="2" t="inlineStr">
         <is>
           <t>5126020009</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
+      <c r="E255" s="2" t="inlineStr">
         <is>
           <t>5126-020-009</t>
         </is>
@@ -63300,6 +64546,11 @@
       <c r="T255" t="inlineStr">
         <is>
           <t>184</t>
+        </is>
+      </c>
+      <c r="U255" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -63319,12 +64570,12 @@
           <t>9422 Firth Avenue Apartments</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr">
+      <c r="D256" s="2" t="inlineStr">
         <is>
           <t>6048004047</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr">
+      <c r="E256" s="2" t="inlineStr">
         <is>
           <t>6048-004-047</t>
         </is>
@@ -63387,6 +64638,11 @@
       <c r="T256" t="inlineStr">
         <is>
           <t>185</t>
+        </is>
+      </c>
+      <c r="U256" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -63406,12 +64662,12 @@
           <t>4008 Martin Luther King Blvd Apartments</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr">
+      <c r="D257" s="2" t="inlineStr">
         <is>
           <t>5032007019</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
+      <c r="E257" s="2" t="inlineStr">
         <is>
           <t>5032-007-019</t>
         </is>
@@ -63479,6 +64735,11 @@
       <c r="T257" t="inlineStr">
         <is>
           <t>186</t>
+        </is>
+      </c>
+      <c r="U257" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -63538,6 +64799,11 @@
           <t>187</t>
         </is>
       </c>
+      <c r="U258" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -63600,6 +64866,11 @@
           <t>205</t>
         </is>
       </c>
+      <c r="U259" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -63662,6 +64933,11 @@
           <t>190</t>
         </is>
       </c>
+      <c r="U260" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -63724,6 +65000,11 @@
           <t>192</t>
         </is>
       </c>
+      <c r="U261" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -63741,12 +65022,12 @@
           <t>Heritage Park Escondido Apartments</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr">
+      <c r="D262" s="2" t="inlineStr">
         <is>
           <t>2311104600</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
+      <c r="E262" s="2" t="inlineStr">
         <is>
           <t>2311104600</t>
         </is>
@@ -63814,6 +65095,11 @@
       <c r="T262" t="inlineStr">
         <is>
           <t>193</t>
+        </is>
+      </c>
+      <c r="U262" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -63833,7 +65119,7 @@
           <t>3751 Delmas Terrace Apartments</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
+      <c r="D263" s="2" t="inlineStr">
         <is>
           <t>4313014022</t>
         </is>
@@ -63906,6 +65192,11 @@
       <c r="T263" t="inlineStr">
         <is>
           <t>194</t>
+        </is>
+      </c>
+      <c r="U263" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -63925,7 +65216,7 @@
           <t>1723 Corinth Apartments</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr">
+      <c r="D264" s="2" t="inlineStr">
         <is>
           <t>4261017008</t>
         </is>
@@ -63998,6 +65289,11 @@
       <c r="T264" t="inlineStr">
         <is>
           <t>195</t>
+        </is>
+      </c>
+      <c r="U264" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -64081,12 +65377,12 @@
           <t>Baird Affordable Housing Apartments</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr">
+      <c r="D267" s="2" t="inlineStr">
         <is>
           <t>2126022021</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr">
+      <c r="E267" s="2" t="inlineStr">
         <is>
           <t>2126-022-021</t>
         </is>
@@ -64159,6 +65455,11 @@
       <c r="T267" t="inlineStr">
         <is>
           <t>199</t>
+        </is>
+      </c>
+      <c r="U267" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -64265,6 +65566,11 @@
           <t>203</t>
         </is>
       </c>
+      <c r="U269" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -64282,12 +65588,12 @@
           <t>Hazelhurst Affordable Housing Apartments</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
+      <c r="D270" s="2" t="inlineStr">
         <is>
           <t>2338006014</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
+      <c r="E270" s="2" t="inlineStr">
         <is>
           <t>2338-006-014</t>
         </is>
@@ -64360,6 +65666,11 @@
       <c r="T270" t="inlineStr">
         <is>
           <t>204</t>
+        </is>
+      </c>
+      <c r="U270" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -64475,12 +65786,12 @@
           <t>Bluwater Crossing Apartments</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr">
+      <c r="D274" s="2" t="inlineStr">
         <is>
           <t>2146500200</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr">
+      <c r="E274" s="2" t="inlineStr">
         <is>
           <t>214-650-02-00</t>
         </is>
@@ -64548,6 +65859,11 @@
       <c r="T274" t="inlineStr">
         <is>
           <t>209</t>
+        </is>
+      </c>
+      <c r="U274" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -64607,6 +65923,11 @@
           <t>210</t>
         </is>
       </c>
+      <c r="U275" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -64624,7 +65945,7 @@
           <t>Haven Warner Center</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr">
+      <c r="D276" s="2" t="inlineStr">
         <is>
           <t>2148026046</t>
         </is>
@@ -64697,6 +66018,11 @@
       <c r="T276" t="inlineStr">
         <is>
           <t>211</t>
+        </is>
+      </c>
+      <c r="U276" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -64716,7 +66042,7 @@
           <t>The Arlo</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr">
+      <c r="D277" s="2" t="inlineStr">
         <is>
           <t>5052023039</t>
         </is>
@@ -64789,6 +66115,11 @@
       <c r="T277" t="inlineStr">
         <is>
           <t>212</t>
+        </is>
+      </c>
+      <c r="U277" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -64863,6 +66194,11 @@
           <t>213</t>
         </is>
       </c>
+      <c r="U278" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -64880,7 +66216,7 @@
           <t>Trails at San Dimas</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr">
+      <c r="D279" s="2" t="inlineStr">
         <is>
           <t>8386006015</t>
         </is>
@@ -64953,6 +66289,11 @@
       <c r="T279" t="inlineStr">
         <is>
           <t>214</t>
+        </is>
+      </c>
+      <c r="U279" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -65007,6 +66348,11 @@
           <t>215</t>
         </is>
       </c>
+      <c r="U280" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -65024,12 +66370,12 @@
           <t>Guava Gardens Apartments</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr">
+      <c r="D281" s="2" t="inlineStr">
         <is>
           <t>4701122500</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr">
+      <c r="E281" s="2" t="inlineStr">
         <is>
           <t>470-112-25-00</t>
         </is>
@@ -65097,6 +66443,11 @@
       <c r="T281" t="inlineStr">
         <is>
           <t>216</t>
+        </is>
+      </c>
+      <c r="U281" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -65116,12 +66467,12 @@
           <t>Park View by Angeleno Apartments</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr">
+      <c r="D282" s="2" t="inlineStr">
         <is>
           <t>5157007028</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr">
+      <c r="E282" s="2" t="inlineStr">
         <is>
           <t>5157-007-028</t>
         </is>
@@ -65194,6 +66545,11 @@
       <c r="T282" t="inlineStr">
         <is>
           <t>217</t>
+        </is>
+      </c>
+      <c r="U282" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -65213,7 +66569,7 @@
           <t>1408 Jefferson Blvd Apartments</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr">
+      <c r="D283" s="2" t="inlineStr">
         <is>
           <t>5040021006</t>
         </is>
@@ -65286,6 +66642,11 @@
       <c r="T283" t="inlineStr">
         <is>
           <t>218</t>
+        </is>
+      </c>
+      <c r="U283" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -65305,7 +66666,7 @@
           <t>603 Mariposa Apartments</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr">
+      <c r="D284" s="2" t="inlineStr">
         <is>
           <t>5502031012</t>
         </is>
@@ -65378,6 +66739,11 @@
       <c r="T284" t="inlineStr">
         <is>
           <t>219</t>
+        </is>
+      </c>
+      <c r="U284" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -65397,7 +66763,7 @@
           <t>236 Berendo Apartments</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr">
+      <c r="D285" s="2" t="inlineStr">
         <is>
           <t>5518026004</t>
         </is>
@@ -65470,6 +66836,11 @@
       <c r="T285" t="inlineStr">
         <is>
           <t>220</t>
+        </is>
+      </c>
+      <c r="U285" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -65569,6 +66940,11 @@
           <t>221</t>
         </is>
       </c>
+      <c r="U286" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -65641,6 +67017,11 @@
           <t>222</t>
         </is>
       </c>
+      <c r="U287" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -65713,6 +67094,11 @@
           <t>223</t>
         </is>
       </c>
+      <c r="U288" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -65730,7 +67116,7 @@
           <t>1454 Florence Apartments</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr">
+      <c r="D289" s="2" t="inlineStr">
         <is>
           <t>6018007001</t>
         </is>
@@ -65803,6 +67189,11 @@
       <c r="T289" t="inlineStr">
         <is>
           <t>224</t>
+        </is>
+      </c>
+      <c r="U289" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -65894,6 +67285,11 @@
           <t>227</t>
         </is>
       </c>
+      <c r="U291" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -65911,7 +67307,7 @@
           <t>Colden Oaks Apartments</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr">
+      <c r="D292" s="2" t="inlineStr">
         <is>
           <t>6053006052</t>
         </is>
@@ -65984,6 +67380,11 @@
       <c r="T292" t="inlineStr">
         <is>
           <t>228</t>
+        </is>
+      </c>
+      <c r="U292" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -66003,7 +67404,7 @@
           <t>Hansen illage Apartments</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr">
+      <c r="D293" s="2" t="inlineStr">
         <is>
           <t>2530007014</t>
         </is>
@@ -66076,6 +67477,11 @@
       <c r="T293" t="inlineStr">
         <is>
           <t>230</t>
+        </is>
+      </c>
+      <c r="U293" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -66095,7 +67501,7 @@
           <t>Violet on Virgil</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr">
+      <c r="D294" s="2" t="inlineStr">
         <is>
           <t>5501017044</t>
         </is>
@@ -66168,6 +67574,11 @@
       <c r="T294" t="inlineStr">
         <is>
           <t>231</t>
+        </is>
+      </c>
+      <c r="U294" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -66232,6 +67643,11 @@
           <t>232</t>
         </is>
       </c>
+      <c r="U295" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -66294,6 +67710,11 @@
           <t>232</t>
         </is>
       </c>
+      <c r="U296" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -66311,7 +67732,7 @@
           <t>926 S. Kingsley Apartments</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr">
+      <c r="D297" s="2" t="inlineStr">
         <is>
           <t>5093023058</t>
         </is>
@@ -66384,6 +67805,11 @@
       <c r="T297" t="inlineStr">
         <is>
           <t>233</t>
+        </is>
+      </c>
+      <c r="U297" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -66403,7 +67829,7 @@
           <t>939 S. Kingsley Apartments</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr">
+      <c r="D298" s="2" t="inlineStr">
         <is>
           <t>5093023059</t>
         </is>
@@ -66476,6 +67902,11 @@
       <c r="T298" t="inlineStr">
         <is>
           <t>234</t>
+        </is>
+      </c>
+      <c r="U298" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -66495,12 +67926,12 @@
           <t>3950 Ingraham Apartments</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr">
+      <c r="D299" s="2" t="inlineStr">
         <is>
           <t>5092029007</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr">
+      <c r="E299" s="2" t="inlineStr">
         <is>
           <t>5092-029-007</t>
         </is>
@@ -66568,6 +67999,11 @@
       <c r="T299" t="inlineStr">
         <is>
           <t>235</t>
+        </is>
+      </c>
+      <c r="U299" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -66662,6 +68098,11 @@
           <t>236</t>
         </is>
       </c>
+      <c r="U300" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -66679,7 +68120,7 @@
           <t>Edgemont by Angeleno</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr">
+      <c r="D301" s="2" t="inlineStr">
         <is>
           <t>5540023002</t>
         </is>
@@ -66752,6 +68193,11 @@
       <c r="T301" t="inlineStr">
         <is>
           <t>237</t>
+        </is>
+      </c>
+      <c r="U301" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -66811,6 +68257,11 @@
           <t>57</t>
         </is>
       </c>
+      <c r="U302" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -66863,6 +68314,11 @@
           <t>60</t>
         </is>
       </c>
+      <c r="U303" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -66915,6 +68371,11 @@
           <t>60</t>
         </is>
       </c>
+      <c r="U304" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -66967,6 +68428,11 @@
           <t>89</t>
         </is>
       </c>
+      <c r="U305" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -67019,6 +68485,11 @@
           <t>95</t>
         </is>
       </c>
+      <c r="U306" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -67071,6 +68542,11 @@
           <t>96</t>
         </is>
       </c>
+      <c r="U307" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -67123,6 +68599,11 @@
           <t>96</t>
         </is>
       </c>
+      <c r="U308" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -67175,6 +68656,11 @@
           <t>96</t>
         </is>
       </c>
+      <c r="U309" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -67227,6 +68713,11 @@
           <t>136</t>
         </is>
       </c>
+      <c r="U310" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -67279,6 +68770,11 @@
           <t>138</t>
         </is>
       </c>
+      <c r="U311" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -67336,6 +68832,11 @@
           <t>139</t>
         </is>
       </c>
+      <c r="U312" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -67393,6 +68894,11 @@
           <t>139</t>
         </is>
       </c>
+      <c r="U313" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -67445,6 +68951,11 @@
           <t>140</t>
         </is>
       </c>
+      <c r="U314" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -67502,6 +69013,11 @@
           <t>189</t>
         </is>
       </c>
+      <c r="U315" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -67549,6 +69065,11 @@
           <t>189</t>
         </is>
       </c>
+      <c r="U316" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -67596,6 +69117,11 @@
           <t>189</t>
         </is>
       </c>
+      <c r="U317" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -67643,6 +69169,11 @@
           <t>189</t>
         </is>
       </c>
+      <c r="U318" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -67700,6 +69231,11 @@
           <t>191</t>
         </is>
       </c>
+      <c r="U319" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -67799,6 +69335,11 @@
           <t>202</t>
         </is>
       </c>
+      <c r="U321" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -67866,6 +69407,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="U322" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -67883,7 +69429,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr">
+      <c r="D323" s="2" t="inlineStr">
         <is>
           <t>128101140</t>
         </is>
@@ -67941,6 +69487,11 @@
       <c r="T323" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U323" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -67960,7 +69511,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr">
+      <c r="D324" s="2" t="inlineStr">
         <is>
           <t>128101130</t>
         </is>
@@ -68018,6 +69569,11 @@
       <c r="T324" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U324" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -68037,7 +69593,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr">
+      <c r="D325" s="2" t="inlineStr">
         <is>
           <t>128101120</t>
         </is>
@@ -68095,6 +69651,11 @@
       <c r="T325" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U325" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -68114,7 +69675,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr">
+      <c r="D326" s="2" t="inlineStr">
         <is>
           <t>128101110</t>
         </is>
@@ -68172,6 +69733,11 @@
       <c r="T326" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U326" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -68268,7 +69834,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr">
+      <c r="D328" s="2" t="inlineStr">
         <is>
           <t>128101090</t>
         </is>
@@ -68326,6 +69892,11 @@
       <c r="T328" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U328" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -68345,7 +69916,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr">
+      <c r="D329" s="2" t="inlineStr">
         <is>
           <t>128101080</t>
         </is>
@@ -68403,6 +69974,11 @@
       <c r="T329" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U329" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -68422,7 +69998,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr">
+      <c r="D330" s="2" t="inlineStr">
         <is>
           <t>128101070</t>
         </is>
@@ -68480,6 +70056,11 @@
       <c r="T330" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U330" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -68499,7 +70080,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr">
+      <c r="D331" s="2" t="inlineStr">
         <is>
           <t>128101060</t>
         </is>
@@ -68557,6 +70138,11 @@
       <c r="T331" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U331" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -68626,6 +70212,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="U332" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -68643,7 +70234,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr">
+      <c r="D333" s="2" t="inlineStr">
         <is>
           <t>128101040</t>
         </is>
@@ -68701,6 +70292,11 @@
       <c r="T333" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U333" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -68720,7 +70316,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr">
+      <c r="D334" s="2" t="inlineStr">
         <is>
           <t>128101030</t>
         </is>
@@ -68778,6 +70374,11 @@
       <c r="T334" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U334" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -68797,7 +70398,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr">
+      <c r="D335" s="2" t="inlineStr">
         <is>
           <t>128101020</t>
         </is>
@@ -68855,6 +70456,11 @@
       <c r="T335" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U335" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -68874,7 +70480,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr">
+      <c r="D336" s="2" t="inlineStr">
         <is>
           <t>128101010</t>
         </is>
@@ -68932,6 +70538,11 @@
       <c r="T336" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U336" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -68951,7 +70562,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr">
+      <c r="D337" s="2" t="inlineStr">
         <is>
           <t>128102110</t>
         </is>
@@ -69009,6 +70620,11 @@
       <c r="T337" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U337" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -69028,7 +70644,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr">
+      <c r="D338" s="2" t="inlineStr">
         <is>
           <t>128102100</t>
         </is>
@@ -69086,6 +70702,11 @@
       <c r="T338" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U338" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -69105,7 +70726,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr">
+      <c r="D339" s="2" t="inlineStr">
         <is>
           <t>128102090</t>
         </is>
@@ -69163,6 +70784,11 @@
       <c r="T339" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U339" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -69182,7 +70808,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr">
+      <c r="D340" s="2" t="inlineStr">
         <is>
           <t>128102080</t>
         </is>
@@ -69240,6 +70866,11 @@
       <c r="T340" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U340" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -69259,7 +70890,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr">
+      <c r="D341" s="2" t="inlineStr">
         <is>
           <t>128102070</t>
         </is>
@@ -69317,6 +70948,11 @@
       <c r="T341" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U341" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -69336,7 +70972,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr">
+      <c r="D342" s="2" t="inlineStr">
         <is>
           <t>128102060</t>
         </is>
@@ -69394,6 +71030,11 @@
       <c r="T342" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U342" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -69413,7 +71054,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr">
+      <c r="D343" s="2" t="inlineStr">
         <is>
           <t>128102050</t>
         </is>
@@ -69471,6 +71112,11 @@
       <c r="T343" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U343" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -69490,7 +71136,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr">
+      <c r="D344" s="2" t="inlineStr">
         <is>
           <t>128102040</t>
         </is>
@@ -69548,6 +71194,11 @@
       <c r="T344" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U344" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -69567,7 +71218,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr">
+      <c r="D345" s="2" t="inlineStr">
         <is>
           <t>128102030</t>
         </is>
@@ -69625,6 +71276,11 @@
       <c r="T345" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U345" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -69644,7 +71300,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr">
+      <c r="D346" s="2" t="inlineStr">
         <is>
           <t>128102020</t>
         </is>
@@ -69702,6 +71358,11 @@
       <c r="T346" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U346" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -69721,7 +71382,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr">
+      <c r="D347" s="2" t="inlineStr">
         <is>
           <t>128102010</t>
         </is>
@@ -69779,6 +71440,11 @@
       <c r="T347" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U347" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -69798,7 +71464,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr">
+      <c r="D348" s="2" t="inlineStr">
         <is>
           <t>128102210</t>
         </is>
@@ -69856,6 +71522,11 @@
       <c r="T348" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U348" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -69875,7 +71546,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr">
+      <c r="D349" s="2" t="inlineStr">
         <is>
           <t>128102200</t>
         </is>
@@ -69933,6 +71604,11 @@
       <c r="T349" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U349" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -69952,7 +71628,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr">
+      <c r="D350" s="2" t="inlineStr">
         <is>
           <t>128102190</t>
         </is>
@@ -70010,6 +71686,11 @@
       <c r="T350" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U350" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -70029,7 +71710,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr">
+      <c r="D351" s="2" t="inlineStr">
         <is>
           <t>128102180</t>
         </is>
@@ -70087,6 +71768,11 @@
       <c r="T351" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U351" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -70106,7 +71792,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr">
+      <c r="D352" s="2" t="inlineStr">
         <is>
           <t>128102170</t>
         </is>
@@ -70164,6 +71850,11 @@
       <c r="T352" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U352" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -70183,7 +71874,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr">
+      <c r="D353" s="2" t="inlineStr">
         <is>
           <t>128102160</t>
         </is>
@@ -70241,6 +71932,11 @@
       <c r="T353" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U353" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -70260,7 +71956,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr">
+      <c r="D354" s="2" t="inlineStr">
         <is>
           <t>128102150</t>
         </is>
@@ -70318,6 +72014,11 @@
       <c r="T354" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U354" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -70337,7 +72038,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr">
+      <c r="D355" s="2" t="inlineStr">
         <is>
           <t>128102140</t>
         </is>
@@ -70395,6 +72096,11 @@
       <c r="T355" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U355" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -70414,7 +72120,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr">
+      <c r="D356" s="2" t="inlineStr">
         <is>
           <t>128102130</t>
         </is>
@@ -70472,6 +72178,11 @@
       <c r="T356" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U356" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -70491,7 +72202,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr">
+      <c r="D357" s="2" t="inlineStr">
         <is>
           <t>128102120</t>
         </is>
@@ -70549,6 +72260,11 @@
       <c r="T357" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U357" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -70568,7 +72284,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr">
+      <c r="D358" s="2" t="inlineStr">
         <is>
           <t>128103090</t>
         </is>
@@ -70626,6 +72342,11 @@
       <c r="T358" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U358" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -70645,7 +72366,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr">
+      <c r="D359" s="2" t="inlineStr">
         <is>
           <t>128103080</t>
         </is>
@@ -70703,6 +72424,11 @@
       <c r="T359" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U359" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -70722,7 +72448,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr">
+      <c r="D360" s="2" t="inlineStr">
         <is>
           <t>128103070</t>
         </is>
@@ -70780,6 +72506,11 @@
       <c r="T360" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U360" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -70799,7 +72530,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr">
+      <c r="D361" s="2" t="inlineStr">
         <is>
           <t>128103060</t>
         </is>
@@ -70857,6 +72588,11 @@
       <c r="T361" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U361" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -70876,7 +72612,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr">
+      <c r="D362" s="2" t="inlineStr">
         <is>
           <t>128103050</t>
         </is>
@@ -70934,6 +72670,11 @@
       <c r="T362" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U362" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -70953,7 +72694,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr">
+      <c r="D363" s="2" t="inlineStr">
         <is>
           <t>128103040</t>
         </is>
@@ -71011,6 +72752,11 @@
       <c r="T363" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U363" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -71030,7 +72776,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr">
+      <c r="D364" s="2" t="inlineStr">
         <is>
           <t>128103030</t>
         </is>
@@ -71088,6 +72834,11 @@
       <c r="T364" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U364" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -71107,7 +72858,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr">
+      <c r="D365" s="2" t="inlineStr">
         <is>
           <t>128103020</t>
         </is>
@@ -71165,6 +72916,11 @@
       <c r="T365" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U365" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -71184,7 +72940,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr">
+      <c r="D366" s="2" t="inlineStr">
         <is>
           <t>128103010</t>
         </is>
@@ -71242,6 +72998,11 @@
       <c r="T366" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U366" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -71261,7 +73022,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr">
+      <c r="D367" s="2" t="inlineStr">
         <is>
           <t>128103180</t>
         </is>
@@ -71319,6 +73080,11 @@
       <c r="T367" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U367" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -71338,7 +73104,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr">
+      <c r="D368" s="2" t="inlineStr">
         <is>
           <t>128103170</t>
         </is>
@@ -71396,6 +73162,11 @@
       <c r="T368" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U368" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -71415,7 +73186,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr">
+      <c r="D369" s="2" t="inlineStr">
         <is>
           <t>128103160</t>
         </is>
@@ -71473,6 +73244,11 @@
       <c r="T369" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U369" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -71492,7 +73268,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr">
+      <c r="D370" s="2" t="inlineStr">
         <is>
           <t>128103150</t>
         </is>
@@ -71550,6 +73326,11 @@
       <c r="T370" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U370" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -71569,7 +73350,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr">
+      <c r="D371" s="2" t="inlineStr">
         <is>
           <t>128103140</t>
         </is>
@@ -71627,6 +73408,11 @@
       <c r="T371" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U371" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -71646,7 +73432,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr">
+      <c r="D372" s="2" t="inlineStr">
         <is>
           <t>128103130</t>
         </is>
@@ -71704,6 +73490,11 @@
       <c r="T372" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U372" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -71723,7 +73514,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr">
+      <c r="D373" s="2" t="inlineStr">
         <is>
           <t>128103120</t>
         </is>
@@ -71781,6 +73572,11 @@
       <c r="T373" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U373" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -71800,7 +73596,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr">
+      <c r="D374" s="2" t="inlineStr">
         <is>
           <t>128103110</t>
         </is>
@@ -71858,6 +73654,11 @@
       <c r="T374" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U374" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -71877,7 +73678,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr">
+      <c r="D375" s="2" t="inlineStr">
         <is>
           <t>128103100</t>
         </is>
@@ -71935,6 +73736,11 @@
       <c r="T375" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U375" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -72004,6 +73810,11 @@
           <t>16</t>
         </is>
       </c>
+      <c r="U376" s="2" t="inlineStr">
+        <is>
+          <t>documented</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -72021,7 +73832,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr">
+      <c r="D377" s="2" t="inlineStr">
         <is>
           <t>128105050</t>
         </is>
@@ -72079,6 +73890,11 @@
       <c r="T377" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U377" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -72098,7 +73914,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr">
+      <c r="D378" s="2" t="inlineStr">
         <is>
           <t>128105040</t>
         </is>
@@ -72156,6 +73972,11 @@
       <c r="T378" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U378" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -72175,7 +73996,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr">
+      <c r="D379" s="2" t="inlineStr">
         <is>
           <t>128105030</t>
         </is>
@@ -72233,6 +74054,11 @@
       <c r="T379" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U379" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -72252,7 +74078,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr">
+      <c r="D380" s="2" t="inlineStr">
         <is>
           <t>128105020</t>
         </is>
@@ -72310,6 +74136,11 @@
       <c r="T380" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U380" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -72329,7 +74160,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr">
+      <c r="D381" s="2" t="inlineStr">
         <is>
           <t>128105010</t>
         </is>
@@ -72387,6 +74218,11 @@
       <c r="T381" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U381" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -72406,7 +74242,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr">
+      <c r="D382" s="2" t="inlineStr">
         <is>
           <t>128104020</t>
         </is>
@@ -72464,6 +74300,11 @@
       <c r="T382" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U382" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -72483,7 +74324,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr">
+      <c r="D383" s="2" t="inlineStr">
         <is>
           <t>128104010</t>
         </is>
@@ -72541,6 +74382,11 @@
       <c r="T383" t="inlineStr">
         <is>
           <t>16</t>
+        </is>
+      </c>
+      <c r="U383" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -72560,12 +74406,12 @@
           <t>Bennington Apartments</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr">
+      <c r="D384" s="2" t="inlineStr">
         <is>
           <t>168150010</t>
         </is>
       </c>
-      <c r="E384" t="inlineStr">
+      <c r="E384" s="2" t="inlineStr">
         <is>
           <t>0168-150-010</t>
         </is>
@@ -72628,6 +74474,11 @@
       <c r="T384" t="inlineStr">
         <is>
           <t>225</t>
+        </is>
+      </c>
+      <c r="U384" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -72692,6 +74543,11 @@
           <t>131</t>
         </is>
       </c>
+      <c r="U385" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -72709,7 +74565,7 @@
           <t>Hansen illage Apartments</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr">
+      <c r="D386" s="2" t="inlineStr">
         <is>
           <t>2530007015</t>
         </is>
@@ -72787,6 +74643,11 @@
       <c r="T386" t="inlineStr">
         <is>
           <t>230</t>
+        </is>
+      </c>
+      <c r="U386" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -72806,12 +74667,12 @@
           <t>Verdana Apartments</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr">
+      <c r="D387" s="2" t="inlineStr">
         <is>
           <t>4441201300</t>
         </is>
       </c>
-      <c r="E387" t="inlineStr">
+      <c r="E387" s="2" t="inlineStr">
         <is>
           <t>444-120-13-00</t>
         </is>
@@ -72884,6 +74745,11 @@
       <c r="T387" t="inlineStr">
         <is>
           <t>369</t>
+        </is>
+      </c>
+      <c r="U387" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -72903,12 +74769,12 @@
           <t>Verdana Apartments</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr">
+      <c r="D388" s="2" t="inlineStr">
         <is>
           <t>4441201800</t>
         </is>
       </c>
-      <c r="E388" t="inlineStr">
+      <c r="E388" s="2" t="inlineStr">
         <is>
           <t>444-120-18-00</t>
         </is>
@@ -72981,6 +74847,11 @@
       <c r="T388" t="inlineStr">
         <is>
           <t>369</t>
+        </is>
+      </c>
+      <c r="U388" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -73053,6 +74924,11 @@
       <c r="T389" t="inlineStr">
         <is>
           <t>238</t>
+        </is>
+      </c>
+      <c r="U389" s="2" t="inlineStr">
+        <is>
+          <t>no-situs</t>
         </is>
       </c>
     </row>
@@ -74881,7 +76757,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Value obtained by automation (document scraping, county API calls) — reproducible by re-running the pipeline</t>
+          <t>Value obtained by automation (document scraping, county API calls) or machine-verified against county records — reproducible by re-running the pipeline</t>
         </is>
       </c>
     </row>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -54549,12 +54549,12 @@
           <t>11630 S. Main Street Apartments</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>6083010040</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E148" t="inlineStr">
         <is>
           <t>6083-010-040</t>
         </is>
@@ -54631,7 +54631,7 @@
       </c>
       <c r="U148" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -67732,7 +67732,7 @@
           <t>926 S. Kingsley Apartments</t>
         </is>
       </c>
-      <c r="D297" s="2" t="inlineStr">
+      <c r="D297" t="inlineStr">
         <is>
           <t>5093023058</t>
         </is>
@@ -67809,7 +67809,7 @@
       </c>
       <c r="U297" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -68120,7 +68120,7 @@
           <t>Edgemont by Angeleno</t>
         </is>
       </c>
-      <c r="D301" s="2" t="inlineStr">
+      <c r="D301" t="inlineStr">
         <is>
           <t>5540023002</t>
         </is>
@@ -68197,7 +68197,7 @@
       </c>
       <c r="U301" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -69429,7 +69429,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D323" s="2" t="inlineStr">
+      <c r="D323" t="inlineStr">
         <is>
           <t>128101140</t>
         </is>
@@ -69491,7 +69491,7 @@
       </c>
       <c r="U323" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -69511,7 +69511,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D324" s="2" t="inlineStr">
+      <c r="D324" t="inlineStr">
         <is>
           <t>128101130</t>
         </is>
@@ -69573,7 +69573,7 @@
       </c>
       <c r="U324" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -69593,7 +69593,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D325" s="2" t="inlineStr">
+      <c r="D325" t="inlineStr">
         <is>
           <t>128101120</t>
         </is>
@@ -69655,7 +69655,7 @@
       </c>
       <c r="U325" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -69675,7 +69675,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D326" s="2" t="inlineStr">
+      <c r="D326" t="inlineStr">
         <is>
           <t>128101110</t>
         </is>
@@ -69737,7 +69737,7 @@
       </c>
       <c r="U326" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -69834,7 +69834,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D328" s="2" t="inlineStr">
+      <c r="D328" t="inlineStr">
         <is>
           <t>128101090</t>
         </is>
@@ -69896,7 +69896,7 @@
       </c>
       <c r="U328" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -69916,7 +69916,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D329" s="2" t="inlineStr">
+      <c r="D329" t="inlineStr">
         <is>
           <t>128101080</t>
         </is>
@@ -69978,7 +69978,7 @@
       </c>
       <c r="U329" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -69998,7 +69998,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D330" s="2" t="inlineStr">
+      <c r="D330" t="inlineStr">
         <is>
           <t>128101070</t>
         </is>
@@ -70060,7 +70060,7 @@
       </c>
       <c r="U330" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -70080,7 +70080,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D331" s="2" t="inlineStr">
+      <c r="D331" t="inlineStr">
         <is>
           <t>128101060</t>
         </is>
@@ -70142,7 +70142,7 @@
       </c>
       <c r="U331" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -70234,7 +70234,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D333" s="2" t="inlineStr">
+      <c r="D333" t="inlineStr">
         <is>
           <t>128101040</t>
         </is>
@@ -70296,7 +70296,7 @@
       </c>
       <c r="U333" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -70316,7 +70316,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D334" s="2" t="inlineStr">
+      <c r="D334" t="inlineStr">
         <is>
           <t>128101030</t>
         </is>
@@ -70378,7 +70378,7 @@
       </c>
       <c r="U334" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -70398,7 +70398,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D335" s="2" t="inlineStr">
+      <c r="D335" t="inlineStr">
         <is>
           <t>128101020</t>
         </is>
@@ -70460,7 +70460,7 @@
       </c>
       <c r="U335" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -70480,7 +70480,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D336" s="2" t="inlineStr">
+      <c r="D336" t="inlineStr">
         <is>
           <t>128101010</t>
         </is>
@@ -70542,7 +70542,7 @@
       </c>
       <c r="U336" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -70562,7 +70562,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D337" s="2" t="inlineStr">
+      <c r="D337" t="inlineStr">
         <is>
           <t>128102110</t>
         </is>
@@ -70624,7 +70624,7 @@
       </c>
       <c r="U337" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -70644,7 +70644,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D338" s="2" t="inlineStr">
+      <c r="D338" t="inlineStr">
         <is>
           <t>128102100</t>
         </is>
@@ -70706,7 +70706,7 @@
       </c>
       <c r="U338" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -70726,7 +70726,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D339" s="2" t="inlineStr">
+      <c r="D339" t="inlineStr">
         <is>
           <t>128102090</t>
         </is>
@@ -70788,7 +70788,7 @@
       </c>
       <c r="U339" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -70808,7 +70808,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D340" s="2" t="inlineStr">
+      <c r="D340" t="inlineStr">
         <is>
           <t>128102080</t>
         </is>
@@ -70870,7 +70870,7 @@
       </c>
       <c r="U340" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -70890,7 +70890,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D341" s="2" t="inlineStr">
+      <c r="D341" t="inlineStr">
         <is>
           <t>128102070</t>
         </is>
@@ -70952,7 +70952,7 @@
       </c>
       <c r="U341" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -70972,7 +70972,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D342" s="2" t="inlineStr">
+      <c r="D342" t="inlineStr">
         <is>
           <t>128102060</t>
         </is>
@@ -71034,7 +71034,7 @@
       </c>
       <c r="U342" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -71054,7 +71054,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D343" s="2" t="inlineStr">
+      <c r="D343" t="inlineStr">
         <is>
           <t>128102050</t>
         </is>
@@ -71116,7 +71116,7 @@
       </c>
       <c r="U343" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -71136,7 +71136,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D344" s="2" t="inlineStr">
+      <c r="D344" t="inlineStr">
         <is>
           <t>128102040</t>
         </is>
@@ -71198,7 +71198,7 @@
       </c>
       <c r="U344" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -71218,7 +71218,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D345" s="2" t="inlineStr">
+      <c r="D345" t="inlineStr">
         <is>
           <t>128102030</t>
         </is>
@@ -71280,7 +71280,7 @@
       </c>
       <c r="U345" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -71300,7 +71300,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D346" s="2" t="inlineStr">
+      <c r="D346" t="inlineStr">
         <is>
           <t>128102020</t>
         </is>
@@ -71362,7 +71362,7 @@
       </c>
       <c r="U346" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -71382,7 +71382,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D347" s="2" t="inlineStr">
+      <c r="D347" t="inlineStr">
         <is>
           <t>128102010</t>
         </is>
@@ -71444,7 +71444,7 @@
       </c>
       <c r="U347" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -71464,7 +71464,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D348" s="2" t="inlineStr">
+      <c r="D348" t="inlineStr">
         <is>
           <t>128102210</t>
         </is>
@@ -71526,7 +71526,7 @@
       </c>
       <c r="U348" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -71546,7 +71546,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D349" s="2" t="inlineStr">
+      <c r="D349" t="inlineStr">
         <is>
           <t>128102200</t>
         </is>
@@ -71608,7 +71608,7 @@
       </c>
       <c r="U349" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -71628,7 +71628,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D350" s="2" t="inlineStr">
+      <c r="D350" t="inlineStr">
         <is>
           <t>128102190</t>
         </is>
@@ -71690,7 +71690,7 @@
       </c>
       <c r="U350" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -71710,7 +71710,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D351" s="2" t="inlineStr">
+      <c r="D351" t="inlineStr">
         <is>
           <t>128102180</t>
         </is>
@@ -71772,7 +71772,7 @@
       </c>
       <c r="U351" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -71792,7 +71792,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D352" s="2" t="inlineStr">
+      <c r="D352" t="inlineStr">
         <is>
           <t>128102170</t>
         </is>
@@ -71854,7 +71854,7 @@
       </c>
       <c r="U352" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -71874,7 +71874,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D353" s="2" t="inlineStr">
+      <c r="D353" t="inlineStr">
         <is>
           <t>128102160</t>
         </is>
@@ -71936,7 +71936,7 @@
       </c>
       <c r="U353" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -71956,7 +71956,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D354" s="2" t="inlineStr">
+      <c r="D354" t="inlineStr">
         <is>
           <t>128102150</t>
         </is>
@@ -72018,7 +72018,7 @@
       </c>
       <c r="U354" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -72038,7 +72038,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D355" s="2" t="inlineStr">
+      <c r="D355" t="inlineStr">
         <is>
           <t>128102140</t>
         </is>
@@ -72100,7 +72100,7 @@
       </c>
       <c r="U355" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -72120,7 +72120,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D356" s="2" t="inlineStr">
+      <c r="D356" t="inlineStr">
         <is>
           <t>128102130</t>
         </is>
@@ -72182,7 +72182,7 @@
       </c>
       <c r="U356" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -72202,7 +72202,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D357" s="2" t="inlineStr">
+      <c r="D357" t="inlineStr">
         <is>
           <t>128102120</t>
         </is>
@@ -72264,7 +72264,7 @@
       </c>
       <c r="U357" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -72284,7 +72284,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D358" s="2" t="inlineStr">
+      <c r="D358" t="inlineStr">
         <is>
           <t>128103090</t>
         </is>
@@ -72346,7 +72346,7 @@
       </c>
       <c r="U358" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -72366,7 +72366,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D359" s="2" t="inlineStr">
+      <c r="D359" t="inlineStr">
         <is>
           <t>128103080</t>
         </is>
@@ -72428,7 +72428,7 @@
       </c>
       <c r="U359" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -72448,7 +72448,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D360" s="2" t="inlineStr">
+      <c r="D360" t="inlineStr">
         <is>
           <t>128103070</t>
         </is>
@@ -72510,7 +72510,7 @@
       </c>
       <c r="U360" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -72530,7 +72530,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D361" s="2" t="inlineStr">
+      <c r="D361" t="inlineStr">
         <is>
           <t>128103060</t>
         </is>
@@ -72592,7 +72592,7 @@
       </c>
       <c r="U361" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -72612,7 +72612,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D362" s="2" t="inlineStr">
+      <c r="D362" t="inlineStr">
         <is>
           <t>128103050</t>
         </is>
@@ -72674,7 +72674,7 @@
       </c>
       <c r="U362" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -72694,7 +72694,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D363" s="2" t="inlineStr">
+      <c r="D363" t="inlineStr">
         <is>
           <t>128103040</t>
         </is>
@@ -72756,7 +72756,7 @@
       </c>
       <c r="U363" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -72776,7 +72776,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D364" s="2" t="inlineStr">
+      <c r="D364" t="inlineStr">
         <is>
           <t>128103030</t>
         </is>
@@ -72838,7 +72838,7 @@
       </c>
       <c r="U364" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -72858,7 +72858,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D365" s="2" t="inlineStr">
+      <c r="D365" t="inlineStr">
         <is>
           <t>128103020</t>
         </is>
@@ -72920,7 +72920,7 @@
       </c>
       <c r="U365" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -72940,7 +72940,7 @@
           <t>Montessa Apartments</t>
         </is>
       </c>
-      <c r="D366" s="2" t="inlineStr">
+      <c r="D366" t="inlineStr">
         <is>
           <t>128103010</t>
         </is>
@@ -73002,7 +73002,7 @@
       </c>
       <c r="U366" s="2" t="inlineStr">
         <is>
-          <t>situs-match</t>
+          <t>mismatch</t>
         </is>
       </c>
     </row>
@@ -76489,12 +76489,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>233</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seaport Village Apartments: no assigned parcel's situs matches address '5601 North Paramount Boulevard' (e.g. 7157031001: 2697 E 56TH WAY LONG BEACH CA 90805; 7157031002: 2687 E 56TH WAY LONG BEACH CA 90805)</t>
+          <t>926 S. Kingsley Apartments: no assigned parcel's situs matches address '926 S. Kingsley Drive, Los Angeles, CA' (e.g. 5093023058: 926 S HARVARD BLVD LOS ANGELES CA 90006)</t>
         </is>
       </c>
     </row>
@@ -76506,46 +76506,46 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>237</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>569 W. 6th Street. Apartments: grant city 'Los Angeles' appears in no assigned parcel's situs</t>
+          <t>Edgemont by Angeleno: no assigned parcel's situs matches address '1178 N. Edgemont Street, Los Angeles, CA' (e.g. 5540023002: 1178 N HELIOTROPE DR LOS ANGELES CA 90029)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>possible-missing-parcel</t>
+          <t>assignment-mismatch</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Alvarado Streets Apartments: parcel 5136019023 shares situs '1136 S ALVARADO ST LOS ANGELES CA 90006' (Auto, Recreation EQPT, C, $1,039,983) but is not assigned to any project</t>
+          <t>Seaport Village Apartments: no assigned parcel's situs matches address '5601 North Paramount Boulevard' (e.g. 7157031001: 2697 E 56TH WAY LONG BEACH CA 90805; 7157031002: 2687 E 56TH WAY LONG BEACH CA 90805)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>possible-missing-parcel</t>
+          <t>assignment-mismatch</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Market Street Village Apartmen: parcel 5351441600 shares situs '699 14TH SD' (31, $15,300,000) but is not assigned to any project</t>
+          <t>11630 S. Main Street Apartments: no assigned parcel's situs matches address '11630 Main St, Los Angeles, CA 90061' (e.g. 6083010040: 110 E 116TH ST LOS ANGELES CA 90061)</t>
         </is>
       </c>
     </row>
@@ -76557,12 +76557,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Alexandria II Apartments: parcel 5518012036 shares situs '130 N ALEXANDRIA AVE APT 0104 LOS ANGELES CA 90004' (Five or more apartments, $7,015,185) but is not assigned to any project</t>
+          <t>Alvarado Streets Apartments: parcel 5136019023 shares situs '1136 S ALVARADO ST LOS ANGELES CA 90006' (Auto, Recreation EQPT, C, $1,039,983) but is not assigned to any project</t>
         </is>
       </c>
     </row>
@@ -76574,12 +76574,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kenmore II Apartments: parcel 5518018011 shares situs '200 N KENMORE AVE LOS ANGELES CA 90004' (Five or more apartments, $452,268) but is not assigned to any project</t>
+          <t>Market Street Village Apartmen: parcel 5351441600 shares situs '699 14TH SD' (31, $15,300,000) but is not assigned to any project</t>
         </is>
       </c>
     </row>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -48797,7 +48797,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -48852,7 +48852,7 @@
       </c>
       <c r="U86" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -48904,7 +48904,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -48959,7 +48959,7 @@
       </c>
       <c r="U87" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -49011,7 +49011,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -49066,7 +49066,7 @@
       </c>
       <c r="U88" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -49118,7 +49118,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -49173,7 +49173,7 @@
       </c>
       <c r="U89" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -49225,7 +49225,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -49280,7 +49280,7 @@
       </c>
       <c r="U90" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -49332,7 +49332,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -49387,7 +49387,7 @@
       </c>
       <c r="U91" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -49439,7 +49439,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -49494,7 +49494,7 @@
       </c>
       <c r="U92" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -49546,7 +49546,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -49601,7 +49601,7 @@
       </c>
       <c r="U93" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -49653,7 +49653,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -49708,7 +49708,7 @@
       </c>
       <c r="U94" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -49760,7 +49760,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -49815,7 +49815,7 @@
       </c>
       <c r="U95" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -49867,7 +49867,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -49922,7 +49922,7 @@
       </c>
       <c r="U96" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -49974,7 +49974,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -50029,7 +50029,7 @@
       </c>
       <c r="U97" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -50081,7 +50081,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -50136,7 +50136,7 @@
       </c>
       <c r="U98" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -50188,7 +50188,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -50243,7 +50243,7 @@
       </c>
       <c r="U99" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -50295,7 +50295,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -50350,7 +50350,7 @@
       </c>
       <c r="U100" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -50402,7 +50402,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -50457,7 +50457,7 @@
       </c>
       <c r="U101" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -50509,7 +50509,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -50564,7 +50564,7 @@
       </c>
       <c r="U102" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -50616,7 +50616,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -50671,7 +50671,7 @@
       </c>
       <c r="U103" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -50723,7 +50723,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -50778,7 +50778,7 @@
       </c>
       <c r="U104" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -50830,7 +50830,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -50885,7 +50885,7 @@
       </c>
       <c r="U105" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -50937,7 +50937,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -50992,7 +50992,7 @@
       </c>
       <c r="U106" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -51044,7 +51044,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -51099,7 +51099,7 @@
       </c>
       <c r="U107" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -51151,7 +51151,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -51206,7 +51206,7 @@
       </c>
       <c r="U108" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -51258,7 +51258,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -51313,7 +51313,7 @@
       </c>
       <c r="U109" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -51365,7 +51365,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -51420,7 +51420,7 @@
       </c>
       <c r="U110" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -51472,7 +51472,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -51527,7 +51527,7 @@
       </c>
       <c r="U111" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -51579,7 +51579,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -51634,7 +51634,7 @@
       </c>
       <c r="U112" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -51686,7 +51686,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -51741,7 +51741,7 @@
       </c>
       <c r="U113" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -51793,7 +51793,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -51848,7 +51848,7 @@
       </c>
       <c r="U114" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -51900,7 +51900,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -51955,7 +51955,7 @@
       </c>
       <c r="U115" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -52007,7 +52007,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -52062,7 +52062,7 @@
       </c>
       <c r="U116" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -52114,7 +52114,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -52169,7 +52169,7 @@
       </c>
       <c r="U117" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -52221,7 +52221,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Multi-parcel (33)</t>
+          <t>Multi-parcel (33); situs reviewed 2026-08-22: complex fronts 5601 N Paramount Blvd; buildings carry E 56th Way situs (Drew, portal map)</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -52276,7 +52276,7 @@
       </c>
       <c r="U118" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -54576,7 +54576,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Legacy AIN 6083010038 consolidated to 6083010040</t>
+          <t>situs reviewed 2026-08-22 (Drew, assessor portal): AIN confirmed; county situs is 114 E 116TH ST, differs from marketing address 11630 S Main St</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -54631,7 +54631,7 @@
       </c>
       <c r="U148" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>documented</t>
         </is>
       </c>
     </row>
@@ -60775,17 +60775,17 @@
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>4276017047</t>
+          <t>5141004003</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>4276-017-047</t>
+          <t>5141-004-003</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2424 WILSHIRE BLVD SANTA MONICA CA 90403</t>
+          <t>2424 WILSHIRE BLVD LOS ANGELES CA</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -60795,7 +60795,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>collaborator-sheet</t>
+          <t>manual-repo-edit</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -60803,6 +60803,11 @@
           <t>manual_verified</t>
         </is>
       </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Corrected 2026-08-22 (Drew, assessor portal): prior parcel was 2424 Wilshire SANTA MONICA; Park Wilshire is the LA one</t>
+        </is>
+      </c>
       <c r="K215" s="2" t="inlineStr">
         <is>
           <t>2026</t>
@@ -60810,17 +60815,17 @@
       </c>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t>2946701</t>
+          <t>8600000</t>
         </is>
       </c>
       <c r="M215" s="2" t="inlineStr">
         <is>
-          <t>576523</t>
+          <t>11100000</t>
         </is>
       </c>
       <c r="N215" s="2" t="inlineStr">
         <is>
-          <t>3523224</t>
+          <t>19700000</t>
         </is>
       </c>
       <c r="O215" s="2" t="inlineStr">
@@ -60830,12 +60835,12 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="Q215" s="2" t="inlineStr">
         <is>
-          <t>Office Buildings</t>
+          <t>Five or more apartments</t>
         </is>
       </c>
       <c r="R215" s="2" t="inlineStr">
@@ -67732,14 +67737,19 @@
           <t>926 S. Kingsley Apartments</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>5093023058</t>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>5093023056</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>5093-023-056</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>926 S HARVARD BLVD LOS ANGELES CA 90006</t>
+          <t>926 S KINGSLEY DR LOS ANGELES CA 90006</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -67749,12 +67759,12 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>script-finder-auto (2026-08-21)</t>
+          <t>manual-repo-edit</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>Resolved by LA county situs/geocode search</t>
+          <t>Corrected 2026-08-22 (Drew, assessor portal): prior geocode pick 5093023058 sits at 926 S Harvard Blvd</t>
         </is>
       </c>
       <c r="K297" s="2" t="inlineStr">
@@ -67764,17 +67774,17 @@
       </c>
       <c r="L297" s="2" t="inlineStr">
         <is>
-          <t>1396325</t>
+          <t>2827070</t>
         </is>
       </c>
       <c r="M297" s="2" t="inlineStr">
         <is>
-          <t>587224</t>
+          <t>1172181</t>
         </is>
       </c>
       <c r="N297" s="2" t="inlineStr">
         <is>
-          <t>1983549</t>
+          <t>3999251</t>
         </is>
       </c>
       <c r="O297" s="2" t="inlineStr">
@@ -67784,12 +67794,12 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="Q297" s="2" t="inlineStr">
         <is>
-          <t>Five or more apartments</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="R297" s="2" t="inlineStr">
@@ -67809,7 +67819,7 @@
       </c>
       <c r="U297" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -68120,14 +68130,19 @@
           <t>Edgemont by Angeleno</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>5540023002</t>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>5540025003</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>5540-025-003</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>1178 N HELIOTROPE DR LOS ANGELES CA 90029</t>
+          <t>1178 N EDGEMONT ST LOS ANGELES CA 90029</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -68137,12 +68152,12 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>script-finder-auto (2026-08-21)</t>
+          <t>manual-repo-edit</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>Resolved by LA county situs/geocode search</t>
+          <t>Corrected 2026-08-22 (Drew, assessor portal): prior geocode pick 5540023002 sits at 1178 N Heliotrope Dr</t>
         </is>
       </c>
       <c r="K301" s="2" t="inlineStr">
@@ -68152,17 +68167,17 @@
       </c>
       <c r="L301" s="2" t="inlineStr">
         <is>
-          <t>271221</t>
+          <t>1186056</t>
         </is>
       </c>
       <c r="M301" s="2" t="inlineStr">
         <is>
-          <t>331491</t>
+          <t>62424</t>
         </is>
       </c>
       <c r="N301" s="2" t="inlineStr">
         <is>
-          <t>602712</t>
+          <t>1248480</t>
         </is>
       </c>
       <c r="O301" s="2" t="inlineStr">
@@ -68172,12 +68187,12 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
         <is>
-          <t>Five or more apartments</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="R301" s="2" t="inlineStr">
@@ -68197,7 +68212,7 @@
       </c>
       <c r="U301" s="2" t="inlineStr">
         <is>
-          <t>mismatch</t>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -74943,10 +74958,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C104"/>
+  <dimension ref="A1:C97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
   </cols>
@@ -76467,119 +76482,119 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>assignment-mismatch</t>
+          <t>possible-missing-parcel</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Park Wilshire Apartments: grant city 'Los Angeles' appears in no assigned parcel's situs</t>
+          <t>Alvarado Streets Apartments: parcel 5136019023 shares situs '1136 S ALVARADO ST LOS ANGELES CA 90006' (Auto, Recreation EQPT, C, $1,039,983) but is not assigned to any project</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>assignment-mismatch</t>
+          <t>possible-missing-parcel</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>926 S. Kingsley Apartments: no assigned parcel's situs matches address '926 S. Kingsley Drive, Los Angeles, CA' (e.g. 5093023058: 926 S HARVARD BLVD LOS ANGELES CA 90006)</t>
+          <t>Market Street Village Apartmen: parcel 5351441600 shares situs '699 14TH SD' (31, $15,300,000) but is not assigned to any project</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>assignment-mismatch</t>
+          <t>units-undercount</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Edgemont by Angeleno: no assigned parcel's situs matches address '1178 N. Edgemont Street, Los Angeles, CA' (e.g. 5540023002: 1178 N HELIOTROPE DR LOS ANGELES CA 90029)</t>
+          <t>The Waterloo Apartments: county records 5 units on assigned parcels vs 154 in the grant — parcels may be missing</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>assignment-mismatch</t>
+          <t>units-undercount</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>68</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Seaport Village Apartments: no assigned parcel's situs matches address '5601 North Paramount Boulevard' (e.g. 7157031001: 2697 E 56TH WAY LONG BEACH CA 90805; 7157031002: 2687 E 56TH WAY LONG BEACH CA 90805)</t>
+          <t>Candlewood North Apartments: county records 68 units on assigned parcels vs 189 in the grant — parcels may be missing</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>assignment-mismatch</t>
+          <t>units-undercount</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>110</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>11630 S. Main Street Apartments: no assigned parcel's situs matches address '11630 Main St, Los Angeles, CA 90061' (e.g. 6083010040: 110 E 116TH ST LOS ANGELES CA 90061)</t>
+          <t>Kenmore I Apartments: county records 24 units on assigned parcels vs 42 in the grant — parcels may be missing</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>possible-missing-parcel</t>
+          <t>units-undercount</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>181</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Alvarado Streets Apartments: parcel 5136019023 shares situs '1136 S ALVARADO ST LOS ANGELES CA 90006' (Auto, Recreation EQPT, C, $1,039,983) but is not assigned to any project</t>
+          <t>The Hive Apartments: county records 50 units on assigned parcels vs 152 in the grant — parcels may be missing</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>possible-missing-parcel</t>
+          <t>units-undercount</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>195</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Market Street Village Apartmen: parcel 5351441600 shares situs '699 14TH SD' (31, $15,300,000) but is not assigned to any project</t>
+          <t>1723 Corinth Apartments: county records 10 units on assigned parcels vs 41 in the grant — parcels may be missing</t>
         </is>
       </c>
     </row>
@@ -76591,131 +76606,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>231</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>The Waterloo Apartments: county records 5 units on assigned parcels vs 154 in the grant — parcels may be missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>units-undercount</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Candlewood North Apartments: county records 68 units on assigned parcels vs 189 in the grant — parcels may be missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>units-undercount</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Kenmore I Apartments: county records 24 units on assigned parcels vs 42 in the grant — parcels may be missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>units-undercount</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>The Hive Apartments: county records 50 units on assigned parcels vs 152 in the grant — parcels may be missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>units-undercount</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>1723 Corinth Apartments: county records 10 units on assigned parcels vs 41 in the grant — parcels may be missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>units-undercount</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
           <t>Violet on Virgil: county records 159 units on assigned parcels vs 302 in the grant — parcels may be missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>units-undercount</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>926 S. Kingsley Apartments: county records 1 units on assigned parcels vs 136 in the grant — parcels may be missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>units-undercount</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Edgemont by Angeleno: county records 8 units on assigned parcels vs 34 in the grant — parcels may be missing</t>
         </is>
       </c>
     </row>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -40962,7 +40962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U389"/>
+  <dimension ref="A1:U390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -48497,6 +48497,11 @@
           <t>collaborator-sheet</t>
         </is>
       </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Reviewed 2026-08-22: grant covers PAR 2 only (229 units, per staff report and entity name). Same-situs siblings excluded: 5351441600 (PAR 3, commercial), 5351441400 (PAR 1), 5351441700 (PAR 4, 1450 Market — separate 242-unit phase).</t>
+        </is>
+      </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
           <t>2026</t>
@@ -74944,6 +74949,108 @@
       <c r="U389" s="2" t="inlineStr">
         <is>
           <t>no-situs</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Alvarado Streets Apartments</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>5136019023</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>5136-019-023</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>1136 S ALVARADO ST LOS ANGELES CA 90006</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>Added 2026-08-22 (Drew): same-situs Auto/Recreation parcel, likely complex parking; ownership not independently verified — assumed part of property</t>
+        </is>
+      </c>
+      <c r="K390" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L390" s="2" t="inlineStr">
+        <is>
+          <t>1039983</t>
+        </is>
+      </c>
+      <c r="M390" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N390" s="2" t="inlineStr">
+        <is>
+          <t>1039983</t>
+        </is>
+      </c>
+      <c r="O390" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P390" s="2" t="inlineStr">
+        <is>
+          <t>1952</t>
+        </is>
+      </c>
+      <c r="Q390" s="2" t="inlineStr">
+        <is>
+          <t>Auto, Recreation EQPT, Construction EQPT, Sales &amp; Service</t>
+        </is>
+      </c>
+      <c r="R390" s="2" t="inlineStr">
+        <is>
+          <t>la-county-api</t>
+        </is>
+      </c>
+      <c r="S390" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="T390" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U390" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
         </is>
       </c>
     </row>
@@ -74958,7 +75065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C97"/>
+  <dimension ref="A1:C95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -76482,34 +76589,34 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>possible-missing-parcel</t>
+          <t>units-undercount</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Alvarado Streets Apartments: parcel 5136019023 shares situs '1136 S ALVARADO ST LOS ANGELES CA 90006' (Auto, Recreation EQPT, C, $1,039,983) but is not assigned to any project</t>
+          <t>The Waterloo Apartments: county records 5 units on assigned parcels vs 154 in the grant — parcels may be missing</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>possible-missing-parcel</t>
+          <t>units-undercount</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>68</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Market Street Village Apartmen: parcel 5351441600 shares situs '699 14TH SD' (31, $15,300,000) but is not assigned to any project</t>
+          <t>Candlewood North Apartments: county records 68 units on assigned parcels vs 189 in the grant — parcels may be missing</t>
         </is>
       </c>
     </row>
@@ -76521,12 +76628,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>110</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>The Waterloo Apartments: county records 5 units on assigned parcels vs 154 in the grant — parcels may be missing</t>
+          <t>Kenmore I Apartments: county records 24 units on assigned parcels vs 42 in the grant — parcels may be missing</t>
         </is>
       </c>
     </row>
@@ -76538,12 +76645,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>181</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Candlewood North Apartments: county records 68 units on assigned parcels vs 189 in the grant — parcels may be missing</t>
+          <t>The Hive Apartments: county records 50 units on assigned parcels vs 152 in the grant — parcels may be missing</t>
         </is>
       </c>
     </row>
@@ -76555,12 +76662,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>195</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kenmore I Apartments: county records 24 units on assigned parcels vs 42 in the grant — parcels may be missing</t>
+          <t>1723 Corinth Apartments: county records 10 units on assigned parcels vs 41 in the grant — parcels may be missing</t>
         </is>
       </c>
     </row>
@@ -76572,44 +76679,10 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>231</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
-        <is>
-          <t>The Hive Apartments: county records 50 units on assigned parcels vs 152 in the grant — parcels may be missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>units-undercount</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>1723 Corinth Apartments: county records 10 units on assigned parcels vs 41 in the grant — parcels may be missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>units-undercount</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
         <is>
           <t>Violet on Virgil: county records 159 units on assigned parcels vs 302 in the grant — parcels may be missing</t>
         </is>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -40962,7 +40962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U390"/>
+  <dimension ref="A1:U391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42059,6 +42059,11 @@
           <t>manual_verified</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Pre-construction site (demolition not started): project will occupy 5402-028-023 and 5402-028-022; county values/units reflect existing buildings (units reviewed 2026-08-22, Drew)</t>
+        </is>
+      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2026</t>
@@ -75049,6 +75054,103 @@
         </is>
       </c>
       <c r="U390" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>The Waterloo Apartments</t>
+        </is>
+      </c>
+      <c r="D391" s="2" t="inlineStr">
+        <is>
+          <t>5402028022</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>5402-028-022</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>Pre-construction site (demolition not started): project will occupy 5402-028-023 and 5402-028-022; county values/units reflect existing buildings (units reviewed 2026-08-22, Drew)</t>
+        </is>
+      </c>
+      <c r="K391" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L391" s="2" t="inlineStr">
+        <is>
+          <t>831300</t>
+        </is>
+      </c>
+      <c r="M391" s="2" t="inlineStr">
+        <is>
+          <t>306000</t>
+        </is>
+      </c>
+      <c r="N391" s="2" t="inlineStr">
+        <is>
+          <t>1137300</t>
+        </is>
+      </c>
+      <c r="O391" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P391" s="2" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="Q391" s="2" t="inlineStr">
+        <is>
+          <t>Two Units</t>
+        </is>
+      </c>
+      <c r="R391" s="2" t="inlineStr">
+        <is>
+          <t>la-county-api</t>
+        </is>
+      </c>
+      <c r="S391" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="T391" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="U391" s="2" t="inlineStr">
         <is>
           <t>situs-match</t>
         </is>
@@ -75065,7 +75167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C95"/>
+  <dimension ref="A1:C94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -76594,12 +76696,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>68</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>The Waterloo Apartments: county records 5 units on assigned parcels vs 154 in the grant — parcels may be missing</t>
+          <t>Candlewood North Apartments: county records 68 units on assigned parcels vs 189 in the grant — parcels may be missing</t>
         </is>
       </c>
     </row>
@@ -76611,12 +76713,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>110</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Candlewood North Apartments: county records 68 units on assigned parcels vs 189 in the grant — parcels may be missing</t>
+          <t>Kenmore I Apartments: county records 24 units on assigned parcels vs 42 in the grant — parcels may be missing</t>
         </is>
       </c>
     </row>
@@ -76628,12 +76730,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>181</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Kenmore I Apartments: county records 24 units on assigned parcels vs 42 in the grant — parcels may be missing</t>
+          <t>The Hive Apartments: county records 50 units on assigned parcels vs 152 in the grant — parcels may be missing</t>
         </is>
       </c>
     </row>
@@ -76645,12 +76747,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>195</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>The Hive Apartments: county records 50 units on assigned parcels vs 152 in the grant — parcels may be missing</t>
+          <t>1723 Corinth Apartments: county records 10 units on assigned parcels vs 41 in the grant — parcels may be missing</t>
         </is>
       </c>
     </row>
@@ -76662,27 +76764,10 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>231</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
-        <is>
-          <t>1723 Corinth Apartments: county records 10 units on assigned parcels vs 41 in the grant — parcels may be missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>units-undercount</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
         <is>
           <t>Violet on Virgil: county records 159 units on assigned parcels vs 302 in the grant — parcels may be missing</t>
         </is>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -16059,14 +16059,14 @@
           <t>Kingdom Development, Inc.</t>
         </is>
       </c>
-      <c r="W111" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="X111" t="inlineStr">
-        <is>
-          <t>42</t>
+      <c r="W111" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="X111" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="Y111" s="2" t="inlineStr">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="AL111" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -40962,7 +40962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U391"/>
+  <dimension ref="A1:U395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -65253,7 +65253,7 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Resolved by LA county situs/geocode search</t>
+          <t>Resolved by LA county situs/geocode search; Pre-construction/stale county record; building may not yet be built (units reviewed 2026-08-22, Drew)</t>
         </is>
       </c>
       <c r="K264" s="2" t="inlineStr">
@@ -75151,6 +75151,399 @@
         </is>
       </c>
       <c r="U391" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Candlewood North Apartments</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>2764001012</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>2764-001-012</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>Added 2026-08-22 (Drew, assessor portal): complex spans 2764-001-012..014</t>
+        </is>
+      </c>
+      <c r="K392" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L392" s="2" t="inlineStr">
+        <is>
+          <t>8339520</t>
+        </is>
+      </c>
+      <c r="M392" s="2" t="inlineStr">
+        <is>
+          <t>7956000</t>
+        </is>
+      </c>
+      <c r="N392" s="2" t="inlineStr">
+        <is>
+          <t>16295520</t>
+        </is>
+      </c>
+      <c r="O392" s="2" t="inlineStr">
+        <is>
+          <t>8364491</t>
+        </is>
+      </c>
+      <c r="P392" s="2" t="inlineStr">
+        <is>
+          <t>1965</t>
+        </is>
+      </c>
+      <c r="Q392" s="2" t="inlineStr">
+        <is>
+          <t>Five or more apartments</t>
+        </is>
+      </c>
+      <c r="R392" s="2" t="inlineStr">
+        <is>
+          <t>la-county-api</t>
+        </is>
+      </c>
+      <c r="S392" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="T392" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="U392" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Candlewood North Apartments</t>
+        </is>
+      </c>
+      <c r="D393" s="2" t="inlineStr">
+        <is>
+          <t>2764001014</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="inlineStr">
+        <is>
+          <t>2764-001-014</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>Added 2026-08-22 (Drew, assessor portal): complex spans 2764-001-012..014</t>
+        </is>
+      </c>
+      <c r="K393" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L393" s="2" t="inlineStr">
+        <is>
+          <t>9016800</t>
+        </is>
+      </c>
+      <c r="M393" s="2" t="inlineStr">
+        <is>
+          <t>8896440</t>
+        </is>
+      </c>
+      <c r="N393" s="2" t="inlineStr">
+        <is>
+          <t>17913240</t>
+        </is>
+      </c>
+      <c r="O393" s="2" t="inlineStr">
+        <is>
+          <t>9194867</t>
+        </is>
+      </c>
+      <c r="P393" s="2" t="inlineStr">
+        <is>
+          <t>1964</t>
+        </is>
+      </c>
+      <c r="Q393" s="2" t="inlineStr">
+        <is>
+          <t>Five or more apartments</t>
+        </is>
+      </c>
+      <c r="R393" s="2" t="inlineStr">
+        <is>
+          <t>la-county-api</t>
+        </is>
+      </c>
+      <c r="S393" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="U393" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>The Hive Apartments</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>7157012023</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="inlineStr">
+        <is>
+          <t>7157-012-023</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>5700 ACKERFIELD AVE LONG BEACH CA</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>Added 2026-08-22 (Drew): staff report prose gives two addresses, 5700 and 5565 Ackerfield; this is 5700</t>
+        </is>
+      </c>
+      <c r="K394" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L394" s="2" t="inlineStr">
+        <is>
+          <t>4762701</t>
+        </is>
+      </c>
+      <c r="M394" s="2" t="inlineStr">
+        <is>
+          <t>20566211</t>
+        </is>
+      </c>
+      <c r="N394" s="2" t="inlineStr">
+        <is>
+          <t>25328912</t>
+        </is>
+      </c>
+      <c r="O394" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P394" s="2" t="inlineStr">
+        <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="Q394" s="2" t="inlineStr">
+        <is>
+          <t>Five or more apartments</t>
+        </is>
+      </c>
+      <c r="R394" s="2" t="inlineStr">
+        <is>
+          <t>la-county-api</t>
+        </is>
+      </c>
+      <c r="S394" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="T394" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="U394" s="2" t="inlineStr">
+        <is>
+          <t>situs-match</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Violet on Virgil</t>
+        </is>
+      </c>
+      <c r="D395" s="2" t="inlineStr">
+        <is>
+          <t>5501017045</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="inlineStr">
+        <is>
+          <t>5501-017-045</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>manual-repo-edit</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>Added 2026-08-22 (Drew, assessor portal): additional lot completing the 302-unit site</t>
+        </is>
+      </c>
+      <c r="K395" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L395" s="2" t="inlineStr">
+        <is>
+          <t>20247672</t>
+        </is>
+      </c>
+      <c r="M395" s="2" t="inlineStr">
+        <is>
+          <t>33588722</t>
+        </is>
+      </c>
+      <c r="N395" s="2" t="inlineStr">
+        <is>
+          <t>53836394</t>
+        </is>
+      </c>
+      <c r="O395" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P395" s="2" t="inlineStr">
+        <is>
+          <t>1972</t>
+        </is>
+      </c>
+      <c r="Q395" s="2" t="inlineStr">
+        <is>
+          <t>Five or more apartments</t>
+        </is>
+      </c>
+      <c r="R395" s="2" t="inlineStr">
+        <is>
+          <t>la-county-api</t>
+        </is>
+      </c>
+      <c r="S395" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="T395" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="U395" s="2" t="inlineStr">
         <is>
           <t>situs-match</t>
         </is>
@@ -75167,7 +75560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C94"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -75999,12 +76392,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>134</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>total_units: generated '24' -&gt; manual '42'</t>
+          <t>total_units: generated '69' -&gt; manual '68'</t>
         </is>
       </c>
     </row>
@@ -76016,12 +76409,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>137</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>total_units: generated '69' -&gt; manual '68'</t>
+          <t>total_units: generated '42' -&gt; manual '41'</t>
         </is>
       </c>
     </row>
@@ -76033,12 +76426,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>152</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>total_units: generated '42' -&gt; manual '41'</t>
+          <t>total_units: generated '52' -&gt; manual '152'</t>
         </is>
       </c>
     </row>
@@ -76050,12 +76443,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>155</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>total_units: generated '52' -&gt; manual '152'</t>
+          <t>entity: generated 'A limited partnership to be formed by Kairos Investment Management and Pacific Housing' -&gt; manual 'TBD LP'</t>
         </is>
       </c>
     </row>
@@ -76067,7 +76460,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>156</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -76084,12 +76477,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>171</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>entity: generated 'A limited partnership to be formed by Kairos Investment Management and Pacific Housing' -&gt; manual 'TBD LP'</t>
+          <t>city_cut: generated '15900.0' -&gt; manual '6300'</t>
         </is>
       </c>
     </row>
@@ -76101,12 +76494,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>181</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>city_cut: generated '15900.0' -&gt; manual '6300'</t>
+          <t>total_units: generated '52' -&gt; manual '152'</t>
         </is>
       </c>
     </row>
@@ -76118,12 +76511,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>195</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>total_units: generated '52' -&gt; manual '152'</t>
+          <t>total_units: generated '42' -&gt; manual '41'</t>
         </is>
       </c>
     </row>
@@ -76135,12 +76528,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>199</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>total_units: generated '42' -&gt; manual '41'</t>
+          <t>city_cut: generated '5550.0' -&gt; manual '5500'</t>
         </is>
       </c>
     </row>
@@ -76152,12 +76545,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>204</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>city_cut: generated '5550.0' -&gt; manual '5500'</t>
+          <t>total_units: generated '50' -&gt; manual '49'</t>
         </is>
       </c>
     </row>
@@ -76169,12 +76562,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>206</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>total_units: generated '50' -&gt; manual '49'</t>
+          <t>county: generated 'San Diego' -&gt; manual 'Los Angeles'</t>
         </is>
       </c>
     </row>
@@ -76186,12 +76579,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>209</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>county: generated 'San Diego' -&gt; manual 'Los Angeles'</t>
+          <t>investor_1: generated 'Zenith Property Group LLC' -&gt; manual 'Red Stone Equity Partners'</t>
         </is>
       </c>
     </row>
@@ -76208,7 +76601,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>investor_1: generated 'Zenith Property Group LLC' -&gt; manual 'Red Stone Equity Partners'</t>
+          <t>term_years: generated '35' -&gt; manual '15'</t>
         </is>
       </c>
     </row>
@@ -76220,12 +76613,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>210</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>term_years: generated '35' -&gt; manual '15'</t>
+          <t>term_years: generated '55' -&gt; manual '10'</t>
         </is>
       </c>
     </row>
@@ -76237,12 +76630,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>term_years: generated '55' -&gt; manual '10'</t>
+          <t>term_years: generated '15' -&gt; manual '10'</t>
         </is>
       </c>
     </row>
@@ -76254,12 +76647,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>228</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>term_years: generated '15' -&gt; manual '10'</t>
+          <t>term_years: generated '10' -&gt; manual '15'</t>
         </is>
       </c>
     </row>
@@ -76271,12 +76664,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>217</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>term_years: generated '10' -&gt; manual '15'</t>
+          <t>total_units: generated '35' -&gt; manual '34'</t>
         </is>
       </c>
     </row>
@@ -76288,12 +76681,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>233</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>total_units: generated '35' -&gt; manual '34'</t>
+          <t>term_years: generated '55' -&gt; manual '10'</t>
         </is>
       </c>
     </row>
@@ -76305,12 +76698,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>236</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>term_years: generated '55' -&gt; manual '10'</t>
+          <t>total_units: generated '136' -&gt; manual '108'</t>
         </is>
       </c>
     </row>
@@ -76322,29 +76715,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>225</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>total_units: generated '136' -&gt; manual '108'</t>
+          <t>term_years: generated '30' -&gt; manual '55'</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>term_years: generated '30' -&gt; manual '55'</t>
+          <t>entity '381 Turk Street Associates, a California' ~ SCC LP '421 Turk Street Associates, L.P.' (#3326, San Francisco, score 92)</t>
         </is>
       </c>
     </row>
@@ -76356,12 +76749,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>entity '381 Turk Street Associates, a California' ~ SCC LP '421 Turk Street Associates, L.P.' (#3326, San Francisco, score 92)</t>
+          <t>entity 'BIF NON OZ 7524 S HOOVER ST, LP' ~ SCC LP 'BIF NON OZ 7518 S Hoover St, LP' (#14953, Los Angeles, score 93)</t>
         </is>
       </c>
     </row>
@@ -76373,12 +76766,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>entity 'BIF NON OZ 7524 S HOOVER ST, LP' ~ SCC LP 'BIF NON OZ 7518 S Hoover St, LP' (#14953, Los Angeles, score 93)</t>
+          <t>entity 'BIF NON OZ 4228 WESTERN AVE, LP' ~ SCC LP 'BIF NON OZ 4209 Western Ave, LP' (#14952, Los Angeles, score 93)</t>
         </is>
       </c>
     </row>
@@ -76390,12 +76783,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>122</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>entity 'BIF NON OZ 4228 WESTERN AVE, LP' ~ SCC LP 'BIF NON OZ 4209 Western Ave, LP' (#14952, Los Angeles, score 93)</t>
+          <t>entity '861 Fedora LLLP' ~ SCC LP '836 Fedora L.P.' (#1594, Los Angeles, score 90)</t>
         </is>
       </c>
     </row>
@@ -76407,7 +76800,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>165</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -76419,17 +76812,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>scc-possible-match</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>entity '861 Fedora LLLP' ~ SCC LP '836 Fedora L.P.' (#1594, Los Angeles, score 90)</t>
+          <t>AIN 5036031006 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
@@ -76441,12 +76834,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AIN 5036031006 (Los Angeles) has no current roll data; using manual value</t>
+          <t>AIN 4262018026 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
@@ -76458,12 +76851,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>132</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AIN 4262018026 (Los Angeles) has no current roll data; using manual value</t>
+          <t>AIN 6020022027 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
@@ -76475,29 +76868,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>137</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AIN 6020022027 (Los Angeles) has no current roll data; using manual value</t>
+          <t>AIN 2125017014 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>158</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AIN 2125017014 (Los Angeles) has no current roll data; using manual value</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -76509,7 +76902,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>196</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -76526,12 +76919,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN (none) (Santa Barbara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -76543,12 +76936,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>206</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AIN (none) (Santa Barbara): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -76560,7 +76953,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>207</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -76577,7 +76970,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>208</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -76594,12 +76987,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>215</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 5539028040 (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -76611,29 +77004,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AIN 5539028040 (Los Angeles): no roll values from any source</t>
+          <t>AIN (none) (Contra Costa): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AIN (none) (Contra Costa): no roll values from any source</t>
+          <t>AIN 128101150 (Solano) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
@@ -76650,7 +77043,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AIN 128101150 (Solano) has no current roll data; using manual value</t>
+          <t>AIN 128101050 (Solano) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
@@ -76667,109 +77060,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AIN 128101050 (Solano) has no current roll data; using manual value</t>
+          <t>AIN 128105060 (Solano) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>units-undercount</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>110</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AIN 128105060 (Solano) has no current roll data; using manual value</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>units-undercount</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Candlewood North Apartments: county records 68 units on assigned parcels vs 189 in the grant — parcels may be missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>units-undercount</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
           <t>Kenmore I Apartments: county records 24 units on assigned parcels vs 42 in the grant — parcels may be missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>units-undercount</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>The Hive Apartments: county records 50 units on assigned parcels vs 152 in the grant — parcels may be missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>units-undercount</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>1723 Corinth Apartments: county records 10 units on assigned parcels vs 41 in the grant — parcels may be missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>units-undercount</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Violet on Virgil: county records 159 units on assigned parcels vs 302 in the grant — parcels may be missing</t>
         </is>
       </c>
     </row>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -75560,7 +75560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -77061,23 +77061,6 @@
       <c r="C88" t="inlineStr">
         <is>
           <t>AIN 128105060 (Solano) has no current roll data; using manual value</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>units-undercount</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Kenmore I Apartments: county records 24 units on assigned parcels vs 42 in the grant — parcels may be missing</t>
         </is>
       </c>
     </row>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -37727,14 +37727,14 @@
           <t>PS 4228 Western Ave, LP, a Delaware limited partnership</t>
         </is>
       </c>
-      <c r="E285" s="2" t="inlineStr">
-        <is>
-          <t>Healdsburg</t>
-        </is>
-      </c>
-      <c r="F285" s="2" t="inlineStr">
-        <is>
-          <t>Sonoma</t>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="G285" s="2" t="inlineStr">
@@ -37785,6 +37785,11 @@
       <c r="AK285" t="inlineStr">
         <is>
           <t>generated</t>
+        </is>
+      </c>
+      <c r="AL285" t="inlineStr">
+        <is>
+          <t>county:manual-repo-edit; city:manual-repo-edit</t>
         </is>
       </c>
     </row>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -2106,6 +2106,11 @@
           <t>operative</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
           <t>1-CMFA-Agenda-02-23-24.pdf</t>
@@ -7425,6 +7430,11 @@
           <t>operative</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
           <t>CMFA-Agendas-10-11-2024.pdf</t>
@@ -8865,6 +8875,11 @@
           <t>operative</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
           <t>1-CMFA-Agenda-12-13-2024.pdf</t>
@@ -11077,6 +11092,11 @@
           <t>operative</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="Q75" s="3" t="inlineStr">
         <is>
           <t>1-CMFA-Agenda-05-16-2025.pdf</t>
@@ -26489,16 +26509,6 @@
           <t>True</t>
         </is>
       </c>
-      <c r="O191" t="inlineStr">
-        <is>
-          <t>11145</t>
-        </is>
-      </c>
-      <c r="P191" t="inlineStr">
-        <is>
-          <t>2022-12-02</t>
-        </is>
-      </c>
       <c r="T191" t="inlineStr">
         <is>
           <t>Standard Property Company</t>
@@ -30371,6 +30381,11 @@
           <t>operative</t>
         </is>
       </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
       <c r="Z222" t="inlineStr">
         <is>
           <t>15</t>
@@ -32144,16 +32159,6 @@
       <c r="N237" t="inlineStr">
         <is>
           <t>True</t>
-        </is>
-      </c>
-      <c r="O237" t="inlineStr">
-        <is>
-          <t>11142</t>
-        </is>
-      </c>
-      <c r="P237" t="inlineStr">
-        <is>
-          <t>2022-12-08</t>
         </is>
       </c>
       <c r="T237" t="inlineStr">

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -2111,6 +2111,16 @@
           <t>True</t>
         </is>
       </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>15163</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
           <t>1-CMFA-Agenda-02-23-24.pdf</t>
@@ -11097,6 +11107,16 @@
           <t>True</t>
         </is>
       </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15318</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
       <c r="Q75" s="3" t="inlineStr">
         <is>
           <t>1-CMFA-Agenda-05-16-2025.pdf</t>
@@ -26509,6 +26529,16 @@
           <t>True</t>
         </is>
       </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>11145</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>2022-12-02</t>
+        </is>
+      </c>
       <c r="T191" t="inlineStr">
         <is>
           <t>Standard Property Company</t>
@@ -32161,6 +32191,16 @@
           <t>True</t>
         </is>
       </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>11142</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>2022-12-08</t>
+        </is>
+      </c>
       <c r="T237" t="inlineStr">
         <is>
           <t>Standard Property Company</t>
@@ -32597,6 +32637,21 @@
       <c r="K241" s="2" t="inlineStr">
         <is>
           <t>pulled</t>
+        </is>
+      </c>
+      <c r="N241" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="O241" s="2" t="inlineStr">
+        <is>
+          <t>15163</t>
+        </is>
+      </c>
+      <c r="P241" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="Q241" s="3" t="inlineStr">
@@ -75570,7 +75625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C88"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -76788,68 +76843,68 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>scc-possible-match</t>
+          <t>scc-manual-unmatched</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>entity '861 Fedora LLLP' ~ SCC LP '836 Fedora L.P.' (#1594, Los Angeles, score 90)</t>
+          <t>manual scc_filed=True but no BOE certificate matches entity 'Hillsdale Property LP'; closest: 'Hillsdale Property San Mateo, LP' (#15018, San Mateo, score 78)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>scc-possible-match</t>
+          <t>scc-manual-unmatched</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>entity '861 Fedora LLLP' ~ SCC LP '836 Fedora L.P.' (#1594, Los Angeles, score 90)</t>
+          <t>manual scc_filed=True but no BOE certificate matches entity 'Post Chaparral, LP, a Delaware limited p'; closest: 'Post Palmdale Chaparral, LP' (#15197, Los Angeles, score 76)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>122</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AIN 5036031006 (Los Angeles) has no current roll data; using manual value</t>
+          <t>entity '861 Fedora LLLP' ~ SCC LP '836 Fedora L.P.' (#1594, Los Angeles, score 90)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>165</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AIN 4262018026 (Los Angeles) has no current roll data; using manual value</t>
+          <t>entity '861 Fedora LLLP' ~ SCC LP '836 Fedora L.P.' (#1594, Los Angeles, score 90)</t>
         </is>
       </c>
     </row>
@@ -76861,12 +76916,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AIN 6020022027 (Los Angeles) has no current roll data; using manual value</t>
+          <t>AIN 5036031006 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
@@ -76878,46 +76933,46 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AIN 2125017014 (Los Angeles) has no current roll data; using manual value</t>
+          <t>AIN 4262018026 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>132</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 6020022027 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>137</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 2125017014 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
@@ -76929,12 +76984,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>158</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AIN (none) (Santa Barbara): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -76946,7 +77001,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>196</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -76963,12 +77018,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN (none) (Santa Barbara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -76980,7 +77035,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>206</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -76997,12 +77052,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>207</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AIN 5539028040 (Los Angeles): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -77014,46 +77069,46 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>208</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AIN (none) (Contra Costa): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>215</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AIN 128101150 (Solano) has no current roll data; using manual value</t>
+          <t>AIN 5539028040 (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AIN 128101050 (Solano) has no current roll data; using manual value</t>
+          <t>AIN (none) (Contra Costa): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -77069,6 +77124,40 @@
         </is>
       </c>
       <c r="C88" t="inlineStr">
+        <is>
+          <t>AIN 128101150 (Solano) has no current roll data; using manual value</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>fetch-fallback</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>AIN 128101050 (Solano) has no current roll data; using manual value</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>fetch-fallback</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
         <is>
           <t>AIN 128105060 (Solano) has no current roll data; using manual value</t>
         </is>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -5589,6 +5589,11 @@
           <t>authorize</t>
         </is>
       </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
           <t>operative</t>
@@ -5726,6 +5731,11 @@
           <t>authorize</t>
         </is>
       </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
           <t>operative</t>
@@ -5863,6 +5873,11 @@
           <t>authorize</t>
         </is>
       </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
           <t>operative</t>
@@ -6157,6 +6172,11 @@
           <t>authorize</t>
         </is>
       </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
           <t>operative</t>
@@ -6299,6 +6319,11 @@
           <t>authorize</t>
         </is>
       </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
           <t>superseded</t>
@@ -7572,6 +7597,11 @@
           <t>authorize</t>
         </is>
       </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
           <t>operative</t>
@@ -8272,6 +8302,11 @@
           <t>authorize</t>
         </is>
       </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
           <t>operative</t>
@@ -9012,6 +9047,11 @@
           <t>authorize</t>
         </is>
       </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
           <t>operative</t>
@@ -9306,6 +9346,11 @@
           <t>authorize</t>
         </is>
       </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
           <t>operative</t>
@@ -9575,6 +9620,11 @@
           <t>authorize</t>
         </is>
       </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
           <t>operative</t>
@@ -9712,6 +9762,11 @@
           <t>authorize</t>
         </is>
       </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
           <t>operative</t>
@@ -10673,7 +10728,12 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>operative</t>
+          <t>superseded</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>360</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -13685,6 +13745,11 @@
           <t>authorize</t>
         </is>
       </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
           <t>operative</t>
@@ -13964,6 +14029,11 @@
           <t>authorize</t>
         </is>
       </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
           <t>operative</t>
@@ -19516,6 +19586,11 @@
           <t>authorize</t>
         </is>
       </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
           <t>operative</t>
@@ -19645,12 +19720,12 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>pulled</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>pulled</t>
+          <t>operative</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -19790,6 +19865,11 @@
           <t>authorize</t>
         </is>
       </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
           <t>operative</t>
@@ -19922,6 +20002,11 @@
           <t>authorize</t>
         </is>
       </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
           <t>operative</t>
@@ -20054,6 +20139,11 @@
           <t>authorize</t>
         </is>
       </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
           <t>operative</t>
@@ -20186,6 +20276,11 @@
           <t>authorize</t>
         </is>
       </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
           <t>operative</t>
@@ -20308,14 +20403,14 @@
           <t>authorize</t>
         </is>
       </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>pulled</t>
+        </is>
+      </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>superseded</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>147</t>
+          <t>pulled</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -27236,6 +27331,11 @@
           <t>Santa Clara</t>
         </is>
       </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>26-140</t>
+        </is>
+      </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
           <t>2026-03-13</t>
@@ -27244,6 +27344,11 @@
       <c r="I197" s="2" t="inlineStr">
         <is>
           <t>preliminary_only</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr">
@@ -33102,6 +33207,11 @@
           <t>San Mateo</t>
         </is>
       </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>24-362</t>
+        </is>
+      </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
           <t>2024-08-30</t>
@@ -33110,6 +33220,11 @@
       <c r="I245" s="2" t="inlineStr">
         <is>
           <t>authorize</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
         </is>
       </c>
       <c r="K245" s="2" t="inlineStr">
@@ -39061,6 +39176,11 @@
           <t>San Mateo</t>
         </is>
       </c>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>26-351</t>
+        </is>
+      </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
           <t>2026-06-12</t>
@@ -39071,14 +39191,14 @@
           <t>authorize</t>
         </is>
       </c>
+      <c r="J297" s="2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
       <c r="K297" s="2" t="inlineStr">
         <is>
-          <t>superseded</t>
-        </is>
-      </c>
-      <c r="L297" t="inlineStr">
-        <is>
-          <t>71</t>
+          <t>operative</t>
         </is>
       </c>
       <c r="Q297" s="3" t="inlineStr">
@@ -39536,7 +39656,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>360</t>
         </is>
       </c>
       <c r="Q301" s="3" t="inlineStr">
@@ -53955,7 +54075,7 @@
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>360</t>
         </is>
       </c>
       <c r="U140" s="2" t="inlineStr">

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -75745,7 +75745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -77031,34 +77031,34 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>scc-superseded-only</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>132</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AIN 5036031006 (Los Angeles) has no current roll data; using manual value</t>
+          <t>operative entity 'PS 7518 Hoover St, LP' has no SCC, but the property's superseded grant 10 ('BIF NON OZ 7518 S Hoover St, LP, a Delaw') holds SCC 14953 (2024-11-25) — new sponsor's LP must file its own</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>scc-superseded-only</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>134</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AIN 4262018026 (Los Angeles) has no current roll data; using manual value</t>
+          <t>operative entity 'PS 10705 Avalon Blvd, LP' has no SCC, but the property's superseded grant 303 ('BIF NON OZ 10705 Avalon Blvd, LP, a Cali') holds SCC 14852 (2024-10-03) — new sponsor's LP must file its own</t>
         </is>
       </c>
     </row>
@@ -77070,12 +77070,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AIN 6020022027 (Los Angeles) has no current roll data; using manual value</t>
+          <t>AIN 5036031006 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
@@ -77087,46 +77087,46 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AIN 2125017014 (Los Angeles) has no current roll data; using manual value</t>
+          <t>AIN 4262018026 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>132</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 6020022027 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>137</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 2125017014 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
@@ -77138,12 +77138,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>158</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AIN (none) (Santa Barbara): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -77155,7 +77155,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>196</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -77172,12 +77172,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN (none) (Santa Barbara): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -77189,7 +77189,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>206</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -77206,12 +77206,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>207</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AIN 5539028040 (Los Angeles): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -77223,46 +77223,46 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>208</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AIN (none) (Contra Costa): no roll values from any source</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>215</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AIN 128101150 (Solano) has no current roll data; using manual value</t>
+          <t>AIN 5539028040 (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AIN 128101050 (Solano) has no current roll data; using manual value</t>
+          <t>AIN (none) (Contra Costa): no roll values from any source</t>
         </is>
       </c>
     </row>
@@ -77278,6 +77278,40 @@
         </is>
       </c>
       <c r="C90" t="inlineStr">
+        <is>
+          <t>AIN 128101150 (Solano) has no current roll data; using manual value</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>fetch-fallback</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>AIN 128101050 (Solano) has no current roll data; using manual value</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>fetch-fallback</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
         <is>
           <t>AIN 128105060 (Solano) has no current roll data; using manual value</t>
         </is>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -58947,7 +58947,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -59049,7 +59049,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -59151,7 +59151,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -59253,7 +59253,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -59355,7 +59355,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -59457,7 +59457,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -59559,7 +59559,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -59661,7 +59661,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -59763,7 +59763,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -59865,7 +59865,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -60151,7 +60151,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -61398,7 +61398,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -75745,7 +75745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C92"/>
+  <dimension ref="A1:C104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -77314,6 +77314,210 @@
       <c r="C92" t="inlineStr">
         <is>
           <t>AIN 128105060 (Solano) has no current roll data; using manual value</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>parcel-dedup</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>AIN 5518013024 (Alexandria II Apartments) also assigned under operative grant 162; this row marked legacy_redundant so sums count it once</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>parcel-dedup</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>AIN 5094017020 (Fedora Apartments) also assigned under operative grant 165; this row marked legacy_redundant so sums count it once</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>parcel-dedup</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>AIN 5518020021 (Kenmore II Apartments) also assigned under operative grant 168; this row marked legacy_redundant so sums count it once</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>parcel-dedup</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>AIN 5094023025 (Kenmore III Apartments) also assigned under operative grant 169; this row marked legacy_redundant so sums count it once</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>parcel-dedup</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>AIN 5503024012 (Kingsley Apartments) also assigned under operative grant 170; this row marked legacy_redundant so sums count it once</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>parcel-dedup</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>AIN 5094005005 (Mariposa I Apartments) also assigned under operative grant 173; this row marked legacy_redundant so sums count it once</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>parcel-dedup</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>AIN 5094006003 (Mariposa III Apartments) also assigned under operative grant 174; this row marked legacy_redundant so sums count it once</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>parcel-dedup</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>AIN 5502019004 (Mariposa IV Apartments) also assigned under operative grant 175; this row marked legacy_redundant so sums count it once</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>parcel-dedup</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>AIN 5517005016 (Oxford II Apartments) also assigned under operative grant 177; this row marked legacy_redundant so sums count it once</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>parcel-dedup</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>AIN 5080006008 (Western Apartments) also assigned under operative grant 179; this row marked legacy_redundant so sums count it once</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>parcel-dedup</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>AIN 7157012023 (The Hive at Ackerfield Apartments) also assigned under operative grant 181; this row marked legacy_redundant so sums count it once</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>parcel-dedup</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>AIN 5518026004 (236 Berendo Apartments) also assigned under operative grant 220; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN306"/>
+  <dimension ref="A1:AO306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -477,9 +477,9 @@
     <col width="12" customWidth="1" min="27" max="27"/>
     <col width="12" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="38" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
     <col width="38" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="38" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="12" customWidth="1" min="34" max="34"/>
     <col width="12" customWidth="1" min="35" max="35"/>
@@ -487,7 +487,8 @@
     <col width="12" customWidth="1" min="37" max="37"/>
     <col width="12" customWidth="1" min="38" max="38"/>
     <col width="12" customWidth="1" min="39" max="39"/>
-    <col width="38" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="40" max="40"/>
+    <col width="38" customWidth="1" min="41" max="41"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -638,55 +639,60 @@
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
+          <t>years_since_approval</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
           <t>grant_description</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>address</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>estimated_closing</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>new_build</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>built</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>acquisition_price_m</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>acquisition_date</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>link</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>leasing_link</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>row_source</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>field_overrides</t>
         </is>
@@ -825,15 +831,20 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE2" s="2" t="inlineStr">
+      <c r="AF2" s="2" t="inlineStr">
         <is>
           <t>1136 S. Alvarado Street, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -972,25 +983,30 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE3" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE3" s="2" t="inlineStr">
+      <c r="AF3" s="2" t="inlineStr">
         <is>
           <t>2025 New Jersey St., Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>built:collaborator-sheet; investor_1:collaborator-sheet</t>
         </is>
@@ -1129,20 +1145,25 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>660 Mariposa Ave., Mountain View, CA</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -1271,20 +1292,25 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>363 E. Gilbert St., San Bernardino, CA</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -1413,20 +1439,25 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>840 17th St, San Diego, CA 92101</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -1555,20 +1586,25 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE7" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>381 Turk St., San Francisco, CA</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; city:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -1692,25 +1728,30 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>26409 Gading Rd, Hayward, CA 94544</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>https://www.townhomesongadingapts.com/</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>leasing_link:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -1849,20 +1890,25 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>1317 S. Grand St, Los Angeles, CA 90015</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -1991,20 +2037,25 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>1411 Flower St, Los Angeles, CA 90015</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>investor_2:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -2143,20 +2194,25 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>7518 S. Hoover, Los Angeles, CA 90044</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
         <is>
           <t>investor_2:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -2295,25 +2351,30 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>820 W MacArthur Blvd, Oakland, CA 94608</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
+      <c r="AH12" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -2452,20 +2513,25 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE13" s="2" t="inlineStr">
+      <c r="AF13" s="2" t="inlineStr">
         <is>
           <t>801-809 Waterloo Street, CA</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
+      <c r="AN13" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
+      <c r="AO13" t="inlineStr">
         <is>
           <t>restricted_units:collaborator-sheet</t>
         </is>
@@ -2599,20 +2665,25 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AF14" t="inlineStr">
         <is>
           <t>275 Turk St, San Francisco, CA</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
+      <c r="AN14" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr">
+      <c r="AO14" t="inlineStr">
         <is>
           <t>investor_2:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -2756,25 +2827,30 @@
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AF15" t="inlineStr">
         <is>
           <t>2415 Valdez St, Oakland, CA 94612</t>
         </is>
       </c>
-      <c r="AL15" t="inlineStr">
+      <c r="AM15" t="inlineStr">
         <is>
           <t>https://www.electriclofts.com/</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
+      <c r="AN15" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
+      <c r="AO15" t="inlineStr">
         <is>
           <t>leasing_link:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -2903,25 +2979,30 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AF16" t="inlineStr">
         <is>
           <t>6762 Hawthorn Ave, Los Angeles, CA 90028</t>
         </is>
       </c>
-      <c r="AH16" t="inlineStr">
+      <c r="AI16" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
+      <c r="AN16" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN16" t="inlineStr">
+      <c r="AO16" t="inlineStr">
         <is>
           <t>built:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -3045,25 +3126,30 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE17" s="2" t="inlineStr">
+        <is>
           <t>Charitable Affordable Housing Grant for an Affordable Rental Housing Facility Located in the City of Vacaville, Solano County, California</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
+      <c r="AF17" t="inlineStr">
         <is>
           <t>343 Moon River Pl, Vacaville, CA 95687</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
+      <c r="AH17" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
+      <c r="AN17" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
+      <c r="AO17" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -3207,30 +3293,35 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE18" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
+      <c r="AF18" t="inlineStr">
         <is>
           <t>4252 S CRENSHAW BLVD LOS ANGELES CA 90008</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
+      <c r="AH18" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH18" t="inlineStr">
+      <c r="AI18" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
+      <c r="AN18" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
+      <c r="AO18" t="inlineStr">
         <is>
           <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -3374,25 +3465,30 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE19" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
+      <c r="AF19" t="inlineStr">
         <is>
           <t>1735 S Mission Rd, Fallbrook, CA 92028</t>
         </is>
       </c>
-      <c r="AH19" t="inlineStr">
+      <c r="AI19" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
+      <c r="AN19" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN19" t="inlineStr">
+      <c r="AO19" t="inlineStr">
         <is>
           <t>built:collaborator-sheet; city:collaborator-sheet; nonprofit_partner:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -3536,25 +3632,30 @@
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE20" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
+      <c r="AF20" t="inlineStr">
         <is>
           <t>1100-1200 E. Fairhaven Avenue, Santa Ana, CA</t>
         </is>
       </c>
-      <c r="AH20" t="inlineStr">
+      <c r="AI20" t="inlineStr">
         <is>
           <t>1969</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
+      <c r="AN20" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
+      <c r="AO20" t="inlineStr">
         <is>
           <t>investor_2:collaborator-sheet; built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -3693,30 +3794,35 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE21" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AF21" t="inlineStr">
         <is>
           <t>7940 Reseda Boulevard, Reseda, CA</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
+      <c r="AJ21" t="inlineStr">
         <is>
           <t>17600000</t>
         </is>
       </c>
-      <c r="AJ21" t="inlineStr">
+      <c r="AK21" t="inlineStr">
         <is>
           <t>2024-06-28</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
+      <c r="AN21" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
+      <c r="AO21" t="inlineStr">
         <is>
           <t>acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -3855,30 +3961,35 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE22" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr">
+      <c r="AF22" t="inlineStr">
         <is>
           <t>18325 Saticoy St, Reseda, CA 91335</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
+      <c r="AJ22" t="inlineStr">
         <is>
           <t>16300000</t>
         </is>
       </c>
-      <c r="AJ22" t="inlineStr">
+      <c r="AK22" t="inlineStr">
         <is>
           <t>2024-06-13</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
+      <c r="AN22" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr">
+      <c r="AO22" t="inlineStr">
         <is>
           <t>acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -4017,25 +4128,30 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE23" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr">
+      <c r="AF23" t="inlineStr">
         <is>
           <t>2701 Randolph St., Huntington Park, CA</t>
         </is>
       </c>
-      <c r="AH23" t="inlineStr">
+      <c r="AI23" t="inlineStr">
         <is>
           <t>1989</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
+      <c r="AN23" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
+      <c r="AO23" t="inlineStr">
         <is>
           <t>built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -4159,25 +4275,30 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE24" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE24" s="2" t="inlineStr">
+      <c r="AF24" s="2" t="inlineStr">
         <is>
           <t>445 N Avalon Blvd</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr">
+      <c r="AH24" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
+      <c r="AN24" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
+      <c r="AO24" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet</t>
         </is>
@@ -4311,20 +4432,25 @@
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE25" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr">
+      <c r="AF25" t="inlineStr">
         <is>
           <t>4209 S Western Ave, Los Angeles, CA 90062</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
+      <c r="AN25" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
+      <c r="AO25" t="inlineStr">
         <is>
           <t>resolution:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -4458,20 +4584,25 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE26" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr">
+      <c r="AF26" t="inlineStr">
         <is>
           <t>1130 W Martin Luther King Jr Blvd, Los Angeles, CA 90037</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
+      <c r="AN26" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN26" t="inlineStr">
+      <c r="AO26" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -4610,25 +4741,30 @@
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE27" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
+      <c r="AF27" t="inlineStr">
         <is>
           <t>441 W 3rd St, San Pedro, CA 90731</t>
         </is>
       </c>
-      <c r="AH27" t="inlineStr">
+      <c r="AI27" t="inlineStr">
         <is>
           <t>1987</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
+      <c r="AN27" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
+      <c r="AO27" t="inlineStr">
         <is>
           <t>built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -4767,45 +4903,50 @@
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE28" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr">
+      <c r="AF28" t="inlineStr">
         <is>
           <t>1422-1428 6th St., Santa Monica, CA</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr">
+      <c r="AH28" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH28" t="inlineStr">
+      <c r="AI28" t="inlineStr">
         <is>
           <t>1997</t>
         </is>
       </c>
-      <c r="AI28" t="inlineStr">
+      <c r="AJ28" t="inlineStr">
         <is>
           <t>17170000</t>
         </is>
       </c>
-      <c r="AJ28" t="inlineStr">
+      <c r="AK28" t="inlineStr">
         <is>
           <t>2024-09-12</t>
         </is>
       </c>
-      <c r="AK28" t="inlineStr">
+      <c r="AL28" t="inlineStr">
         <is>
           <t>https://www.1422on6th.com/</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
+      <c r="AN28" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN28" t="inlineStr">
+      <c r="AO28" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet; acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; link:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -4944,20 +5085,25 @@
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE29" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AF29" t="inlineStr">
         <is>
           <t>1422-1432 7th, Santa Monica, CA</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
+      <c r="AN29" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN29" t="inlineStr">
+      <c r="AO29" t="inlineStr">
         <is>
           <t>total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -5096,20 +5242,25 @@
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE30" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr">
+      <c r="AF30" t="inlineStr">
         <is>
           <t>1423-1425 6th, Santa Monica, CA</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
+      <c r="AN30" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr">
+      <c r="AO30" t="inlineStr">
         <is>
           <t>total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -5248,25 +5399,30 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE31" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AF31" t="inlineStr">
         <is>
           <t>1522 6th St, Santa Monica, CA</t>
         </is>
       </c>
-      <c r="AH31" t="inlineStr">
+      <c r="AI31" t="inlineStr">
         <is>
           <t>2004</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
+      <c r="AN31" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr">
+      <c r="AO31" t="inlineStr">
         <is>
           <t>built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -5405,30 +5561,35 @@
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE32" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE32" t="inlineStr">
+      <c r="AF32" t="inlineStr">
         <is>
           <t>1537 7th, Santa Monica, CA</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
+      <c r="AJ32" t="inlineStr">
         <is>
           <t>5390000</t>
         </is>
       </c>
-      <c r="AJ32" t="inlineStr">
+      <c r="AK32" t="inlineStr">
         <is>
           <t>2024-09-12</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
+      <c r="AN32" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr">
+      <c r="AO32" t="inlineStr">
         <is>
           <t>acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -5567,25 +5728,30 @@
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE33" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE33" t="inlineStr">
+      <c r="AF33" t="inlineStr">
         <is>
           <t>2001-2029 Olympic Blvd, Santa Monica</t>
         </is>
       </c>
-      <c r="AH33" t="inlineStr">
+      <c r="AI33" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
+      <c r="AN33" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr">
+      <c r="AO33" t="inlineStr">
         <is>
           <t>built:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -5719,25 +5885,30 @@
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE34" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE34" t="inlineStr">
+      <c r="AF34" t="inlineStr">
         <is>
           <t>7518 S. Hoover, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG34" t="inlineStr">
+      <c r="AH34" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
+      <c r="AN34" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN34" t="inlineStr">
+      <c r="AO34" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -5876,20 +6047,25 @@
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE35" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE35" t="inlineStr">
+      <c r="AF35" t="inlineStr">
         <is>
           <t>4481 Appian Way, El Sobrante, CA 94803</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
+      <c r="AN35" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
+      <c r="AO35" t="inlineStr">
         <is>
           <t>city:collaborator-sheet; county:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -6028,20 +6204,25 @@
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE36" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE36" t="inlineStr">
+      <c r="AF36" t="inlineStr">
         <is>
           <t>4930 Polk St, North Highlands, CA 95660</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
+      <c r="AN36" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN36" t="inlineStr">
+      <c r="AO36" t="inlineStr">
         <is>
           <t>city:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -6180,20 +6361,25 @@
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE37" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE37" s="2" t="inlineStr">
+      <c r="AF37" s="2" t="inlineStr">
         <is>
           <t>9301 – 9609 Crenshaw</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
+      <c r="AN37" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN37" t="inlineStr">
+      <c r="AO37" t="inlineStr">
         <is>
           <t>resolution:collaborator-sheet</t>
         </is>
@@ -6332,25 +6518,30 @@
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE38" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE38" t="inlineStr">
+      <c r="AF38" t="inlineStr">
         <is>
           <t>2330 E. 3rd Street, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG38" t="inlineStr">
+      <c r="AH38" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
+      <c r="AN38" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN38" t="inlineStr">
+      <c r="AO38" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; property_name:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -6489,30 +6680,35 @@
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE39" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE39" t="inlineStr">
+      <c r="AF39" t="inlineStr">
         <is>
           <t>12300 Sherman Way, North Hollywood, CA 91605</t>
         </is>
       </c>
-      <c r="AG39" t="inlineStr">
+      <c r="AH39" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH39" t="inlineStr">
+      <c r="AI39" t="inlineStr">
         <is>
           <t>1965</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
+      <c r="AN39" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN39" t="inlineStr">
+      <c r="AO39" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -6651,25 +6847,30 @@
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE40" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE40" t="inlineStr">
+      <c r="AF40" t="inlineStr">
         <is>
           <t>6200 S Broadway, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG40" t="inlineStr">
+      <c r="AH40" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
+      <c r="AN40" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN40" t="inlineStr">
+      <c r="AO40" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -6803,25 +7004,30 @@
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE41" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE41" t="inlineStr">
+      <c r="AF41" t="inlineStr">
         <is>
           <t>4228 Western Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG41" t="inlineStr">
+      <c r="AH41" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
+      <c r="AN41" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN41" t="inlineStr">
+      <c r="AO41" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -6945,25 +7151,30 @@
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE42" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE42" t="inlineStr">
+      <c r="AF42" t="inlineStr">
         <is>
           <t>4327 S Vermont, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG42" t="inlineStr">
+      <c r="AH42" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
+      <c r="AN42" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN42" t="inlineStr">
+      <c r="AO42" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -7092,25 +7303,30 @@
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE43" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE43" t="inlineStr">
+      <c r="AF43" t="inlineStr">
         <is>
           <t>110 Imperial Highway, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG43" t="inlineStr">
+      <c r="AH43" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
+      <c r="AN43" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN43" t="inlineStr">
+      <c r="AO43" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -7244,25 +7460,30 @@
       </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE44" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE44" t="inlineStr">
+      <c r="AF44" t="inlineStr">
         <is>
           <t>400 Canal St, San Rafael, CA 94901</t>
         </is>
       </c>
-      <c r="AG44" t="inlineStr">
+      <c r="AH44" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
+      <c r="AN44" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN44" t="inlineStr">
+      <c r="AO44" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -7401,25 +7622,30 @@
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE45" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE45" t="inlineStr">
+      <c r="AF45" t="inlineStr">
         <is>
           <t>228 N Soto Street, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG45" t="inlineStr">
+      <c r="AH45" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
+      <c r="AN45" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN45" t="inlineStr">
+      <c r="AO45" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -7563,25 +7789,30 @@
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE46" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE46" t="inlineStr">
+      <c r="AF46" t="inlineStr">
         <is>
           <t>2414 N Tustin Ave, Santa Ana, CA 92705</t>
         </is>
       </c>
-      <c r="AG46" t="inlineStr">
+      <c r="AH46" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
+      <c r="AN46" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN46" t="inlineStr">
+      <c r="AO46" t="inlineStr">
         <is>
           <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -7708,27 +7939,27 @@
           <t>7950</t>
         </is>
       </c>
-      <c r="AD47" s="2" t="inlineStr">
+      <c r="AE47" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE47" t="inlineStr">
+      <c r="AF47" t="inlineStr">
         <is>
           <t>4752 Main St, Los Angeles, CA 90037</t>
         </is>
       </c>
-      <c r="AG47" t="inlineStr">
+      <c r="AH47" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
+      <c r="AN47" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN47" t="inlineStr">
+      <c r="AO47" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -7867,25 +8098,30 @@
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE48" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE48" t="inlineStr">
+      <c r="AF48" t="inlineStr">
         <is>
           <t>6171 Mission Gorge Rd, San Diego, CA 92120</t>
         </is>
       </c>
-      <c r="AG48" t="inlineStr">
+      <c r="AH48" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
+      <c r="AN48" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN48" t="inlineStr">
+      <c r="AO48" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -8019,25 +8255,30 @@
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE49" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE49" t="inlineStr">
+      <c r="AF49" t="inlineStr">
         <is>
           <t>3500 Edison St, San Mateo, CA 94403</t>
         </is>
       </c>
-      <c r="AG49" t="inlineStr">
+      <c r="AH49" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
+      <c r="AN49" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN49" t="inlineStr">
+      <c r="AO49" t="inlineStr">
         <is>
           <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; scc_filed:collaborator-sheet; investor_1:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -8161,25 +8402,30 @@
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE50" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE50" t="inlineStr">
+      <c r="AF50" t="inlineStr">
         <is>
           <t>21701 Foothill Blvd, Hayward, CA 94541</t>
         </is>
       </c>
-      <c r="AG50" t="inlineStr">
+      <c r="AH50" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
+      <c r="AN50" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN50" t="inlineStr">
+      <c r="AO50" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -8318,25 +8564,30 @@
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE51" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE51" t="inlineStr">
+      <c r="AF51" t="inlineStr">
         <is>
           <t>699 14th Street, San Diego, CA</t>
         </is>
       </c>
-      <c r="AG51" t="inlineStr">
+      <c r="AH51" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
+      <c r="AN51" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN51" t="inlineStr">
+      <c r="AO51" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -8470,30 +8721,35 @@
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE52" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE52" t="inlineStr">
+      <c r="AF52" t="inlineStr">
         <is>
           <t>220 47th St, San Diego, CA 92102</t>
         </is>
       </c>
-      <c r="AG52" t="inlineStr">
+      <c r="AH52" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH52" t="inlineStr">
+      <c r="AI52" t="inlineStr">
         <is>
           <t>1984</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
+      <c r="AN52" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN52" t="inlineStr">
+      <c r="AO52" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet; manual_status:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -8622,25 +8878,30 @@
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE53" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE53" t="inlineStr">
+      <c r="AF53" t="inlineStr">
         <is>
           <t>1201 Fulton Ave, Sacramento, CA 95825</t>
         </is>
       </c>
-      <c r="AG53" t="inlineStr">
+      <c r="AH53" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
+      <c r="AN53" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN53" t="inlineStr">
+      <c r="AO53" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; city:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -8769,30 +9030,35 @@
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE54" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE54" t="inlineStr">
+      <c r="AF54" t="inlineStr">
         <is>
           <t>6930 Fair Oaks Blvd, Carmichael, CA 95608</t>
         </is>
       </c>
-      <c r="AG54" t="inlineStr">
+      <c r="AH54" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH54" t="inlineStr">
+      <c r="AI54" t="inlineStr">
         <is>
           <t>1973/1991</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
+      <c r="AN54" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN54" t="inlineStr">
+      <c r="AO54" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet; manual_status:collaborator-sheet; city:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -8931,25 +9197,30 @@
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE55" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE55" s="2" t="inlineStr">
+      <c r="AF55" s="2" t="inlineStr">
         <is>
           <t>5601 North Paramount Boulevard</t>
         </is>
       </c>
-      <c r="AG55" t="inlineStr">
+      <c r="AH55" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
+      <c r="AN55" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN55" t="inlineStr">
+      <c r="AO55" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; resolution:collaborator-sheet; total_units:collaborator-sheet</t>
         </is>
@@ -9093,25 +9364,30 @@
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE56" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE56" s="2" t="inlineStr">
+      <c r="AF56" s="2" t="inlineStr">
         <is>
           <t>1457 North Main Street, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG56" t="inlineStr">
+      <c r="AH56" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
+      <c r="AN56" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN56" t="inlineStr">
+      <c r="AO56" t="inlineStr">
         <is>
           <t>investor_2:collaborator-sheet; new_build:collaborator-sheet</t>
         </is>
@@ -9235,25 +9511,30 @@
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE57" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE57" t="inlineStr">
+      <c r="AF57" t="inlineStr">
         <is>
           <t>651 Addison St, Berkeley, CA 94710</t>
         </is>
       </c>
-      <c r="AL57" t="inlineStr">
+      <c r="AM57" t="inlineStr">
         <is>
           <t>https://bridgehousing.com/properties/viewpoint/</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
+      <c r="AN57" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN57" t="inlineStr">
+      <c r="AO57" t="inlineStr">
         <is>
           <t>leasing_link:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -9397,50 +9678,55 @@
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE58" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE58" t="inlineStr">
+      <c r="AF58" t="inlineStr">
         <is>
           <t>2130 Southwest Expy, San Jose, CA 95126</t>
         </is>
       </c>
-      <c r="AG58" t="inlineStr">
+      <c r="AH58" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH58" t="inlineStr">
+      <c r="AI58" t="inlineStr">
         <is>
           <t>1969</t>
         </is>
       </c>
-      <c r="AI58" t="inlineStr">
+      <c r="AJ58" t="inlineStr">
         <is>
           <t>61.1</t>
         </is>
       </c>
-      <c r="AJ58" t="inlineStr">
+      <c r="AK58" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="AK58" t="inlineStr">
+      <c r="AL58" t="inlineStr">
         <is>
           <t>https://www.ethos-re.com/news/sofi-at-los-gatos-creek-adam-siegman-comments-on-affordable-housing</t>
         </is>
       </c>
-      <c r="AL58" t="inlineStr">
+      <c r="AM58" t="inlineStr">
         <is>
           <t>https://www.losgatoslandingapts.com/</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
+      <c r="AN58" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN58" t="inlineStr">
+      <c r="AO58" t="inlineStr">
         <is>
           <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; built:collaborator-sheet; acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; link:collaborator-sheet; leasing_link:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -9569,25 +9855,30 @@
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE59" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE59" t="inlineStr">
+      <c r="AF59" t="inlineStr">
         <is>
           <t>38441 5th St W, Palmdale, CA 93551</t>
         </is>
       </c>
-      <c r="AG59" t="inlineStr">
+      <c r="AH59" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
+      <c r="AN59" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN59" t="inlineStr">
+      <c r="AO59" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -9726,30 +10017,35 @@
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE60" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE60" t="inlineStr">
+      <c r="AF60" t="inlineStr">
         <is>
           <t>99 OCEAN AVE SAN FRANCISCO, CA 94112-2548</t>
         </is>
       </c>
-      <c r="AG60" t="inlineStr">
+      <c r="AH60" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AH60" t="inlineStr">
+      <c r="AI60" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
+      <c r="AN60" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN60" t="inlineStr">
+      <c r="AO60" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet; city:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -9888,25 +10184,30 @@
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE61" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE61" t="inlineStr">
+      <c r="AF61" t="inlineStr">
         <is>
           <t>5150 El Camino Real, Los Altos, CA</t>
         </is>
       </c>
-      <c r="AG61" t="inlineStr">
+      <c r="AH61" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
+      <c r="AN61" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN61" t="inlineStr">
+      <c r="AO61" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -10025,25 +10326,30 @@
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE62" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE62" t="inlineStr">
+      <c r="AF62" t="inlineStr">
         <is>
           <t>11422 S Broadway, Los Angeles, CA 90061</t>
         </is>
       </c>
-      <c r="AG62" t="inlineStr">
+      <c r="AH62" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
+      <c r="AN62" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN62" t="inlineStr">
+      <c r="AO62" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; resolution:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -10182,25 +10488,30 @@
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE63" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE63" t="inlineStr">
+      <c r="AF63" t="inlineStr">
         <is>
           <t>2533 S Mansfield Ave, Los Angeles, CA 90016</t>
         </is>
       </c>
-      <c r="AG63" t="inlineStr">
+      <c r="AH63" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
+      <c r="AN63" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN63" t="inlineStr">
+      <c r="AO63" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -10339,20 +10650,25 @@
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE64" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE64" t="inlineStr">
+      <c r="AF64" t="inlineStr">
         <is>
           <t>3081 N Main St, Walnut Creek, CA 94597</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
+      <c r="AN64" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN64" t="inlineStr">
+      <c r="AO64" t="inlineStr">
         <is>
           <t>resolution:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -10471,20 +10787,25 @@
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE65" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE65" t="inlineStr">
+      <c r="AF65" t="inlineStr">
         <is>
           <t>333 Douglas St, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
+      <c r="AN65" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN65" t="inlineStr">
+      <c r="AO65" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; resolution:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -10623,30 +10944,35 @@
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE66" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE66" s="2" t="inlineStr">
+      <c r="AF66" s="2" t="inlineStr">
         <is>
           <t>7777 Valley View Street</t>
         </is>
       </c>
-      <c r="AG66" t="inlineStr">
+      <c r="AH66" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH66" t="inlineStr">
+      <c r="AI66" t="inlineStr">
         <is>
           <t>1978</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
+      <c r="AN66" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN66" t="inlineStr">
+      <c r="AO66" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet</t>
         </is>
@@ -10775,20 +11101,25 @@
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE67" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE67" t="inlineStr">
+      <c r="AF67" t="inlineStr">
         <is>
           <t>920 S. Gramercy Place, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
+      <c r="AN67" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN67" t="inlineStr">
+      <c r="AO67" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -10927,15 +11258,20 @@
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE68" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE68" s="2" t="inlineStr">
+      <c r="AF68" s="2" t="inlineStr">
         <is>
           <t>1250 S. Euclid St., Anaheim, CA</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
+      <c r="AN68" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -11074,30 +11410,35 @@
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE69" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE69" t="inlineStr">
+      <c r="AF69" t="inlineStr">
         <is>
           <t>9830 Reseda Blvd, Northridge, CA 91324</t>
         </is>
       </c>
-      <c r="AG69" t="inlineStr">
+      <c r="AH69" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH69" t="inlineStr">
+      <c r="AI69" t="inlineStr">
         <is>
           <t>1964</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
+      <c r="AN69" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN69" t="inlineStr">
+      <c r="AO69" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -11226,20 +11567,25 @@
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE70" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE70" t="inlineStr">
+      <c r="AF70" t="inlineStr">
         <is>
           <t>10535 Lindley Ave, Granada Hills, CA 91326</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
+      <c r="AN70" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN70" t="inlineStr">
+      <c r="AO70" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -11368,20 +11714,25 @@
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE71" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE71" t="inlineStr">
+      <c r="AF71" t="inlineStr">
         <is>
           <t>26 Terrace View Ct, Daly City, CA 94015</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
+      <c r="AN71" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN71" t="inlineStr">
+      <c r="AO71" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -11510,30 +11861,35 @@
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE72" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE72" t="inlineStr">
+      <c r="AF72" t="inlineStr">
         <is>
           <t>1212 Whipple Ave, Redwood City, CA 94062</t>
         </is>
       </c>
-      <c r="AJ72" t="inlineStr">
+      <c r="AK72" t="inlineStr">
         <is>
           <t>2024-12-05</t>
         </is>
       </c>
-      <c r="AL72" t="inlineStr">
+      <c r="AM72" t="inlineStr">
         <is>
           <t>https://www.theheltsley.com/</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
+      <c r="AN72" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN72" t="inlineStr">
+      <c r="AO72" t="inlineStr">
         <is>
           <t>acquisition_date:collaborator-sheet; leasing_link:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -11662,30 +12018,35 @@
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE73" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE73" t="inlineStr">
+      <c r="AF73" t="inlineStr">
         <is>
           <t>5880 3rd St, San Francisco, CA 94124</t>
         </is>
       </c>
-      <c r="AG73" t="inlineStr">
+      <c r="AH73" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH73" t="inlineStr">
+      <c r="AI73" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
+      <c r="AN73" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN73" t="inlineStr">
+      <c r="AO73" t="inlineStr">
         <is>
           <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; built:collaborator-sheet; city:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -11824,25 +12185,30 @@
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE74" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE74" t="inlineStr">
+      <c r="AF74" t="inlineStr">
         <is>
           <t>1540 W Court St, Los Angeles, CA 90026</t>
         </is>
       </c>
-      <c r="AG74" t="inlineStr">
+      <c r="AH74" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
+      <c r="AN74" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN74" t="inlineStr">
+      <c r="AO74" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -11981,25 +12347,30 @@
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE75" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE75" t="inlineStr">
+      <c r="AF75" t="inlineStr">
         <is>
           <t>5040 Logan Avenue, San Diego, CA 92113</t>
         </is>
       </c>
-      <c r="AG75" t="inlineStr">
+      <c r="AH75" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
+      <c r="AN75" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN75" t="inlineStr">
+      <c r="AO75" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; scc_filed:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -12128,25 +12499,30 @@
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE76" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE76" t="inlineStr">
+      <c r="AF76" t="inlineStr">
         <is>
           <t>5474 Reservoir Dr, San Diego, CA 92120</t>
         </is>
       </c>
-      <c r="AG76" t="inlineStr">
+      <c r="AH76" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
+      <c r="AN76" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN76" t="inlineStr">
+      <c r="AO76" t="inlineStr">
         <is>
           <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -12275,25 +12651,30 @@
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE77" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE77" t="inlineStr">
+      <c r="AF77" t="inlineStr">
         <is>
           <t>1451 W. MLK Blvd, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG77" t="inlineStr">
+      <c r="AH77" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
+      <c r="AN77" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN77" t="inlineStr">
+      <c r="AO77" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet; manual_status:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -12417,25 +12798,30 @@
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE78" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE78" t="inlineStr">
+      <c r="AF78" t="inlineStr">
         <is>
           <t>11630 Main St, Los Angeles, CA 90061</t>
         </is>
       </c>
-      <c r="AG78" t="inlineStr">
+      <c r="AH78" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
+      <c r="AN78" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN78" t="inlineStr">
+      <c r="AO78" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -12579,30 +12965,35 @@
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE79" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE79" t="inlineStr">
+      <c r="AF79" t="inlineStr">
         <is>
           <t>3400 Richmond Pkwy, Richmond, CA 94806</t>
         </is>
       </c>
-      <c r="AG79" t="inlineStr">
+      <c r="AH79" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AK79" t="inlineStr">
+      <c r="AL79" t="inlineStr">
         <is>
           <t>https://www.cmfa-ca.com/wp-content/uploads/2025/01/CMFA-Staff-Reports-01-10-25.pdf</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
+      <c r="AN79" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN79" t="inlineStr">
+      <c r="AO79" t="inlineStr">
         <is>
           <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; link:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -12726,25 +13117,30 @@
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE80" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE80" t="inlineStr">
+      <c r="AF80" t="inlineStr">
         <is>
           <t>10811 S. Compton Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG80" t="inlineStr">
+      <c r="AH80" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
+      <c r="AN80" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN80" t="inlineStr">
+      <c r="AO80" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -12868,25 +13264,30 @@
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE81" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE81" t="inlineStr">
+      <c r="AF81" t="inlineStr">
         <is>
           <t>4101 Somerset Drive, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG81" t="inlineStr">
+      <c r="AH81" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
+      <c r="AN81" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN81" t="inlineStr">
+      <c r="AO81" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -13010,25 +13411,30 @@
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE82" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE82" t="inlineStr">
+      <c r="AF82" t="inlineStr">
         <is>
           <t>321 E. Florence Ave, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG82" t="inlineStr">
+      <c r="AH82" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
+      <c r="AN82" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN82" t="inlineStr">
+      <c r="AO82" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -13152,25 +13558,30 @@
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE83" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE83" t="inlineStr">
+      <c r="AF83" t="inlineStr">
         <is>
           <t>9300 Compton Ave., Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG83" t="inlineStr">
+      <c r="AH83" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
+      <c r="AN83" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN83" t="inlineStr">
+      <c r="AO83" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -13294,25 +13705,30 @@
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE84" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE84" t="inlineStr">
+      <c r="AF84" t="inlineStr">
         <is>
           <t>6401 S. Avalon Blvd., Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG84" t="inlineStr">
+      <c r="AH84" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
+      <c r="AN84" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN84" t="inlineStr">
+      <c r="AO84" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -13436,25 +13852,30 @@
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE85" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE85" t="inlineStr">
+      <c r="AF85" t="inlineStr">
         <is>
           <t>9515 Compton Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG85" t="inlineStr">
+      <c r="AH85" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
+      <c r="AN85" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN85" t="inlineStr">
+      <c r="AO85" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -13578,25 +13999,30 @@
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE86" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE86" t="inlineStr">
+      <c r="AF86" t="inlineStr">
         <is>
           <t>569 W. 6th Street, San Pedro, CA</t>
         </is>
       </c>
-      <c r="AG86" t="inlineStr">
+      <c r="AH86" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
+      <c r="AN86" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN86" t="inlineStr">
+      <c r="AO86" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -13720,25 +14146,30 @@
       </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE87" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE87" t="inlineStr">
+      <c r="AF87" t="inlineStr">
         <is>
           <t>685 W. 4th St., Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG87" t="inlineStr">
+      <c r="AH87" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
+      <c r="AN87" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN87" t="inlineStr">
+      <c r="AO87" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -13882,25 +14313,30 @@
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE88" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE88" t="inlineStr">
+      <c r="AF88" t="inlineStr">
         <is>
           <t>209 Westmoreland Ave, Los Angeles, CA 90004</t>
         </is>
       </c>
-      <c r="AG88" t="inlineStr">
+      <c r="AH88" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
+      <c r="AN88" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN88" t="inlineStr">
+      <c r="AO88" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -14024,25 +14460,30 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE89" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE89" t="inlineStr">
+      <c r="AF89" t="inlineStr">
         <is>
           <t>17188 Chatsworth St., Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG89" t="inlineStr">
+      <c r="AH89" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
+      <c r="AN89" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN89" t="inlineStr">
+      <c r="AO89" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -14166,25 +14607,30 @@
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE90" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE90" t="inlineStr">
+      <c r="AF90" t="inlineStr">
         <is>
           <t>1700 Newbury Park Dr, San Jose, CA 95133</t>
         </is>
       </c>
-      <c r="AJ90" t="inlineStr">
+      <c r="AK90" t="inlineStr">
         <is>
           <t>2025-09-03</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
+      <c r="AN90" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN90" t="inlineStr">
+      <c r="AO90" t="inlineStr">
         <is>
           <t>acquisition_date:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -14308,25 +14754,30 @@
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE91" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE91" t="inlineStr">
+      <c r="AF91" t="inlineStr">
         <is>
           <t>18615 E Arrow Hwy, Covina, CA 91722</t>
         </is>
       </c>
-      <c r="AG91" t="inlineStr">
+      <c r="AH91" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
+      <c r="AN91" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN91" t="inlineStr">
+      <c r="AO91" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -14450,25 +14901,30 @@
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE92" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE92" t="inlineStr">
+      <c r="AF92" t="inlineStr">
         <is>
           <t>10910 Huston St, North Hollywood, CA 91601</t>
         </is>
       </c>
-      <c r="AG92" t="inlineStr">
+      <c r="AH92" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
+      <c r="AN92" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN92" t="inlineStr">
+      <c r="AO92" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -14607,25 +15063,30 @@
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE93" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE93" t="inlineStr">
+      <c r="AF93" t="inlineStr">
         <is>
           <t>4640 Arden Way, El Monte, CA 91731</t>
         </is>
       </c>
-      <c r="AG93" t="inlineStr">
+      <c r="AH93" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
+      <c r="AN93" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN93" t="inlineStr">
+      <c r="AO93" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -14749,25 +15210,30 @@
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE94" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE94" t="inlineStr">
+      <c r="AF94" t="inlineStr">
         <is>
           <t>800 Reliant Wy, American Canyon, CA 94503</t>
         </is>
       </c>
-      <c r="AG94" t="inlineStr">
+      <c r="AH94" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
+      <c r="AN94" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN94" t="inlineStr">
+      <c r="AO94" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; resolution:collaborator-sheet; nonprofit_partner:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -14906,30 +15372,35 @@
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE95" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE95" t="inlineStr">
+      <c r="AF95" t="inlineStr">
         <is>
           <t>601 Telegraph Canyon Road, Chula Vista, CA 91910</t>
         </is>
       </c>
-      <c r="AG95" t="inlineStr">
+      <c r="AH95" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH95" t="inlineStr">
+      <c r="AI95" t="inlineStr">
         <is>
           <t>1981</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
+      <c r="AN95" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN95" t="inlineStr">
+      <c r="AO95" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -15073,30 +15544,35 @@
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE96" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE96" t="inlineStr">
+      <c r="AF96" t="inlineStr">
         <is>
           <t>1026 S De Anza Blvd, San Jose, CA 95129</t>
         </is>
       </c>
-      <c r="AJ96" t="inlineStr">
+      <c r="AK96" t="inlineStr">
         <is>
           <t>2025-08-29</t>
         </is>
       </c>
-      <c r="AK96" t="inlineStr">
+      <c r="AL96" t="inlineStr">
         <is>
           <t>https://rebusinessonline.com/sack-properties-belveron-partners-buy-164-unit-multifamily-property-in-san-jose-california/</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
+      <c r="AN96" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN96" t="inlineStr">
+      <c r="AO96" t="inlineStr">
         <is>
           <t>investor_2:collaborator-sheet; acquisition_date:collaborator-sheet; link:collaborator-sheet; resolution:collaborator-sheet; investor_1:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -15240,35 +15716,40 @@
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE97" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE97" t="inlineStr">
+      <c r="AF97" t="inlineStr">
         <is>
           <t>355 Kiely Blvd, San Jose, CA 95129</t>
         </is>
       </c>
-      <c r="AH97" t="inlineStr">
+      <c r="AI97" t="inlineStr">
         <is>
           <t>1972</t>
         </is>
       </c>
-      <c r="AI97" t="inlineStr">
+      <c r="AJ97" t="inlineStr">
         <is>
           <t>410</t>
         </is>
       </c>
-      <c r="AJ97" t="inlineStr">
+      <c r="AK97" t="inlineStr">
         <is>
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
+      <c r="AN97" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN97" t="inlineStr">
+      <c r="AO97" t="inlineStr">
         <is>
           <t>investor_2:collaborator-sheet; built:collaborator-sheet; acquisition_price_m:collaborator-sheet; acquisition_date:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -15392,25 +15873,30 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE98" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE98" t="inlineStr">
+      <c r="AF98" t="inlineStr">
         <is>
           <t>601 E 8th St, Azusa, CA 91702</t>
         </is>
       </c>
-      <c r="AG98" t="inlineStr">
+      <c r="AH98" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
+      <c r="AN98" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN98" t="inlineStr">
+      <c r="AO98" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -15539,30 +16025,35 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE99" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE99" t="inlineStr">
+      <c r="AF99" t="inlineStr">
         <is>
           <t>38000 Camden St, Fremont, CA 94536</t>
         </is>
       </c>
-      <c r="AG99" t="inlineStr">
+      <c r="AH99" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AL99" t="inlineStr">
+      <c r="AM99" t="inlineStr">
         <is>
           <t>https://www.camdenvillageapts.com/</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
+      <c r="AN99" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN99" t="inlineStr">
+      <c r="AO99" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; leasing_link:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -15701,25 +16192,30 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE100" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE100" t="inlineStr">
+      <c r="AF100" t="inlineStr">
         <is>
           <t>1734 S. Barrington Ave., Los Angeles, CA, 90025</t>
         </is>
       </c>
-      <c r="AG100" t="inlineStr">
+      <c r="AH100" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
+      <c r="AN100" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN100" t="inlineStr">
+      <c r="AO100" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -15858,25 +16354,30 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE101" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE101" t="inlineStr">
+      <c r="AF101" t="inlineStr">
         <is>
           <t>4129 Centinela Avenue, Los Angeles, CA 90066</t>
         </is>
       </c>
-      <c r="AG101" t="inlineStr">
+      <c r="AH101" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
+      <c r="AN101" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN101" t="inlineStr">
+      <c r="AO101" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -16015,25 +16516,30 @@
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE102" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE102" t="inlineStr">
+      <c r="AF102" t="inlineStr">
         <is>
           <t>4706 Centinela Avenue, Los Angeles, CA 90066</t>
         </is>
       </c>
-      <c r="AG102" t="inlineStr">
+      <c r="AH102" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
+      <c r="AN102" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN102" t="inlineStr">
+      <c r="AO102" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -16172,25 +16678,30 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE103" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE103" t="inlineStr">
+      <c r="AF103" t="inlineStr">
         <is>
           <t>1747 Stoner Avenue, Los Angeles, CA 90025</t>
         </is>
       </c>
-      <c r="AG103" t="inlineStr">
+      <c r="AH103" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
+      <c r="AN103" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN103" t="inlineStr">
+      <c r="AO103" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -16314,25 +16825,30 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE104" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE104" t="inlineStr">
+      <c r="AF104" t="inlineStr">
         <is>
           <t>2025 E. 4th Street, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG104" t="inlineStr">
+      <c r="AH104" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
+      <c r="AN104" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN104" t="inlineStr">
+      <c r="AO104" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -16456,25 +16972,30 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE105" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE105" t="inlineStr">
+      <c r="AF105" t="inlineStr">
         <is>
           <t>247 S. Alexandria Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG105" t="inlineStr">
+      <c r="AH105" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
+      <c r="AN105" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN105" t="inlineStr">
+      <c r="AO105" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -16598,25 +17119,30 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE106" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE106" t="inlineStr">
+      <c r="AF106" t="inlineStr">
         <is>
           <t>808 S. Hobart Boulevard, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG106" t="inlineStr">
+      <c r="AH106" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
+      <c r="AN106" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN106" t="inlineStr">
+      <c r="AO106" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -16740,25 +17266,30 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE107" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE107" t="inlineStr">
+      <c r="AF107" t="inlineStr">
         <is>
           <t>454 S. Catalina Street, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG107" t="inlineStr">
+      <c r="AH107" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
+      <c r="AN107" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN107" t="inlineStr">
+      <c r="AO107" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -16882,25 +17413,30 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE108" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE108" t="inlineStr">
+      <c r="AF108" t="inlineStr">
         <is>
           <t>103 S. Edgemont Street, Los Angeles, CA 90004</t>
         </is>
       </c>
-      <c r="AG108" t="inlineStr">
+      <c r="AH108" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
+      <c r="AN108" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN108" t="inlineStr">
+      <c r="AO108" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -17024,25 +17560,30 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE109" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE109" t="inlineStr">
+      <c r="AF109" t="inlineStr">
         <is>
           <t>974 S. Gramercy Place, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG109" t="inlineStr">
+      <c r="AH109" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
+      <c r="AN109" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN109" t="inlineStr">
+      <c r="AO109" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -17166,25 +17707,30 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE110" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE110" t="inlineStr">
+      <c r="AF110" t="inlineStr">
         <is>
           <t>832 Irolo Street, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG110" t="inlineStr">
+      <c r="AH110" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
+      <c r="AN110" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN110" t="inlineStr">
+      <c r="AO110" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -17308,25 +17854,30 @@
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE111" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE111" t="inlineStr">
+      <c r="AF111" t="inlineStr">
         <is>
           <t>941 S. Kenmore Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG111" t="inlineStr">
+      <c r="AH111" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
+      <c r="AN111" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN111" t="inlineStr">
+      <c r="AO111" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -17440,25 +17991,30 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE112" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE112" t="inlineStr">
+      <c r="AF112" t="inlineStr">
         <is>
           <t>426 S. Manhattan Place, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG112" t="inlineStr">
+      <c r="AH112" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
+      <c r="AN112" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN112" t="inlineStr">
+      <c r="AO112" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -17582,25 +18138,30 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE113" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE113" t="inlineStr">
+      <c r="AF113" t="inlineStr">
         <is>
           <t>260 S. Mariposa Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG113" t="inlineStr">
+      <c r="AH113" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
+      <c r="AN113" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN113" t="inlineStr">
+      <c r="AO113" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -17724,25 +18285,30 @@
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE114" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE114" t="inlineStr">
+      <c r="AF114" t="inlineStr">
         <is>
           <t>739 S. Normandie Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG114" t="inlineStr">
+      <c r="AH114" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
+      <c r="AN114" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN114" t="inlineStr">
+      <c r="AO114" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -17866,25 +18432,30 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE115" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE115" t="inlineStr">
+      <c r="AF115" t="inlineStr">
         <is>
           <t>1111 S. Norton Avenue, Los Angeles, CA 90019</t>
         </is>
       </c>
-      <c r="AG115" t="inlineStr">
+      <c r="AH115" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
+      <c r="AN115" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN115" t="inlineStr">
+      <c r="AO115" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -18008,25 +18579,30 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE116" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE116" t="inlineStr">
+      <c r="AF116" t="inlineStr">
         <is>
           <t>975-985 S. Oxford Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG116" t="inlineStr">
+      <c r="AH116" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
+      <c r="AN116" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN116" t="inlineStr">
+      <c r="AO116" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -18150,25 +18726,30 @@
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE117" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE117" t="inlineStr">
+      <c r="AF117" t="inlineStr">
         <is>
           <t>960 S. Oxford Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG117" t="inlineStr">
+      <c r="AH117" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
+      <c r="AN117" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN117" t="inlineStr">
+      <c r="AO117" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -18292,25 +18873,30 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE118" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE118" t="inlineStr">
+      <c r="AF118" t="inlineStr">
         <is>
           <t>3715 W. 1st Street, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG118" t="inlineStr">
+      <c r="AH118" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
+      <c r="AN118" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN118" t="inlineStr">
+      <c r="AO118" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -18434,25 +19020,30 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE119" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE119" t="inlineStr">
+      <c r="AF119" t="inlineStr">
         <is>
           <t>515 S. St. Andrews Place, Los Angeles, CA 90020</t>
         </is>
       </c>
-      <c r="AG119" t="inlineStr">
+      <c r="AH119" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
+      <c r="AN119" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN119" t="inlineStr">
+      <c r="AO119" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -18566,25 +19157,30 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE120" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE120" t="inlineStr">
+      <c r="AF120" t="inlineStr">
         <is>
           <t>516 S. St. Andrews Place, Los Angeles, CA 90020</t>
         </is>
       </c>
-      <c r="AG120" t="inlineStr">
+      <c r="AH120" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
+      <c r="AN120" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN120" t="inlineStr">
+      <c r="AO120" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -18723,25 +19319,30 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE121" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE121" t="inlineStr">
+      <c r="AF121" t="inlineStr">
         <is>
           <t>2345 Northrop Ave, Sacramento, CA 95825</t>
         </is>
       </c>
-      <c r="AG121" t="inlineStr">
+      <c r="AH121" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
+      <c r="AN121" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN121" t="inlineStr">
+      <c r="AO121" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; city:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -18860,25 +19461,30 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE122" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE122" t="inlineStr">
+      <c r="AF122" t="inlineStr">
         <is>
           <t>130 S. Alexandria Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG122" t="inlineStr">
+      <c r="AH122" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
+      <c r="AN122" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN122" t="inlineStr">
+      <c r="AO122" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -19007,25 +19613,30 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE123" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE123" t="inlineStr">
+      <c r="AF123" t="inlineStr">
         <is>
           <t>861 Fedora Street, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG123" t="inlineStr">
+      <c r="AH123" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM123" t="inlineStr">
+      <c r="AN123" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN123" t="inlineStr">
+      <c r="AO123" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -19154,25 +19765,30 @@
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE124" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE124" t="inlineStr">
+      <c r="AF124" t="inlineStr">
         <is>
           <t>200 S. Kenmore Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG124" t="inlineStr">
+      <c r="AH124" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM124" t="inlineStr">
+      <c r="AN124" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN124" t="inlineStr">
+      <c r="AO124" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -19301,25 +19917,30 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE125" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE125" t="inlineStr">
+      <c r="AF125" t="inlineStr">
         <is>
           <t>915 S. Kenmore Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG125" t="inlineStr">
+      <c r="AH125" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM125" t="inlineStr">
+      <c r="AN125" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN125" t="inlineStr">
+      <c r="AO125" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -19448,25 +20069,30 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE126" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE126" t="inlineStr">
+      <c r="AF126" t="inlineStr">
         <is>
           <t>530 Kingsley Drive, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG126" t="inlineStr">
+      <c r="AH126" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM126" t="inlineStr">
+      <c r="AN126" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN126" t="inlineStr">
+      <c r="AO126" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; property_name:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -19595,25 +20221,30 @@
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE127" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE127" t="inlineStr">
+      <c r="AF127" t="inlineStr">
         <is>
           <t>727 S. Mariposa Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG127" t="inlineStr">
+      <c r="AH127" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM127" t="inlineStr">
+      <c r="AN127" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN127" t="inlineStr">
+      <c r="AO127" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -19742,25 +20373,30 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE128" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE128" t="inlineStr">
+      <c r="AF128" t="inlineStr">
         <is>
           <t>750-752 S. Mariposa Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG128" t="inlineStr">
+      <c r="AH128" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM128" t="inlineStr">
+      <c r="AN128" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN128" t="inlineStr">
+      <c r="AO128" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -19889,25 +20525,30 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE129" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE129" t="inlineStr">
+      <c r="AF129" t="inlineStr">
         <is>
           <t>520 S. Mariposa Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG129" t="inlineStr">
+      <c r="AH129" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM129" t="inlineStr">
+      <c r="AN129" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN129" t="inlineStr">
+      <c r="AO129" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -20036,25 +20677,30 @@
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE130" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE130" t="inlineStr">
+      <c r="AF130" t="inlineStr">
         <is>
           <t>207 N. Oxford Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG130" t="inlineStr">
+      <c r="AH130" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM130" t="inlineStr">
+      <c r="AN130" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN130" t="inlineStr">
+      <c r="AO130" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -20183,25 +20829,30 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE131" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE131" t="inlineStr">
+      <c r="AF131" t="inlineStr">
         <is>
           <t>1057 S. Western Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG131" t="inlineStr">
+      <c r="AH131" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM131" t="inlineStr">
+      <c r="AN131" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN131" t="inlineStr">
+      <c r="AO131" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -20325,25 +20976,30 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE132" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE132" t="inlineStr">
+      <c r="AF132" t="inlineStr">
         <is>
           <t>1260 Grove St, Healdsburg, CA 95448</t>
         </is>
       </c>
-      <c r="AG132" t="inlineStr">
+      <c r="AH132" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM132" t="inlineStr">
+      <c r="AN132" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN132" t="inlineStr">
+      <c r="AO132" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -20467,20 +21123,25 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE133" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE133" t="inlineStr">
+      <c r="AF133" t="inlineStr">
         <is>
           <t>7524 S. Hoover St, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM133" t="inlineStr">
+      <c r="AN133" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN133" t="inlineStr">
+      <c r="AO133" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -20604,25 +21265,30 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE134" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE134" t="inlineStr">
+      <c r="AF134" t="inlineStr">
         <is>
           <t>10705 Avalon Blvd, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG134" t="inlineStr">
+      <c r="AH134" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM134" t="inlineStr">
+      <c r="AN134" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN134" t="inlineStr">
+      <c r="AO134" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -20751,25 +21417,30 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE135" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE135" t="inlineStr">
+      <c r="AF135" t="inlineStr">
         <is>
           <t>236 N. Berendo Street., Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG135" t="inlineStr">
+      <c r="AH135" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM135" t="inlineStr">
+      <c r="AN135" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN135" t="inlineStr">
+      <c r="AO135" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -20878,25 +21549,30 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE136" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE136" s="2" t="inlineStr">
+      <c r="AF136" s="2" t="inlineStr">
         <is>
           <t>5805 Charlotte Drive, San Jose, CA</t>
         </is>
       </c>
-      <c r="AF136" s="2" t="inlineStr">
+      <c r="AG136" s="2" t="inlineStr">
         <is>
           <t>December, 2025</t>
         </is>
       </c>
-      <c r="AM136" t="inlineStr">
+      <c r="AN136" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN136" t="inlineStr">
+      <c r="AO136" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -21020,25 +21696,30 @@
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE137" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE137" t="inlineStr">
+      <c r="AF137" t="inlineStr">
         <is>
           <t>18337 Kittridge St, Reseda, CA 91335</t>
         </is>
       </c>
-      <c r="AG137" t="inlineStr">
+      <c r="AH137" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM137" t="inlineStr">
+      <c r="AN137" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN137" t="inlineStr">
+      <c r="AO137" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -21177,25 +21858,30 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE138" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE138" t="inlineStr">
+      <c r="AF138" t="inlineStr">
         <is>
           <t>3765 Tamarack Ln, Santa Clara, CA 95051</t>
         </is>
       </c>
-      <c r="AG138" t="inlineStr">
+      <c r="AH138" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM138" t="inlineStr">
+      <c r="AN138" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN138" t="inlineStr">
+      <c r="AO138" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -21324,25 +22010,30 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE139" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE139" t="inlineStr">
+      <c r="AF139" t="inlineStr">
         <is>
           <t>5210 Monterey Rd, San Jose, CA 95111</t>
         </is>
       </c>
-      <c r="AG139" t="inlineStr">
+      <c r="AH139" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM139" t="inlineStr">
+      <c r="AN139" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN139" t="inlineStr">
+      <c r="AO139" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; nonprofit_partner:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -21471,25 +22162,30 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE140" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE140" t="inlineStr">
+      <c r="AF140" t="inlineStr">
         <is>
           <t>1180 Lochinvar Ave, Sunnyvale, CA 94087</t>
         </is>
       </c>
-      <c r="AG140" t="inlineStr">
+      <c r="AH140" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM140" t="inlineStr">
+      <c r="AN140" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN140" t="inlineStr">
+      <c r="AO140" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -21613,30 +22309,35 @@
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE141" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE141" t="inlineStr">
+      <c r="AF141" t="inlineStr">
         <is>
           <t>5669 N Fresno St, Fresno, CA 93710</t>
         </is>
       </c>
-      <c r="AG141" t="inlineStr">
+      <c r="AH141" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH141" t="inlineStr">
+      <c r="AI141" t="inlineStr">
         <is>
           <t>1984</t>
         </is>
       </c>
-      <c r="AM141" t="inlineStr">
+      <c r="AN141" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN141" t="inlineStr">
+      <c r="AO141" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -21760,20 +22461,25 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE142" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE142" t="inlineStr">
+      <c r="AF142" t="inlineStr">
         <is>
           <t>9033 Ramsgate Avenue, Westchester, CA</t>
         </is>
       </c>
-      <c r="AM142" t="inlineStr">
+      <c r="AN142" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN142" t="inlineStr">
+      <c r="AO142" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -21910,27 +22616,27 @@
           <t>16500</t>
         </is>
       </c>
-      <c r="AD143" s="2" t="inlineStr">
+      <c r="AE143" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE143" t="inlineStr">
+      <c r="AF143" t="inlineStr">
         <is>
           <t>805 71st Avenue, Oakland, CA</t>
         </is>
       </c>
-      <c r="AG143" t="inlineStr">
+      <c r="AH143" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM143" t="inlineStr">
+      <c r="AN143" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN143" t="inlineStr">
+      <c r="AO143" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -22054,25 +22760,30 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE144" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE144" t="inlineStr">
+      <c r="AF144" t="inlineStr">
         <is>
           <t>740 S. Western Avenue, Santa Maria, CA 93458</t>
         </is>
       </c>
-      <c r="AG144" t="inlineStr">
+      <c r="AH144" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM144" t="inlineStr">
+      <c r="AN144" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN144" t="inlineStr">
+      <c r="AO144" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; property_name:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -22189,27 +22900,27 @@
           <t>16500</t>
         </is>
       </c>
-      <c r="AD145" s="2" t="inlineStr">
+      <c r="AE145" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE145" t="inlineStr">
+      <c r="AF145" t="inlineStr">
         <is>
           <t>2130 N Marks Ave, Fresno, CA 93722</t>
         </is>
       </c>
-      <c r="AG145" t="inlineStr">
+      <c r="AH145" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM145" t="inlineStr">
+      <c r="AN145" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN145" t="inlineStr">
+      <c r="AO145" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -22333,25 +23044,30 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE146" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE146" t="inlineStr">
+      <c r="AF146" t="inlineStr">
         <is>
           <t>7655 S San Pedro St, Los Angeles, CA 90003</t>
         </is>
       </c>
-      <c r="AG146" t="inlineStr">
+      <c r="AH146" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM146" t="inlineStr">
+      <c r="AN146" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN146" t="inlineStr">
+      <c r="AO146" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -22495,25 +23211,30 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE147" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE147" t="inlineStr">
+      <c r="AF147" t="inlineStr">
         <is>
           <t>805 71st Avenue, Oakland, CA</t>
         </is>
       </c>
-      <c r="AG147" t="inlineStr">
+      <c r="AH147" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM147" t="inlineStr">
+      <c r="AN147" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN147" t="inlineStr">
+      <c r="AO147" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -22642,30 +23363,35 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE148" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE148" s="2" t="inlineStr">
+      <c r="AF148" s="2" t="inlineStr">
         <is>
           <t>2424 Wilshire</t>
         </is>
       </c>
-      <c r="AG148" t="inlineStr">
+      <c r="AH148" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH148" t="inlineStr">
+      <c r="AI148" t="inlineStr">
         <is>
           <t>1929</t>
         </is>
       </c>
-      <c r="AM148" t="inlineStr">
+      <c r="AN148" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN148" t="inlineStr">
+      <c r="AO148" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet; manual_status:collaborator-sheet</t>
         </is>
@@ -22794,25 +23520,30 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE149" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE149" t="inlineStr">
+      <c r="AF149" t="inlineStr">
         <is>
           <t>841 S Serrano Ave, Los Angeles, CA 90005</t>
         </is>
       </c>
-      <c r="AG149" t="inlineStr">
+      <c r="AH149" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM149" t="inlineStr">
+      <c r="AN149" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN149" t="inlineStr">
+      <c r="AO149" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -22941,25 +23672,30 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE150" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE150" t="inlineStr">
+      <c r="AF150" t="inlineStr">
         <is>
           <t>715 Normandie Ave, Los Angeles, CA 90005</t>
         </is>
       </c>
-      <c r="AG150" t="inlineStr">
+      <c r="AH150" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM150" t="inlineStr">
+      <c r="AN150" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN150" t="inlineStr">
+      <c r="AO150" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -23088,25 +23824,30 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE151" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE151" t="inlineStr">
+      <c r="AF151" t="inlineStr">
         <is>
           <t>682 Irolo Street, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG151" t="inlineStr">
+      <c r="AH151" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM151" t="inlineStr">
+      <c r="AN151" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN151" t="inlineStr">
+      <c r="AO151" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -23228,27 +23969,27 @@
           <t>22800</t>
         </is>
       </c>
-      <c r="AD152" s="2" t="inlineStr">
+      <c r="AE152" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE152" t="inlineStr">
+      <c r="AF152" t="inlineStr">
         <is>
           <t>5565 Ackerfield Avenue / 5700 Ackerfield Avenue, Long Beach, CA</t>
         </is>
       </c>
-      <c r="AG152" t="inlineStr">
+      <c r="AH152" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM152" t="inlineStr">
+      <c r="AN152" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN152" t="inlineStr">
+      <c r="AO152" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -23372,30 +24113,35 @@
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE153" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE153" t="inlineStr">
+      <c r="AF153" t="inlineStr">
         <is>
           <t>12100 226th St, Hawaiian Gardens, CA 90716</t>
         </is>
       </c>
-      <c r="AG153" t="inlineStr">
+      <c r="AH153" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH153" t="inlineStr">
+      <c r="AI153" t="inlineStr">
         <is>
           <t>1990</t>
         </is>
       </c>
-      <c r="AM153" t="inlineStr">
+      <c r="AN153" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN153" t="inlineStr">
+      <c r="AO153" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -23519,25 +24265,30 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE154" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE154" t="inlineStr">
+      <c r="AF154" t="inlineStr">
         <is>
           <t>2000 Crystal Springs Rd, San Bruno, CA 94066</t>
         </is>
       </c>
-      <c r="AG154" t="inlineStr">
+      <c r="AH154" t="inlineStr">
         <is>
           <t>NO/YES</t>
         </is>
       </c>
-      <c r="AM154" t="inlineStr">
+      <c r="AN154" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN154" t="inlineStr">
+      <c r="AO154" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -23661,30 +24412,35 @@
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE155" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE155" t="inlineStr">
+      <c r="AF155" t="inlineStr">
         <is>
           <t>1070 San Miguel Road, Concord, CA</t>
         </is>
       </c>
-      <c r="AG155" t="inlineStr">
+      <c r="AH155" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH155" t="inlineStr">
+      <c r="AI155" t="inlineStr">
         <is>
           <t>1974</t>
         </is>
       </c>
-      <c r="AM155" t="inlineStr">
+      <c r="AN155" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN155" t="inlineStr">
+      <c r="AO155" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -23808,30 +24564,35 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE156" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE156" t="inlineStr">
+      <c r="AF156" t="inlineStr">
         <is>
           <t>36000 Fremont Boulevard, Fremont, CA</t>
         </is>
       </c>
-      <c r="AG156" t="inlineStr">
+      <c r="AH156" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH156" t="inlineStr">
+      <c r="AI156" t="inlineStr">
         <is>
           <t>1969</t>
         </is>
       </c>
-      <c r="AM156" t="inlineStr">
+      <c r="AN156" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN156" t="inlineStr">
+      <c r="AO156" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -23928,17 +24689,22 @@
           <t>63825</t>
         </is>
       </c>
-      <c r="AE157" t="inlineStr">
+      <c r="AD157" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
         <is>
           <t>439 West El Norte Parkway / 1045 Morning View Drive, Escondido, CA</t>
         </is>
       </c>
-      <c r="AM157" t="inlineStr">
+      <c r="AN157" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN157" t="inlineStr">
+      <c r="AO157" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -24065,27 +24831,27 @@
           <t>5000</t>
         </is>
       </c>
-      <c r="AD158" s="2" t="inlineStr">
+      <c r="AE158" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE158" s="2" t="inlineStr">
+      <c r="AF158" s="2" t="inlineStr">
         <is>
           <t>452 square feet that were designed to support independent living and housing stability. Every unit will include a private bathroom, kitchen</t>
         </is>
       </c>
-      <c r="AG158" t="inlineStr">
+      <c r="AH158" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM158" t="inlineStr">
+      <c r="AN158" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN158" t="inlineStr">
+      <c r="AO158" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; total_units:collaborator-sheet</t>
         </is>
@@ -24209,20 +24975,25 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE159" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE159" t="inlineStr">
+      <c r="AF159" t="inlineStr">
         <is>
           <t>1141 N. Vermont Avenue, Los Angeles, CA 90029</t>
         </is>
       </c>
-      <c r="AM159" t="inlineStr">
+      <c r="AN159" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN159" t="inlineStr">
+      <c r="AO159" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -24351,25 +25122,30 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE160" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE160" t="inlineStr">
+      <c r="AF160" t="inlineStr">
         <is>
           <t>3048 W. 12th Street, CA 90006</t>
         </is>
       </c>
-      <c r="AG160" t="inlineStr">
+      <c r="AH160" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM160" t="inlineStr">
+      <c r="AN160" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN160" t="inlineStr">
+      <c r="AO160" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -24493,20 +25269,25 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE161" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE161" t="inlineStr">
+      <c r="AF161" t="inlineStr">
         <is>
           <t>2933 W. 8th Street, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM161" t="inlineStr">
+      <c r="AN161" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN161" t="inlineStr">
+      <c r="AO161" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -24620,20 +25401,25 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE162" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE162" t="inlineStr">
+      <c r="AF162" t="inlineStr">
         <is>
           <t>130 S. Alexandria Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM162" t="inlineStr">
+      <c r="AN162" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN162" t="inlineStr">
+      <c r="AO162" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -24757,20 +25543,25 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE163" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE163" t="inlineStr">
+      <c r="AF163" t="inlineStr">
         <is>
           <t>437 N. Ardmore Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM163" t="inlineStr">
+      <c r="AN163" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN163" t="inlineStr">
+      <c r="AO163" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -24894,20 +25685,25 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE164" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE164" t="inlineStr">
+      <c r="AF164" t="inlineStr">
         <is>
           <t>249 S. Ave 55, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM164" t="inlineStr">
+      <c r="AN164" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN164" t="inlineStr">
+      <c r="AO164" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -25031,20 +25827,25 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE165" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE165" t="inlineStr">
+      <c r="AF165" t="inlineStr">
         <is>
           <t>861 Fedora Street, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM165" t="inlineStr">
+      <c r="AN165" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN165" t="inlineStr">
+      <c r="AO165" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -25168,20 +25969,25 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE166" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE166" t="inlineStr">
+      <c r="AF166" t="inlineStr">
         <is>
           <t>516 N. Harvard Boulevard, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM166" t="inlineStr">
+      <c r="AN166" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN166" t="inlineStr">
+      <c r="AO166" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -25305,20 +26111,25 @@
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE167" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE167" t="inlineStr">
+      <c r="AF167" t="inlineStr">
         <is>
           <t>5200 Hollywood Boulevard, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM167" t="inlineStr">
+      <c r="AN167" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN167" t="inlineStr">
+      <c r="AO167" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -25442,20 +26253,25 @@
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE168" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE168" t="inlineStr">
+      <c r="AF168" t="inlineStr">
         <is>
           <t>200 S. Kenmore Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM168" t="inlineStr">
+      <c r="AN168" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN168" t="inlineStr">
+      <c r="AO168" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -25579,20 +26395,25 @@
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE169" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE169" t="inlineStr">
+      <c r="AF169" t="inlineStr">
         <is>
           <t>915 S. Kenmore Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM169" t="inlineStr">
+      <c r="AN169" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN169" t="inlineStr">
+      <c r="AO169" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -25716,20 +26537,25 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE170" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE170" t="inlineStr">
+      <c r="AF170" t="inlineStr">
         <is>
           <t>530 Kingsley Drive, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM170" t="inlineStr">
+      <c r="AN170" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN170" t="inlineStr">
+      <c r="AO170" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -25853,20 +26679,25 @@
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE171" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE171" t="inlineStr">
+      <c r="AF171" t="inlineStr">
         <is>
           <t>5406 Lexington Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM171" t="inlineStr">
+      <c r="AN171" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN171" t="inlineStr">
+      <c r="AO171" t="inlineStr">
         <is>
           <t>address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -25980,20 +26811,25 @@
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE172" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE172" t="inlineStr">
+      <c r="AF172" t="inlineStr">
         <is>
           <t>410 S. Manhattan Place / 509 S. Manhattan Place, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM172" t="inlineStr">
+      <c r="AN172" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN172" t="inlineStr">
+      <c r="AO172" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -26117,20 +26953,25 @@
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE173" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE173" t="inlineStr">
+      <c r="AF173" t="inlineStr">
         <is>
           <t>727 S. Mariposa Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM173" t="inlineStr">
+      <c r="AN173" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN173" t="inlineStr">
+      <c r="AO173" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -26254,20 +27095,25 @@
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE174" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE174" t="inlineStr">
+      <c r="AF174" t="inlineStr">
         <is>
           <t>750-752 S. Mariposa Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM174" t="inlineStr">
+      <c r="AN174" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN174" t="inlineStr">
+      <c r="AO174" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -26391,20 +27237,25 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE175" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE175" t="inlineStr">
+      <c r="AF175" t="inlineStr">
         <is>
           <t>520 S. Mariposa Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM175" t="inlineStr">
+      <c r="AN175" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN175" t="inlineStr">
+      <c r="AO175" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -26528,20 +27379,25 @@
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE176" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE176" t="inlineStr">
+      <c r="AF176" t="inlineStr">
         <is>
           <t>5635 Monte Vista Street, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM176" t="inlineStr">
+      <c r="AN176" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN176" t="inlineStr">
+      <c r="AO176" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -26665,20 +27521,25 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE177" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE177" t="inlineStr">
+      <c r="AF177" t="inlineStr">
         <is>
           <t>207 S. Oxford St, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM177" t="inlineStr">
+      <c r="AN177" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN177" t="inlineStr">
+      <c r="AO177" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -26802,20 +27663,25 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE178" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE178" t="inlineStr">
+      <c r="AF178" t="inlineStr">
         <is>
           <t>300 W. Avenue 37, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM178" t="inlineStr">
+      <c r="AN178" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN178" t="inlineStr">
+      <c r="AO178" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -26939,20 +27805,25 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE179" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE179" t="inlineStr">
+      <c r="AF179" t="inlineStr">
         <is>
           <t>1057 S. Western Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM179" t="inlineStr">
+      <c r="AN179" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN179" t="inlineStr">
+      <c r="AO179" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -27066,20 +27937,25 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE180" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE180" t="inlineStr">
+      <c r="AF180" t="inlineStr">
         <is>
           <t>132 S. Westmoreland Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM180" t="inlineStr">
+      <c r="AN180" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN180" t="inlineStr">
+      <c r="AO180" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -27208,20 +28084,25 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE181" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE181" t="inlineStr">
+      <c r="AF181" t="inlineStr">
         <is>
           <t>5565 &amp; 5575 Ackerfield Avenue, Long Beach, CA</t>
         </is>
       </c>
-      <c r="AM181" t="inlineStr">
+      <c r="AN181" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN181" t="inlineStr">
+      <c r="AO181" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -27350,20 +28231,25 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE182" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE182" t="inlineStr">
+      <c r="AF182" t="inlineStr">
         <is>
           <t>4256 Whittier Blvd Apartments, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM182" t="inlineStr">
+      <c r="AN182" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN182" t="inlineStr">
+      <c r="AO182" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -27487,25 +28373,30 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE183" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE183" t="inlineStr">
+      <c r="AF183" t="inlineStr">
         <is>
           <t>225 W. 25th St, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG183" t="inlineStr">
+      <c r="AH183" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM183" t="inlineStr">
+      <c r="AN183" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN183" t="inlineStr">
+      <c r="AO183" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -27629,25 +28520,30 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE184" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE184" t="inlineStr">
+      <c r="AF184" t="inlineStr">
         <is>
           <t>9422 Firth Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG184" t="inlineStr">
+      <c r="AH184" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM184" t="inlineStr">
+      <c r="AN184" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN184" t="inlineStr">
+      <c r="AO184" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -27771,25 +28667,30 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE185" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE185" t="inlineStr">
+      <c r="AF185" t="inlineStr">
         <is>
           <t>4008 Martin Luther King Boulevard, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AG185" t="inlineStr">
+      <c r="AH185" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM185" t="inlineStr">
+      <c r="AN185" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN185" t="inlineStr">
+      <c r="AO185" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -27913,25 +28814,30 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE186" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE186" t="inlineStr">
+      <c r="AF186" t="inlineStr">
         <is>
           <t>3200 W 5th St, Santa Ana, CA 92703</t>
         </is>
       </c>
-      <c r="AH186" t="inlineStr">
+      <c r="AI186" t="inlineStr">
         <is>
           <t>1987</t>
         </is>
       </c>
-      <c r="AM186" t="inlineStr">
+      <c r="AN186" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN186" t="inlineStr">
+      <c r="AO186" t="inlineStr">
         <is>
           <t>built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -28048,22 +28954,22 @@
           <t>20250</t>
         </is>
       </c>
-      <c r="AD187" s="2" t="inlineStr">
+      <c r="AE187" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE187" t="inlineStr">
+      <c r="AF187" t="inlineStr">
         <is>
           <t>11720 San Pablo Ave, El Cerrito, CA 94530</t>
         </is>
       </c>
-      <c r="AM187" t="inlineStr">
+      <c r="AN187" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN187" t="inlineStr">
+      <c r="AO187" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -28180,32 +29086,32 @@
           <t>33150</t>
         </is>
       </c>
-      <c r="AD188" s="2" t="inlineStr">
+      <c r="AE188" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE188" t="inlineStr">
+      <c r="AF188" t="inlineStr">
         <is>
           <t>201 S 4th St, San Jose, CA 95112</t>
         </is>
       </c>
-      <c r="AG188" t="inlineStr">
+      <c r="AH188" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH188" t="inlineStr">
+      <c r="AI188" t="inlineStr">
         <is>
           <t>1987</t>
         </is>
       </c>
-      <c r="AM188" t="inlineStr">
+      <c r="AN188" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN188" t="inlineStr">
+      <c r="AO188" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -28329,25 +29235,30 @@
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE189" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE189" t="inlineStr">
+      <c r="AF189" t="inlineStr">
         <is>
           <t>2311 Ivy Hill Way, San Ramon, CA 94582</t>
         </is>
       </c>
-      <c r="AG189" t="inlineStr">
+      <c r="AH189" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM189" t="inlineStr">
+      <c r="AN189" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN189" t="inlineStr">
+      <c r="AO189" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -28451,25 +29362,30 @@
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE190" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE190" s="2" t="inlineStr">
+      <c r="AF190" s="2" t="inlineStr">
         <is>
           <t>234 Escuela Avenue, Mountain View, CA</t>
         </is>
       </c>
-      <c r="AF190" s="2" t="inlineStr">
+      <c r="AG190" s="2" t="inlineStr">
         <is>
           <t>February, 2026</t>
         </is>
       </c>
-      <c r="AM190" t="inlineStr">
+      <c r="AN190" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN190" t="inlineStr">
+      <c r="AO190" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -28571,22 +29487,27 @@
           <t>29400</t>
         </is>
       </c>
-      <c r="AD191" t="inlineStr">
+      <c r="AD191" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE191" t="inlineStr">
         <is>
           <t>Loan / $100,000</t>
         </is>
       </c>
-      <c r="AE191" t="inlineStr">
+      <c r="AF191" t="inlineStr">
         <is>
           <t>707 W Santa Ana Street, Anaheim CA 92805</t>
         </is>
       </c>
-      <c r="AM191" t="inlineStr">
+      <c r="AN191" t="inlineStr">
         <is>
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="AN191" t="inlineStr">
+      <c r="AO191" t="inlineStr">
         <is>
           <t>*:collaborator-sheet</t>
         </is>
@@ -28688,22 +29609,27 @@
           <t>29400</t>
         </is>
       </c>
-      <c r="AD192" t="inlineStr">
+      <c r="AD192" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE192" t="inlineStr">
         <is>
           <t>Loan / $100,000</t>
         </is>
       </c>
-      <c r="AE192" t="inlineStr">
+      <c r="AF192" t="inlineStr">
         <is>
           <t>2549 E. Valley Parkway, Escondido, CA 92027</t>
         </is>
       </c>
-      <c r="AM192" t="inlineStr">
+      <c r="AN192" t="inlineStr">
         <is>
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="AN192" t="inlineStr">
+      <c r="AO192" t="inlineStr">
         <is>
           <t>*:collaborator-sheet</t>
         </is>
@@ -28827,25 +29753,30 @@
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE193" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE193" t="inlineStr">
+      <c r="AF193" t="inlineStr">
         <is>
           <t>3751 Delmas Terrace, Los Angeles, CA 90034</t>
         </is>
       </c>
-      <c r="AG193" t="inlineStr">
+      <c r="AH193" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM193" t="inlineStr">
+      <c r="AN193" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN193" t="inlineStr">
+      <c r="AO193" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -28969,25 +29900,30 @@
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE194" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE194" t="inlineStr">
+      <c r="AF194" t="inlineStr">
         <is>
           <t>1723 Corinth Ave, Los Angeles, CA 90025</t>
         </is>
       </c>
-      <c r="AG194" t="inlineStr">
+      <c r="AH194" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM194" t="inlineStr">
+      <c r="AN194" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN194" t="inlineStr">
+      <c r="AO194" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -29101,25 +30037,30 @@
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE195" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE195" t="inlineStr">
+      <c r="AF195" t="inlineStr">
         <is>
           <t>9750 Airport Blvd, Westchester, CA 90045</t>
         </is>
       </c>
-      <c r="AF195" s="2" t="inlineStr">
+      <c r="AG195" s="2" t="inlineStr">
         <is>
           <t>March, 2026</t>
         </is>
       </c>
-      <c r="AM195" t="inlineStr">
+      <c r="AN195" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN195" t="inlineStr">
+      <c r="AO195" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -29236,27 +30177,27 @@
           <t>15000</t>
         </is>
       </c>
-      <c r="AD196" s="2" t="inlineStr">
+      <c r="AE196" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE196" t="inlineStr">
+      <c r="AF196" t="inlineStr">
         <is>
           <t>12342 Osborne Pl, Pacoima, CA 91331</t>
         </is>
       </c>
-      <c r="AG196" t="inlineStr">
+      <c r="AH196" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM196" t="inlineStr">
+      <c r="AN196" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN196" t="inlineStr">
+      <c r="AO196" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -29378,27 +30319,27 @@
           <t>39600</t>
         </is>
       </c>
-      <c r="AD197" s="2" t="inlineStr">
+      <c r="AE197" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE197" t="inlineStr">
+      <c r="AF197" t="inlineStr">
         <is>
           <t>220 Humboldt Ct. Sunnyvale, CA</t>
         </is>
       </c>
-      <c r="AG197" t="inlineStr">
+      <c r="AH197" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM197" t="inlineStr">
+      <c r="AN197" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN197" t="inlineStr">
+      <c r="AO197" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -29522,20 +30463,25 @@
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE198" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE198" t="inlineStr">
+      <c r="AF198" t="inlineStr">
         <is>
           <t>6840 Baird Ave, Los Angeles, CA 91335</t>
         </is>
       </c>
-      <c r="AM198" t="inlineStr">
+      <c r="AN198" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN198" t="inlineStr">
+      <c r="AO198" t="inlineStr">
         <is>
           <t>city_cut:collaborator-sheet; address:manual-repo-edit</t>
         </is>
@@ -29652,22 +30598,22 @@
           <t>10500</t>
         </is>
       </c>
-      <c r="AD199" s="2" t="inlineStr">
+      <c r="AE199" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE199" t="inlineStr">
+      <c r="AF199" t="inlineStr">
         <is>
           <t>1408 W Jefferson Blvd, Los Angeles, CA 90007</t>
         </is>
       </c>
-      <c r="AM199" t="inlineStr">
+      <c r="AN199" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN199" t="inlineStr">
+      <c r="AO199" t="inlineStr">
         <is>
           <t>resolution:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -29796,20 +30742,25 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE200" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE200" t="inlineStr">
+      <c r="AF200" t="inlineStr">
         <is>
           <t>1311 W Battles Rd, Santa Maria, CA 93458</t>
         </is>
       </c>
-      <c r="AM200" t="inlineStr">
+      <c r="AN200" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN200" t="inlineStr">
+      <c r="AO200" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -29933,30 +30884,35 @@
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE201" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE201" t="inlineStr">
+      <c r="AF201" t="inlineStr">
         <is>
           <t>609 Frederick St, Santa Cruz, CA 95062</t>
         </is>
       </c>
-      <c r="AG201" t="inlineStr">
+      <c r="AH201" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH201" t="inlineStr">
+      <c r="AI201" t="inlineStr">
         <is>
           <t>1980</t>
         </is>
       </c>
-      <c r="AM201" t="inlineStr">
+      <c r="AN201" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN201" t="inlineStr">
+      <c r="AO201" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -30080,20 +31036,25 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE202" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE202" t="inlineStr">
+      <c r="AF202" t="inlineStr">
         <is>
           <t>4350 Galbrath Dr, Sacramento, CA 95842</t>
         </is>
       </c>
-      <c r="AM202" t="inlineStr">
+      <c r="AN202" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN202" t="inlineStr">
+      <c r="AO202" t="inlineStr">
         <is>
           <t>city:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -30217,25 +31178,30 @@
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE203" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE203" t="inlineStr">
+      <c r="AF203" t="inlineStr">
         <is>
           <t>6144 Hazelhurst Place, North Hollywood, CA 91606</t>
         </is>
       </c>
-      <c r="AG203" t="inlineStr">
+      <c r="AH203" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM203" t="inlineStr">
+      <c r="AN203" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN203" t="inlineStr">
+      <c r="AO203" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:manual-repo-edit</t>
         </is>
@@ -30349,25 +31315,30 @@
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE204" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE204" s="2" t="inlineStr">
+      <c r="AF204" s="2" t="inlineStr">
         <is>
           <t>11720 San Pablo Avenue, El Cerrito, CA</t>
         </is>
       </c>
-      <c r="AF204" s="2" t="inlineStr">
+      <c r="AG204" s="2" t="inlineStr">
         <is>
           <t>June, 2026</t>
         </is>
       </c>
-      <c r="AM204" t="inlineStr">
+      <c r="AN204" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN204" t="inlineStr">
+      <c r="AO204" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -30496,20 +31467,25 @@
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE205" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE205" t="inlineStr">
+      <c r="AF205" t="inlineStr">
         <is>
           <t>1845 N Broadway, Escondido, CA 92026</t>
         </is>
       </c>
-      <c r="AM205" t="inlineStr">
+      <c r="AN205" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN205" t="inlineStr">
+      <c r="AO205" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; county:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -30623,25 +31599,30 @@
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE206" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE206" s="2" t="inlineStr">
+      <c r="AF206" s="2" t="inlineStr">
         <is>
           <t>2625 Cullen Street, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AF206" s="2" t="inlineStr">
+      <c r="AG206" s="2" t="inlineStr">
         <is>
           <t>April, 2026</t>
         </is>
       </c>
-      <c r="AM206" t="inlineStr">
+      <c r="AN206" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN206" t="inlineStr">
+      <c r="AO206" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -30750,25 +31731,30 @@
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE207" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE207" t="inlineStr">
+      <c r="AF207" t="inlineStr">
         <is>
           <t>2481 Sawtelle Blvd, Los Angeles, CA 90064</t>
         </is>
       </c>
-      <c r="AF207" s="2" t="inlineStr">
+      <c r="AG207" s="2" t="inlineStr">
         <is>
           <t>April, 2026</t>
         </is>
       </c>
-      <c r="AM207" t="inlineStr">
+      <c r="AN207" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN207" t="inlineStr">
+      <c r="AO207" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -30892,20 +31878,25 @@
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE208" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE208" t="inlineStr">
+      <c r="AF208" t="inlineStr">
         <is>
           <t>6790 Embarcadero Ln, Carlsbad, CA 92011</t>
         </is>
       </c>
-      <c r="AM208" t="inlineStr">
+      <c r="AN208" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN208" t="inlineStr">
+      <c r="AO208" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; address:collaborator-sheet; term_years:collaborator-sheet</t>
         </is>
@@ -31024,20 +32015,25 @@
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE209" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE209" s="2" t="inlineStr">
+      <c r="AF209" s="2" t="inlineStr">
         <is>
           <t>6633 Valley Hi</t>
         </is>
       </c>
-      <c r="AM209" t="inlineStr">
+      <c r="AN209" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN209" t="inlineStr">
+      <c r="AO209" t="inlineStr">
         <is>
           <t>term_years:collaborator-sheet</t>
         </is>
@@ -31151,25 +32147,30 @@
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE210" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE210" t="inlineStr">
+      <c r="AF210" t="inlineStr">
         <is>
           <t>6530 Independence Ave, Canoga Park, CA 91303</t>
         </is>
       </c>
-      <c r="AF210" s="2" t="inlineStr">
+      <c r="AG210" s="2" t="inlineStr">
         <is>
           <t>August, 2026</t>
         </is>
       </c>
-      <c r="AM210" t="inlineStr">
+      <c r="AN210" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN210" t="inlineStr">
+      <c r="AO210" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -31283,30 +32284,35 @@
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE211" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE211" s="2" t="inlineStr">
+      <c r="AF211" s="2" t="inlineStr">
         <is>
           <t>2075 West Jefferson Blvd., Los Angeles</t>
         </is>
       </c>
-      <c r="AF211" s="2" t="inlineStr">
+      <c r="AG211" s="2" t="inlineStr">
         <is>
           <t>August, 2026</t>
         </is>
       </c>
-      <c r="AG211" t="inlineStr">
+      <c r="AH211" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM211" t="inlineStr">
+      <c r="AN211" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN211" t="inlineStr">
+      <c r="AO211" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -31420,25 +32426,30 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE212" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE212" s="2" t="inlineStr">
+      <c r="AF212" s="2" t="inlineStr">
         <is>
           <t>5416 Jackson Street, North Highlands</t>
         </is>
       </c>
-      <c r="AF212" s="2" t="inlineStr">
+      <c r="AG212" s="2" t="inlineStr">
         <is>
           <t>September, 2026</t>
         </is>
       </c>
-      <c r="AM212" t="inlineStr">
+      <c r="AN212" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN212" t="inlineStr">
+      <c r="AO212" t="inlineStr">
         <is>
           <t>city:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -31552,30 +32563,35 @@
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE213" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE213" s="2" t="inlineStr">
+      <c r="AF213" s="2" t="inlineStr">
         <is>
           <t>444 North Amelia Avenue, San Dimas</t>
         </is>
       </c>
-      <c r="AF213" s="2" t="inlineStr">
+      <c r="AG213" s="2" t="inlineStr">
         <is>
           <t>September, 2026</t>
         </is>
       </c>
-      <c r="AG213" t="inlineStr">
+      <c r="AH213" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM213" t="inlineStr">
+      <c r="AN213" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN213" t="inlineStr">
+      <c r="AO213" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -31694,35 +32710,40 @@
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE214" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE214" s="2" t="inlineStr">
+      <c r="AF214" s="2" t="inlineStr">
         <is>
           <t>511 N. Hoover Street, Los Angeles</t>
         </is>
       </c>
-      <c r="AF214" s="2" t="inlineStr">
+      <c r="AG214" s="2" t="inlineStr">
         <is>
           <t>July, 2026</t>
         </is>
       </c>
-      <c r="AG214" t="inlineStr">
+      <c r="AH214" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AK214" t="inlineStr">
+      <c r="AL214" t="inlineStr">
         <is>
           <t>https://cscda.org/wp-content/uploads/2026/06/CSCDA-Agenda-Packet-7.2.26.pdf</t>
         </is>
       </c>
-      <c r="AM214" t="inlineStr">
+      <c r="AN214" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN214" t="inlineStr">
+      <c r="AO214" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; link:collaborator-sheet; resolution:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -31846,25 +32867,30 @@
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE215" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE215" t="inlineStr">
+      <c r="AF215" t="inlineStr">
         <is>
           <t>5035 Guava Ave, La Mesa, CA 91942</t>
         </is>
       </c>
-      <c r="AG215" t="inlineStr">
+      <c r="AH215" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM215" t="inlineStr">
+      <c r="AN215" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN215" t="inlineStr">
+      <c r="AO215" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -31988,25 +33014,30 @@
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE216" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE216" t="inlineStr">
+      <c r="AF216" t="inlineStr">
         <is>
           <t>217 N. Park View Street, Los Angeles, CA 90026</t>
         </is>
       </c>
-      <c r="AG216" t="inlineStr">
+      <c r="AH216" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM216" t="inlineStr">
+      <c r="AN216" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN216" t="inlineStr">
+      <c r="AO216" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:manual-repo-edit</t>
         </is>
@@ -32120,25 +33151,30 @@
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE217" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE217" t="inlineStr">
+      <c r="AF217" t="inlineStr">
         <is>
           <t>1408 W Jefferson Blvd Los Angeles, California 90007</t>
         </is>
       </c>
-      <c r="AG217" t="inlineStr">
+      <c r="AH217" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM217" t="inlineStr">
+      <c r="AN217" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN217" t="inlineStr">
+      <c r="AO217" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -32262,25 +33298,30 @@
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE218" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE218" t="inlineStr">
+      <c r="AF218" t="inlineStr">
         <is>
           <t>603 S Mariposa AveLos Angeles, CA 90005</t>
         </is>
       </c>
-      <c r="AG218" t="inlineStr">
+      <c r="AH218" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM218" t="inlineStr">
+      <c r="AN218" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN218" t="inlineStr">
+      <c r="AO218" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -32394,25 +33435,30 @@
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE219" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE219" t="inlineStr">
+      <c r="AF219" t="inlineStr">
         <is>
           <t>236 N Berendo St, Los Angeles, CA 90004</t>
         </is>
       </c>
-      <c r="AG219" t="inlineStr">
+      <c r="AH219" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM219" t="inlineStr">
+      <c r="AN219" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN219" t="inlineStr">
+      <c r="AO219" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
         </is>
@@ -32536,25 +33582,30 @@
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE220" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE220" t="inlineStr">
+      <c r="AF220" t="inlineStr">
         <is>
           <t>6219 Banner Avenue, Los Angeles, CA 90038</t>
         </is>
       </c>
-      <c r="AG220" t="inlineStr">
+      <c r="AH220" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM220" t="inlineStr">
+      <c r="AN220" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN220" t="inlineStr">
+      <c r="AO220" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -32668,25 +33719,30 @@
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE221" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE221" s="2" t="inlineStr">
+      <c r="AF221" s="2" t="inlineStr">
         <is>
           <t>16077 Ashland Avenue, San Lorenzo</t>
         </is>
       </c>
-      <c r="AF221" s="2" t="inlineStr">
+      <c r="AG221" s="2" t="inlineStr">
         <is>
           <t>July, 2026</t>
         </is>
       </c>
-      <c r="AM221" t="inlineStr">
+      <c r="AN221" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN221" t="inlineStr">
+      <c r="AO221" t="inlineStr">
         <is>
           <t>city:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -32738,17 +33794,17 @@
           <t>15</t>
         </is>
       </c>
-      <c r="AE222" t="inlineStr">
+      <c r="AF222" t="inlineStr">
         <is>
           <t>2121 WOOD ST OAKLAND 94607</t>
         </is>
       </c>
-      <c r="AM222" t="inlineStr">
+      <c r="AN222" t="inlineStr">
         <is>
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="AN222" t="inlineStr">
+      <c r="AO222" t="inlineStr">
         <is>
           <t>*:collaborator-sheet</t>
         </is>
@@ -32857,30 +33913,35 @@
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE223" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE223" s="2" t="inlineStr">
+      <c r="AF223" s="2" t="inlineStr">
         <is>
           <t>1454 West Florence Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AF223" s="2" t="inlineStr">
+      <c r="AG223" s="2" t="inlineStr">
         <is>
           <t>June, 2026</t>
         </is>
       </c>
-      <c r="AG223" t="inlineStr">
+      <c r="AH223" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM223" t="inlineStr">
+      <c r="AN223" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN223" t="inlineStr">
+      <c r="AO223" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -32994,20 +34055,25 @@
       </c>
       <c r="AD224" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE224" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE224" t="inlineStr">
+      <c r="AF224" t="inlineStr">
         <is>
           <t>2780 N Texas St, Fairfield, CA 94533</t>
         </is>
       </c>
-      <c r="AM224" t="inlineStr">
+      <c r="AN224" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN224" t="inlineStr">
+      <c r="AO224" t="inlineStr">
         <is>
           <t>address:collaborator-sheet; term_years:collaborator-sheet</t>
         </is>
@@ -33121,25 +34187,30 @@
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE225" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE225" s="2" t="inlineStr">
+      <c r="AF225" s="2" t="inlineStr">
         <is>
           <t>142 Fig Tree Lane, Martinez, CA</t>
         </is>
       </c>
-      <c r="AF225" s="2" t="inlineStr">
+      <c r="AG225" s="2" t="inlineStr">
         <is>
           <t>July, 2026</t>
         </is>
       </c>
-      <c r="AM225" t="inlineStr">
+      <c r="AN225" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN225" t="inlineStr">
+      <c r="AO225" t="inlineStr">
         <is>
           <t>manual_status:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; term_years:collaborator-sheet</t>
         </is>
@@ -33253,20 +34324,25 @@
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE226" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE226" t="inlineStr">
+      <c r="AF226" t="inlineStr">
         <is>
           <t>1 Shoal Ct, Sacramento, CA 95831</t>
         </is>
       </c>
-      <c r="AM226" t="inlineStr">
+      <c r="AN226" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN226" t="inlineStr">
+      <c r="AO226" t="inlineStr">
         <is>
           <t>address:collaborator-sheet</t>
         </is>
@@ -33375,25 +34451,30 @@
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE227" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE227" s="2" t="inlineStr">
+      <c r="AF227" s="2" t="inlineStr">
         <is>
           <t>225 West Colden Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AF227" s="2" t="inlineStr">
+      <c r="AG227" s="2" t="inlineStr">
         <is>
           <t>June, 2026</t>
         </is>
       </c>
-      <c r="AM227" t="inlineStr">
+      <c r="AN227" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN227" t="inlineStr">
+      <c r="AO227" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet; term_years:collaborator-sheet</t>
         </is>
@@ -33507,25 +34588,30 @@
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE228" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE228" s="2" t="inlineStr">
+      <c r="AF228" s="2" t="inlineStr">
         <is>
           <t>220 47th Street, San Diego</t>
         </is>
       </c>
-      <c r="AF228" s="2" t="inlineStr">
+      <c r="AG228" s="2" t="inlineStr">
         <is>
           <t>September, 2026</t>
         </is>
       </c>
-      <c r="AM228" t="inlineStr">
+      <c r="AN228" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN228" t="inlineStr">
+      <c r="AO228" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -33634,30 +34720,35 @@
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE229" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE229" t="inlineStr">
+      <c r="AF229" t="inlineStr">
         <is>
           <t>11821 Foothill Blvd, Lake View Terrace, CA 91342</t>
         </is>
       </c>
-      <c r="AF229" s="2" t="inlineStr">
+      <c r="AG229" s="2" t="inlineStr">
         <is>
           <t>June, 2026</t>
         </is>
       </c>
-      <c r="AG229" t="inlineStr">
+      <c r="AH229" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AM229" t="inlineStr">
+      <c r="AN229" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN229" t="inlineStr">
+      <c r="AO229" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
@@ -33771,25 +34862,30 @@
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE230" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE230" s="2" t="inlineStr">
+      <c r="AF230" s="2" t="inlineStr">
         <is>
           <t>160 S. Virgil Avenue, Los Angeles</t>
         </is>
       </c>
-      <c r="AF230" s="2" t="inlineStr">
+      <c r="AG230" s="2" t="inlineStr">
         <is>
           <t>September, 2026</t>
         </is>
       </c>
-      <c r="AM230" t="inlineStr">
+      <c r="AN230" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN230" t="inlineStr">
+      <c r="AO230" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -33898,35 +34994,40 @@
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE231" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE231" s="2" t="inlineStr">
+      <c r="AF231" s="2" t="inlineStr">
         <is>
           <t>12091 Bayport Street, Garden Grove, CA</t>
         </is>
       </c>
-      <c r="AF231" s="2" t="inlineStr">
+      <c r="AG231" s="2" t="inlineStr">
         <is>
           <t>July, 2026</t>
         </is>
       </c>
-      <c r="AG231" t="inlineStr">
+      <c r="AH231" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AK231" t="inlineStr">
+      <c r="AL231" t="inlineStr">
         <is>
           <t>https://vistria.com/vistria-real-estate-acquires-orange-county-apartment-community/</t>
         </is>
       </c>
-      <c r="AM231" t="inlineStr">
+      <c r="AN231" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN231" t="inlineStr">
+      <c r="AO231" t="inlineStr">
         <is>
           <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; link:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -34040,25 +35141,30 @@
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE232" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE232" s="2" t="inlineStr">
+      <c r="AF232" s="2" t="inlineStr">
         <is>
           <t>926 S. Kingsley Drive, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AF232" s="2" t="inlineStr">
+      <c r="AG232" s="2" t="inlineStr">
         <is>
           <t>September, 2026</t>
         </is>
       </c>
-      <c r="AM232" t="inlineStr">
+      <c r="AN232" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN232" t="inlineStr">
+      <c r="AO232" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet; term_years:collaborator-sheet</t>
         </is>
@@ -34172,25 +35278,30 @@
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE233" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE233" s="2" t="inlineStr">
+      <c r="AF233" s="2" t="inlineStr">
         <is>
           <t>939 S. Kingsley Drive, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AF233" s="2" t="inlineStr">
+      <c r="AG233" s="2" t="inlineStr">
         <is>
           <t>September, 2026</t>
         </is>
       </c>
-      <c r="AM233" t="inlineStr">
+      <c r="AN233" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN233" t="inlineStr">
+      <c r="AO233" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -34304,25 +35415,30 @@
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE234" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE234" s="2" t="inlineStr">
+      <c r="AF234" s="2" t="inlineStr">
         <is>
           <t>3950 W. Ingraham Street, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AF234" s="2" t="inlineStr">
+      <c r="AG234" s="2" t="inlineStr">
         <is>
           <t>September, 2026</t>
         </is>
       </c>
-      <c r="AM234" t="inlineStr">
+      <c r="AN234" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN234" t="inlineStr">
+      <c r="AO234" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -34436,30 +35552,35 @@
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE235" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE235" s="2" t="inlineStr">
+      <c r="AF235" s="2" t="inlineStr">
         <is>
           <t>6985 S. Centinela Avenue, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AF235" s="2" t="inlineStr">
+      <c r="AG235" s="2" t="inlineStr">
         <is>
           <t>September, 2026</t>
         </is>
       </c>
-      <c r="AG235" t="inlineStr">
+      <c r="AH235" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AM235" t="inlineStr">
+      <c r="AN235" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN235" t="inlineStr">
+      <c r="AO235" t="inlineStr">
         <is>
           <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -34573,25 +35694,30 @@
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE236" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE236" s="2" t="inlineStr">
+      <c r="AF236" s="2" t="inlineStr">
         <is>
           <t>1178 N. Edgemont Street, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AF236" s="2" t="inlineStr">
+      <c r="AG236" s="2" t="inlineStr">
         <is>
           <t>August, 2026</t>
         </is>
       </c>
-      <c r="AM236" t="inlineStr">
+      <c r="AN236" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN236" t="inlineStr">
+      <c r="AO236" t="inlineStr">
         <is>
           <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
@@ -34688,32 +35814,37 @@
           <t>25050</t>
         </is>
       </c>
-      <c r="AD237" t="inlineStr">
+      <c r="AD237" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE237" t="inlineStr">
         <is>
           <t>Loan / $100,000</t>
         </is>
       </c>
-      <c r="AE237" t="inlineStr">
+      <c r="AF237" t="inlineStr">
         <is>
           <t>900 E Stanley Blvd, Livermore, CA 94550</t>
         </is>
       </c>
-      <c r="AG237" t="inlineStr">
+      <c r="AH237" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="AH237" t="inlineStr">
+      <c r="AI237" t="inlineStr">
         <is>
           <t>1988</t>
         </is>
       </c>
-      <c r="AM237" t="inlineStr">
+      <c r="AN237" t="inlineStr">
         <is>
           <t>collaborator-sheet</t>
         </is>
       </c>
-      <c r="AN237" t="inlineStr">
+      <c r="AO237" t="inlineStr">
         <is>
           <t>*:collaborator-sheet</t>
         </is>
@@ -34805,12 +35936,12 @@
           <t>CMFA-Minutes-07-14-23.pdf</t>
         </is>
       </c>
-      <c r="AD238" s="2" t="inlineStr">
+      <c r="AE238" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM238" t="inlineStr">
+      <c r="AN238" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -34902,12 +36033,12 @@
           <t>CMFA-Minutes-07-14-23.pdf</t>
         </is>
       </c>
-      <c r="AD239" s="2" t="inlineStr">
+      <c r="AE239" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM239" t="inlineStr">
+      <c r="AN239" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -35051,10 +36182,15 @@
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE240" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM240" t="inlineStr">
+      <c r="AN240" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -35146,12 +36282,12 @@
           <t>2-CMFA-Minutes-02-2-24.pdf</t>
         </is>
       </c>
-      <c r="AD241" s="2" t="inlineStr">
+      <c r="AE241" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM241" t="inlineStr">
+      <c r="AN241" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -35288,17 +36424,17 @@
           <t>16650</t>
         </is>
       </c>
-      <c r="AD242" s="2" t="inlineStr">
+      <c r="AE242" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE242" s="2" t="inlineStr">
+      <c r="AF242" s="2" t="inlineStr">
         <is>
           <t>45 units restricted and 66 market-rate units, including</t>
         </is>
       </c>
-      <c r="AM242" t="inlineStr">
+      <c r="AN242" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -35427,10 +36563,15 @@
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE243" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM243" t="inlineStr">
+      <c r="AN243" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -35567,12 +36708,12 @@
           <t>7950</t>
         </is>
       </c>
-      <c r="AD244" s="2" t="inlineStr">
+      <c r="AE244" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM244" t="inlineStr">
+      <c r="AN244" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -35701,10 +36842,15 @@
       </c>
       <c r="AD245" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE245" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM245" t="inlineStr">
+      <c r="AN245" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -35841,17 +36987,17 @@
           <t>73200</t>
         </is>
       </c>
-      <c r="AD246" s="2" t="inlineStr">
+      <c r="AE246" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE246" s="2" t="inlineStr">
+      <c r="AF246" s="2" t="inlineStr">
         <is>
           <t>5 levels of Type III construction, consisting of</t>
         </is>
       </c>
-      <c r="AM246" t="inlineStr">
+      <c r="AN246" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -35995,15 +37141,20 @@
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE247" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE247" s="2" t="inlineStr">
+      <c r="AF247" s="2" t="inlineStr">
         <is>
           <t>5 and State Highway 55 and is close to the Downtown Santa Ana and Irvine Business complexes, which are two large employment hubs in the area</t>
         </is>
       </c>
-      <c r="AM247" t="inlineStr">
+      <c r="AN247" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -36115,12 +37266,12 @@
           <t>7950</t>
         </is>
       </c>
-      <c r="AD248" s="2" t="inlineStr">
+      <c r="AE248" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM248" t="inlineStr">
+      <c r="AN248" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -36227,12 +37378,12 @@
           <t>5700</t>
         </is>
       </c>
-      <c r="AD249" s="2" t="inlineStr">
+      <c r="AE249" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM249" t="inlineStr">
+      <c r="AN249" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -36354,12 +37505,12 @@
           <t>5000</t>
         </is>
       </c>
-      <c r="AD250" s="2" t="inlineStr">
+      <c r="AE250" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM250" t="inlineStr">
+      <c r="AN250" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -36466,17 +37617,17 @@
           <t>25650</t>
         </is>
       </c>
-      <c r="AD251" s="2" t="inlineStr">
+      <c r="AE251" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE251" s="2" t="inlineStr">
+      <c r="AF251" s="2" t="inlineStr">
         <is>
           <t>700 square feet. Amenities at the property include a rooftop sky deck with barbeque area and fireplace, fully equipped fitness center</t>
         </is>
       </c>
-      <c r="AM251" t="inlineStr">
+      <c r="AN251" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -36588,17 +37739,17 @@
           <t>7800</t>
         </is>
       </c>
-      <c r="AD252" s="2" t="inlineStr">
+      <c r="AE252" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE252" s="2" t="inlineStr">
+      <c r="AF252" s="2" t="inlineStr">
         <is>
           <t>1301-1307 N. Cherokee Avenue in</t>
         </is>
       </c>
-      <c r="AM252" t="inlineStr">
+      <c r="AN252" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -36737,10 +37888,15 @@
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE253" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM253" t="inlineStr">
+      <c r="AN253" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -36852,12 +38008,12 @@
           <t>23400</t>
         </is>
       </c>
-      <c r="AD254" s="2" t="inlineStr">
+      <c r="AE254" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM254" t="inlineStr">
+      <c r="AN254" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -36969,12 +38125,12 @@
           <t>12600</t>
         </is>
       </c>
-      <c r="AD255" s="2" t="inlineStr">
+      <c r="AE255" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM255" t="inlineStr">
+      <c r="AN255" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -37086,17 +38242,17 @@
           <t>6300</t>
         </is>
       </c>
-      <c r="AD256" s="2" t="inlineStr">
+      <c r="AE256" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE256" s="2" t="inlineStr">
+      <c r="AF256" s="2" t="inlineStr">
         <is>
           <t>501 S. Burlington Avenue Apartments project is a three-story,</t>
         </is>
       </c>
-      <c r="AM256" t="inlineStr">
+      <c r="AN256" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -37208,17 +38364,17 @@
           <t>7200</t>
         </is>
       </c>
-      <c r="AD257" s="2" t="inlineStr">
+      <c r="AE257" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE257" s="2" t="inlineStr">
+      <c r="AF257" s="2" t="inlineStr">
         <is>
           <t>625 S. Burlington Avenue Apartments project is a four-story,</t>
         </is>
       </c>
-      <c r="AM257" t="inlineStr">
+      <c r="AN257" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -37345,12 +38501,12 @@
           <t>28200</t>
         </is>
       </c>
-      <c r="AD258" s="2" t="inlineStr">
+      <c r="AE258" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM258" t="inlineStr">
+      <c r="AN258" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -37477,12 +38633,12 @@
           <t>37500</t>
         </is>
       </c>
-      <c r="AD259" s="2" t="inlineStr">
+      <c r="AE259" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM259" t="inlineStr">
+      <c r="AN259" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -37601,15 +38757,20 @@
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE260" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE260" s="2" t="inlineStr">
+      <c r="AF260" s="2" t="inlineStr">
         <is>
           <t>2022 and are sized to offset the electricity needs of all common areas. The grant for this project will create 99 units of affordable housing in</t>
         </is>
       </c>
-      <c r="AM260" t="inlineStr">
+      <c r="AN260" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -37736,12 +38897,12 @@
           <t>24000</t>
         </is>
       </c>
-      <c r="AD261" s="2" t="inlineStr">
+      <c r="AE261" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM261" t="inlineStr">
+      <c r="AN261" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -37868,12 +39029,12 @@
           <t>28950</t>
         </is>
       </c>
-      <c r="AD262" s="2" t="inlineStr">
+      <c r="AE262" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM262" t="inlineStr">
+      <c r="AN262" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -38000,12 +39161,12 @@
           <t>22200</t>
         </is>
       </c>
-      <c r="AD263" s="2" t="inlineStr">
+      <c r="AE263" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM263" t="inlineStr">
+      <c r="AN263" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -38117,12 +39278,12 @@
           <t>7200</t>
         </is>
       </c>
-      <c r="AD264" s="2" t="inlineStr">
+      <c r="AE264" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM264" t="inlineStr">
+      <c r="AN264" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -38234,12 +39395,12 @@
           <t>14400</t>
         </is>
       </c>
-      <c r="AD265" s="2" t="inlineStr">
+      <c r="AE265" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM265" t="inlineStr">
+      <c r="AN265" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -38351,12 +39512,12 @@
           <t>37500</t>
         </is>
       </c>
-      <c r="AD266" s="2" t="inlineStr">
+      <c r="AE266" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM266" t="inlineStr">
+      <c r="AN266" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -38485,10 +39646,15 @@
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE267" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM267" t="inlineStr">
+      <c r="AN267" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -38617,10 +39783,15 @@
       </c>
       <c r="AD268" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE268" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM268" t="inlineStr">
+      <c r="AN268" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -38732,12 +39903,12 @@
           <t>92250</t>
         </is>
       </c>
-      <c r="AD269" s="2" t="inlineStr">
+      <c r="AE269" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM269" t="inlineStr">
+      <c r="AN269" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -38834,17 +40005,17 @@
           <t>34350.0</t>
         </is>
       </c>
-      <c r="AD270" s="2" t="inlineStr">
+      <c r="AE270" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE270" s="2" t="inlineStr">
+      <c r="AF270" s="2" t="inlineStr">
         <is>
           <t>229 of which are designated as affordable housing for residents earning at or below 80% of</t>
         </is>
       </c>
-      <c r="AM270" t="inlineStr">
+      <c r="AN270" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -38986,12 +40157,12 @@
           <t>5000</t>
         </is>
       </c>
-      <c r="AD271" s="2" t="inlineStr">
+      <c r="AE271" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM271" t="inlineStr">
+      <c r="AN271" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -39133,12 +40304,12 @@
           <t>103050</t>
         </is>
       </c>
-      <c r="AD272" s="2" t="inlineStr">
+      <c r="AE272" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM272" t="inlineStr">
+      <c r="AN272" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -39250,17 +40421,17 @@
           <t>10350</t>
         </is>
       </c>
-      <c r="AD273" s="2" t="inlineStr">
+      <c r="AE273" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE273" s="2" t="inlineStr">
+      <c r="AF273" s="2" t="inlineStr">
         <is>
           <t>17188 Chatsworth St. Apartments, is a new construction</t>
         </is>
       </c>
-      <c r="AM273" t="inlineStr">
+      <c r="AN273" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -39409,10 +40580,15 @@
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE274" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM274" t="inlineStr">
+      <c r="AN274" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -39561,10 +40737,15 @@
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE275" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM275" t="inlineStr">
+      <c r="AN275" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -39676,17 +40857,17 @@
           <t>45300</t>
         </is>
       </c>
-      <c r="AD276" s="2" t="inlineStr">
+      <c r="AE276" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE276" s="2" t="inlineStr">
+      <c r="AF276" s="2" t="inlineStr">
         <is>
           <t>160 S Virgil Ave</t>
         </is>
       </c>
-      <c r="AM276" t="inlineStr">
+      <c r="AN276" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -39798,17 +40979,17 @@
           <t>7800</t>
         </is>
       </c>
-      <c r="AD277" s="2" t="inlineStr">
+      <c r="AE277" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE277" s="2" t="inlineStr">
+      <c r="AF277" s="2" t="inlineStr">
         <is>
           <t>236 Berendo Street Apartments project is a proposed new construction of a 5-story,</t>
         </is>
       </c>
-      <c r="AM277" t="inlineStr">
+      <c r="AN277" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -39930,17 +41111,17 @@
           <t>14850</t>
         </is>
       </c>
-      <c r="AD278" s="2" t="inlineStr">
+      <c r="AE278" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE278" s="2" t="inlineStr">
+      <c r="AF278" s="2" t="inlineStr">
         <is>
           <t>2022 and are sized to offset the electricity needs of all common areas. The grant for this project will create 99 units of affordable housing in</t>
         </is>
       </c>
-      <c r="AM278" t="inlineStr">
+      <c r="AN278" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -40052,12 +41233,12 @@
           <t>31200</t>
         </is>
       </c>
-      <c r="AD279" s="2" t="inlineStr">
+      <c r="AE279" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM279" t="inlineStr">
+      <c r="AN279" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -40169,12 +41350,12 @@
           <t>22200</t>
         </is>
       </c>
-      <c r="AD280" s="2" t="inlineStr">
+      <c r="AE280" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM280" t="inlineStr">
+      <c r="AN280" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -40286,12 +41467,12 @@
           <t>12600</t>
         </is>
       </c>
-      <c r="AD281" s="2" t="inlineStr">
+      <c r="AE281" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM281" t="inlineStr">
+      <c r="AN281" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -40408,17 +41589,17 @@
           <t>14850</t>
         </is>
       </c>
-      <c r="AD282" s="2" t="inlineStr">
+      <c r="AE282" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE282" s="2" t="inlineStr">
+      <c r="AF282" s="2" t="inlineStr">
         <is>
           <t>2022 and are sized to offset the electricity needs of all common areas. The grant for this project will create 99 units of affordable housing in</t>
         </is>
       </c>
-      <c r="AM282" t="inlineStr">
+      <c r="AN282" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -40540,17 +41721,17 @@
           <t>5550</t>
         </is>
       </c>
-      <c r="AD283" s="2" t="inlineStr">
+      <c r="AE283" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE283" s="2" t="inlineStr">
+      <c r="AF283" s="2" t="inlineStr">
         <is>
           <t>1 mile north of the historic Healdsburg Plaza</t>
         </is>
       </c>
-      <c r="AM283" t="inlineStr">
+      <c r="AN283" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -40662,12 +41843,12 @@
           <t>13500</t>
         </is>
       </c>
-      <c r="AD284" s="2" t="inlineStr">
+      <c r="AE284" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM284" t="inlineStr">
+      <c r="AN284" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -40744,17 +41925,17 @@
           <t>2-CMFA-Minutes-10-24-25.pdf</t>
         </is>
       </c>
-      <c r="AD285" s="2" t="inlineStr">
+      <c r="AE285" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM285" t="inlineStr">
+      <c r="AN285" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
       </c>
-      <c r="AN285" t="inlineStr">
+      <c r="AO285" t="inlineStr">
         <is>
           <t>county:manual-repo-edit; city:manual-repo-edit</t>
         </is>
@@ -40878,10 +42059,15 @@
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE286" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM286" t="inlineStr">
+      <c r="AN286" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -40993,12 +42179,12 @@
           <t>15150</t>
         </is>
       </c>
-      <c r="AD287" s="2" t="inlineStr">
+      <c r="AE287" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM287" t="inlineStr">
+      <c r="AN287" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -41122,15 +42308,20 @@
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE288" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE288" s="2" t="inlineStr">
+      <c r="AF288" s="2" t="inlineStr">
         <is>
           <t>3048</t>
         </is>
       </c>
-      <c r="AM288" t="inlineStr">
+      <c r="AN288" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -41242,17 +42433,17 @@
           <t>30900</t>
         </is>
       </c>
-      <c r="AD289" s="2" t="inlineStr">
+      <c r="AE289" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE289" s="2" t="inlineStr">
+      <c r="AF289" s="2" t="inlineStr">
         <is>
           <t>4440</t>
         </is>
       </c>
-      <c r="AM289" t="inlineStr">
+      <c r="AN289" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -41364,12 +42555,12 @@
           <t>28800</t>
         </is>
       </c>
-      <c r="AD290" s="2" t="inlineStr">
+      <c r="AE290" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM290" t="inlineStr">
+      <c r="AN290" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -41436,12 +42627,12 @@
           <t>2-CMFA-Minutes-02-20-26.pdf</t>
         </is>
       </c>
-      <c r="AD291" s="2" t="inlineStr">
+      <c r="AE291" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM291" t="inlineStr">
+      <c r="AN291" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -41553,17 +42744,17 @@
           <t>5000</t>
         </is>
       </c>
-      <c r="AD292" s="2" t="inlineStr">
+      <c r="AE292" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE292" s="2" t="inlineStr">
+      <c r="AF292" s="2" t="inlineStr">
         <is>
           <t>3601 Fernwood</t>
         </is>
       </c>
-      <c r="AM292" t="inlineStr">
+      <c r="AN292" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -41675,17 +42866,17 @@
           <t>5000</t>
         </is>
       </c>
-      <c r="AD293" s="2" t="inlineStr">
+      <c r="AE293" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE293" s="2" t="inlineStr">
+      <c r="AF293" s="2" t="inlineStr">
         <is>
           <t>119 East Johnson</t>
         </is>
       </c>
-      <c r="AM293" t="inlineStr">
+      <c r="AN293" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -41797,17 +42988,17 @@
           <t>22650</t>
         </is>
       </c>
-      <c r="AD294" s="2" t="inlineStr">
+      <c r="AE294" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE294" s="2" t="inlineStr">
+      <c r="AF294" s="2" t="inlineStr">
         <is>
           <t>24650 Amador Street in Hayward, CA</t>
         </is>
       </c>
-      <c r="AM294" t="inlineStr">
+      <c r="AN294" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -41884,12 +43075,12 @@
           <t>2-CMFA-Minutes-04-17-26.pdf</t>
         </is>
       </c>
-      <c r="AD295" s="2" t="inlineStr">
+      <c r="AE295" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM295" t="inlineStr">
+      <c r="AN295" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -42013,15 +43204,20 @@
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE296" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE296" s="2" t="inlineStr">
+      <c r="AF296" s="2" t="inlineStr">
         <is>
           <t>79 acres. The unit mix consists of 4 studios,</t>
         </is>
       </c>
-      <c r="AM296" t="inlineStr">
+      <c r="AN296" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -42145,15 +43341,20 @@
       </c>
       <c r="AD297" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE297" s="2" t="inlineStr">
+        <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE297" s="2" t="inlineStr">
+      <c r="AF297" s="2" t="inlineStr">
         <is>
           <t>81 acres. The unit mix consists of 5 studios,</t>
         </is>
       </c>
-      <c r="AM297" t="inlineStr">
+      <c r="AN297" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -42265,17 +43466,17 @@
           <t>14850</t>
         </is>
       </c>
-      <c r="AD298" s="2" t="inlineStr">
+      <c r="AE298" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE298" s="2" t="inlineStr">
+      <c r="AF298" s="2" t="inlineStr">
         <is>
           <t>6754 Valjean Ave, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM298" t="inlineStr">
+      <c r="AN298" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -42387,17 +43588,17 @@
           <t>13200</t>
         </is>
       </c>
-      <c r="AD299" s="2" t="inlineStr">
+      <c r="AE299" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE299" s="2" t="inlineStr">
+      <c r="AF299" s="2" t="inlineStr">
         <is>
           <t>7408 S. Figueroa St., Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM299" t="inlineStr">
+      <c r="AN299" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -42516,15 +43717,20 @@
       </c>
       <c r="AD300" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE300" s="2" t="inlineStr">
+        <is>
           <t>Charitable Affordable Housing Grant for an Affordable Rental Housing Facility Located in the City of Daly City, San Mateo County, California</t>
         </is>
       </c>
-      <c r="AE300" s="2" t="inlineStr">
+      <c r="AF300" s="2" t="inlineStr">
         <is>
           <t>79 acres. The unit mix consists of 4 studios,</t>
         </is>
       </c>
-      <c r="AM300" t="inlineStr">
+      <c r="AN300" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -42643,15 +43849,20 @@
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE301" s="2" t="inlineStr">
+        <is>
           <t>Charitable Affordable Housing Grant for an Affordable Rental Housing Facility Located in the City of Redwood City, San Mateo County, California</t>
         </is>
       </c>
-      <c r="AE301" s="2" t="inlineStr">
+      <c r="AF301" s="2" t="inlineStr">
         <is>
           <t>81 acres. The unit mix consists of 5 studios,</t>
         </is>
       </c>
-      <c r="AM301" t="inlineStr">
+      <c r="AN301" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -42763,17 +43974,17 @@
           <t>24600</t>
         </is>
       </c>
-      <c r="AD302" s="2" t="inlineStr">
+      <c r="AE302" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE302" s="2" t="inlineStr">
+      <c r="AF302" s="2" t="inlineStr">
         <is>
           <t>12534 San Fernando Rd, Los Angeles, CA</t>
         </is>
       </c>
-      <c r="AM302" t="inlineStr">
+      <c r="AN302" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -42885,17 +44096,17 @@
           <t>7200</t>
         </is>
       </c>
-      <c r="AD303" s="2" t="inlineStr">
+      <c r="AE303" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE303" s="2" t="inlineStr">
+      <c r="AF303" s="2" t="inlineStr">
         <is>
           <t>1248–1254 North Cherokee Avenue in</t>
         </is>
       </c>
-      <c r="AM303" t="inlineStr">
+      <c r="AN303" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -42987,17 +44198,17 @@
           <t>19200</t>
         </is>
       </c>
-      <c r="AD304" s="2" t="inlineStr">
+      <c r="AE304" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AE304" s="2" t="inlineStr">
+      <c r="AF304" s="2" t="inlineStr">
         <is>
           <t>8513 Paradise Valley Road in the unincorporated community of Spring Valley in San Diego</t>
         </is>
       </c>
-      <c r="AM304" t="inlineStr">
+      <c r="AN304" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -43104,12 +44315,12 @@
           <t>22200</t>
         </is>
       </c>
-      <c r="AD305" s="2" t="inlineStr">
+      <c r="AE305" s="2" t="inlineStr">
         <is>
           <t>Grant up to $10,000 (Charitable Affordable Housing)</t>
         </is>
       </c>
-      <c r="AM305" t="inlineStr">
+      <c r="AN305" t="inlineStr">
         <is>
           <t>generated</t>
         </is>
@@ -43198,20 +44409,25 @@
       </c>
       <c r="AD306" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE306" s="2" t="inlineStr">
+        <is>
           <t>Grant of $5,000</t>
         </is>
       </c>
-      <c r="AE306" s="2" t="inlineStr">
+      <c r="AF306" s="2" t="inlineStr">
         <is>
           <t>438 &amp; 480 Camino Del Rio South, San Diego, CA</t>
         </is>
       </c>
-      <c r="AF306" s="2" t="inlineStr">
+      <c r="AG306" s="2" t="inlineStr">
         <is>
           <t>October, 2026</t>
         </is>
       </c>
-      <c r="AM306" t="inlineStr">
+      <c r="AN306" t="inlineStr">
         <is>
           <t>generated</t>
         </is>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -37472,14 +37472,14 @@
       </c>
       <c r="W250" s="2" t="inlineStr">
         <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="X250" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="X250" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="Y250" s="2" t="inlineStr">
         <is>
           <t>at 80% AMI</t>
@@ -37497,12 +37497,12 @@
       </c>
       <c r="AB250" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>604800</t>
         </is>
       </c>
       <c r="AC250" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>151200</t>
         </is>
       </c>
       <c r="AE250" s="2" t="inlineStr">
@@ -40124,14 +40124,14 @@
       </c>
       <c r="W271" s="2" t="inlineStr">
         <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="X271" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="X271" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="Y271" s="2" t="inlineStr">
         <is>
           <t>at 80% AMI</t>
@@ -40149,12 +40149,12 @@
       </c>
       <c r="AB271" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>604800</t>
         </is>
       </c>
       <c r="AC271" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>151200</t>
         </is>
       </c>
       <c r="AE271" s="2" t="inlineStr">
@@ -40545,14 +40545,14 @@
       </c>
       <c r="W274" s="2" t="inlineStr">
         <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="X274" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="X274" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="Y274" s="2" t="inlineStr">
         <is>
           <t>at 80% AMI</t>
@@ -40570,12 +40570,12 @@
       </c>
       <c r="AB274" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>604800</t>
         </is>
       </c>
       <c r="AC274" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>151200</t>
         </is>
       </c>
       <c r="AD274" s="2" t="inlineStr">
@@ -79943,7 +79943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C104"/>
+  <dimension ref="A1:C96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -80520,12 +80520,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>total_units: generated '24' -&gt; manual '52'</t>
+          <t>investor_1: generated 'Ethos Real Estate' -&gt; manual 'Vistria Group'</t>
         </is>
       </c>
     </row>
@@ -80537,12 +80537,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>total_units: generated '22' -&gt; manual '72'</t>
+          <t>total_units: generated '144' -&gt; manual '145'</t>
         </is>
       </c>
     </row>
@@ -80554,12 +80554,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>total_units: generated '24' -&gt; manual '48'</t>
+          <t>total_units: generated '29' -&gt; manual '196'</t>
         </is>
       </c>
     </row>
@@ -80571,12 +80571,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>total_units: generated '65' -&gt; manual '165'</t>
+          <t>investor_1: generated 'Vintage Housing Holdings, LLC' -&gt; manual 'Kennedy Wilson'</t>
         </is>
       </c>
     </row>
@@ -80588,12 +80588,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>investor_1: generated 'Ethos Real Estate' -&gt; manual 'Vistria Group'</t>
+          <t>nonprofit_partner: generated 'Pacific Housing, Inc.' -&gt; manual 'Hearthstone Housing Foundation'</t>
         </is>
       </c>
     </row>
@@ -80605,12 +80605,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>total_units: generated '144' -&gt; manual '145'</t>
+          <t>total_units: generated '32' -&gt; manual '31'</t>
         </is>
       </c>
     </row>
@@ -80622,12 +80622,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>total_units: generated '42' -&gt; manual '356'</t>
+          <t>city_cut: generated '4650.0' -&gt; manual '4500'</t>
         </is>
       </c>
     </row>
@@ -80639,12 +80639,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>158</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>total_units: generated '29' -&gt; manual '196'</t>
+          <t>total_units: generated '30' -&gt; manual '29'</t>
         </is>
       </c>
     </row>
@@ -80656,12 +80656,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>95</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>investor_1: generated 'Vintage Housing Holdings, LLC' -&gt; manual 'Kennedy Wilson'</t>
+          <t>investor_1: generated 'Belveron Partners' -&gt; manual 'Sack Capital Partners'</t>
         </is>
       </c>
     </row>
@@ -80673,12 +80673,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>134</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>nonprofit_partner: generated 'Pacific Housing, Inc.' -&gt; manual 'Hearthstone Housing Foundation'</t>
+          <t>total_units: generated '69' -&gt; manual '68'</t>
         </is>
       </c>
     </row>
@@ -80690,12 +80690,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>137</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>total_units: generated '8' -&gt; manual '1008'</t>
+          <t>total_units: generated '42' -&gt; manual '41'</t>
         </is>
       </c>
     </row>
@@ -80707,12 +80707,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>155</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>total_units: generated '32' -&gt; manual '31'</t>
+          <t>entity: generated 'A limited partnership to be formed by Kairos Investment Management and Pacific Housing' -&gt; manual 'TBD LP'</t>
         </is>
       </c>
     </row>
@@ -80724,12 +80724,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>156</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>city_cut: generated '4650.0' -&gt; manual '4500'</t>
+          <t>entity: generated 'A limited partnership to be formed by Kairos Investment Management and Pacific Housing' -&gt; manual 'TBD LP'</t>
         </is>
       </c>
     </row>
@@ -80741,12 +80741,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>171</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>total_units: generated '30' -&gt; manual '29'</t>
+          <t>city_cut: generated '15900.0' -&gt; manual '6300'</t>
         </is>
       </c>
     </row>
@@ -80758,12 +80758,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>195</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>investor_1: generated 'Belveron Partners' -&gt; manual 'Sack Capital Partners'</t>
+          <t>total_units: generated '42' -&gt; manual '41'</t>
         </is>
       </c>
     </row>
@@ -80775,12 +80775,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>199</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>total_units: generated '69' -&gt; manual '68'</t>
+          <t>city_cut: generated '5550.0' -&gt; manual '5500'</t>
         </is>
       </c>
     </row>
@@ -80792,12 +80792,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>204</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>total_units: generated '42' -&gt; manual '41'</t>
+          <t>total_units: generated '50' -&gt; manual '49'</t>
         </is>
       </c>
     </row>
@@ -80809,12 +80809,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>206</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>total_units: generated '52' -&gt; manual '152'</t>
+          <t>county: generated 'San Diego' -&gt; manual 'Los Angeles'</t>
         </is>
       </c>
     </row>
@@ -80826,12 +80826,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>209</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>entity: generated 'A limited partnership to be formed by Kairos Investment Management and Pacific Housing' -&gt; manual 'TBD LP'</t>
+          <t>investor_1: generated 'Zenith Property Group LLC' -&gt; manual 'Red Stone Equity Partners'</t>
         </is>
       </c>
     </row>
@@ -80843,12 +80843,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>209</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>entity: generated 'A limited partnership to be formed by Kairos Investment Management and Pacific Housing' -&gt; manual 'TBD LP'</t>
+          <t>term_years: generated '35' -&gt; manual '15'</t>
         </is>
       </c>
     </row>
@@ -80860,12 +80860,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>210</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>city_cut: generated '15900.0' -&gt; manual '6300'</t>
+          <t>term_years: generated '55' -&gt; manual '10'</t>
         </is>
       </c>
     </row>
@@ -80877,12 +80877,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>total_units: generated '52' -&gt; manual '152'</t>
+          <t>term_years: generated '15' -&gt; manual '10'</t>
         </is>
       </c>
     </row>
@@ -80894,12 +80894,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>228</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>total_units: generated '42' -&gt; manual '41'</t>
+          <t>term_years: generated '10' -&gt; manual '15'</t>
         </is>
       </c>
     </row>
@@ -80911,12 +80911,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>217</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>city_cut: generated '5550.0' -&gt; manual '5500'</t>
+          <t>total_units: generated '35' -&gt; manual '34'</t>
         </is>
       </c>
     </row>
@@ -80928,12 +80928,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>233</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>total_units: generated '50' -&gt; manual '49'</t>
+          <t>term_years: generated '55' -&gt; manual '10'</t>
         </is>
       </c>
     </row>
@@ -80945,12 +80945,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>236</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>county: generated 'San Diego' -&gt; manual 'Los Angeles'</t>
+          <t>total_units: generated '136' -&gt; manual '108'</t>
         </is>
       </c>
     </row>
@@ -80962,556 +80962,556 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>225</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>investor_1: generated 'Zenith Property Group LLC' -&gt; manual 'Red Stone Equity Partners'</t>
+          <t>term_years: generated '30' -&gt; manual '55'</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>term_years: generated '35' -&gt; manual '15'</t>
+          <t>entity '381 Turk Street Associates, a California' ~ SCC LP '421 Turk Street Associates, L.P.' (#3326, San Francisco, score 92)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>term_years: generated '55' -&gt; manual '10'</t>
+          <t>entity 'BIF NON OZ 7524 S HOOVER ST, LP' ~ SCC LP 'BIF NON OZ 7518 S Hoover St, LP' (#14953, Los Angeles, score 93)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>term_years: generated '15' -&gt; manual '10'</t>
+          <t>entity 'BIF NON OZ 4228 WESTERN AVE, LP' ~ SCC LP 'BIF NON OZ 4209 Western Ave, LP' (#14952, Los Angeles, score 93)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-manual-unmatched</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>term_years: generated '10' -&gt; manual '15'</t>
+          <t>manual scc_filed=True but no BOE certificate matches entity 'Hillsdale Property LP'; closest: 'Hillsdale Property San Mateo, LP' (#15018, San Mateo, score 78)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-manual-unmatched</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>total_units: generated '35' -&gt; manual '34'</t>
+          <t>manual scc_filed=True but no BOE certificate matches entity 'Post Chaparral, LP, a Delaware limited p'; closest: 'Post Palmdale Chaparral, LP' (#15197, Los Angeles, score 76)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>122</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>term_years: generated '55' -&gt; manual '10'</t>
+          <t>entity '861 Fedora LLLP' ~ SCC LP '836 Fedora L.P.' (#1594, Los Angeles, score 90)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>165</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>total_units: generated '136' -&gt; manual '108'</t>
+          <t>entity '861 Fedora LLLP' ~ SCC LP '836 Fedora L.P.' (#1594, Los Angeles, score 90)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-superseded-only</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>132</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>term_years: generated '30' -&gt; manual '55'</t>
+          <t>operative entity 'PS 7518 Hoover St, LP' has no SCC, but the property's superseded grant 10 ('BIF NON OZ 7518 S Hoover St, LP, a Delaw') holds SCC 14953 (2024-11-25) — new sponsor's LP must file its own</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>scc-possible-match</t>
+          <t>scc-superseded-only</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>134</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>entity '381 Turk Street Associates, a California' ~ SCC LP '421 Turk Street Associates, L.P.' (#3326, San Francisco, score 92)</t>
+          <t>operative entity 'PS 10705 Avalon Blvd, LP' has no SCC, but the property's superseded grant 303 ('BIF NON OZ 10705 Avalon Blvd, LP, a Cali') holds SCC 14852 (2024-10-03) — new sponsor's LP must file its own</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>scc-possible-match</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>entity 'BIF NON OZ 7524 S HOOVER ST, LP' ~ SCC LP 'BIF NON OZ 7518 S Hoover St, LP' (#14953, Los Angeles, score 93)</t>
+          <t>AIN 5036031006 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>scc-possible-match</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>entity 'BIF NON OZ 4228 WESTERN AVE, LP' ~ SCC LP 'BIF NON OZ 4209 Western Ave, LP' (#14952, Los Angeles, score 93)</t>
+          <t>AIN 4262018026 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>scc-manual-unmatched</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>132</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>manual scc_filed=True but no BOE certificate matches entity 'Hillsdale Property LP'; closest: 'Hillsdale Property San Mateo, LP' (#15018, San Mateo, score 78)</t>
+          <t>AIN 6020022027 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>scc-manual-unmatched</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>137</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>manual scc_filed=True but no BOE certificate matches entity 'Post Chaparral, LP, a Delaware limited p'; closest: 'Post Palmdale Chaparral, LP' (#15197, Los Angeles, score 76)</t>
+          <t>AIN 2125017014 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>scc-possible-match</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>158</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>entity '861 Fedora LLLP' ~ SCC LP '836 Fedora L.P.' (#1594, Los Angeles, score 90)</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>scc-possible-match</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>196</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>entity '861 Fedora LLLP' ~ SCC LP '836 Fedora L.P.' (#1594, Los Angeles, score 90)</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>scc-superseded-only</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>operative entity 'PS 7518 Hoover St, LP' has no SCC, but the property's superseded grant 10 ('BIF NON OZ 7518 S Hoover St, LP, a Delaw') holds SCC 14953 (2024-11-25) — new sponsor's LP must file its own</t>
+          <t>AIN (none) (Santa Barbara): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>scc-superseded-only</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>206</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>operative entity 'PS 10705 Avalon Blvd, LP' has no SCC, but the property's superseded grant 303 ('BIF NON OZ 10705 Avalon Blvd, LP, a Cali') holds SCC 14852 (2024-10-03) — new sponsor's LP must file its own</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>207</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AIN 5036031006 (Los Angeles) has no current roll data; using manual value</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>208</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AIN 4262018026 (Los Angeles) has no current roll data; using manual value</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>215</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AIN 6020022027 (Los Angeles) has no current roll data; using manual value</t>
+          <t>AIN 5539028040 (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AIN 2125017014 (Los Angeles) has no current roll data; using manual value</t>
+          <t>AIN (none) (Contra Costa): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 128101150 (Solano) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 128101050 (Solano) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AIN (none) (Santa Barbara): no roll values from any source</t>
+          <t>AIN 128105060 (Solano) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>parcel-dedup</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>121</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 5518013024 (Alexandria II Apartments) also assigned under operative grant 162; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>parcel-dedup</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>122</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 5094017020 (Fedora Apartments) also assigned under operative grant 165; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>parcel-dedup</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>123</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
+          <t>AIN 5518020021 (Kenmore II Apartments) also assigned under operative grant 168; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>parcel-dedup</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>124</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AIN 5539028040 (Los Angeles): no roll values from any source</t>
+          <t>AIN 5094023025 (Kenmore III Apartments) also assigned under operative grant 169; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>parcel-no-values</t>
+          <t>parcel-dedup</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>125</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AIN (none) (Contra Costa): no roll values from any source</t>
+          <t>AIN 5503024012 (Kingsley Apartments) also assigned under operative grant 170; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>parcel-dedup</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>126</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AIN 128101150 (Solano) has no current roll data; using manual value</t>
+          <t>AIN 5094005005 (Mariposa I Apartments) also assigned under operative grant 173; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>parcel-dedup</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>127</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AIN 128101050 (Solano) has no current roll data; using manual value</t>
+          <t>AIN 5094006003 (Mariposa III Apartments) also assigned under operative grant 174; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>fetch-fallback</t>
+          <t>parcel-dedup</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AIN 128105060 (Solano) has no current roll data; using manual value</t>
+          <t>AIN 5502019004 (Mariposa IV Apartments) also assigned under operative grant 175; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>
@@ -81523,12 +81523,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>129</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AIN 5518013024 (Alexandria II Apartments) also assigned under operative grant 162; this row marked legacy_redundant so sums count it once</t>
+          <t>AIN 5517005016 (Oxford II Apartments) also assigned under operative grant 177; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>
@@ -81540,12 +81540,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>130</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AIN 5094017020 (Fedora Apartments) also assigned under operative grant 165; this row marked legacy_redundant so sums count it once</t>
+          <t>AIN 5080006008 (Western Apartments) also assigned under operative grant 179; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>
@@ -81557,12 +81557,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>152</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AIN 5518020021 (Kenmore II Apartments) also assigned under operative grant 168; this row marked legacy_redundant so sums count it once</t>
+          <t>AIN 7157012023 (The Hive at Ackerfield Apartments) also assigned under operative grant 181; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>
@@ -81574,146 +81574,10 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>135</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
-        <is>
-          <t>AIN 5094023025 (Kenmore III Apartments) also assigned under operative grant 169; this row marked legacy_redundant so sums count it once</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>parcel-dedup</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>AIN 5503024012 (Kingsley Apartments) also assigned under operative grant 170; this row marked legacy_redundant so sums count it once</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>parcel-dedup</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>AIN 5094005005 (Mariposa I Apartments) also assigned under operative grant 173; this row marked legacy_redundant so sums count it once</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>parcel-dedup</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>AIN 5094006003 (Mariposa III Apartments) also assigned under operative grant 174; this row marked legacy_redundant so sums count it once</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>parcel-dedup</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>AIN 5502019004 (Mariposa IV Apartments) also assigned under operative grant 175; this row marked legacy_redundant so sums count it once</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>parcel-dedup</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>AIN 5517005016 (Oxford II Apartments) also assigned under operative grant 177; this row marked legacy_redundant so sums count it once</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>parcel-dedup</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>AIN 5080006008 (Western Apartments) also assigned under operative grant 179; this row marked legacy_redundant so sums count it once</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>parcel-dedup</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>AIN 7157012023 (The Hive at Ackerfield Apartments) also assigned under operative grant 181; this row marked legacy_redundant so sums count it once</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>parcel-dedup</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
         <is>
           <t>AIN 5518026004 (236 Berendo Apartments) also assigned under operative grant 220; this row marked legacy_redundant so sums count it once</t>
         </is>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -467,7 +467,7 @@
     <col width="38" customWidth="1" min="17" max="17"/>
     <col width="38" customWidth="1" min="18" max="18"/>
     <col width="38" customWidth="1" min="19" max="19"/>
-    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="31" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
     <col width="38" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -8203,9 +8203,9 @@
           <t>2-CMFA-Minutes-10-11-2024-1.pdf</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Vistria Group</t>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>Ethos Real Estate</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; scc_filed:collaborator-sheet; investor_1:collaborator-sheet; address:collaborator-sheet</t>
+          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; scc_filed:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -9160,7 +9160,7 @@
           <t>Pacific Housing, Inc.</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="W55" s="2" t="inlineStr">
         <is>
           <t>356</t>
         </is>
@@ -9222,7 +9222,7 @@
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; resolution:collaborator-sheet; total_units:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; resolution:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -12913,22 +12913,22 @@
           <t>2-CMFA-Minutes-06-27-2025.pdf</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr">
+      <c r="T79" s="2" t="inlineStr">
+        <is>
+          <t>Vintage Housing Holdings, LLC</t>
+        </is>
+      </c>
+      <c r="U79" s="2" t="inlineStr">
         <is>
           <t>Kennedy Wilson</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Vintage Housing Holdings</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Hearthstone Housing Foundation</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>Pacific Housing, Inc.</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
         <is>
           <t>1008</t>
         </is>
@@ -12995,7 +12995,7 @@
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>investor_2:collaborator-sheet; new_build:collaborator-sheet; link:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; link:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -13374,9 +13374,9 @@
           <t>Housing on Merit</t>
         </is>
       </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>31</t>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
@@ -13394,14 +13394,14 @@
           <t>30</t>
         </is>
       </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>4500</t>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>4650.0</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>18600</t>
+          <t>19200</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet; city_cut:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; restricted_units:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -15492,9 +15492,9 @@
           <t>2-CMFA-Minutes-08-08-25.pdf</t>
         </is>
       </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Sack Capital Partners</t>
+      <c r="T96" s="2" t="inlineStr">
+        <is>
+          <t>Belveron Partners</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>investor_2:collaborator-sheet; acquisition_date:collaborator-sheet; link:collaborator-sheet; resolution:collaborator-sheet; investor_1:collaborator-sheet; address:collaborator-sheet</t>
+          <t>investor_2:collaborator-sheet; acquisition_date:collaborator-sheet; link:collaborator-sheet; resolution:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -21228,16 +21228,16 @@
           <t>Housing On Merit</t>
         </is>
       </c>
-      <c r="W134" t="inlineStr">
+      <c r="W134" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="X134" s="2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="X134" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="Y134" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -21255,12 +21255,12 @@
       </c>
       <c r="AB134" s="2" t="inlineStr">
         <is>
-          <t>40800</t>
+          <t>41400</t>
         </is>
       </c>
       <c r="AC134" s="2" t="inlineStr">
         <is>
-          <t>10200</t>
+          <t>10350</t>
         </is>
       </c>
       <c r="AD134" s="2" t="inlineStr">
@@ -21290,7 +21290,7 @@
       </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -21659,16 +21659,16 @@
           <t>Las Palmas Housing &amp; Development Corporation</t>
         </is>
       </c>
-      <c r="W137" t="inlineStr">
+      <c r="W137" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="X137" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="X137" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="Y137" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -21686,12 +21686,12 @@
       </c>
       <c r="AB137" s="2" t="inlineStr">
         <is>
-          <t>24600</t>
+          <t>25200</t>
         </is>
       </c>
       <c r="AC137" s="2" t="inlineStr">
         <is>
-          <t>6150</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="AD137" s="2" t="inlineStr">
@@ -21721,7 +21721,7 @@
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -23936,14 +23936,14 @@
       </c>
       <c r="W152" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="X152" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="X152" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
       <c r="Y152" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -23961,12 +23961,12 @@
       </c>
       <c r="AB152" s="2" t="inlineStr">
         <is>
-          <t>91200</t>
+          <t>91800</t>
         </is>
       </c>
       <c r="AC152" s="2" t="inlineStr">
         <is>
-          <t>22800</t>
+          <t>22950</t>
         </is>
       </c>
       <c r="AE152" s="2" t="inlineStr">
@@ -23991,7 +23991,7 @@
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; total_units:manual-repo-edit; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -24310,9 +24310,9 @@
           <t>Trailview Apartments</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>TBD LP</t>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>A limited partnership to be formed by Kairos Investment Management and Pacific Housing</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -24442,7 +24442,7 @@
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -24462,9 +24462,9 @@
           <t>Casa Serena Apartments</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>TBD LP</t>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>A limited partnership to be formed by Kairos Investment Management and Pacific Housing</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -24594,7 +24594,7 @@
       </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; built:collaborator-sheet; entity:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; built:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -24796,16 +24796,16 @@
           <t>A Community of Friends</t>
         </is>
       </c>
-      <c r="W158" t="inlineStr">
+      <c r="W158" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="X158" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="X158" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="Y158" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -24823,7 +24823,7 @@
       </c>
       <c r="AB158" s="2" t="inlineStr">
         <is>
-          <t>17400</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="AC158" s="2" t="inlineStr">
@@ -24853,7 +24853,7 @@
       </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet; total_units:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; manual_status:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -26662,21 +26662,21 @@
           <t>55</t>
         </is>
       </c>
-      <c r="AA171" t="inlineStr">
+      <c r="AA171" s="2" t="inlineStr">
+        <is>
+          <t>15900.0</t>
+        </is>
+      </c>
+      <c r="AB171" s="2" t="inlineStr">
+        <is>
+          <t>25200</t>
+        </is>
+      </c>
+      <c r="AC171" s="2" t="inlineStr">
         <is>
           <t>6300</t>
         </is>
       </c>
-      <c r="AB171" s="2" t="inlineStr">
-        <is>
-          <t>25200</t>
-        </is>
-      </c>
-      <c r="AC171" s="2" t="inlineStr">
-        <is>
-          <t>6300</t>
-        </is>
-      </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -26699,7 +26699,7 @@
       </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>address:collaborator-sheet; city_cut:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -28049,14 +28049,14 @@
       </c>
       <c r="W181" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="X181" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="X181" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
       <c r="Y181" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -28074,12 +28074,12 @@
       </c>
       <c r="AB181" s="2" t="inlineStr">
         <is>
-          <t>91200</t>
+          <t>91800</t>
         </is>
       </c>
       <c r="AC181" s="2" t="inlineStr">
         <is>
-          <t>22800</t>
+          <t>22950</t>
         </is>
       </c>
       <c r="AD181" s="2" t="inlineStr">
@@ -28104,7 +28104,7 @@
       </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>manual_status:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>manual_status:collaborator-sheet; total_units:manual-repo-edit; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -29863,16 +29863,16 @@
           <t>Foundation for Affordable Housing</t>
         </is>
       </c>
-      <c r="W194" t="inlineStr">
+      <c r="W194" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="X194" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="X194" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="Y194" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -29890,12 +29890,12 @@
       </c>
       <c r="AB194" s="2" t="inlineStr">
         <is>
-          <t>24600</t>
+          <t>25200</t>
         </is>
       </c>
       <c r="AC194" s="2" t="inlineStr">
         <is>
-          <t>6150</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="AD194" s="2" t="inlineStr">
@@ -29925,7 +29925,7 @@
       </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -30446,9 +30446,9 @@
           <t>30</t>
         </is>
       </c>
-      <c r="AA198" t="inlineStr">
-        <is>
-          <t>5500</t>
+      <c r="AA198" s="2" t="inlineStr">
+        <is>
+          <t>5550.0</t>
         </is>
       </c>
       <c r="AB198" s="2" t="inlineStr">
@@ -30483,7 +30483,7 @@
       </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>city_cut:collaborator-sheet; address:manual-repo-edit</t>
+          <t>address:manual-repo-edit</t>
         </is>
       </c>
     </row>
@@ -31141,16 +31141,16 @@
           <t>Las Palmas Housing &amp; Development Corporation</t>
         </is>
       </c>
-      <c r="W203" t="inlineStr">
+      <c r="W203" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X203" s="2" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="X203" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="Y203" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -31168,12 +31168,12 @@
       </c>
       <c r="AB203" s="2" t="inlineStr">
         <is>
-          <t>29400</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>7350</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
@@ -31203,7 +31203,7 @@
       </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:manual-repo-edit</t>
+          <t>new_build:collaborator-sheet; address:manual-repo-edit</t>
         </is>
       </c>
     </row>
@@ -31370,9 +31370,9 @@
           <t>Escondido</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>Los Angeles</t>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G205" s="2" t="inlineStr">
@@ -31487,7 +31487,7 @@
       </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>manual_status:collaborator-sheet; county:collaborator-sheet; address:collaborator-sheet</t>
+          <t>manual_status:collaborator-sheet; address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -31831,9 +31831,9 @@
           <t>2-CMFA-Minutes-05-29-26.pdf</t>
         </is>
       </c>
-      <c r="T208" t="inlineStr">
-        <is>
-          <t>Red Stone Equity Partners</t>
+      <c r="T208" s="2" t="inlineStr">
+        <is>
+          <t>Zenith Property Group LLC</t>
         </is>
       </c>
       <c r="V208" s="2" t="inlineStr">
@@ -31856,9 +31856,9 @@
           <t>100% at 80% AMI</t>
         </is>
       </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="Z208" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
       <c r="AA208" s="2" t="inlineStr">
@@ -31898,7 +31898,7 @@
       </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>investor_1:collaborator-sheet; address:collaborator-sheet; term_years:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -31998,9 +31998,9 @@
           <t>100% at 80% AMI</t>
         </is>
       </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>10</t>
+      <c r="Z209" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
         </is>
       </c>
       <c r="AB209" s="2" t="inlineStr">
@@ -32031,11 +32031,6 @@
       <c r="AN209" t="inlineStr">
         <is>
           <t>generated</t>
-        </is>
-      </c>
-      <c r="AO209" t="inlineStr">
-        <is>
-          <t>term_years:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -32977,16 +32972,16 @@
           <t>Las Palmas Housing &amp; Development Corporation</t>
         </is>
       </c>
-      <c r="W216" t="inlineStr">
+      <c r="W216" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="X216" s="2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="X216" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="Y216" s="2" t="inlineStr">
         <is>
           <t>100% at 80% AMI</t>
@@ -33004,12 +32999,12 @@
       </c>
       <c r="AB216" s="2" t="inlineStr">
         <is>
-          <t>20400</t>
+          <t>21000</t>
         </is>
       </c>
       <c r="AC216" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="AD216" s="2" t="inlineStr">
@@ -33039,7 +33034,7 @@
       </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; total_units:collaborator-sheet; address:manual-repo-edit</t>
+          <t>new_build:collaborator-sheet; address:manual-repo-edit</t>
         </is>
       </c>
     </row>
@@ -34033,9 +34028,9 @@
           <t>100% at 80% AMI</t>
         </is>
       </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>55</t>
+      <c r="Z224" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="AA224" s="2" t="inlineStr">
@@ -34075,7 +34070,7 @@
       </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>address:collaborator-sheet; term_years:collaborator-sheet</t>
+          <t>address:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -34170,9 +34165,9 @@
           <t>80% at 80% AMI</t>
         </is>
       </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>10</t>
+      <c r="Z225" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="AB225" s="2" t="inlineStr">
@@ -34212,7 +34207,7 @@
       </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>manual_status:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet; term_years:collaborator-sheet</t>
+          <t>manual_status:collaborator-sheet; investor_1:collaborator-sheet; nonprofit_partner:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -34434,9 +34429,9 @@
           <t>50% at 80% AMI</t>
         </is>
       </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>15</t>
+      <c r="Z227" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="AB227" s="2" t="inlineStr">
@@ -34476,7 +34471,7 @@
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet; term_years:collaborator-sheet</t>
+          <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -35124,9 +35119,9 @@
           <t>100% at 80% AMI</t>
         </is>
       </c>
-      <c r="Z232" t="inlineStr">
-        <is>
-          <t>10</t>
+      <c r="Z232" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
         </is>
       </c>
       <c r="AB232" s="2" t="inlineStr">
@@ -35166,7 +35161,7 @@
       </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet; term_years:collaborator-sheet</t>
+          <t>investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -35520,16 +35515,16 @@
           <t>Integrity Housing</t>
         </is>
       </c>
-      <c r="W235" t="inlineStr">
+      <c r="W235" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="X235" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
       <c r="Y235" s="2" t="inlineStr">
         <is>
           <t>80%</t>
@@ -35542,12 +35537,12 @@
       </c>
       <c r="AB235" s="2" t="inlineStr">
         <is>
-          <t>64800</t>
+          <t>81600</t>
         </is>
       </c>
       <c r="AC235" s="2" t="inlineStr">
         <is>
-          <t>16200</t>
+          <t>20400</t>
         </is>
       </c>
       <c r="AD235" s="2" t="inlineStr">
@@ -35582,7 +35577,7 @@
       </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; total_units:collaborator-sheet; restricted_units:collaborator-sheet</t>
+          <t>new_build:collaborator-sheet; investor_1:collaborator-sheet; restricted_units:collaborator-sheet</t>
         </is>
       </c>
     </row>
@@ -79943,10 +79938,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C96"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
   </cols>
@@ -80498,1086 +80493,610 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>investor_1: generated 'Oak Road' -&gt; manual 'Eleos Ventures, LLC'</t>
+          <t>entity '381 Turk Street Associates, a California' ~ SCC LP '421 Turk Street Associates, L.P.' (#3326, San Francisco, score 92)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>investor_1: generated 'Ethos Real Estate' -&gt; manual 'Vistria Group'</t>
+          <t>entity 'BIF NON OZ 7524 S HOOVER ST, LP' ~ SCC LP 'BIF NON OZ 7518 S Hoover St, LP' (#14953, Los Angeles, score 93)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>total_units: generated '144' -&gt; manual '145'</t>
+          <t>entity 'BIF NON OZ 4228 WESTERN AVE, LP' ~ SCC LP 'BIF NON OZ 4209 Western Ave, LP' (#14952, Los Angeles, score 93)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-manual-unmatched</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>total_units: generated '29' -&gt; manual '196'</t>
+          <t>manual scc_filed=True but no BOE certificate matches entity 'Hillsdale Property LP'; closest: 'Hillsdale Property San Mateo, LP' (#15018, San Mateo, score 78)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-manual-unmatched</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>investor_1: generated 'Vintage Housing Holdings, LLC' -&gt; manual 'Kennedy Wilson'</t>
+          <t>manual scc_filed=True but no BOE certificate matches entity 'Post Chaparral, LP, a Delaware limited p'; closest: 'Post Palmdale Chaparral, LP' (#15197, Los Angeles, score 76)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>122</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>nonprofit_partner: generated 'Pacific Housing, Inc.' -&gt; manual 'Hearthstone Housing Foundation'</t>
+          <t>entity '861 Fedora LLLP' ~ SCC LP '836 Fedora L.P.' (#1594, Los Angeles, score 90)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-possible-match</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>165</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>total_units: generated '32' -&gt; manual '31'</t>
+          <t>entity '861 Fedora LLLP' ~ SCC LP '836 Fedora L.P.' (#1594, Los Angeles, score 90)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-superseded-only</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>132</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>city_cut: generated '4650.0' -&gt; manual '4500'</t>
+          <t>operative entity 'PS 7518 Hoover St, LP' has no SCC, but the property's superseded grant 10 ('BIF NON OZ 7518 S Hoover St, LP, a Delaw') holds SCC 14953 (2024-11-25) — new sponsor's LP must file its own</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>scc-superseded-only</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>134</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>total_units: generated '30' -&gt; manual '29'</t>
+          <t>operative entity 'PS 10705 Avalon Blvd, LP' has no SCC, but the property's superseded grant 303 ('BIF NON OZ 10705 Avalon Blvd, LP, a Cali') holds SCC 14852 (2024-10-03) — new sponsor's LP must file its own</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>investor_1: generated 'Belveron Partners' -&gt; manual 'Sack Capital Partners'</t>
+          <t>AIN 5036031006 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>total_units: generated '69' -&gt; manual '68'</t>
+          <t>AIN 4262018026 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>132</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>total_units: generated '42' -&gt; manual '41'</t>
+          <t>AIN 6020022027 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>137</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>entity: generated 'A limited partnership to be formed by Kairos Investment Management and Pacific Housing' -&gt; manual 'TBD LP'</t>
+          <t>AIN 2125017014 (Los Angeles) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>158</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>entity: generated 'A limited partnership to be formed by Kairos Investment Management and Pacific Housing' -&gt; manual 'TBD LP'</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>196</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>city_cut: generated '15900.0' -&gt; manual '6300'</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>total_units: generated '42' -&gt; manual '41'</t>
+          <t>AIN (none) (Santa Barbara): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>206</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>city_cut: generated '5550.0' -&gt; manual '5500'</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>207</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>total_units: generated '50' -&gt; manual '49'</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>208</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>county: generated 'San Diego' -&gt; manual 'Los Angeles'</t>
+          <t>AIN (none) (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>215</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>investor_1: generated 'Zenith Property Group LLC' -&gt; manual 'Red Stone Equity Partners'</t>
+          <t>AIN 5539028040 (Los Angeles): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-no-values</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>226</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>term_years: generated '35' -&gt; manual '15'</t>
+          <t>AIN (none) (Contra Costa): no roll values from any source</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>term_years: generated '55' -&gt; manual '10'</t>
+          <t>AIN 128101150 (Solano) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>term_years: generated '15' -&gt; manual '10'</t>
+          <t>AIN 128101050 (Solano) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>fetch-fallback</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>term_years: generated '10' -&gt; manual '15'</t>
+          <t>AIN 128105060 (Solano) has no current roll data; using manual value</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-dedup</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>121</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>total_units: generated '35' -&gt; manual '34'</t>
+          <t>AIN 5518013024 (Alexandria II Apartments) also assigned under operative grant 162; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-dedup</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>122</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>term_years: generated '55' -&gt; manual '10'</t>
+          <t>AIN 5094017020 (Fedora Apartments) also assigned under operative grant 165; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-dedup</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>123</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>total_units: generated '136' -&gt; manual '108'</t>
+          <t>AIN 5518020021 (Kenmore II Apartments) also assigned under operative grant 168; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>override-conflict</t>
+          <t>parcel-dedup</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>124</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>term_years: generated '30' -&gt; manual '55'</t>
+          <t>AIN 5094023025 (Kenmore III Apartments) also assigned under operative grant 169; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>scc-possible-match</t>
+          <t>parcel-dedup</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>125</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>entity '381 Turk Street Associates, a California' ~ SCC LP '421 Turk Street Associates, L.P.' (#3326, San Francisco, score 92)</t>
+          <t>AIN 5503024012 (Kingsley Apartments) also assigned under operative grant 170; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>scc-possible-match</t>
+          <t>parcel-dedup</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>126</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>entity 'BIF NON OZ 7524 S HOOVER ST, LP' ~ SCC LP 'BIF NON OZ 7518 S Hoover St, LP' (#14953, Los Angeles, score 93)</t>
+          <t>AIN 5094005005 (Mariposa I Apartments) also assigned under operative grant 173; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>scc-possible-match</t>
+          <t>parcel-dedup</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>127</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>entity 'BIF NON OZ 4228 WESTERN AVE, LP' ~ SCC LP 'BIF NON OZ 4209 Western Ave, LP' (#14952, Los Angeles, score 93)</t>
+          <t>AIN 5094006003 (Mariposa III Apartments) also assigned under operative grant 174; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>scc-manual-unmatched</t>
+          <t>parcel-dedup</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>manual scc_filed=True but no BOE certificate matches entity 'Hillsdale Property LP'; closest: 'Hillsdale Property San Mateo, LP' (#15018, San Mateo, score 78)</t>
+          <t>AIN 5502019004 (Mariposa IV Apartments) also assigned under operative grant 175; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>scc-manual-unmatched</t>
+          <t>parcel-dedup</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>129</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>manual scc_filed=True but no BOE certificate matches entity 'Post Chaparral, LP, a Delaware limited p'; closest: 'Post Palmdale Chaparral, LP' (#15197, Los Angeles, score 76)</t>
+          <t>AIN 5517005016 (Oxford II Apartments) also assigned under operative grant 177; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>scc-possible-match</t>
+          <t>parcel-dedup</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>130</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>entity '861 Fedora LLLP' ~ SCC LP '836 Fedora L.P.' (#1594, Los Angeles, score 90)</t>
+          <t>AIN 5080006008 (Western Apartments) also assigned under operative grant 179; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>scc-possible-match</t>
+          <t>parcel-dedup</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>152</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>entity '861 Fedora LLLP' ~ SCC LP '836 Fedora L.P.' (#1594, Los Angeles, score 90)</t>
+          <t>AIN 7157012023 (The Hive at Ackerfield Apartments) also assigned under operative grant 181; this row marked legacy_redundant so sums count it once</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>scc-superseded-only</t>
+          <t>parcel-dedup</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>135</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
-        <is>
-          <t>operative entity 'PS 7518 Hoover St, LP' has no SCC, but the property's superseded grant 10 ('BIF NON OZ 7518 S Hoover St, LP, a Delaw') holds SCC 14953 (2024-11-25) — new sponsor's LP must file its own</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>scc-superseded-only</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>operative entity 'PS 10705 Avalon Blvd, LP' has no SCC, but the property's superseded grant 303 ('BIF NON OZ 10705 Avalon Blvd, LP, a Cali') holds SCC 14852 (2024-10-03) — new sponsor's LP must file its own</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>fetch-fallback</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>AIN 5036031006 (Los Angeles) has no current roll data; using manual value</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>fetch-fallback</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>AIN 4262018026 (Los Angeles) has no current roll data; using manual value</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>fetch-fallback</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>AIN 6020022027 (Los Angeles) has no current roll data; using manual value</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>fetch-fallback</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>AIN 2125017014 (Los Angeles) has no current roll data; using manual value</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>AIN (none) (Santa Barbara): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>AIN (none) (Los Angeles): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>AIN 5539028040 (Los Angeles): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>parcel-no-values</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>AIN (none) (Contra Costa): no roll values from any source</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>fetch-fallback</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>AIN 128101150 (Solano) has no current roll data; using manual value</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>fetch-fallback</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>AIN 128101050 (Solano) has no current roll data; using manual value</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>fetch-fallback</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>AIN 128105060 (Solano) has no current roll data; using manual value</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>parcel-dedup</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>AIN 5518013024 (Alexandria II Apartments) also assigned under operative grant 162; this row marked legacy_redundant so sums count it once</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>parcel-dedup</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>AIN 5094017020 (Fedora Apartments) also assigned under operative grant 165; this row marked legacy_redundant so sums count it once</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>parcel-dedup</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>AIN 5518020021 (Kenmore II Apartments) also assigned under operative grant 168; this row marked legacy_redundant so sums count it once</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>parcel-dedup</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>AIN 5094023025 (Kenmore III Apartments) also assigned under operative grant 169; this row marked legacy_redundant so sums count it once</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>parcel-dedup</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>AIN 5503024012 (Kingsley Apartments) also assigned under operative grant 170; this row marked legacy_redundant so sums count it once</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>parcel-dedup</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>AIN 5094005005 (Mariposa I Apartments) also assigned under operative grant 173; this row marked legacy_redundant so sums count it once</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>parcel-dedup</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>AIN 5094006003 (Mariposa III Apartments) also assigned under operative grant 174; this row marked legacy_redundant so sums count it once</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>parcel-dedup</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>AIN 5502019004 (Mariposa IV Apartments) also assigned under operative grant 175; this row marked legacy_redundant so sums count it once</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>parcel-dedup</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>AIN 5517005016 (Oxford II Apartments) also assigned under operative grant 177; this row marked legacy_redundant so sums count it once</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>parcel-dedup</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>AIN 5080006008 (Western Apartments) also assigned under operative grant 179; this row marked legacy_redundant so sums count it once</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>parcel-dedup</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>AIN 7157012023 (The Hive at Ackerfield Apartments) also assigned under operative grant 181; this row marked legacy_redundant so sums count it once</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>parcel-dedup</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
         <is>
           <t>AIN 5518026004 (236 Berendo Apartments) also assigned under operative grant 220; this row marked legacy_redundant so sums count it once</t>
         </is>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grants" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parcels" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA findings" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="County summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA findings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -81349,6 +81350,1020 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>operative_projects</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>with_scc_filed</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jpa_closing_fees</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>jpa_annual_fees</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>confirmed_exemption</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>confirmed_tax_reduction</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>total_units</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>restricted_units</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>city_cut</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alameda</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>626400</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>156600</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>83017361</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>830174</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>1044</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>979</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>102000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Contra Costa</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>896400</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>224300</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>46831134</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>468311</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>142350</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Fresno</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>166800</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>41700</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>41700</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6121000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1562450</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>348365149</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3483651</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10198</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>8629</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1111775</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Marin</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>59400</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14850</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Napa</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>88800</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>22200</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>22200</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1071600</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>267900</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>204152723</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2041527</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1837</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>187250</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sacramento</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>676800</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>169200</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>23179668</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>231797</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>109800</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Bernardino</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>42600</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10650</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4156500</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>41565</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>10650</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1519300</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>382325</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>49157189</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>491572</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2653</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>240716</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>197400</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>49350</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>35400</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>San Mateo</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>847800</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>211950</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>28000</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1147</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>142275</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Santa Barbara</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>276000</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>69000</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>57000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Santa Clara</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1538400</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>384600</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>35568556</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>355686</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2739</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2065</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>210600</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>22500</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>22500</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Solano</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>180600</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>45150</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7127607</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>71276</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>28500</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sonoma</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>22200</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5550</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>5550</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>14421500</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3640275</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>801583887</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>8015839</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>24379</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>20423</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2470266</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -82552,7 +83567,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -81350,7 +81350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -81363,6 +81363,8 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -81403,15 +81405,25 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>estimated_exemption</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_tax_reduction</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>total_units</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>restricted_units</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>city_cut</t>
         </is>
@@ -81455,15 +81467,25 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
+          <t>260499619</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2604996</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>1044</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>979</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>102000</t>
         </is>
@@ -81507,15 +81529,25 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
+          <t>318881999</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>3188820</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
           <t>1494</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>1303</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>142350</t>
         </is>
@@ -81559,15 +81591,25 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>29735832</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>297358</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>278</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>278</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>41700</t>
         </is>
@@ -81611,15 +81653,25 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>1264768719</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>12647687</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>10198</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>8629</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>1111775</t>
         </is>
@@ -81663,15 +81715,25 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>33215308</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>332153</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -81715,15 +81777,25 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>45778059</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>457781</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>148</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>22200</t>
         </is>
@@ -81767,15 +81839,25 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>420796578</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4207966</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1837</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1413</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>187250</t>
         </is>
@@ -81819,15 +81901,25 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>143948867</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1439489</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>1128</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>109800</t>
         </is>
@@ -81871,15 +81963,25 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>4156500</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>41565</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>10650</t>
         </is>
@@ -81923,15 +82025,25 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>403625076</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4036251</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>2653</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>2202</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>240716</t>
         </is>
@@ -81975,15 +82087,25 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>113957436</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1139574</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>329</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>236</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -82027,15 +82149,25 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>138012042</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1380120</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1413</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1147</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>142275</t>
         </is>
@@ -82079,15 +82211,25 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>22282532</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>222825</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>460</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>460</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>57000</t>
         </is>
@@ -82131,15 +82273,25 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
+          <t>624773704</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>6247737</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>2739</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>2065</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210600</t>
         </is>
@@ -82183,15 +82335,25 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>9584501</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>95845</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>22500</t>
         </is>
@@ -82235,15 +82397,25 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>35835370</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>358354</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>301</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>190</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>28500</t>
         </is>
@@ -82287,15 +82459,25 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>9941350</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>99413</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>5550</t>
         </is>
@@ -82339,15 +82521,25 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>3879793492</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>38797935</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>24379</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>20423</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>2470266</t>
         </is>

--- a/output/dataset/review.xlsx
+++ b/output/dataset/review.xlsx
@@ -81653,12 +81653,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1264768719</t>
+          <t>1266439164</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12647687</t>
+          <t>12664392</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -82025,12 +82025,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>403625076</t>
+          <t>404140279</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4036251</t>
+          <t>4041403</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -82521,12 +82521,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3879793492</t>
+          <t>3881979140</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38797935</t>
+          <t>38819791</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
